--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="255">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -594,58 +594,55 @@
     <t>ems/fcasts/update_period</t>
   </si>
   <si>
-    <t>B0gUAuzRUlrkye1</t>
-  </si>
-  <si>
-    <t>dHgL4gbOpvpcHKz</t>
-  </si>
-  <si>
-    <t>y7bMb12eBvtJ8b0</t>
-  </si>
-  <si>
-    <t>b7H16UTMMdvYwkU</t>
-  </si>
-  <si>
-    <t>Eo8DW9m2MAGNf82</t>
-  </si>
-  <si>
-    <t>CO3Y8q2flOzMpz7</t>
-  </si>
-  <si>
-    <t>rPrwX4wRKBxQcSa</t>
-  </si>
-  <si>
-    <t>HtTmLv45OthAjh6</t>
-  </si>
-  <si>
-    <t>JGt1PfTbwm9Cnuo</t>
-  </si>
-  <si>
-    <t>m4EZz0BTC7a0LBF</t>
+    <t>QIDo2Rf8HWcrrrK</t>
+  </si>
+  <si>
+    <t>mMna0fdFv2mFxIA</t>
+  </si>
+  <si>
+    <t>LTjj3htgEzFPFwG</t>
+  </si>
+  <si>
+    <t>wUnlhLunAQkmiYg</t>
+  </si>
+  <si>
+    <t>TzFCeFv75nGXK76</t>
+  </si>
+  <si>
+    <t>Whx5cbqKg1TTcfv</t>
+  </si>
+  <si>
+    <t>TqTxlkKDgzonG7H</t>
+  </si>
+  <si>
+    <t>1elq9ieTruo5sEm</t>
+  </si>
+  <si>
+    <t>RxBT5EAnLtY3JdD</t>
+  </si>
+  <si>
+    <t>g06giXT84GgespH</t>
+  </si>
+  <si>
+    <t>hh_4536_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3564_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
   </si>
   <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_2959_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3863_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
+    <t>hh_2896_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2455_0.csv</t>
   </si>
   <si>
     <t>average</t>
@@ -669,25 +666,22 @@
     <t>local</t>
   </si>
   <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
     <t>ev_freetime_2.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_43.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_47.csv</t>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
   </si>
   <si>
     <t>ev_parttime_88.csv</t>
   </si>
   <si>
-    <t>ev_parttime_90.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_41.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_42.csv</t>
+    <t>ev_freetime_0.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -699,10 +693,7 @@
     <t>['time']</t>
   </si>
   <si>
-    <t>rule-based</t>
-  </si>
-  <si>
-    <t>mpc</t>
+    <t>linopy</t>
   </si>
   <si>
     <t>['linear']</t>
@@ -739,12 +730,6 @@
   </si>
   <si>
     <t>ev/fcast/random_forest_classifier/features</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/retraining_period</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/update_period</t>
   </si>
   <si>
     <t>psh/owner</t>
@@ -1742,10 +1727,10 @@
         <v>191</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1754,7 +1739,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1766,13 +1751,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>5527000</v>
+        <v>4536000</v>
       </c>
       <c r="O2" t="s">
         <v>201</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -1787,25 +1772,25 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V2" t="s">
+        <v>210</v>
+      </c>
+      <c r="W2">
+        <v>90</v>
+      </c>
+      <c r="X2" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y2">
+        <v>90</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA2" t="s">
         <v>211</v>
-      </c>
-      <c r="W2">
-        <v>90</v>
-      </c>
-      <c r="X2" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y2">
-        <v>90</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>212</v>
       </c>
       <c r="AB2">
         <v>0</v>
@@ -1817,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="AG2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH2">
         <v>1</v>
@@ -1832,26 +1817,26 @@
         <v>9</v>
       </c>
       <c r="AL2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN2">
+        <v>90</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP2">
+        <v>90</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR2" t="s">
         <v>211</v>
       </c>
-      <c r="AN2">
-        <v>90</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP2">
-        <v>90</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>212</v>
-      </c>
       <c r="AS2">
         <v>0</v>
       </c>
@@ -1859,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="AX2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY2">
         <v>1</v>
@@ -1874,26 +1859,26 @@
         <v>9</v>
       </c>
       <c r="BC2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE2">
+        <v>90</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG2">
+        <v>90</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI2" t="s">
         <v>211</v>
       </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG2">
-        <v>90</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ2">
         <v>0</v>
       </c>
@@ -1901,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="BO2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP2">
         <v>1</v>
@@ -1916,34 +1901,49 @@
         <v>9</v>
       </c>
       <c r="BT2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV2">
+        <v>90</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX2">
+        <v>90</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ2" t="s">
         <v>211</v>
       </c>
-      <c r="BV2">
-        <v>90</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX2">
-        <v>90</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ2" t="s">
+      <c r="CA2">
+        <v>1</v>
+      </c>
+      <c r="CB2">
+        <v>1</v>
+      </c>
+      <c r="CC2">
+        <v>5700</v>
+      </c>
+      <c r="CD2" t="s">
         <v>212</v>
       </c>
-      <c r="CA2">
-        <v>0</v>
-      </c>
-      <c r="CB2">
-        <v>0</v>
+      <c r="CE2">
+        <v>0</v>
+      </c>
+      <c r="CF2">
+        <v>40</v>
+      </c>
+      <c r="CG2" t="b">
+        <v>1</v>
       </c>
       <c r="CH2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI2">
         <v>1</v>
@@ -1958,28 +1958,28 @@
         <v>9</v>
       </c>
       <c r="CM2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN2" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO2">
+        <v>90</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ2">
+        <v>90</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS2" t="s">
         <v>211</v>
       </c>
-      <c r="CO2">
-        <v>90</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ2">
-        <v>90</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>212</v>
-      </c>
       <c r="CT2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU2">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA2">
         <v>1</v>
@@ -2003,28 +2003,28 @@
         <v>9</v>
       </c>
       <c r="DE2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF2" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG2">
+        <v>90</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI2">
+        <v>90</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK2" t="s">
         <v>211</v>
       </c>
-      <c r="DG2">
-        <v>90</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI2">
-        <v>90</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>212</v>
-      </c>
       <c r="DL2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM2">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="DR2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS2">
         <v>1</v>
@@ -2048,28 +2048,28 @@
         <v>9</v>
       </c>
       <c r="DW2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX2" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY2">
+        <v>90</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA2">
+        <v>90</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC2" t="s">
         <v>211</v>
       </c>
-      <c r="DY2">
-        <v>90</v>
-      </c>
-      <c r="DZ2" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA2">
-        <v>90</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>212</v>
-      </c>
       <c r="ED2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE2">
         <v>0</v>
@@ -2078,70 +2078,16 @@
         <v>0</v>
       </c>
       <c r="EI2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK2">
-        <v>2</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>216</v>
-      </c>
-      <c r="EM2">
-        <v>50000</v>
-      </c>
-      <c r="EN2">
-        <v>7200</v>
-      </c>
-      <c r="EO2">
-        <v>7200</v>
-      </c>
-      <c r="EP2">
-        <v>50000</v>
-      </c>
-      <c r="EQ2">
-        <v>90000</v>
-      </c>
-      <c r="ER2">
-        <v>80000</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="s">
+        <v>0</v>
+      </c>
+      <c r="FD2" t="s">
         <v>221</v>
-      </c>
-      <c r="EV2">
-        <v>75000</v>
-      </c>
-      <c r="EW2">
-        <v>7200</v>
-      </c>
-      <c r="EX2">
-        <v>11000</v>
-      </c>
-      <c r="EY2">
-        <v>100000</v>
-      </c>
-      <c r="EZ2">
-        <v>90000</v>
-      </c>
-      <c r="FA2">
-        <v>80000</v>
-      </c>
-      <c r="FB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FD2" t="s">
-        <v>223</v>
       </c>
       <c r="FE2">
         <v>0.05</v>
@@ -2156,52 +2102,70 @@
         <v>8.5</v>
       </c>
       <c r="FI2" t="s">
+        <v>222</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>223</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>214</v>
+      </c>
+      <c r="FL2">
+        <v>1</v>
+      </c>
+      <c r="FM2">
+        <v>1</v>
+      </c>
+      <c r="FN2">
+        <v>4500</v>
+      </c>
+      <c r="FO2">
+        <v>4500</v>
+      </c>
+      <c r="FP2">
+        <v>0.95</v>
+      </c>
+      <c r="FQ2">
+        <v>0.1</v>
+      </c>
+      <c r="FR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FT2" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU2">
+        <v>0</v>
+      </c>
+      <c r="FV2">
+        <v>0</v>
+      </c>
+      <c r="GA2" t="s">
+        <v>214</v>
+      </c>
+      <c r="GB2" t="s">
         <v>224</v>
       </c>
-      <c r="FJ2" t="s">
-        <v>225</v>
-      </c>
-      <c r="FK2" t="s">
-        <v>215</v>
-      </c>
-      <c r="FL2">
-        <v>0</v>
-      </c>
-      <c r="FM2">
-        <v>0</v>
-      </c>
-      <c r="FT2" t="s">
-        <v>215</v>
-      </c>
-      <c r="FU2">
-        <v>0</v>
-      </c>
-      <c r="FV2">
-        <v>0</v>
-      </c>
-      <c r="GA2" t="s">
-        <v>215</v>
-      </c>
-      <c r="GB2" t="s">
-        <v>226</v>
-      </c>
       <c r="GC2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD2">
         <v>86400</v>
       </c>
       <c r="GE2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI2">
         <v>86400</v>
@@ -2242,13 +2206,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>5527000</v>
+        <v>3564000</v>
       </c>
       <c r="O3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2263,25 +2227,25 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V3" t="s">
+        <v>210</v>
+      </c>
+      <c r="W3">
+        <v>90</v>
+      </c>
+      <c r="X3" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y3">
+        <v>90</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA3" t="s">
         <v>211</v>
-      </c>
-      <c r="W3">
-        <v>90</v>
-      </c>
-      <c r="X3" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y3">
-        <v>90</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>212</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -2293,7 +2257,7 @@
         <v>6</v>
       </c>
       <c r="AG3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH3">
         <v>1</v>
@@ -2308,26 +2272,26 @@
         <v>9</v>
       </c>
       <c r="AL3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN3">
+        <v>90</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP3">
+        <v>90</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR3" t="s">
         <v>211</v>
       </c>
-      <c r="AN3">
-        <v>90</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP3">
-        <v>90</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>212</v>
-      </c>
       <c r="AS3">
         <v>0</v>
       </c>
@@ -2335,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="AX3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY3">
         <v>1</v>
@@ -2350,26 +2314,26 @@
         <v>9</v>
       </c>
       <c r="BC3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE3">
+        <v>90</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG3">
+        <v>90</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI3" t="s">
         <v>211</v>
       </c>
-      <c r="BE3">
-        <v>90</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG3">
-        <v>90</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ3">
         <v>0</v>
       </c>
@@ -2377,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="BO3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP3">
         <v>1</v>
@@ -2392,49 +2356,34 @@
         <v>9</v>
       </c>
       <c r="BT3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV3">
+        <v>90</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX3">
+        <v>90</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ3" t="s">
         <v>211</v>
       </c>
-      <c r="BV3">
-        <v>90</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX3">
-        <v>90</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>212</v>
-      </c>
       <c r="CA3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB3">
-        <v>1</v>
-      </c>
-      <c r="CC3">
-        <v>8900</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>213</v>
-      </c>
-      <c r="CE3">
-        <v>0</v>
-      </c>
-      <c r="CF3">
-        <v>40</v>
-      </c>
-      <c r="CG3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI3">
         <v>1</v>
@@ -2449,28 +2398,28 @@
         <v>9</v>
       </c>
       <c r="CM3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN3" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO3">
+        <v>90</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ3">
+        <v>90</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS3" t="s">
         <v>211</v>
       </c>
-      <c r="CO3">
-        <v>90</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ3">
-        <v>90</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>212</v>
-      </c>
       <c r="CT3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU3">
         <v>0</v>
@@ -2479,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA3">
         <v>1</v>
@@ -2494,28 +2443,28 @@
         <v>9</v>
       </c>
       <c r="DE3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF3" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG3">
+        <v>90</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI3">
+        <v>90</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK3" t="s">
         <v>211</v>
       </c>
-      <c r="DG3">
-        <v>90</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI3">
-        <v>90</v>
-      </c>
-      <c r="DJ3" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK3" t="s">
-        <v>212</v>
-      </c>
       <c r="DL3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM3">
         <v>0</v>
@@ -2524,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="DR3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS3">
         <v>1</v>
@@ -2539,46 +2488,100 @@
         <v>9</v>
       </c>
       <c r="DW3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX3" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY3">
+        <v>90</v>
+      </c>
+      <c r="DZ3" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA3">
+        <v>90</v>
+      </c>
+      <c r="EB3" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC3" t="s">
         <v>211</v>
       </c>
-      <c r="DY3">
-        <v>90</v>
-      </c>
-      <c r="DZ3" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA3">
-        <v>90</v>
-      </c>
-      <c r="EB3" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC3" t="s">
-        <v>212</v>
-      </c>
       <c r="ED3" t="s">
+        <v>214</v>
+      </c>
+      <c r="EE3">
+        <v>0</v>
+      </c>
+      <c r="EF3">
+        <v>0</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>214</v>
+      </c>
+      <c r="EJ3">
+        <v>1</v>
+      </c>
+      <c r="EK3">
+        <v>2</v>
+      </c>
+      <c r="EL3" t="s">
         <v>215</v>
       </c>
-      <c r="EE3">
-        <v>0</v>
-      </c>
-      <c r="EF3">
-        <v>0</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>215</v>
-      </c>
-      <c r="EJ3">
-        <v>0</v>
-      </c>
-      <c r="EK3">
+      <c r="EM3">
+        <v>75000</v>
+      </c>
+      <c r="EN3">
+        <v>7200</v>
+      </c>
+      <c r="EO3">
+        <v>11000</v>
+      </c>
+      <c r="EP3">
+        <v>100000</v>
+      </c>
+      <c r="EQ3">
+        <v>90000</v>
+      </c>
+      <c r="ER3">
+        <v>80000</v>
+      </c>
+      <c r="ES3" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET3" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU3" t="s">
+        <v>219</v>
+      </c>
+      <c r="EV3">
+        <v>50000</v>
+      </c>
+      <c r="EW3">
+        <v>7200</v>
+      </c>
+      <c r="EX3">
+        <v>7200</v>
+      </c>
+      <c r="EY3">
+        <v>50000</v>
+      </c>
+      <c r="EZ3">
+        <v>90000</v>
+      </c>
+      <c r="FA3">
+        <v>80000</v>
+      </c>
+      <c r="FB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC3" t="b">
         <v>0</v>
       </c>
       <c r="FD3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE3">
         <v>0.05</v>
@@ -2593,70 +2596,52 @@
         <v>8.5</v>
       </c>
       <c r="FI3" t="s">
+        <v>222</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>223</v>
+      </c>
+      <c r="FK3" t="s">
+        <v>214</v>
+      </c>
+      <c r="FL3">
+        <v>0</v>
+      </c>
+      <c r="FM3">
+        <v>0</v>
+      </c>
+      <c r="FT3" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU3">
+        <v>0</v>
+      </c>
+      <c r="FV3">
+        <v>0</v>
+      </c>
+      <c r="GA3" t="s">
+        <v>214</v>
+      </c>
+      <c r="GB3" t="s">
         <v>224</v>
       </c>
-      <c r="FJ3" t="s">
-        <v>225</v>
-      </c>
-      <c r="FK3" t="s">
-        <v>215</v>
-      </c>
-      <c r="FL3">
-        <v>1</v>
-      </c>
-      <c r="FM3">
-        <v>1</v>
-      </c>
-      <c r="FN3">
-        <v>5500</v>
-      </c>
-      <c r="FO3">
-        <v>5500</v>
-      </c>
-      <c r="FP3">
-        <v>0.95</v>
-      </c>
-      <c r="FQ3">
-        <v>0.1</v>
-      </c>
-      <c r="FR3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FS3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FT3" t="s">
-        <v>215</v>
-      </c>
-      <c r="FU3">
-        <v>0</v>
-      </c>
-      <c r="FV3">
-        <v>0</v>
-      </c>
-      <c r="GA3" t="s">
-        <v>215</v>
-      </c>
-      <c r="GB3" t="s">
-        <v>226</v>
-      </c>
       <c r="GC3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD3">
         <v>86400</v>
       </c>
       <c r="GE3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI3">
         <v>86400</v>
@@ -2673,10 +2658,10 @@
         <v>193</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -2685,7 +2670,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2697,13 +2682,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>3296000</v>
+        <v>3863000</v>
       </c>
       <c r="O4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -2718,25 +2703,25 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V4" t="s">
+        <v>210</v>
+      </c>
+      <c r="W4">
+        <v>90</v>
+      </c>
+      <c r="X4" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y4">
+        <v>90</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA4" t="s">
         <v>211</v>
-      </c>
-      <c r="W4">
-        <v>90</v>
-      </c>
-      <c r="X4" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y4">
-        <v>90</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>212</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -2748,7 +2733,7 @@
         <v>6</v>
       </c>
       <c r="AG4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH4">
         <v>1</v>
@@ -2763,26 +2748,26 @@
         <v>9</v>
       </c>
       <c r="AL4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN4">
+        <v>90</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP4">
+        <v>90</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR4" t="s">
         <v>211</v>
       </c>
-      <c r="AN4">
-        <v>90</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP4">
-        <v>90</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>212</v>
-      </c>
       <c r="AS4">
         <v>0</v>
       </c>
@@ -2790,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="AX4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY4">
         <v>1</v>
@@ -2805,26 +2790,26 @@
         <v>9</v>
       </c>
       <c r="BC4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE4">
+        <v>90</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG4">
+        <v>90</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI4" t="s">
         <v>211</v>
       </c>
-      <c r="BE4">
-        <v>90</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG4">
-        <v>90</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ4">
         <v>0</v>
       </c>
@@ -2832,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="BO4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP4">
         <v>1</v>
@@ -2847,49 +2832,49 @@
         <v>9</v>
       </c>
       <c r="BT4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV4">
+        <v>90</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX4">
+        <v>90</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ4" t="s">
         <v>211</v>
       </c>
-      <c r="BV4">
-        <v>90</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX4">
-        <v>90</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ4" t="s">
+      <c r="CA4">
+        <v>1</v>
+      </c>
+      <c r="CB4">
+        <v>1</v>
+      </c>
+      <c r="CC4">
+        <v>6400</v>
+      </c>
+      <c r="CD4" t="s">
         <v>212</v>
       </c>
-      <c r="CA4">
-        <v>1</v>
-      </c>
-      <c r="CB4">
-        <v>1</v>
-      </c>
-      <c r="CC4">
-        <v>4200</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>213</v>
-      </c>
       <c r="CE4">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG4" t="b">
         <v>1</v>
       </c>
       <c r="CH4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI4">
         <v>1</v>
@@ -2904,28 +2889,28 @@
         <v>9</v>
       </c>
       <c r="CM4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN4" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO4">
+        <v>90</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ4">
+        <v>90</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS4" t="s">
         <v>211</v>
       </c>
-      <c r="CO4">
-        <v>90</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ4">
-        <v>90</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>212</v>
-      </c>
       <c r="CT4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU4">
         <v>0</v>
@@ -2934,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="CZ4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA4">
         <v>1</v>
@@ -2949,28 +2934,28 @@
         <v>9</v>
       </c>
       <c r="DE4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF4" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG4">
+        <v>90</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI4">
+        <v>90</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK4" t="s">
         <v>211</v>
       </c>
-      <c r="DG4">
-        <v>90</v>
-      </c>
-      <c r="DH4" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI4">
-        <v>90</v>
-      </c>
-      <c r="DJ4" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK4" t="s">
-        <v>212</v>
-      </c>
       <c r="DL4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM4">
         <v>0</v>
@@ -2979,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="DR4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS4">
         <v>1</v>
@@ -2994,28 +2979,28 @@
         <v>9</v>
       </c>
       <c r="DW4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX4" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY4">
+        <v>90</v>
+      </c>
+      <c r="DZ4" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA4">
+        <v>90</v>
+      </c>
+      <c r="EB4" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC4" t="s">
         <v>211</v>
       </c>
-      <c r="DY4">
-        <v>90</v>
-      </c>
-      <c r="DZ4" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA4">
-        <v>90</v>
-      </c>
-      <c r="EB4" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC4" t="s">
-        <v>212</v>
-      </c>
       <c r="ED4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE4">
         <v>0</v>
@@ -3024,43 +3009,16 @@
         <v>0</v>
       </c>
       <c r="EI4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK4">
-        <v>1</v>
-      </c>
-      <c r="EL4" t="s">
-        <v>217</v>
-      </c>
-      <c r="EM4">
-        <v>75000</v>
-      </c>
-      <c r="EN4">
-        <v>7200</v>
-      </c>
-      <c r="EO4">
-        <v>11000</v>
-      </c>
-      <c r="EP4">
-        <v>100000</v>
-      </c>
-      <c r="EQ4">
-        <v>90000</v>
-      </c>
-      <c r="ER4">
-        <v>80000</v>
-      </c>
-      <c r="ES4" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET4" t="b">
         <v>0</v>
       </c>
       <c r="FD4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE4">
         <v>0.05</v>
@@ -3075,13 +3033,13 @@
         <v>8.5</v>
       </c>
       <c r="FI4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="FJ4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="FK4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FL4">
         <v>1</v>
@@ -3090,10 +3048,10 @@
         <v>1</v>
       </c>
       <c r="FN4">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="FO4">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="FP4">
         <v>0.95</v>
@@ -3108,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="FT4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FU4">
         <v>0</v>
@@ -3117,28 +3075,28 @@
         <v>0</v>
       </c>
       <c r="GA4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="GB4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="GC4" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD4">
         <v>86400</v>
       </c>
       <c r="GE4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI4">
         <v>86400</v>
@@ -3179,13 +3137,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>3648000</v>
+        <v>3125000</v>
       </c>
       <c r="O5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -3200,25 +3158,25 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V5" t="s">
+        <v>210</v>
+      </c>
+      <c r="W5">
+        <v>90</v>
+      </c>
+      <c r="X5" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y5">
+        <v>90</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA5" t="s">
         <v>211</v>
-      </c>
-      <c r="W5">
-        <v>90</v>
-      </c>
-      <c r="X5" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y5">
-        <v>90</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>212</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -3230,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="AG5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -3245,26 +3203,26 @@
         <v>9</v>
       </c>
       <c r="AL5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN5">
+        <v>90</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP5">
+        <v>90</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR5" t="s">
         <v>211</v>
       </c>
-      <c r="AN5">
-        <v>90</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP5">
-        <v>90</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>212</v>
-      </c>
       <c r="AS5">
         <v>0</v>
       </c>
@@ -3272,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="AX5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY5">
         <v>1</v>
@@ -3287,26 +3245,26 @@
         <v>9</v>
       </c>
       <c r="BC5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE5">
+        <v>90</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG5">
+        <v>90</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI5" t="s">
         <v>211</v>
       </c>
-      <c r="BE5">
-        <v>90</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG5">
-        <v>90</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ5">
         <v>0</v>
       </c>
@@ -3314,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="BO5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP5">
         <v>1</v>
@@ -3329,37 +3287,37 @@
         <v>9</v>
       </c>
       <c r="BT5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV5">
+        <v>90</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX5">
+        <v>90</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ5" t="s">
         <v>211</v>
       </c>
-      <c r="BV5">
-        <v>90</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX5">
-        <v>90</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ5" t="s">
+      <c r="CA5">
+        <v>1</v>
+      </c>
+      <c r="CB5">
+        <v>1</v>
+      </c>
+      <c r="CC5">
+        <v>5400</v>
+      </c>
+      <c r="CD5" t="s">
         <v>212</v>
-      </c>
-      <c r="CA5">
-        <v>1</v>
-      </c>
-      <c r="CB5">
-        <v>1</v>
-      </c>
-      <c r="CC5">
-        <v>6400</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>213</v>
       </c>
       <c r="CE5">
         <v>-20</v>
@@ -3371,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="CH5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI5">
         <v>1</v>
@@ -3386,28 +3344,28 @@
         <v>9</v>
       </c>
       <c r="CM5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN5" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO5">
+        <v>90</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ5">
+        <v>90</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS5" t="s">
         <v>211</v>
       </c>
-      <c r="CO5">
-        <v>90</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ5">
-        <v>90</v>
-      </c>
-      <c r="CR5" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS5" t="s">
-        <v>212</v>
-      </c>
       <c r="CT5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU5">
         <v>0</v>
@@ -3416,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA5">
         <v>1</v>
@@ -3431,28 +3389,28 @@
         <v>9</v>
       </c>
       <c r="DE5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF5" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG5">
+        <v>90</v>
+      </c>
+      <c r="DH5" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI5">
+        <v>90</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK5" t="s">
         <v>211</v>
       </c>
-      <c r="DG5">
-        <v>90</v>
-      </c>
-      <c r="DH5" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI5">
-        <v>90</v>
-      </c>
-      <c r="DJ5" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK5" t="s">
-        <v>212</v>
-      </c>
       <c r="DL5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM5">
         <v>0</v>
@@ -3461,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="DR5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS5">
         <v>1</v>
@@ -3476,46 +3434,100 @@
         <v>9</v>
       </c>
       <c r="DW5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX5" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY5">
+        <v>90</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA5">
+        <v>90</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC5" t="s">
         <v>211</v>
       </c>
-      <c r="DY5">
-        <v>90</v>
-      </c>
-      <c r="DZ5" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA5">
-        <v>90</v>
-      </c>
-      <c r="EB5" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC5" t="s">
-        <v>212</v>
-      </c>
       <c r="ED5" t="s">
+        <v>214</v>
+      </c>
+      <c r="EE5">
+        <v>0</v>
+      </c>
+      <c r="EF5">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>214</v>
+      </c>
+      <c r="EJ5">
+        <v>1</v>
+      </c>
+      <c r="EK5">
+        <v>2</v>
+      </c>
+      <c r="EL5" t="s">
         <v>215</v>
       </c>
-      <c r="EE5">
-        <v>0</v>
-      </c>
-      <c r="EF5">
-        <v>0</v>
-      </c>
-      <c r="EI5" t="s">
-        <v>215</v>
-      </c>
-      <c r="EJ5">
-        <v>0</v>
-      </c>
-      <c r="EK5">
+      <c r="EM5">
+        <v>50000</v>
+      </c>
+      <c r="EN5">
+        <v>7200</v>
+      </c>
+      <c r="EO5">
+        <v>7200</v>
+      </c>
+      <c r="EP5">
+        <v>50000</v>
+      </c>
+      <c r="EQ5">
+        <v>90000</v>
+      </c>
+      <c r="ER5">
+        <v>80000</v>
+      </c>
+      <c r="ES5" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="s">
+        <v>220</v>
+      </c>
+      <c r="EV5">
+        <v>75000</v>
+      </c>
+      <c r="EW5">
+        <v>7200</v>
+      </c>
+      <c r="EX5">
+        <v>11000</v>
+      </c>
+      <c r="EY5">
+        <v>100000</v>
+      </c>
+      <c r="EZ5">
+        <v>90000</v>
+      </c>
+      <c r="FA5">
+        <v>80000</v>
+      </c>
+      <c r="FB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="b">
         <v>0</v>
       </c>
       <c r="FD5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE5">
         <v>0.05</v>
@@ -3530,13 +3542,13 @@
         <v>8.5</v>
       </c>
       <c r="FI5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="FJ5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="FK5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FL5">
         <v>1</v>
@@ -3545,10 +3557,10 @@
         <v>1</v>
       </c>
       <c r="FN5">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="FO5">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="FP5">
         <v>0.95</v>
@@ -3563,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="FT5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FU5">
         <v>0</v>
@@ -3572,28 +3584,28 @@
         <v>0</v>
       </c>
       <c r="GA5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="GB5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="GC5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD5">
         <v>86400</v>
       </c>
       <c r="GE5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI5">
         <v>86400</v>
@@ -3610,10 +3622,10 @@
         <v>195</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3622,7 +3634,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3634,13 +3646,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>2012000</v>
+        <v>3564000</v>
       </c>
       <c r="O6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -3655,25 +3667,25 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V6" t="s">
+        <v>210</v>
+      </c>
+      <c r="W6">
+        <v>90</v>
+      </c>
+      <c r="X6" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y6">
+        <v>90</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA6" t="s">
         <v>211</v>
-      </c>
-      <c r="W6">
-        <v>90</v>
-      </c>
-      <c r="X6" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y6">
-        <v>90</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>212</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -3685,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH6">
         <v>1</v>
@@ -3700,26 +3712,26 @@
         <v>9</v>
       </c>
       <c r="AL6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN6">
+        <v>90</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP6">
+        <v>90</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR6" t="s">
         <v>211</v>
       </c>
-      <c r="AN6">
-        <v>90</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP6">
-        <v>90</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>212</v>
-      </c>
       <c r="AS6">
         <v>0</v>
       </c>
@@ -3727,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="AX6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -3742,26 +3754,26 @@
         <v>9</v>
       </c>
       <c r="BC6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE6">
+        <v>90</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG6">
+        <v>90</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI6" t="s">
         <v>211</v>
       </c>
-      <c r="BE6">
-        <v>90</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG6">
-        <v>90</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ6">
         <v>0</v>
       </c>
@@ -3769,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="BO6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP6">
         <v>1</v>
@@ -3784,34 +3796,49 @@
         <v>9</v>
       </c>
       <c r="BT6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV6">
+        <v>90</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX6">
+        <v>90</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>211</v>
       </c>
-      <c r="BV6">
-        <v>90</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX6">
-        <v>90</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ6" t="s">
+      <c r="CA6">
+        <v>1</v>
+      </c>
+      <c r="CB6">
+        <v>1</v>
+      </c>
+      <c r="CC6">
+        <v>4800</v>
+      </c>
+      <c r="CD6" t="s">
         <v>212</v>
       </c>
-      <c r="CA6">
-        <v>0</v>
-      </c>
-      <c r="CB6">
-        <v>0</v>
+      <c r="CE6">
+        <v>0</v>
+      </c>
+      <c r="CF6">
+        <v>40</v>
+      </c>
+      <c r="CG6" t="b">
+        <v>1</v>
       </c>
       <c r="CH6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI6">
         <v>1</v>
@@ -3826,28 +3853,28 @@
         <v>9</v>
       </c>
       <c r="CM6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN6" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO6">
+        <v>90</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ6">
+        <v>90</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS6" t="s">
         <v>211</v>
       </c>
-      <c r="CO6">
-        <v>90</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ6">
-        <v>90</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>212</v>
-      </c>
       <c r="CT6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU6">
         <v>0</v>
@@ -3856,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA6">
         <v>1</v>
@@ -3871,28 +3898,28 @@
         <v>9</v>
       </c>
       <c r="DE6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF6" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG6">
+        <v>90</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI6">
+        <v>90</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK6" t="s">
         <v>211</v>
       </c>
-      <c r="DG6">
-        <v>90</v>
-      </c>
-      <c r="DH6" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI6">
-        <v>90</v>
-      </c>
-      <c r="DJ6" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK6" t="s">
-        <v>212</v>
-      </c>
       <c r="DL6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM6">
         <v>0</v>
@@ -3901,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="DR6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS6">
         <v>1</v>
@@ -3916,28 +3943,28 @@
         <v>9</v>
       </c>
       <c r="DW6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX6" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY6">
+        <v>90</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA6">
+        <v>90</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC6" t="s">
         <v>211</v>
       </c>
-      <c r="DY6">
-        <v>90</v>
-      </c>
-      <c r="DZ6" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA6">
-        <v>90</v>
-      </c>
-      <c r="EB6" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC6" t="s">
-        <v>212</v>
-      </c>
       <c r="ED6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE6">
         <v>0</v>
@@ -3946,16 +3973,43 @@
         <v>0</v>
       </c>
       <c r="EI6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK6">
+        <v>1</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>216</v>
+      </c>
+      <c r="EM6">
+        <v>50000</v>
+      </c>
+      <c r="EN6">
+        <v>7200</v>
+      </c>
+      <c r="EO6">
+        <v>7200</v>
+      </c>
+      <c r="EP6">
+        <v>50000</v>
+      </c>
+      <c r="EQ6">
+        <v>90000</v>
+      </c>
+      <c r="ER6">
+        <v>80000</v>
+      </c>
+      <c r="ES6" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET6" t="b">
         <v>0</v>
       </c>
       <c r="FD6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE6">
         <v>0.05</v>
@@ -3970,52 +4024,52 @@
         <v>8.5</v>
       </c>
       <c r="FI6" t="s">
+        <v>222</v>
+      </c>
+      <c r="FJ6" t="s">
+        <v>223</v>
+      </c>
+      <c r="FK6" t="s">
+        <v>214</v>
+      </c>
+      <c r="FL6">
+        <v>0</v>
+      </c>
+      <c r="FM6">
+        <v>0</v>
+      </c>
+      <c r="FT6" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU6">
+        <v>0</v>
+      </c>
+      <c r="FV6">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="s">
+        <v>214</v>
+      </c>
+      <c r="GB6" t="s">
         <v>224</v>
       </c>
-      <c r="FJ6" t="s">
-        <v>225</v>
-      </c>
-      <c r="FK6" t="s">
-        <v>215</v>
-      </c>
-      <c r="FL6">
-        <v>0</v>
-      </c>
-      <c r="FM6">
-        <v>0</v>
-      </c>
-      <c r="FT6" t="s">
-        <v>215</v>
-      </c>
-      <c r="FU6">
-        <v>0</v>
-      </c>
-      <c r="FV6">
-        <v>0</v>
-      </c>
-      <c r="GA6" t="s">
-        <v>215</v>
-      </c>
-      <c r="GB6" t="s">
-        <v>226</v>
-      </c>
       <c r="GC6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD6">
         <v>86400</v>
       </c>
       <c r="GE6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI6">
         <v>86400</v>
@@ -4056,13 +4110,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>2959000</v>
+        <v>5527000</v>
       </c>
       <c r="O7" t="s">
         <v>205</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -4077,25 +4131,25 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V7" t="s">
+        <v>210</v>
+      </c>
+      <c r="W7">
+        <v>90</v>
+      </c>
+      <c r="X7" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y7">
+        <v>90</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA7" t="s">
         <v>211</v>
-      </c>
-      <c r="W7">
-        <v>90</v>
-      </c>
-      <c r="X7" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y7">
-        <v>90</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>212</v>
       </c>
       <c r="AB7">
         <v>0</v>
@@ -4107,7 +4161,7 @@
         <v>6</v>
       </c>
       <c r="AG7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH7">
         <v>1</v>
@@ -4122,26 +4176,26 @@
         <v>9</v>
       </c>
       <c r="AL7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN7">
+        <v>90</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP7">
+        <v>90</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR7" t="s">
         <v>211</v>
       </c>
-      <c r="AN7">
-        <v>90</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP7">
-        <v>90</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>212</v>
-      </c>
       <c r="AS7">
         <v>0</v>
       </c>
@@ -4149,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="AX7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -4164,26 +4218,26 @@
         <v>9</v>
       </c>
       <c r="BC7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE7">
+        <v>90</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG7">
+        <v>90</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI7" t="s">
         <v>211</v>
       </c>
-      <c r="BE7">
-        <v>90</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG7">
-        <v>90</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ7">
         <v>0</v>
       </c>
@@ -4191,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="BO7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP7">
         <v>1</v>
@@ -4206,37 +4260,37 @@
         <v>9</v>
       </c>
       <c r="BT7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV7">
+        <v>90</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX7">
+        <v>90</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>211</v>
       </c>
-      <c r="BV7">
-        <v>90</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX7">
-        <v>90</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ7" t="s">
+      <c r="CA7">
+        <v>1</v>
+      </c>
+      <c r="CB7">
+        <v>1</v>
+      </c>
+      <c r="CC7">
+        <v>8000</v>
+      </c>
+      <c r="CD7" t="s">
         <v>212</v>
-      </c>
-      <c r="CA7">
-        <v>1</v>
-      </c>
-      <c r="CB7">
-        <v>1</v>
-      </c>
-      <c r="CC7">
-        <v>3800</v>
-      </c>
-      <c r="CD7" t="s">
-        <v>213</v>
       </c>
       <c r="CE7">
         <v>0</v>
@@ -4248,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="CH7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI7">
         <v>1</v>
@@ -4263,28 +4317,28 @@
         <v>9</v>
       </c>
       <c r="CM7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN7" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO7">
+        <v>90</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ7">
+        <v>90</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS7" t="s">
         <v>211</v>
       </c>
-      <c r="CO7">
-        <v>90</v>
-      </c>
-      <c r="CP7" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ7">
-        <v>90</v>
-      </c>
-      <c r="CR7" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS7" t="s">
-        <v>212</v>
-      </c>
       <c r="CT7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU7">
         <v>0</v>
@@ -4293,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA7">
         <v>1</v>
@@ -4308,28 +4362,28 @@
         <v>9</v>
       </c>
       <c r="DE7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF7" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG7">
+        <v>90</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI7">
+        <v>90</v>
+      </c>
+      <c r="DJ7" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK7" t="s">
         <v>211</v>
       </c>
-      <c r="DG7">
-        <v>90</v>
-      </c>
-      <c r="DH7" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI7">
-        <v>90</v>
-      </c>
-      <c r="DJ7" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK7" t="s">
-        <v>212</v>
-      </c>
       <c r="DL7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM7">
         <v>0</v>
@@ -4338,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="DR7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS7">
         <v>1</v>
@@ -4353,28 +4407,28 @@
         <v>9</v>
       </c>
       <c r="DW7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX7" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY7">
+        <v>90</v>
+      </c>
+      <c r="DZ7" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA7">
+        <v>90</v>
+      </c>
+      <c r="EB7" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC7" t="s">
         <v>211</v>
       </c>
-      <c r="DY7">
-        <v>90</v>
-      </c>
-      <c r="DZ7" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA7">
-        <v>90</v>
-      </c>
-      <c r="EB7" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC7" t="s">
-        <v>212</v>
-      </c>
       <c r="ED7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE7">
         <v>0</v>
@@ -4383,16 +4437,43 @@
         <v>0</v>
       </c>
       <c r="EI7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK7">
+        <v>1</v>
+      </c>
+      <c r="EL7" t="s">
+        <v>217</v>
+      </c>
+      <c r="EM7">
+        <v>75000</v>
+      </c>
+      <c r="EN7">
+        <v>7200</v>
+      </c>
+      <c r="EO7">
+        <v>11000</v>
+      </c>
+      <c r="EP7">
+        <v>100000</v>
+      </c>
+      <c r="EQ7">
+        <v>90000</v>
+      </c>
+      <c r="ER7">
+        <v>80000</v>
+      </c>
+      <c r="ES7" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="b">
         <v>0</v>
       </c>
       <c r="FD7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE7">
         <v>0.05</v>
@@ -4407,70 +4488,52 @@
         <v>8.5</v>
       </c>
       <c r="FI7" t="s">
+        <v>222</v>
+      </c>
+      <c r="FJ7" t="s">
+        <v>223</v>
+      </c>
+      <c r="FK7" t="s">
+        <v>214</v>
+      </c>
+      <c r="FL7">
+        <v>0</v>
+      </c>
+      <c r="FM7">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU7">
+        <v>0</v>
+      </c>
+      <c r="FV7">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="s">
+        <v>214</v>
+      </c>
+      <c r="GB7" t="s">
         <v>224</v>
       </c>
-      <c r="FJ7" t="s">
-        <v>225</v>
-      </c>
-      <c r="FK7" t="s">
-        <v>215</v>
-      </c>
-      <c r="FL7">
-        <v>1</v>
-      </c>
-      <c r="FM7">
-        <v>1</v>
-      </c>
-      <c r="FN7">
-        <v>3000</v>
-      </c>
-      <c r="FO7">
-        <v>3000</v>
-      </c>
-      <c r="FP7">
-        <v>0.95</v>
-      </c>
-      <c r="FQ7">
-        <v>0.1</v>
-      </c>
-      <c r="FR7" t="b">
-        <v>0</v>
-      </c>
-      <c r="FS7" t="b">
-        <v>0</v>
-      </c>
-      <c r="FT7" t="s">
-        <v>215</v>
-      </c>
-      <c r="FU7">
-        <v>0</v>
-      </c>
-      <c r="FV7">
-        <v>0</v>
-      </c>
-      <c r="GA7" t="s">
-        <v>215</v>
-      </c>
-      <c r="GB7" t="s">
-        <v>226</v>
-      </c>
       <c r="GC7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD7">
         <v>86400</v>
       </c>
       <c r="GE7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI7">
         <v>86400</v>
@@ -4511,13 +4574,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3863000</v>
+        <v>2896000</v>
       </c>
       <c r="O8" t="s">
         <v>206</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -4532,25 +4595,25 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V8" t="s">
+        <v>210</v>
+      </c>
+      <c r="W8">
+        <v>90</v>
+      </c>
+      <c r="X8" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y8">
+        <v>90</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA8" t="s">
         <v>211</v>
-      </c>
-      <c r="W8">
-        <v>90</v>
-      </c>
-      <c r="X8" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y8">
-        <v>90</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>212</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -4562,7 +4625,7 @@
         <v>6</v>
       </c>
       <c r="AG8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH8">
         <v>1</v>
@@ -4577,26 +4640,26 @@
         <v>9</v>
       </c>
       <c r="AL8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN8">
+        <v>90</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP8">
+        <v>90</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR8" t="s">
         <v>211</v>
       </c>
-      <c r="AN8">
-        <v>90</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP8">
-        <v>90</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>212</v>
-      </c>
       <c r="AS8">
         <v>0</v>
       </c>
@@ -4604,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="AX8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY8">
         <v>1</v>
@@ -4619,26 +4682,26 @@
         <v>9</v>
       </c>
       <c r="BC8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE8">
+        <v>90</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG8">
+        <v>90</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI8" t="s">
         <v>211</v>
       </c>
-      <c r="BE8">
-        <v>90</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG8">
-        <v>90</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ8">
         <v>0</v>
       </c>
@@ -4646,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="BO8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -4661,37 +4724,37 @@
         <v>9</v>
       </c>
       <c r="BT8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV8">
+        <v>90</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX8">
+        <v>90</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ8" t="s">
         <v>211</v>
       </c>
-      <c r="BV8">
-        <v>90</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX8">
-        <v>90</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ8" t="s">
+      <c r="CA8">
+        <v>1</v>
+      </c>
+      <c r="CB8">
+        <v>1</v>
+      </c>
+      <c r="CC8">
+        <v>4900</v>
+      </c>
+      <c r="CD8" t="s">
         <v>212</v>
-      </c>
-      <c r="CA8">
-        <v>1</v>
-      </c>
-      <c r="CB8">
-        <v>1</v>
-      </c>
-      <c r="CC8">
-        <v>5000</v>
-      </c>
-      <c r="CD8" t="s">
-        <v>213</v>
       </c>
       <c r="CE8">
         <v>0</v>
@@ -4703,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="CH8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI8">
         <v>1</v>
@@ -4718,28 +4781,28 @@
         <v>9</v>
       </c>
       <c r="CM8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN8" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO8">
+        <v>90</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ8">
+        <v>90</v>
+      </c>
+      <c r="CR8" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS8" t="s">
         <v>211</v>
       </c>
-      <c r="CO8">
-        <v>90</v>
-      </c>
-      <c r="CP8" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ8">
-        <v>90</v>
-      </c>
-      <c r="CR8" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS8" t="s">
-        <v>212</v>
-      </c>
       <c r="CT8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU8">
         <v>0</v>
@@ -4748,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA8">
         <v>1</v>
@@ -4763,28 +4826,28 @@
         <v>9</v>
       </c>
       <c r="DE8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF8" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG8">
+        <v>90</v>
+      </c>
+      <c r="DH8" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI8">
+        <v>90</v>
+      </c>
+      <c r="DJ8" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK8" t="s">
         <v>211</v>
       </c>
-      <c r="DG8">
-        <v>90</v>
-      </c>
-      <c r="DH8" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI8">
-        <v>90</v>
-      </c>
-      <c r="DJ8" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK8" t="s">
-        <v>212</v>
-      </c>
       <c r="DL8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM8">
         <v>0</v>
@@ -4793,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="DR8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS8">
         <v>1</v>
@@ -4808,28 +4871,28 @@
         <v>9</v>
       </c>
       <c r="DW8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX8" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY8">
+        <v>90</v>
+      </c>
+      <c r="DZ8" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA8">
+        <v>90</v>
+      </c>
+      <c r="EB8" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC8" t="s">
         <v>211</v>
       </c>
-      <c r="DY8">
-        <v>90</v>
-      </c>
-      <c r="DZ8" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA8">
-        <v>90</v>
-      </c>
-      <c r="EB8" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC8" t="s">
-        <v>212</v>
-      </c>
       <c r="ED8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE8">
         <v>0</v>
@@ -4838,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="EI8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ8">
         <v>1</v>
@@ -4874,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="FD8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE8">
         <v>0.05</v>
@@ -4889,13 +4952,13 @@
         <v>8.5</v>
       </c>
       <c r="FI8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="FJ8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="FK8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FL8">
         <v>1</v>
@@ -4904,10 +4967,10 @@
         <v>1</v>
       </c>
       <c r="FN8">
-        <v>3900</v>
+        <v>2900</v>
       </c>
       <c r="FO8">
-        <v>3900</v>
+        <v>2900</v>
       </c>
       <c r="FP8">
         <v>0.95</v>
@@ -4922,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="FT8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FU8">
         <v>0</v>
@@ -4931,28 +4994,28 @@
         <v>0</v>
       </c>
       <c r="GA8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="GB8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="GC8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD8">
         <v>86400</v>
       </c>
       <c r="GE8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI8">
         <v>86400</v>
@@ -4993,13 +5056,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3863000</v>
+        <v>2455000</v>
       </c>
       <c r="O9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -5014,25 +5077,25 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V9" t="s">
+        <v>210</v>
+      </c>
+      <c r="W9">
+        <v>90</v>
+      </c>
+      <c r="X9" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y9">
+        <v>90</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA9" t="s">
         <v>211</v>
-      </c>
-      <c r="W9">
-        <v>90</v>
-      </c>
-      <c r="X9" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y9">
-        <v>90</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>212</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -5044,7 +5107,7 @@
         <v>6</v>
       </c>
       <c r="AG9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH9">
         <v>1</v>
@@ -5059,26 +5122,26 @@
         <v>9</v>
       </c>
       <c r="AL9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN9">
+        <v>90</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP9">
+        <v>90</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR9" t="s">
         <v>211</v>
       </c>
-      <c r="AN9">
-        <v>90</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP9">
-        <v>90</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>212</v>
-      </c>
       <c r="AS9">
         <v>0</v>
       </c>
@@ -5086,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="AX9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY9">
         <v>1</v>
@@ -5101,26 +5164,26 @@
         <v>9</v>
       </c>
       <c r="BC9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE9">
+        <v>90</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG9">
+        <v>90</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI9" t="s">
         <v>211</v>
       </c>
-      <c r="BE9">
-        <v>90</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG9">
-        <v>90</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ9">
         <v>0</v>
       </c>
@@ -5128,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="BO9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP9">
         <v>1</v>
@@ -5143,37 +5206,37 @@
         <v>9</v>
       </c>
       <c r="BT9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV9">
+        <v>90</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX9">
+        <v>90</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ9" t="s">
         <v>211</v>
       </c>
-      <c r="BV9">
-        <v>90</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX9">
-        <v>90</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ9" t="s">
+      <c r="CA9">
+        <v>1</v>
+      </c>
+      <c r="CB9">
+        <v>1</v>
+      </c>
+      <c r="CC9">
+        <v>3300</v>
+      </c>
+      <c r="CD9" t="s">
         <v>212</v>
-      </c>
-      <c r="CA9">
-        <v>1</v>
-      </c>
-      <c r="CB9">
-        <v>1</v>
-      </c>
-      <c r="CC9">
-        <v>6600</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>213</v>
       </c>
       <c r="CE9">
         <v>0</v>
@@ -5185,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="CH9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI9">
         <v>1</v>
@@ -5200,28 +5263,28 @@
         <v>9</v>
       </c>
       <c r="CM9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN9" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO9">
+        <v>90</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ9">
+        <v>90</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS9" t="s">
         <v>211</v>
       </c>
-      <c r="CO9">
-        <v>90</v>
-      </c>
-      <c r="CP9" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ9">
-        <v>90</v>
-      </c>
-      <c r="CR9" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS9" t="s">
-        <v>212</v>
-      </c>
       <c r="CT9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU9">
         <v>0</v>
@@ -5230,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA9">
         <v>1</v>
@@ -5245,28 +5308,28 @@
         <v>9</v>
       </c>
       <c r="DE9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF9" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG9">
+        <v>90</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI9">
+        <v>90</v>
+      </c>
+      <c r="DJ9" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK9" t="s">
         <v>211</v>
       </c>
-      <c r="DG9">
-        <v>90</v>
-      </c>
-      <c r="DH9" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI9">
-        <v>90</v>
-      </c>
-      <c r="DJ9" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK9" t="s">
-        <v>212</v>
-      </c>
       <c r="DL9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM9">
         <v>0</v>
@@ -5275,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="DR9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS9">
         <v>1</v>
@@ -5290,28 +5353,28 @@
         <v>9</v>
       </c>
       <c r="DW9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX9" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY9">
+        <v>90</v>
+      </c>
+      <c r="DZ9" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA9">
+        <v>90</v>
+      </c>
+      <c r="EB9" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC9" t="s">
         <v>211</v>
       </c>
-      <c r="DY9">
-        <v>90</v>
-      </c>
-      <c r="DZ9" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA9">
-        <v>90</v>
-      </c>
-      <c r="EB9" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC9" t="s">
-        <v>212</v>
-      </c>
       <c r="ED9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE9">
         <v>0</v>
@@ -5320,70 +5383,16 @@
         <v>0</v>
       </c>
       <c r="EI9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK9">
-        <v>2</v>
-      </c>
-      <c r="EL9" t="s">
-        <v>219</v>
-      </c>
-      <c r="EM9">
-        <v>50000</v>
-      </c>
-      <c r="EN9">
-        <v>7200</v>
-      </c>
-      <c r="EO9">
-        <v>7200</v>
-      </c>
-      <c r="EP9">
-        <v>50000</v>
-      </c>
-      <c r="EQ9">
-        <v>90000</v>
-      </c>
-      <c r="ER9">
-        <v>80000</v>
-      </c>
-      <c r="ES9" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET9" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU9" t="s">
-        <v>222</v>
-      </c>
-      <c r="EV9">
-        <v>50000</v>
-      </c>
-      <c r="EW9">
-        <v>7200</v>
-      </c>
-      <c r="EX9">
-        <v>7200</v>
-      </c>
-      <c r="EY9">
-        <v>50000</v>
-      </c>
-      <c r="EZ9">
-        <v>90000</v>
-      </c>
-      <c r="FA9">
-        <v>80000</v>
-      </c>
-      <c r="FB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC9" t="b">
         <v>0</v>
       </c>
       <c r="FD9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE9">
         <v>0.05</v>
@@ -5398,52 +5407,70 @@
         <v>8.5</v>
       </c>
       <c r="FI9" t="s">
+        <v>222</v>
+      </c>
+      <c r="FJ9" t="s">
+        <v>223</v>
+      </c>
+      <c r="FK9" t="s">
+        <v>214</v>
+      </c>
+      <c r="FL9">
+        <v>1</v>
+      </c>
+      <c r="FM9">
+        <v>1</v>
+      </c>
+      <c r="FN9">
+        <v>2500</v>
+      </c>
+      <c r="FO9">
+        <v>2500</v>
+      </c>
+      <c r="FP9">
+        <v>0.95</v>
+      </c>
+      <c r="FQ9">
+        <v>0.1</v>
+      </c>
+      <c r="FR9" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="b">
+        <v>0</v>
+      </c>
+      <c r="FT9" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU9">
+        <v>0</v>
+      </c>
+      <c r="FV9">
+        <v>0</v>
+      </c>
+      <c r="GA9" t="s">
+        <v>214</v>
+      </c>
+      <c r="GB9" t="s">
         <v>224</v>
       </c>
-      <c r="FJ9" t="s">
-        <v>225</v>
-      </c>
-      <c r="FK9" t="s">
-        <v>215</v>
-      </c>
-      <c r="FL9">
-        <v>0</v>
-      </c>
-      <c r="FM9">
-        <v>0</v>
-      </c>
-      <c r="FT9" t="s">
-        <v>215</v>
-      </c>
-      <c r="FU9">
-        <v>0</v>
-      </c>
-      <c r="FV9">
-        <v>0</v>
-      </c>
-      <c r="GA9" t="s">
-        <v>215</v>
-      </c>
-      <c r="GB9" t="s">
-        <v>226</v>
-      </c>
       <c r="GC9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD9">
         <v>86400</v>
       </c>
       <c r="GE9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI9">
         <v>86400</v>
@@ -5484,13 +5511,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>3125000</v>
+        <v>5527000</v>
       </c>
       <c r="O10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -5505,25 +5532,25 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V10" t="s">
+        <v>210</v>
+      </c>
+      <c r="W10">
+        <v>90</v>
+      </c>
+      <c r="X10" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y10">
+        <v>90</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA10" t="s">
         <v>211</v>
-      </c>
-      <c r="W10">
-        <v>90</v>
-      </c>
-      <c r="X10" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y10">
-        <v>90</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>212</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -5535,7 +5562,7 @@
         <v>6</v>
       </c>
       <c r="AG10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH10">
         <v>1</v>
@@ -5550,26 +5577,26 @@
         <v>9</v>
       </c>
       <c r="AL10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN10">
+        <v>90</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP10">
+        <v>90</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR10" t="s">
         <v>211</v>
       </c>
-      <c r="AN10">
-        <v>90</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP10">
-        <v>90</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>212</v>
-      </c>
       <c r="AS10">
         <v>0</v>
       </c>
@@ -5577,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="AX10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY10">
         <v>1</v>
@@ -5592,26 +5619,26 @@
         <v>9</v>
       </c>
       <c r="BC10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE10">
+        <v>90</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG10">
+        <v>90</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI10" t="s">
         <v>211</v>
       </c>
-      <c r="BE10">
-        <v>90</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG10">
-        <v>90</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ10">
         <v>0</v>
       </c>
@@ -5619,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="BO10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -5634,49 +5661,34 @@
         <v>9</v>
       </c>
       <c r="BT10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV10">
+        <v>90</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX10">
+        <v>90</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ10" t="s">
         <v>211</v>
       </c>
-      <c r="BV10">
-        <v>90</v>
-      </c>
-      <c r="BW10" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX10">
-        <v>90</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>212</v>
-      </c>
       <c r="CA10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB10">
-        <v>1</v>
-      </c>
-      <c r="CC10">
-        <v>4300</v>
-      </c>
-      <c r="CD10" t="s">
-        <v>213</v>
-      </c>
-      <c r="CE10">
-        <v>0</v>
-      </c>
-      <c r="CF10">
-        <v>40</v>
-      </c>
-      <c r="CG10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI10">
         <v>1</v>
@@ -5691,28 +5703,28 @@
         <v>9</v>
       </c>
       <c r="CM10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN10" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO10">
+        <v>90</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ10">
+        <v>90</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS10" t="s">
         <v>211</v>
       </c>
-      <c r="CO10">
-        <v>90</v>
-      </c>
-      <c r="CP10" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ10">
-        <v>90</v>
-      </c>
-      <c r="CR10" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS10" t="s">
-        <v>212</v>
-      </c>
       <c r="CT10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU10">
         <v>0</v>
@@ -5721,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA10">
         <v>1</v>
@@ -5736,28 +5748,28 @@
         <v>9</v>
       </c>
       <c r="DE10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF10" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG10">
+        <v>90</v>
+      </c>
+      <c r="DH10" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI10">
+        <v>90</v>
+      </c>
+      <c r="DJ10" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK10" t="s">
         <v>211</v>
       </c>
-      <c r="DG10">
-        <v>90</v>
-      </c>
-      <c r="DH10" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI10">
-        <v>90</v>
-      </c>
-      <c r="DJ10" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK10" t="s">
-        <v>212</v>
-      </c>
       <c r="DL10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM10">
         <v>0</v>
@@ -5766,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="DR10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS10">
         <v>1</v>
@@ -5781,28 +5793,28 @@
         <v>9</v>
       </c>
       <c r="DW10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX10" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY10">
+        <v>90</v>
+      </c>
+      <c r="DZ10" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA10">
+        <v>90</v>
+      </c>
+      <c r="EB10" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC10" t="s">
         <v>211</v>
       </c>
-      <c r="DY10">
-        <v>90</v>
-      </c>
-      <c r="DZ10" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA10">
-        <v>90</v>
-      </c>
-      <c r="EB10" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC10" t="s">
-        <v>212</v>
-      </c>
       <c r="ED10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE10">
         <v>0</v>
@@ -5811,43 +5823,16 @@
         <v>0</v>
       </c>
       <c r="EI10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK10">
-        <v>1</v>
-      </c>
-      <c r="EL10" t="s">
-        <v>220</v>
-      </c>
-      <c r="EM10">
-        <v>75000</v>
-      </c>
-      <c r="EN10">
-        <v>7200</v>
-      </c>
-      <c r="EO10">
-        <v>11000</v>
-      </c>
-      <c r="EP10">
-        <v>100000</v>
-      </c>
-      <c r="EQ10">
-        <v>90000</v>
-      </c>
-      <c r="ER10">
-        <v>80000</v>
-      </c>
-      <c r="ES10" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET10" t="b">
         <v>0</v>
       </c>
       <c r="FD10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE10">
         <v>0.05</v>
@@ -5862,52 +5847,52 @@
         <v>8.5</v>
       </c>
       <c r="FI10" t="s">
+        <v>222</v>
+      </c>
+      <c r="FJ10" t="s">
+        <v>223</v>
+      </c>
+      <c r="FK10" t="s">
+        <v>214</v>
+      </c>
+      <c r="FL10">
+        <v>0</v>
+      </c>
+      <c r="FM10">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="s">
+        <v>214</v>
+      </c>
+      <c r="FU10">
+        <v>0</v>
+      </c>
+      <c r="FV10">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="s">
+        <v>214</v>
+      </c>
+      <c r="GB10" t="s">
         <v>224</v>
       </c>
-      <c r="FJ10" t="s">
-        <v>225</v>
-      </c>
-      <c r="FK10" t="s">
-        <v>215</v>
-      </c>
-      <c r="FL10">
-        <v>0</v>
-      </c>
-      <c r="FM10">
-        <v>0</v>
-      </c>
-      <c r="FT10" t="s">
-        <v>215</v>
-      </c>
-      <c r="FU10">
-        <v>0</v>
-      </c>
-      <c r="FV10">
-        <v>0</v>
-      </c>
-      <c r="GA10" t="s">
-        <v>215</v>
-      </c>
-      <c r="GB10" t="s">
-        <v>226</v>
-      </c>
       <c r="GC10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD10">
         <v>86400</v>
       </c>
       <c r="GE10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI10">
         <v>86400</v>
@@ -5924,10 +5909,10 @@
         <v>200</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -5936,7 +5921,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -5948,13 +5933,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>3564000</v>
+        <v>3125000</v>
       </c>
       <c r="O11" t="s">
+        <v>204</v>
+      </c>
+      <c r="P11" t="s">
         <v>208</v>
-      </c>
-      <c r="P11" t="s">
-        <v>209</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -5969,25 +5954,25 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V11" t="s">
+        <v>210</v>
+      </c>
+      <c r="W11">
+        <v>90</v>
+      </c>
+      <c r="X11" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y11">
+        <v>90</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA11" t="s">
         <v>211</v>
-      </c>
-      <c r="W11">
-        <v>90</v>
-      </c>
-      <c r="X11" t="s">
-        <v>211</v>
-      </c>
-      <c r="Y11">
-        <v>90</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>212</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -5999,7 +5984,7 @@
         <v>6</v>
       </c>
       <c r="AG11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AH11">
         <v>1</v>
@@ -6014,26 +5999,26 @@
         <v>9</v>
       </c>
       <c r="AL11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AM11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN11">
+        <v>90</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP11">
+        <v>90</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AR11" t="s">
         <v>211</v>
       </c>
-      <c r="AN11">
-        <v>90</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>211</v>
-      </c>
-      <c r="AP11">
-        <v>90</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>212</v>
-      </c>
       <c r="AS11">
         <v>0</v>
       </c>
@@ -6041,7 +6026,7 @@
         <v>0</v>
       </c>
       <c r="AX11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AY11">
         <v>1</v>
@@ -6056,26 +6041,26 @@
         <v>9</v>
       </c>
       <c r="BC11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BD11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BE11">
+        <v>90</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BG11">
+        <v>90</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI11" t="s">
         <v>211</v>
       </c>
-      <c r="BE11">
-        <v>90</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG11">
-        <v>90</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>211</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>212</v>
-      </c>
       <c r="BJ11">
         <v>0</v>
       </c>
@@ -6083,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="BO11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BP11">
         <v>1</v>
@@ -6098,49 +6083,49 @@
         <v>9</v>
       </c>
       <c r="BT11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BU11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BV11">
+        <v>90</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BX11">
+        <v>90</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BZ11" t="s">
         <v>211</v>
       </c>
-      <c r="BV11">
-        <v>90</v>
-      </c>
-      <c r="BW11" t="s">
-        <v>211</v>
-      </c>
-      <c r="BX11">
-        <v>90</v>
-      </c>
-      <c r="BY11" t="s">
-        <v>211</v>
-      </c>
-      <c r="BZ11" t="s">
+      <c r="CA11">
+        <v>1</v>
+      </c>
+      <c r="CB11">
+        <v>1</v>
+      </c>
+      <c r="CC11">
+        <v>4300</v>
+      </c>
+      <c r="CD11" t="s">
         <v>212</v>
       </c>
-      <c r="CA11">
-        <v>1</v>
-      </c>
-      <c r="CB11">
-        <v>1</v>
-      </c>
-      <c r="CC11">
-        <v>4600</v>
-      </c>
-      <c r="CD11" t="s">
-        <v>213</v>
-      </c>
       <c r="CE11">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG11" t="b">
         <v>1</v>
       </c>
       <c r="CH11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="CI11">
         <v>1</v>
@@ -6155,28 +6140,28 @@
         <v>9</v>
       </c>
       <c r="CM11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="CN11" t="s">
+        <v>210</v>
+      </c>
+      <c r="CO11">
+        <v>90</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>210</v>
+      </c>
+      <c r="CQ11">
+        <v>90</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>210</v>
+      </c>
+      <c r="CS11" t="s">
         <v>211</v>
       </c>
-      <c r="CO11">
-        <v>90</v>
-      </c>
-      <c r="CP11" t="s">
-        <v>211</v>
-      </c>
-      <c r="CQ11">
-        <v>90</v>
-      </c>
-      <c r="CR11" t="s">
-        <v>211</v>
-      </c>
-      <c r="CS11" t="s">
-        <v>212</v>
-      </c>
       <c r="CT11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="CU11">
         <v>0</v>
@@ -6185,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="CZ11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DA11">
         <v>1</v>
@@ -6200,28 +6185,28 @@
         <v>9</v>
       </c>
       <c r="DE11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DF11" t="s">
+        <v>210</v>
+      </c>
+      <c r="DG11">
+        <v>90</v>
+      </c>
+      <c r="DH11" t="s">
+        <v>210</v>
+      </c>
+      <c r="DI11">
+        <v>90</v>
+      </c>
+      <c r="DJ11" t="s">
+        <v>210</v>
+      </c>
+      <c r="DK11" t="s">
         <v>211</v>
       </c>
-      <c r="DG11">
-        <v>90</v>
-      </c>
-      <c r="DH11" t="s">
-        <v>211</v>
-      </c>
-      <c r="DI11">
-        <v>90</v>
-      </c>
-      <c r="DJ11" t="s">
-        <v>211</v>
-      </c>
-      <c r="DK11" t="s">
-        <v>212</v>
-      </c>
       <c r="DL11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DM11">
         <v>0</v>
@@ -6230,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="DR11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="DS11">
         <v>1</v>
@@ -6245,28 +6230,28 @@
         <v>9</v>
       </c>
       <c r="DW11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="DX11" t="s">
+        <v>210</v>
+      </c>
+      <c r="DY11">
+        <v>90</v>
+      </c>
+      <c r="DZ11" t="s">
+        <v>210</v>
+      </c>
+      <c r="EA11">
+        <v>90</v>
+      </c>
+      <c r="EB11" t="s">
+        <v>210</v>
+      </c>
+      <c r="EC11" t="s">
         <v>211</v>
       </c>
-      <c r="DY11">
-        <v>90</v>
-      </c>
-      <c r="DZ11" t="s">
-        <v>211</v>
-      </c>
-      <c r="EA11">
-        <v>90</v>
-      </c>
-      <c r="EB11" t="s">
-        <v>211</v>
-      </c>
-      <c r="EC11" t="s">
-        <v>212</v>
-      </c>
       <c r="ED11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EE11">
         <v>0</v>
@@ -6275,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="EI11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="EJ11">
         <v>0</v>
@@ -6284,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="FD11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="FE11">
         <v>0.05</v>
@@ -6299,13 +6284,13 @@
         <v>8.5</v>
       </c>
       <c r="FI11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="FJ11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="FK11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FL11">
         <v>1</v>
@@ -6314,10 +6299,10 @@
         <v>1</v>
       </c>
       <c r="FN11">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="FO11">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="FP11">
         <v>0.95</v>
@@ -6332,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="FT11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="FU11">
         <v>0</v>
@@ -6341,28 +6326,28 @@
         <v>0</v>
       </c>
       <c r="GA11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="GB11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="GC11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="GD11">
         <v>86400</v>
       </c>
       <c r="GE11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="GF11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="GG11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GH11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="GI11">
         <v>86400</v>
@@ -6395,13 +6380,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -6989,7 +6974,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7301,22 +7286,22 @@
         <v>158</v>
       </c>
       <c r="DF1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="DI1" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="DG1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="DH1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="DI1" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="DJ1" s="1" t="s">
         <v>163</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="DL1" s="1" t="s">
         <v>165</v>
@@ -7400,7 +7385,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -8057,10 +8042,10 @@
         <v>188</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -8117,58 +8102,58 @@
         <v>174</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>182</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\02 - config\example_single_market\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDFA954-CCD5-47CB-8AFF-7921CCAD63CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sfh" sheetId="1" r:id="rId1"/>
@@ -14,12 +20,25 @@
     <sheet name="producer" sheetId="5" r:id="rId5"/>
     <sheet name="storage" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="270">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -594,57 +613,57 @@
     <t>ems/fcasts/update_period</t>
   </si>
   <si>
-    <t>QIDo2Rf8HWcrrrK</t>
-  </si>
-  <si>
-    <t>mMna0fdFv2mFxIA</t>
-  </si>
-  <si>
-    <t>LTjj3htgEzFPFwG</t>
-  </si>
-  <si>
-    <t>wUnlhLunAQkmiYg</t>
-  </si>
-  <si>
-    <t>TzFCeFv75nGXK76</t>
-  </si>
-  <si>
-    <t>Whx5cbqKg1TTcfv</t>
-  </si>
-  <si>
-    <t>TqTxlkKDgzonG7H</t>
-  </si>
-  <si>
-    <t>1elq9ieTruo5sEm</t>
-  </si>
-  <si>
-    <t>RxBT5EAnLtY3JdD</t>
-  </si>
-  <si>
-    <t>g06giXT84GgespH</t>
-  </si>
-  <si>
-    <t>hh_4536_0.csv</t>
+    <t>uzEoMpDvqUQmolk</t>
+  </si>
+  <si>
+    <t>DGzmAB9lHmVyQZv</t>
+  </si>
+  <si>
+    <t>TYMLJEa1KAhqE59</t>
+  </si>
+  <si>
+    <t>exVNgDckyloeKPg</t>
+  </si>
+  <si>
+    <t>KbSpjvHvz8Y5u7z</t>
+  </si>
+  <si>
+    <t>9ImCBUvCV7wFtHf</t>
+  </si>
+  <si>
+    <t>yHAIaE0rOHnBGoP</t>
+  </si>
+  <si>
+    <t>rNrxz3A1u6iRhO2</t>
+  </si>
+  <si>
+    <t>Ec93eXNNvTukTxN</t>
+  </si>
+  <si>
+    <t>ZzD5Fsx2AOCTX8N</t>
+  </si>
+  <si>
+    <t>hh_2532_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4402_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
   </si>
   <si>
     <t>hh_3564_0.csv</t>
   </si>
   <si>
-    <t>hh_3863_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
     <t>hh_2896_0.csv</t>
   </si>
   <si>
-    <t>hh_2455_0.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -657,6 +676,42 @@
     <t>[1, 0, 0]</t>
   </si>
   <si>
+    <t>heat_2532_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3125_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2896_0.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
     <t>pv_config.json</t>
   </si>
   <si>
@@ -666,22 +721,31 @@
     <t>local</t>
   </si>
   <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_47.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_42.csv</t>
+  </si>
+  <si>
     <t>ev_parttime_90.csv</t>
   </si>
   <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_1.csv</t>
-  </si>
-  <si>
     <t>ev_parttime_88.csv</t>
   </si>
   <si>
-    <t>ev_freetime_0.csv</t>
+    <t>ev_fulltime_43.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -789,8 +853,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -853,13 +917,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -897,7 +969,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -931,6 +1003,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -965,9 +1038,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1140,11 +1214,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:GJ11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="1.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="28.90625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="24" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="27.6328125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="25" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="27.36328125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="18" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="9" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="104" max="104" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="105" max="105" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="22" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="110" max="110" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="116" max="116" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="119" max="119" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="120" max="120" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="27.453125" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="123" max="123" width="25" bestFit="1" customWidth="1"/>
+    <col min="124" max="124" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="125" max="125" width="26.08984375" bestFit="1" customWidth="1"/>
+    <col min="126" max="126" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="129" max="129" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="130" max="130" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="131" max="131" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="132" max="132" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="133" max="133" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="134" max="134" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="135" max="135" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="136" max="136" width="7.6328125" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="138" max="138" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="140" max="140" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="142" max="142" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="143" max="143" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="144" max="144" width="24" bestFit="1" customWidth="1"/>
+    <col min="145" max="145" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="146" max="146" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="147" max="147" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="148" max="148" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="149" max="149" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="150" max="150" width="14" bestFit="1" customWidth="1"/>
+    <col min="151" max="151" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="152" max="152" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="153" max="153" width="24" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="155" max="155" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="156" max="156" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="157" max="157" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="158" max="158" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="159" max="159" width="14" bestFit="1" customWidth="1"/>
+    <col min="160" max="160" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="161" max="161" width="40.6328125" bestFit="1" customWidth="1"/>
+    <col min="162" max="162" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="163" max="163" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="164" max="164" width="35.6328125" bestFit="1" customWidth="1"/>
+    <col min="165" max="165" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="166" max="166" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="168" max="168" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="169" max="169" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="170" max="170" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="173" max="173" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="174" max="175" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="176" max="176" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="177" max="177" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="178" max="178" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="179" max="179" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="181" max="181" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="182" max="182" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="183" max="183" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="184" max="184" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="185" max="185" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="186" max="186" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="187" max="187" width="19" bestFit="1" customWidth="1"/>
+    <col min="188" max="188" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="189" max="189" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="190" max="190" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="191" max="191" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="192" max="192" width="23.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:192">
+    <row r="1" spans="1:192" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1986,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:192">
+    <row r="2" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1751,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>4536000</v>
+        <v>2532000</v>
       </c>
       <c r="O2" t="s">
         <v>201</v>
@@ -1838,10 +2105,19 @@
         <v>211</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>19500000</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AW2">
+        <v>55</v>
       </c>
       <c r="AX2" t="s">
         <v>208</v>
@@ -1880,10 +2156,19 @@
         <v>211</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL2">
+        <v>2800000</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>219</v>
+      </c>
+      <c r="BN2">
+        <v>55</v>
       </c>
       <c r="BO2" t="s">
         <v>208</v>
@@ -1928,10 +2213,10 @@
         <v>1</v>
       </c>
       <c r="CC2">
-        <v>5700</v>
+        <v>3800</v>
       </c>
       <c r="CD2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE2">
         <v>0</v>
@@ -1979,7 +2264,7 @@
         <v>211</v>
       </c>
       <c r="CT2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU2">
         <v>0</v>
@@ -2024,7 +2309,7 @@
         <v>211</v>
       </c>
       <c r="DL2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM2">
         <v>0</v>
@@ -2069,7 +2354,7 @@
         <v>211</v>
       </c>
       <c r="ED2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE2">
         <v>0</v>
@@ -2078,16 +2363,43 @@
         <v>0</v>
       </c>
       <c r="EI2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK2">
+        <v>1</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>227</v>
+      </c>
+      <c r="EM2">
+        <v>50000</v>
+      </c>
+      <c r="EN2">
+        <v>7200</v>
+      </c>
+      <c r="EO2">
+        <v>7200</v>
+      </c>
+      <c r="EP2">
+        <v>50000</v>
+      </c>
+      <c r="EQ2">
+        <v>0.9</v>
+      </c>
+      <c r="ER2">
+        <v>0.8</v>
+      </c>
+      <c r="ES2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="b">
         <v>0</v>
       </c>
       <c r="FD2" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE2">
         <v>0.05</v>
@@ -2102,13 +2414,13 @@
         <v>8.5</v>
       </c>
       <c r="FI2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL2">
         <v>1</v>
@@ -2117,10 +2429,10 @@
         <v>1</v>
       </c>
       <c r="FN2">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="FO2">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="FP2">
         <v>0.95</v>
@@ -2135,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="FT2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU2">
         <v>0</v>
@@ -2144,28 +2456,28 @@
         <v>0</v>
       </c>
       <c r="GA2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD2">
         <v>86400</v>
       </c>
       <c r="GE2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI2">
         <v>86400</v>
@@ -2174,7 +2486,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:192">
+    <row r="3" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2206,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>3564000</v>
+        <v>3125000</v>
       </c>
       <c r="O3" t="s">
         <v>202</v>
@@ -2293,10 +2605,19 @@
         <v>211</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU3">
+        <v>19500000</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>213</v>
+      </c>
+      <c r="AW3">
+        <v>55</v>
       </c>
       <c r="AX3" t="s">
         <v>208</v>
@@ -2335,10 +2656,19 @@
         <v>211</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL3">
+        <v>2400000</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BN3">
+        <v>55</v>
       </c>
       <c r="BO3" t="s">
         <v>208</v>
@@ -2377,10 +2707,25 @@
         <v>211</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CC3">
+        <v>5400</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>224</v>
+      </c>
+      <c r="CE3">
+        <v>0</v>
+      </c>
+      <c r="CF3">
+        <v>40</v>
+      </c>
+      <c r="CG3" t="b">
+        <v>1</v>
       </c>
       <c r="CH3" t="s">
         <v>208</v>
@@ -2419,7 +2764,7 @@
         <v>211</v>
       </c>
       <c r="CT3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU3">
         <v>0</v>
@@ -2464,7 +2809,7 @@
         <v>211</v>
       </c>
       <c r="DL3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM3">
         <v>0</v>
@@ -2509,7 +2854,7 @@
         <v>211</v>
       </c>
       <c r="ED3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE3">
         <v>0</v>
@@ -2518,34 +2863,34 @@
         <v>0</v>
       </c>
       <c r="EI3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ3">
         <v>1</v>
       </c>
       <c r="EK3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EL3" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="EM3">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EN3">
         <v>7200</v>
       </c>
       <c r="EO3">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EP3">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EQ3">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER3">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES3" t="b">
         <v>0</v>
@@ -2553,35 +2898,8 @@
       <c r="ET3" t="b">
         <v>0</v>
       </c>
-      <c r="EU3" t="s">
-        <v>219</v>
-      </c>
-      <c r="EV3">
-        <v>50000</v>
-      </c>
-      <c r="EW3">
-        <v>7200</v>
-      </c>
-      <c r="EX3">
-        <v>7200</v>
-      </c>
-      <c r="EY3">
-        <v>50000</v>
-      </c>
-      <c r="EZ3">
-        <v>90000</v>
-      </c>
-      <c r="FA3">
-        <v>80000</v>
-      </c>
-      <c r="FB3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC3" t="b">
-        <v>0</v>
-      </c>
       <c r="FD3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE3">
         <v>0.05</v>
@@ -2596,22 +2914,40 @@
         <v>8.5</v>
       </c>
       <c r="FI3" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM3">
+        <v>1</v>
+      </c>
+      <c r="FN3">
+        <v>3100</v>
+      </c>
+      <c r="FO3">
+        <v>3100</v>
+      </c>
+      <c r="FP3">
+        <v>0.95</v>
+      </c>
+      <c r="FQ3">
+        <v>0.1</v>
+      </c>
+      <c r="FR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS3" t="b">
         <v>0</v>
       </c>
       <c r="FT3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU3">
         <v>0</v>
@@ -2620,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="GA3" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD3">
         <v>86400</v>
       </c>
       <c r="GE3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF3" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG3" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH3" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI3">
         <v>86400</v>
@@ -2650,7 +2986,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:192">
+    <row r="4" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -2682,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>3863000</v>
+        <v>5527000</v>
       </c>
       <c r="O4" t="s">
         <v>203</v>
@@ -2769,10 +3105,19 @@
         <v>211</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <v>5500000</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW4">
+        <v>55</v>
       </c>
       <c r="AX4" t="s">
         <v>208</v>
@@ -2811,10 +3156,19 @@
         <v>211</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL4">
+        <v>2400000</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>219</v>
+      </c>
+      <c r="BN4">
+        <v>55</v>
       </c>
       <c r="BO4" t="s">
         <v>208</v>
@@ -2859,10 +3213,10 @@
         <v>1</v>
       </c>
       <c r="CC4">
-        <v>6400</v>
+        <v>7900</v>
       </c>
       <c r="CD4" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE4">
         <v>0</v>
@@ -2910,7 +3264,7 @@
         <v>211</v>
       </c>
       <c r="CT4" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU4">
         <v>0</v>
@@ -2955,7 +3309,7 @@
         <v>211</v>
       </c>
       <c r="DL4" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM4">
         <v>0</v>
@@ -3000,7 +3354,7 @@
         <v>211</v>
       </c>
       <c r="ED4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE4">
         <v>0</v>
@@ -3009,16 +3363,70 @@
         <v>0</v>
       </c>
       <c r="EI4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK4">
+        <v>2</v>
+      </c>
+      <c r="EL4" t="s">
+        <v>229</v>
+      </c>
+      <c r="EM4">
+        <v>75000</v>
+      </c>
+      <c r="EN4">
+        <v>7200</v>
+      </c>
+      <c r="EO4">
+        <v>11000</v>
+      </c>
+      <c r="EP4">
+        <v>100000</v>
+      </c>
+      <c r="EQ4">
+        <v>0.9</v>
+      </c>
+      <c r="ER4">
+        <v>0.8</v>
+      </c>
+      <c r="ES4" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET4" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU4" t="s">
+        <v>234</v>
+      </c>
+      <c r="EV4">
+        <v>100000</v>
+      </c>
+      <c r="EW4">
+        <v>11000</v>
+      </c>
+      <c r="EX4">
+        <v>22000</v>
+      </c>
+      <c r="EY4">
+        <v>200000</v>
+      </c>
+      <c r="EZ4">
+        <v>90000</v>
+      </c>
+      <c r="FA4">
+        <v>80000</v>
+      </c>
+      <c r="FB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC4" t="b">
         <v>0</v>
       </c>
       <c r="FD4" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE4">
         <v>0.05</v>
@@ -3033,13 +3441,13 @@
         <v>8.5</v>
       </c>
       <c r="FI4" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ4" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL4">
         <v>1</v>
@@ -3048,10 +3456,10 @@
         <v>1</v>
       </c>
       <c r="FN4">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="FO4">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="FP4">
         <v>0.95</v>
@@ -3066,7 +3474,7 @@
         <v>0</v>
       </c>
       <c r="FT4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU4">
         <v>0</v>
@@ -3075,28 +3483,28 @@
         <v>0</v>
       </c>
       <c r="GA4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB4" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC4" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD4">
         <v>86400</v>
       </c>
       <c r="GE4" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF4" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG4" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH4" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI4">
         <v>86400</v>
@@ -3105,7 +3513,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:192">
+    <row r="5" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3113,10 +3521,10 @@
         <v>194</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3125,7 +3533,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3137,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>3125000</v>
+        <v>4402000</v>
       </c>
       <c r="O5" t="s">
         <v>204</v>
@@ -3224,10 +3632,19 @@
         <v>211</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>5500000</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>215</v>
+      </c>
+      <c r="AW5">
+        <v>55</v>
       </c>
       <c r="AX5" t="s">
         <v>208</v>
@@ -3266,10 +3683,19 @@
         <v>211</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL5">
+        <v>2400000</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>221</v>
+      </c>
+      <c r="BN5">
+        <v>55</v>
       </c>
       <c r="BO5" t="s">
         <v>208</v>
@@ -3314,10 +3740,10 @@
         <v>1</v>
       </c>
       <c r="CC5">
-        <v>5400</v>
+        <v>6900</v>
       </c>
       <c r="CD5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE5">
         <v>-20</v>
@@ -3365,7 +3791,7 @@
         <v>211</v>
       </c>
       <c r="CT5" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU5">
         <v>0</v>
@@ -3410,7 +3836,7 @@
         <v>211</v>
       </c>
       <c r="DL5" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM5">
         <v>0</v>
@@ -3455,7 +3881,7 @@
         <v>211</v>
       </c>
       <c r="ED5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE5">
         <v>0</v>
@@ -3464,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="EI5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ5">
         <v>1</v>
@@ -3473,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="EL5" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="EM5">
         <v>50000</v>
@@ -3488,10 +3914,10 @@
         <v>50000</v>
       </c>
       <c r="EQ5">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER5">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES5" t="b">
         <v>0</v>
@@ -3500,19 +3926,19 @@
         <v>0</v>
       </c>
       <c r="EU5" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="EV5">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EW5">
         <v>7200</v>
       </c>
       <c r="EX5">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EY5">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EZ5">
         <v>90000</v>
@@ -3527,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="FD5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE5">
         <v>0.05</v>
@@ -3542,13 +3968,13 @@
         <v>8.5</v>
       </c>
       <c r="FI5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ5" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL5">
         <v>1</v>
@@ -3557,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="FN5">
-        <v>3100</v>
+        <v>4400</v>
       </c>
       <c r="FO5">
-        <v>3100</v>
+        <v>4400</v>
       </c>
       <c r="FP5">
         <v>0.95</v>
@@ -3575,7 +4001,7 @@
         <v>0</v>
       </c>
       <c r="FT5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU5">
         <v>0</v>
@@ -3584,28 +4010,28 @@
         <v>0</v>
       </c>
       <c r="GA5" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB5" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC5" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD5">
         <v>86400</v>
       </c>
       <c r="GE5" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF5" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH5" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI5">
         <v>86400</v>
@@ -3614,7 +4040,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:192">
+    <row r="6" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3622,10 +4048,10 @@
         <v>195</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -3634,7 +4060,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -3646,10 +4072,10 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>3564000</v>
+        <v>3296000</v>
       </c>
       <c r="O6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P6" t="s">
         <v>208</v>
@@ -3733,10 +4159,19 @@
         <v>211</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>5500000</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>216</v>
+      </c>
+      <c r="AW6">
+        <v>55</v>
       </c>
       <c r="AX6" t="s">
         <v>208</v>
@@ -3775,10 +4210,19 @@
         <v>211</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL6">
+        <v>1800000</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>219</v>
+      </c>
+      <c r="BN6">
+        <v>55</v>
       </c>
       <c r="BO6" t="s">
         <v>208</v>
@@ -3823,10 +4267,10 @@
         <v>1</v>
       </c>
       <c r="CC6">
-        <v>4800</v>
+        <v>4000</v>
       </c>
       <c r="CD6" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE6">
         <v>0</v>
@@ -3874,7 +4318,7 @@
         <v>211</v>
       </c>
       <c r="CT6" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU6">
         <v>0</v>
@@ -3919,7 +4363,7 @@
         <v>211</v>
       </c>
       <c r="DL6" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM6">
         <v>0</v>
@@ -3964,7 +4408,7 @@
         <v>211</v>
       </c>
       <c r="ED6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE6">
         <v>0</v>
@@ -3973,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="EI6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ6">
         <v>1</v>
@@ -3982,7 +4426,7 @@
         <v>1</v>
       </c>
       <c r="EL6" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="EM6">
         <v>50000</v>
@@ -3997,10 +4441,10 @@
         <v>50000</v>
       </c>
       <c r="EQ6">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER6">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES6" t="b">
         <v>0</v>
@@ -4009,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="FD6" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE6">
         <v>0.05</v>
@@ -4024,22 +4468,40 @@
         <v>8.5</v>
       </c>
       <c r="FI6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM6">
+        <v>1</v>
+      </c>
+      <c r="FN6">
+        <v>3300</v>
+      </c>
+      <c r="FO6">
+        <v>3300</v>
+      </c>
+      <c r="FP6">
+        <v>0.95</v>
+      </c>
+      <c r="FQ6">
+        <v>0.1</v>
+      </c>
+      <c r="FR6" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="b">
         <v>0</v>
       </c>
       <c r="FT6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU6">
         <v>0</v>
@@ -4048,28 +4510,28 @@
         <v>0</v>
       </c>
       <c r="GA6" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB6" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC6" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD6">
         <v>86400</v>
       </c>
       <c r="GE6" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF6" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG6" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH6" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI6">
         <v>86400</v>
@@ -4078,7 +4540,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:192">
+    <row r="7" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4086,10 +4548,10 @@
         <v>196</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -4098,7 +4560,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4110,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>5527000</v>
+        <v>3296000</v>
       </c>
       <c r="O7" t="s">
         <v>205</v>
@@ -4197,10 +4659,19 @@
         <v>211</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <v>19500000</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>216</v>
+      </c>
+      <c r="AW7">
+        <v>35</v>
       </c>
       <c r="AX7" t="s">
         <v>208</v>
@@ -4239,10 +4710,19 @@
         <v>211</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL7">
+        <v>2800000</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>221</v>
+      </c>
+      <c r="BN7">
+        <v>55</v>
       </c>
       <c r="BO7" t="s">
         <v>208</v>
@@ -4287,16 +4767,16 @@
         <v>1</v>
       </c>
       <c r="CC7">
-        <v>8000</v>
+        <v>5900</v>
       </c>
       <c r="CD7" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE7">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG7" t="b">
         <v>1</v>
@@ -4338,7 +4818,7 @@
         <v>211</v>
       </c>
       <c r="CT7" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU7">
         <v>0</v>
@@ -4383,7 +4863,7 @@
         <v>211</v>
       </c>
       <c r="DL7" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM7">
         <v>0</v>
@@ -4428,7 +4908,7 @@
         <v>211</v>
       </c>
       <c r="ED7" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE7">
         <v>0</v>
@@ -4437,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="EI7" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ7">
         <v>1</v>
@@ -4446,7 +4926,7 @@
         <v>1</v>
       </c>
       <c r="EL7" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="EM7">
         <v>75000</v>
@@ -4461,10 +4941,10 @@
         <v>100000</v>
       </c>
       <c r="EQ7">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER7">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES7" t="b">
         <v>0</v>
@@ -4473,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="FD7" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE7">
         <v>0.05</v>
@@ -4488,22 +4968,40 @@
         <v>8.5</v>
       </c>
       <c r="FI7" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ7" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK7" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM7">
+        <v>1</v>
+      </c>
+      <c r="FN7">
+        <v>3300</v>
+      </c>
+      <c r="FO7">
+        <v>3300</v>
+      </c>
+      <c r="FP7">
+        <v>0.95</v>
+      </c>
+      <c r="FQ7">
+        <v>0.1</v>
+      </c>
+      <c r="FR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="b">
         <v>0</v>
       </c>
       <c r="FT7" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU7">
         <v>0</v>
@@ -4512,28 +5010,28 @@
         <v>0</v>
       </c>
       <c r="GA7" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB7" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC7" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD7">
         <v>86400</v>
       </c>
       <c r="GE7" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF7" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG7" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH7" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI7">
         <v>86400</v>
@@ -4542,7 +5040,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:192">
+    <row r="8" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -4574,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>2896000</v>
+        <v>3564000</v>
       </c>
       <c r="O8" t="s">
         <v>206</v>
@@ -4661,10 +5159,19 @@
         <v>211</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>5500000</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW8">
+        <v>55</v>
       </c>
       <c r="AX8" t="s">
         <v>208</v>
@@ -4703,10 +5210,19 @@
         <v>211</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL8">
+        <v>2100000</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>222</v>
+      </c>
+      <c r="BN8">
+        <v>55</v>
       </c>
       <c r="BO8" t="s">
         <v>208</v>
@@ -4751,16 +5267,16 @@
         <v>1</v>
       </c>
       <c r="CC8">
-        <v>4900</v>
+        <v>4700</v>
       </c>
       <c r="CD8" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE8">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG8" t="b">
         <v>1</v>
@@ -4802,7 +5318,7 @@
         <v>211</v>
       </c>
       <c r="CT8" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU8">
         <v>0</v>
@@ -4847,7 +5363,7 @@
         <v>211</v>
       </c>
       <c r="DL8" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM8">
         <v>0</v>
@@ -4892,7 +5408,7 @@
         <v>211</v>
       </c>
       <c r="ED8" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE8">
         <v>0</v>
@@ -4901,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="EI8" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ8">
         <v>1</v>
@@ -4910,7 +5426,7 @@
         <v>1</v>
       </c>
       <c r="EL8" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="EM8">
         <v>100000</v>
@@ -4925,10 +5441,10 @@
         <v>200000</v>
       </c>
       <c r="EQ8">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER8">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES8" t="b">
         <v>0</v>
@@ -4937,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="FD8" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE8">
         <v>0.05</v>
@@ -4952,13 +5468,13 @@
         <v>8.5</v>
       </c>
       <c r="FI8" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ8" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK8" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL8">
         <v>1</v>
@@ -4967,10 +5483,10 @@
         <v>1</v>
       </c>
       <c r="FN8">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="FO8">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="FP8">
         <v>0.95</v>
@@ -4985,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="FT8" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU8">
         <v>0</v>
@@ -4994,28 +5510,28 @@
         <v>0</v>
       </c>
       <c r="GA8" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB8" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC8" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD8">
         <v>86400</v>
       </c>
       <c r="GE8" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF8" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG8" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH8" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI8">
         <v>86400</v>
@@ -5024,7 +5540,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:192">
+    <row r="9" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5032,10 +5548,10 @@
         <v>198</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -5044,7 +5560,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -5056,10 +5572,10 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>2455000</v>
+        <v>3296000</v>
       </c>
       <c r="O9" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P9" t="s">
         <v>208</v>
@@ -5143,10 +5659,19 @@
         <v>211</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>19500000</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>216</v>
+      </c>
+      <c r="AW9">
+        <v>35</v>
       </c>
       <c r="AX9" t="s">
         <v>208</v>
@@ -5185,10 +5710,19 @@
         <v>211</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL9">
+        <v>2400000</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>223</v>
+      </c>
+      <c r="BN9">
+        <v>55</v>
       </c>
       <c r="BO9" t="s">
         <v>208</v>
@@ -5233,10 +5767,10 @@
         <v>1</v>
       </c>
       <c r="CC9">
-        <v>3300</v>
+        <v>5200</v>
       </c>
       <c r="CD9" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE9">
         <v>0</v>
@@ -5284,7 +5818,7 @@
         <v>211</v>
       </c>
       <c r="CT9" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU9">
         <v>0</v>
@@ -5329,7 +5863,7 @@
         <v>211</v>
       </c>
       <c r="DL9" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM9">
         <v>0</v>
@@ -5374,7 +5908,7 @@
         <v>211</v>
       </c>
       <c r="ED9" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE9">
         <v>0</v>
@@ -5383,16 +5917,70 @@
         <v>0</v>
       </c>
       <c r="EI9" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK9">
+        <v>2</v>
+      </c>
+      <c r="EL9" t="s">
+        <v>232</v>
+      </c>
+      <c r="EM9">
+        <v>75000</v>
+      </c>
+      <c r="EN9">
+        <v>7200</v>
+      </c>
+      <c r="EO9">
+        <v>11000</v>
+      </c>
+      <c r="EP9">
+        <v>100000</v>
+      </c>
+      <c r="EQ9">
+        <v>0.9</v>
+      </c>
+      <c r="ER9">
+        <v>0.8</v>
+      </c>
+      <c r="ES9" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET9" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="s">
+        <v>230</v>
+      </c>
+      <c r="EV9">
+        <v>75000</v>
+      </c>
+      <c r="EW9">
+        <v>7200</v>
+      </c>
+      <c r="EX9">
+        <v>11000</v>
+      </c>
+      <c r="EY9">
+        <v>100000</v>
+      </c>
+      <c r="EZ9">
+        <v>90000</v>
+      </c>
+      <c r="FA9">
+        <v>80000</v>
+      </c>
+      <c r="FB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC9" t="b">
         <v>0</v>
       </c>
       <c r="FD9" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE9">
         <v>0.05</v>
@@ -5407,13 +5995,13 @@
         <v>8.5</v>
       </c>
       <c r="FI9" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ9" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK9" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL9">
         <v>1</v>
@@ -5422,10 +6010,10 @@
         <v>1</v>
       </c>
       <c r="FN9">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="FO9">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="FP9">
         <v>0.95</v>
@@ -5440,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="FT9" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU9">
         <v>0</v>
@@ -5449,28 +6037,28 @@
         <v>0</v>
       </c>
       <c r="GA9" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB9" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC9" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD9">
         <v>86400</v>
       </c>
       <c r="GE9" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF9" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG9" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH9" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI9">
         <v>86400</v>
@@ -5479,7 +6067,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:192">
+    <row r="10" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -5487,10 +6075,10 @@
         <v>199</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -5499,7 +6087,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -5514,7 +6102,7 @@
         <v>5527000</v>
       </c>
       <c r="O10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P10" t="s">
         <v>208</v>
@@ -5598,10 +6186,19 @@
         <v>211</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <v>5500000</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>217</v>
+      </c>
+      <c r="AW10">
+        <v>35</v>
       </c>
       <c r="AX10" t="s">
         <v>208</v>
@@ -5640,10 +6237,19 @@
         <v>211</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL10">
+        <v>2400000</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>219</v>
+      </c>
+      <c r="BN10">
+        <v>55</v>
       </c>
       <c r="BO10" t="s">
         <v>208</v>
@@ -5682,10 +6288,25 @@
         <v>211</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CC10">
+        <v>7000</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>224</v>
+      </c>
+      <c r="CE10">
+        <v>0</v>
+      </c>
+      <c r="CF10">
+        <v>40</v>
+      </c>
+      <c r="CG10" t="b">
+        <v>1</v>
       </c>
       <c r="CH10" t="s">
         <v>208</v>
@@ -5724,7 +6345,7 @@
         <v>211</v>
       </c>
       <c r="CT10" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU10">
         <v>0</v>
@@ -5769,7 +6390,7 @@
         <v>211</v>
       </c>
       <c r="DL10" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM10">
         <v>0</v>
@@ -5814,7 +6435,7 @@
         <v>211</v>
       </c>
       <c r="ED10" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE10">
         <v>0</v>
@@ -5823,16 +6444,43 @@
         <v>0</v>
       </c>
       <c r="EI10" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK10">
+        <v>1</v>
+      </c>
+      <c r="EL10" t="s">
+        <v>233</v>
+      </c>
+      <c r="EM10">
+        <v>100000</v>
+      </c>
+      <c r="EN10">
+        <v>11000</v>
+      </c>
+      <c r="EO10">
+        <v>22000</v>
+      </c>
+      <c r="EP10">
+        <v>200000</v>
+      </c>
+      <c r="EQ10">
+        <v>0.9</v>
+      </c>
+      <c r="ER10">
+        <v>0.8</v>
+      </c>
+      <c r="ES10" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="b">
         <v>0</v>
       </c>
       <c r="FD10" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE10">
         <v>0.05</v>
@@ -5847,22 +6495,40 @@
         <v>8.5</v>
       </c>
       <c r="FI10" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ10" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK10" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM10">
+        <v>1</v>
+      </c>
+      <c r="FN10">
+        <v>5500</v>
+      </c>
+      <c r="FO10">
+        <v>5500</v>
+      </c>
+      <c r="FP10">
+        <v>0.95</v>
+      </c>
+      <c r="FQ10">
+        <v>0.1</v>
+      </c>
+      <c r="FR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="b">
         <v>0</v>
       </c>
       <c r="FT10" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU10">
         <v>0</v>
@@ -5871,28 +6537,28 @@
         <v>0</v>
       </c>
       <c r="GA10" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB10" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC10" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD10">
         <v>86400</v>
       </c>
       <c r="GE10" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF10" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG10" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH10" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI10">
         <v>86400</v>
@@ -5901,7 +6567,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:192">
+    <row r="11" spans="1:192" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -5909,10 +6575,10 @@
         <v>200</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -5921,7 +6587,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -5933,10 +6599,10 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>3125000</v>
+        <v>2896000</v>
       </c>
       <c r="O11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P11" t="s">
         <v>208</v>
@@ -6020,10 +6686,19 @@
         <v>211</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>19500000</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>218</v>
+      </c>
+      <c r="AW11">
+        <v>55</v>
       </c>
       <c r="AX11" t="s">
         <v>208</v>
@@ -6062,10 +6737,19 @@
         <v>211</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL11">
+        <v>2800000</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>223</v>
+      </c>
+      <c r="BN11">
+        <v>55</v>
       </c>
       <c r="BO11" t="s">
         <v>208</v>
@@ -6110,16 +6794,16 @@
         <v>1</v>
       </c>
       <c r="CC11">
-        <v>4300</v>
+        <v>5000</v>
       </c>
       <c r="CD11" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="CE11">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF11">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG11" t="b">
         <v>1</v>
@@ -6161,7 +6845,7 @@
         <v>211</v>
       </c>
       <c r="CT11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="CU11">
         <v>0</v>
@@ -6206,7 +6890,7 @@
         <v>211</v>
       </c>
       <c r="DL11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="DM11">
         <v>0</v>
@@ -6251,7 +6935,7 @@
         <v>211</v>
       </c>
       <c r="ED11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EE11">
         <v>0</v>
@@ -6260,16 +6944,43 @@
         <v>0</v>
       </c>
       <c r="EI11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="EJ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK11">
+        <v>1</v>
+      </c>
+      <c r="EL11" t="s">
+        <v>231</v>
+      </c>
+      <c r="EM11">
+        <v>75000</v>
+      </c>
+      <c r="EN11">
+        <v>7200</v>
+      </c>
+      <c r="EO11">
+        <v>11000</v>
+      </c>
+      <c r="EP11">
+        <v>100000</v>
+      </c>
+      <c r="EQ11">
+        <v>0.9</v>
+      </c>
+      <c r="ER11">
+        <v>0.8</v>
+      </c>
+      <c r="ES11" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET11" t="b">
         <v>0</v>
       </c>
       <c r="FD11" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="FE11">
         <v>0.05</v>
@@ -6284,13 +6995,13 @@
         <v>8.5</v>
       </c>
       <c r="FI11" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="FJ11" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="FK11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FL11">
         <v>1</v>
@@ -6299,10 +7010,10 @@
         <v>1</v>
       </c>
       <c r="FN11">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="FO11">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="FP11">
         <v>0.95</v>
@@ -6317,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="FT11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="FU11">
         <v>0</v>
@@ -6326,28 +7037,28 @@
         <v>0</v>
       </c>
       <c r="GA11" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="GB11" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GC11" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="GD11">
         <v>86400</v>
       </c>
       <c r="GE11" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="GF11" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="GG11" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GH11" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="GI11">
         <v>86400</v>
@@ -6362,11 +7073,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:GM1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:195">
+    <row r="1" spans="2:195" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6380,13 +7091,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -6956,11 +7667,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:ED1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:134">
+    <row r="1" spans="2:134" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6974,7 +7685,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7286,22 +7997,22 @@
         <v>158</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="DJ1" s="1" t="s">
         <v>163</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="DL1" s="1" t="s">
         <v>165</v>
@@ -7367,11 +8078,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:EM1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:143">
+    <row r="1" spans="2:143" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7385,7 +8096,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7805,11 +8516,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:CB1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:80">
+    <row r="1" spans="2:80" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8054,11 +8765,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:AP1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="2:42">
+    <row r="1" spans="2:42" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8102,58 +8813,58 @@
         <v>174</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>182</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\02 - config\example_single_market\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDFA954-CCD5-47CB-8AFF-7921CCAD63CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="sfh" sheetId="1" r:id="rId1"/>
@@ -20,25 +14,12 @@
     <sheet name="producer" sheetId="5" r:id="rId5"/>
     <sheet name="storage" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="254">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -613,55 +594,58 @@
     <t>ems/fcasts/update_period</t>
   </si>
   <si>
-    <t>uzEoMpDvqUQmolk</t>
-  </si>
-  <si>
-    <t>DGzmAB9lHmVyQZv</t>
-  </si>
-  <si>
-    <t>TYMLJEa1KAhqE59</t>
-  </si>
-  <si>
-    <t>exVNgDckyloeKPg</t>
-  </si>
-  <si>
-    <t>KbSpjvHvz8Y5u7z</t>
-  </si>
-  <si>
-    <t>9ImCBUvCV7wFtHf</t>
-  </si>
-  <si>
-    <t>yHAIaE0rOHnBGoP</t>
-  </si>
-  <si>
-    <t>rNrxz3A1u6iRhO2</t>
-  </si>
-  <si>
-    <t>Ec93eXNNvTukTxN</t>
-  </si>
-  <si>
-    <t>ZzD5Fsx2AOCTX8N</t>
-  </si>
-  <si>
-    <t>hh_2532_0.csv</t>
+    <t>1lIPbXNxrtcHbuq</t>
+  </si>
+  <si>
+    <t>1dMs8E6si6MYUqb</t>
+  </si>
+  <si>
+    <t>rZwqUNsMzDDl8Hy</t>
+  </si>
+  <si>
+    <t>n0w3DxDsc0KicUT</t>
+  </si>
+  <si>
+    <t>f9HuzbnqNCXzIlC</t>
+  </si>
+  <si>
+    <t>QRbLyCB6X1yb4BY</t>
+  </si>
+  <si>
+    <t>DbC1ILMdile5yIl</t>
+  </si>
+  <si>
+    <t>MdfdWyPPzFrkYvW</t>
+  </si>
+  <si>
+    <t>Nj2p967l9Vt9bjg</t>
+  </si>
+  <si>
+    <t>DubKsoLCiW6BzEv</t>
+  </si>
+  <si>
+    <t>hh_3564_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3648_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
   </si>
   <si>
     <t>hh_3125_0.csv</t>
   </si>
   <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4402_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2896_0.csv</t>
+    <t>hh_2687_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2262_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
   </si>
   <si>
     <t>average</t>
@@ -676,42 +660,6 @@
     <t>[1, 0, 0]</t>
   </si>
   <si>
-    <t>heat_2532_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3125_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_3296_0.csv</t>
-  </si>
-  <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2896_0.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
     <t>pv_config.json</t>
   </si>
   <si>
@@ -721,31 +669,16 @@
     <t>local</t>
   </si>
   <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
     <t>ev_freetime_1.csv</t>
   </si>
   <si>
-    <t>ev_parttime_89.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_46.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_47.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_42.csv</t>
+    <t>ev_fulltime_41.csv</t>
   </si>
   <si>
     <t>ev_parttime_90.csv</t>
   </si>
   <si>
-    <t>ev_parttime_88.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_43.csv</t>
+    <t>ev_freetime_0.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -853,8 +786,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -917,21 +850,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -969,7 +894,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1003,7 +928,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1038,10 +962,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1214,204 +1137,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:GJ11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="28.90625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="26.90625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="31.36328125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="24.90625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="9" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="22" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="25" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="26.08984375" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="24" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="14" bestFit="1" customWidth="1"/>
-    <col min="151" max="151" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="24" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="156" max="156" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="14" bestFit="1" customWidth="1"/>
-    <col min="160" max="160" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="40.6328125" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="35.6328125" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="174" max="175" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="178" max="178" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="179" max="179" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="182" max="182" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="183" max="183" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="184" max="184" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="185" max="185" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="187" max="187" width="19" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="189" max="189" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="191" max="191" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="192" max="192" width="23.453125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:192">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1986,7 +1716,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:192">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1994,10 +1724,10 @@
         <v>191</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -2006,7 +1736,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -2018,13 +1748,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>2532000</v>
+        <v>3564000</v>
       </c>
       <c r="O2" t="s">
         <v>201</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2039,25 +1769,25 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W2">
         <v>90</v>
       </c>
       <c r="X2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y2">
         <v>90</v>
       </c>
       <c r="Z2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB2">
         <v>0</v>
@@ -2069,7 +1799,7 @@
         <v>6</v>
       </c>
       <c r="AG2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH2">
         <v>1</v>
@@ -2084,43 +1814,34 @@
         <v>9</v>
       </c>
       <c r="AL2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN2">
+        <v>90</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP2">
+        <v>90</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="s">
         <v>209</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN2">
-        <v>90</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP2">
-        <v>90</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS2">
-        <v>1</v>
-      </c>
-      <c r="AT2">
-        <v>1</v>
-      </c>
-      <c r="AU2">
-        <v>19500000</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>212</v>
-      </c>
-      <c r="AW2">
-        <v>55</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>208</v>
       </c>
       <c r="AY2">
         <v>1</v>
@@ -2135,43 +1856,34 @@
         <v>9</v>
       </c>
       <c r="BC2" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE2">
+        <v>90</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG2">
+        <v>90</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="s">
         <v>209</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE2">
-        <v>90</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG2">
-        <v>90</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ2">
-        <v>1</v>
-      </c>
-      <c r="BK2">
-        <v>1</v>
-      </c>
-      <c r="BL2">
-        <v>2800000</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>219</v>
-      </c>
-      <c r="BN2">
-        <v>55</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>208</v>
       </c>
       <c r="BP2">
         <v>1</v>
@@ -2186,25 +1898,25 @@
         <v>9</v>
       </c>
       <c r="BT2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BU2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BV2">
         <v>90</v>
       </c>
       <c r="BW2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BZ2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CA2">
         <v>1</v>
@@ -2213,10 +1925,10 @@
         <v>1</v>
       </c>
       <c r="CC2">
-        <v>3800</v>
+        <v>5200</v>
       </c>
       <c r="CD2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="CE2">
         <v>0</v>
@@ -2228,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="CH2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="CI2">
         <v>1</v>
@@ -2243,37 +1955,37 @@
         <v>9</v>
       </c>
       <c r="CM2" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO2">
+        <v>90</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ2">
+        <v>90</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU2">
+        <v>0</v>
+      </c>
+      <c r="CV2">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="s">
         <v>209</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO2">
-        <v>90</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ2">
-        <v>90</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU2">
-        <v>0</v>
-      </c>
-      <c r="CV2">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>208</v>
       </c>
       <c r="DA2">
         <v>1</v>
@@ -2288,37 +2000,37 @@
         <v>9</v>
       </c>
       <c r="DE2" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG2">
+        <v>90</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI2">
+        <v>90</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM2">
+        <v>0</v>
+      </c>
+      <c r="DN2">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="s">
         <v>209</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG2">
-        <v>90</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI2">
-        <v>90</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM2">
-        <v>0</v>
-      </c>
-      <c r="DN2">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>208</v>
       </c>
       <c r="DS2">
         <v>1</v>
@@ -2333,28 +2045,28 @@
         <v>9</v>
       </c>
       <c r="DW2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY2">
         <v>90</v>
       </c>
       <c r="DZ2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA2">
         <v>90</v>
       </c>
       <c r="EB2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE2">
         <v>0</v>
@@ -2363,43 +2075,16 @@
         <v>0</v>
       </c>
       <c r="EI2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK2">
-        <v>1</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>227</v>
-      </c>
-      <c r="EM2">
-        <v>50000</v>
-      </c>
-      <c r="EN2">
-        <v>7200</v>
-      </c>
-      <c r="EO2">
-        <v>7200</v>
-      </c>
-      <c r="EP2">
-        <v>50000</v>
-      </c>
-      <c r="EQ2">
-        <v>0.9</v>
-      </c>
-      <c r="ER2">
-        <v>0.8</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="b">
         <v>0</v>
       </c>
       <c r="FD2" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE2">
         <v>0.05</v>
@@ -2414,13 +2099,13 @@
         <v>8.5</v>
       </c>
       <c r="FI2" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ2" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL2">
         <v>1</v>
@@ -2429,10 +2114,10 @@
         <v>1</v>
       </c>
       <c r="FN2">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="FO2">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="FP2">
         <v>0.95</v>
@@ -2447,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="FT2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU2">
         <v>0</v>
@@ -2456,28 +2141,28 @@
         <v>0</v>
       </c>
       <c r="GA2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB2" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC2" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD2">
         <v>86400</v>
       </c>
       <c r="GE2" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF2" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH2" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI2">
         <v>86400</v>
@@ -2486,7 +2171,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:192">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -2494,10 +2179,10 @@
         <v>192</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2506,7 +2191,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2518,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>3125000</v>
+        <v>5527000</v>
       </c>
       <c r="O3" t="s">
         <v>202</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2539,25 +2224,25 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W3">
         <v>90</v>
       </c>
       <c r="X3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y3">
         <v>90</v>
       </c>
       <c r="Z3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -2569,7 +2254,7 @@
         <v>6</v>
       </c>
       <c r="AG3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH3">
         <v>1</v>
@@ -2584,43 +2269,34 @@
         <v>9</v>
       </c>
       <c r="AL3" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN3">
+        <v>90</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP3">
+        <v>90</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="s">
         <v>209</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN3">
-        <v>90</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP3">
-        <v>90</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS3">
-        <v>1</v>
-      </c>
-      <c r="AT3">
-        <v>1</v>
-      </c>
-      <c r="AU3">
-        <v>19500000</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>213</v>
-      </c>
-      <c r="AW3">
-        <v>55</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>208</v>
       </c>
       <c r="AY3">
         <v>1</v>
@@ -2635,43 +2311,34 @@
         <v>9</v>
       </c>
       <c r="BC3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE3">
+        <v>90</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG3">
+        <v>90</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="s">
         <v>209</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE3">
-        <v>90</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG3">
-        <v>90</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ3">
-        <v>1</v>
-      </c>
-      <c r="BK3">
-        <v>1</v>
-      </c>
-      <c r="BL3">
-        <v>2400000</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>220</v>
-      </c>
-      <c r="BN3">
-        <v>55</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>208</v>
       </c>
       <c r="BP3">
         <v>1</v>
@@ -2686,49 +2353,34 @@
         <v>9</v>
       </c>
       <c r="BT3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BV3">
+        <v>90</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BX3">
+        <v>90</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>211</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>212</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="s">
         <v>209</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BV3">
-        <v>90</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BX3">
-        <v>90</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>211</v>
-      </c>
-      <c r="CA3">
-        <v>1</v>
-      </c>
-      <c r="CB3">
-        <v>1</v>
-      </c>
-      <c r="CC3">
-        <v>5400</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>224</v>
-      </c>
-      <c r="CE3">
-        <v>0</v>
-      </c>
-      <c r="CF3">
-        <v>40</v>
-      </c>
-      <c r="CG3" t="b">
-        <v>1</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>208</v>
       </c>
       <c r="CI3">
         <v>1</v>
@@ -2743,37 +2395,37 @@
         <v>9</v>
       </c>
       <c r="CM3" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO3">
+        <v>90</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ3">
+        <v>90</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS3" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU3">
+        <v>0</v>
+      </c>
+      <c r="CV3">
+        <v>0</v>
+      </c>
+      <c r="CZ3" t="s">
         <v>209</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO3">
-        <v>90</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ3">
-        <v>90</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS3" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU3">
-        <v>0</v>
-      </c>
-      <c r="CV3">
-        <v>0</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>208</v>
       </c>
       <c r="DA3">
         <v>1</v>
@@ -2788,37 +2440,37 @@
         <v>9</v>
       </c>
       <c r="DE3" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF3" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG3">
+        <v>90</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI3">
+        <v>90</v>
+      </c>
+      <c r="DJ3" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM3">
+        <v>0</v>
+      </c>
+      <c r="DN3">
+        <v>0</v>
+      </c>
+      <c r="DR3" t="s">
         <v>209</v>
-      </c>
-      <c r="DF3" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG3">
-        <v>90</v>
-      </c>
-      <c r="DH3" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI3">
-        <v>90</v>
-      </c>
-      <c r="DJ3" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK3" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL3" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM3">
-        <v>0</v>
-      </c>
-      <c r="DN3">
-        <v>0</v>
-      </c>
-      <c r="DR3" t="s">
-        <v>208</v>
       </c>
       <c r="DS3">
         <v>1</v>
@@ -2833,28 +2485,28 @@
         <v>9</v>
       </c>
       <c r="DW3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY3">
         <v>90</v>
       </c>
       <c r="DZ3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA3">
         <v>90</v>
       </c>
       <c r="EB3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE3">
         <v>0</v>
@@ -2863,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="EI3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ3">
         <v>1</v>
@@ -2872,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="EL3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="EM3">
         <v>50000</v>
@@ -2887,10 +2539,10 @@
         <v>50000</v>
       </c>
       <c r="EQ3">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="ER3">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="ES3" t="b">
         <v>0</v>
@@ -2899,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="FD3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE3">
         <v>0.05</v>
@@ -2914,40 +2566,22 @@
         <v>8.5</v>
       </c>
       <c r="FI3" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ3" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FM3">
-        <v>1</v>
-      </c>
-      <c r="FN3">
-        <v>3100</v>
-      </c>
-      <c r="FO3">
-        <v>3100</v>
-      </c>
-      <c r="FP3">
-        <v>0.95</v>
-      </c>
-      <c r="FQ3">
-        <v>0.1</v>
-      </c>
-      <c r="FR3" t="b">
-        <v>0</v>
-      </c>
-      <c r="FS3" t="b">
         <v>0</v>
       </c>
       <c r="FT3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU3">
         <v>0</v>
@@ -2956,28 +2590,28 @@
         <v>0</v>
       </c>
       <c r="GA3" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB3" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC3" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD3">
         <v>86400</v>
       </c>
       <c r="GE3" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF3" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI3">
         <v>86400</v>
@@ -2986,7 +2620,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:192">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3018,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>5527000</v>
+        <v>3648000</v>
       </c>
       <c r="O4" t="s">
         <v>203</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3039,25 +2673,25 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W4">
         <v>90</v>
       </c>
       <c r="X4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y4">
         <v>90</v>
       </c>
       <c r="Z4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -3069,7 +2703,7 @@
         <v>6</v>
       </c>
       <c r="AG4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH4">
         <v>1</v>
@@ -3084,43 +2718,34 @@
         <v>9</v>
       </c>
       <c r="AL4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN4">
+        <v>90</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP4">
+        <v>90</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="s">
         <v>209</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN4">
-        <v>90</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP4">
-        <v>90</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS4">
-        <v>1</v>
-      </c>
-      <c r="AT4">
-        <v>1</v>
-      </c>
-      <c r="AU4">
-        <v>5500000</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW4">
-        <v>55</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>208</v>
       </c>
       <c r="AY4">
         <v>1</v>
@@ -3135,43 +2760,34 @@
         <v>9</v>
       </c>
       <c r="BC4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE4">
+        <v>90</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG4">
+        <v>90</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="s">
         <v>209</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE4">
-        <v>90</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG4">
-        <v>90</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ4">
-        <v>1</v>
-      </c>
-      <c r="BK4">
-        <v>1</v>
-      </c>
-      <c r="BL4">
-        <v>2400000</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>219</v>
-      </c>
-      <c r="BN4">
-        <v>55</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>208</v>
       </c>
       <c r="BP4">
         <v>1</v>
@@ -3186,49 +2802,49 @@
         <v>9</v>
       </c>
       <c r="BT4" t="s">
+        <v>210</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BV4">
+        <v>90</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BX4">
+        <v>90</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>211</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>212</v>
+      </c>
+      <c r="CA4">
+        <v>1</v>
+      </c>
+      <c r="CB4">
+        <v>1</v>
+      </c>
+      <c r="CC4">
+        <v>5200</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>213</v>
+      </c>
+      <c r="CE4">
+        <v>-20</v>
+      </c>
+      <c r="CF4">
+        <v>50</v>
+      </c>
+      <c r="CG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH4" t="s">
         <v>209</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BV4">
-        <v>90</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BX4">
-        <v>90</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>210</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>211</v>
-      </c>
-      <c r="CA4">
-        <v>1</v>
-      </c>
-      <c r="CB4">
-        <v>1</v>
-      </c>
-      <c r="CC4">
-        <v>7900</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>224</v>
-      </c>
-      <c r="CE4">
-        <v>0</v>
-      </c>
-      <c r="CF4">
-        <v>40</v>
-      </c>
-      <c r="CG4" t="b">
-        <v>1</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>208</v>
       </c>
       <c r="CI4">
         <v>1</v>
@@ -3243,37 +2859,37 @@
         <v>9</v>
       </c>
       <c r="CM4" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO4">
+        <v>90</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ4">
+        <v>90</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU4">
+        <v>0</v>
+      </c>
+      <c r="CV4">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="s">
         <v>209</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO4">
-        <v>90</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ4">
-        <v>90</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU4">
-        <v>0</v>
-      </c>
-      <c r="CV4">
-        <v>0</v>
-      </c>
-      <c r="CZ4" t="s">
-        <v>208</v>
       </c>
       <c r="DA4">
         <v>1</v>
@@ -3288,37 +2904,37 @@
         <v>9</v>
       </c>
       <c r="DE4" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG4">
+        <v>90</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI4">
+        <v>90</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK4" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM4">
+        <v>0</v>
+      </c>
+      <c r="DN4">
+        <v>0</v>
+      </c>
+      <c r="DR4" t="s">
         <v>209</v>
-      </c>
-      <c r="DF4" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG4">
-        <v>90</v>
-      </c>
-      <c r="DH4" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI4">
-        <v>90</v>
-      </c>
-      <c r="DJ4" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK4" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL4" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM4">
-        <v>0</v>
-      </c>
-      <c r="DN4">
-        <v>0</v>
-      </c>
-      <c r="DR4" t="s">
-        <v>208</v>
       </c>
       <c r="DS4">
         <v>1</v>
@@ -3333,28 +2949,28 @@
         <v>9</v>
       </c>
       <c r="DW4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY4">
         <v>90</v>
       </c>
       <c r="DZ4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA4">
         <v>90</v>
       </c>
       <c r="EB4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE4">
         <v>0</v>
@@ -3363,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="EI4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ4">
         <v>1</v>
       </c>
       <c r="EK4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EL4" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="EM4">
         <v>75000</v>
@@ -3387,10 +3003,10 @@
         <v>100000</v>
       </c>
       <c r="EQ4">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="ER4">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="ES4" t="b">
         <v>0</v>
@@ -3398,35 +3014,8 @@
       <c r="ET4" t="b">
         <v>0</v>
       </c>
-      <c r="EU4" t="s">
-        <v>234</v>
-      </c>
-      <c r="EV4">
-        <v>100000</v>
-      </c>
-      <c r="EW4">
-        <v>11000</v>
-      </c>
-      <c r="EX4">
-        <v>22000</v>
-      </c>
-      <c r="EY4">
-        <v>200000</v>
-      </c>
-      <c r="EZ4">
-        <v>90000</v>
-      </c>
-      <c r="FA4">
-        <v>80000</v>
-      </c>
-      <c r="FB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC4" t="b">
-        <v>0</v>
-      </c>
       <c r="FD4" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE4">
         <v>0.05</v>
@@ -3441,40 +3030,22 @@
         <v>8.5</v>
       </c>
       <c r="FI4" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ4" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FM4">
-        <v>1</v>
-      </c>
-      <c r="FN4">
-        <v>5500</v>
-      </c>
-      <c r="FO4">
-        <v>5500</v>
-      </c>
-      <c r="FP4">
-        <v>0.95</v>
-      </c>
-      <c r="FQ4">
-        <v>0.1</v>
-      </c>
-      <c r="FR4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FS4" t="b">
         <v>0</v>
       </c>
       <c r="FT4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU4">
         <v>0</v>
@@ -3483,28 +3054,28 @@
         <v>0</v>
       </c>
       <c r="GA4" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB4" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC4" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD4">
         <v>86400</v>
       </c>
       <c r="GE4" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF4" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG4" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH4" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI4">
         <v>86400</v>
@@ -3513,7 +3084,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:192">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -3521,10 +3092,10 @@
         <v>194</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3533,7 +3104,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3545,13 +3116,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>4402000</v>
+        <v>3296000</v>
       </c>
       <c r="O5" t="s">
         <v>204</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -3566,25 +3137,25 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W5">
         <v>90</v>
       </c>
       <c r="X5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y5">
         <v>90</v>
       </c>
       <c r="Z5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -3596,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="AG5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -3611,43 +3182,34 @@
         <v>9</v>
       </c>
       <c r="AL5" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN5">
+        <v>90</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP5">
+        <v>90</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="s">
         <v>209</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN5">
-        <v>90</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP5">
-        <v>90</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS5">
-        <v>1</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AU5">
-        <v>5500000</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AW5">
-        <v>55</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>208</v>
       </c>
       <c r="AY5">
         <v>1</v>
@@ -3662,43 +3224,34 @@
         <v>9</v>
       </c>
       <c r="BC5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE5">
+        <v>90</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG5">
+        <v>90</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="s">
         <v>209</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE5">
-        <v>90</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG5">
-        <v>90</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ5">
-        <v>1</v>
-      </c>
-      <c r="BK5">
-        <v>1</v>
-      </c>
-      <c r="BL5">
-        <v>2400000</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>221</v>
-      </c>
-      <c r="BN5">
-        <v>55</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>208</v>
       </c>
       <c r="BP5">
         <v>1</v>
@@ -3713,49 +3266,49 @@
         <v>9</v>
       </c>
       <c r="BT5" t="s">
+        <v>210</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>211</v>
+      </c>
+      <c r="BV5">
+        <v>90</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>211</v>
+      </c>
+      <c r="BX5">
+        <v>90</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>211</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>212</v>
+      </c>
+      <c r="CA5">
+        <v>1</v>
+      </c>
+      <c r="CB5">
+        <v>1</v>
+      </c>
+      <c r="CC5">
+        <v>5800</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>213</v>
+      </c>
+      <c r="CE5">
+        <v>0</v>
+      </c>
+      <c r="CF5">
+        <v>40</v>
+      </c>
+      <c r="CG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH5" t="s">
         <v>209</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>210</v>
-      </c>
-      <c r="BV5">
-        <v>90</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>210</v>
-      </c>
-      <c r="BX5">
-        <v>90</v>
-      </c>
-      <c r="BY5" t="s">
-        <v>210</v>
-      </c>
-      <c r="BZ5" t="s">
-        <v>211</v>
-      </c>
-      <c r="CA5">
-        <v>1</v>
-      </c>
-      <c r="CB5">
-        <v>1</v>
-      </c>
-      <c r="CC5">
-        <v>6900</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>224</v>
-      </c>
-      <c r="CE5">
-        <v>-20</v>
-      </c>
-      <c r="CF5">
-        <v>50</v>
-      </c>
-      <c r="CG5" t="b">
-        <v>1</v>
-      </c>
-      <c r="CH5" t="s">
-        <v>208</v>
       </c>
       <c r="CI5">
         <v>1</v>
@@ -3770,37 +3323,37 @@
         <v>9</v>
       </c>
       <c r="CM5" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO5">
+        <v>90</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ5">
+        <v>90</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU5">
+        <v>0</v>
+      </c>
+      <c r="CV5">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="s">
         <v>209</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO5">
-        <v>90</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ5">
-        <v>90</v>
-      </c>
-      <c r="CR5" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS5" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT5" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU5">
-        <v>0</v>
-      </c>
-      <c r="CV5">
-        <v>0</v>
-      </c>
-      <c r="CZ5" t="s">
-        <v>208</v>
       </c>
       <c r="DA5">
         <v>1</v>
@@ -3815,37 +3368,37 @@
         <v>9</v>
       </c>
       <c r="DE5" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF5" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG5">
+        <v>90</v>
+      </c>
+      <c r="DH5" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI5">
+        <v>90</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM5">
+        <v>0</v>
+      </c>
+      <c r="DN5">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="s">
         <v>209</v>
-      </c>
-      <c r="DF5" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG5">
-        <v>90</v>
-      </c>
-      <c r="DH5" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI5">
-        <v>90</v>
-      </c>
-      <c r="DJ5" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK5" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL5" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM5">
-        <v>0</v>
-      </c>
-      <c r="DN5">
-        <v>0</v>
-      </c>
-      <c r="DR5" t="s">
-        <v>208</v>
       </c>
       <c r="DS5">
         <v>1</v>
@@ -3860,28 +3413,28 @@
         <v>9</v>
       </c>
       <c r="DW5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY5">
         <v>90</v>
       </c>
       <c r="DZ5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA5">
         <v>90</v>
       </c>
       <c r="EB5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED5" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE5">
         <v>0</v>
@@ -3890,70 +3443,16 @@
         <v>0</v>
       </c>
       <c r="EI5" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK5">
-        <v>2</v>
-      </c>
-      <c r="EL5" t="s">
-        <v>229</v>
-      </c>
-      <c r="EM5">
-        <v>50000</v>
-      </c>
-      <c r="EN5">
-        <v>7200</v>
-      </c>
-      <c r="EO5">
-        <v>7200</v>
-      </c>
-      <c r="EP5">
-        <v>50000</v>
-      </c>
-      <c r="EQ5">
-        <v>0.9</v>
-      </c>
-      <c r="ER5">
-        <v>0.8</v>
-      </c>
-      <c r="ES5" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET5" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU5" t="s">
-        <v>235</v>
-      </c>
-      <c r="EV5">
-        <v>50000</v>
-      </c>
-      <c r="EW5">
-        <v>7200</v>
-      </c>
-      <c r="EX5">
-        <v>7200</v>
-      </c>
-      <c r="EY5">
-        <v>50000</v>
-      </c>
-      <c r="EZ5">
-        <v>90000</v>
-      </c>
-      <c r="FA5">
-        <v>80000</v>
-      </c>
-      <c r="FB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC5" t="b">
         <v>0</v>
       </c>
       <c r="FD5" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE5">
         <v>0.05</v>
@@ -3968,13 +3467,13 @@
         <v>8.5</v>
       </c>
       <c r="FI5" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ5" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK5" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL5">
         <v>1</v>
@@ -3983,10 +3482,10 @@
         <v>1</v>
       </c>
       <c r="FN5">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="FO5">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="FP5">
         <v>0.95</v>
@@ -4001,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="FT5" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU5">
         <v>0</v>
@@ -4010,28 +3509,28 @@
         <v>0</v>
       </c>
       <c r="GA5" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB5" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC5" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD5">
         <v>86400</v>
       </c>
       <c r="GE5" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF5" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG5" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH5" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI5">
         <v>86400</v>
@@ -4040,7 +3539,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:192">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4048,10 +3547,10 @@
         <v>195</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -4060,7 +3559,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4072,13 +3571,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>3296000</v>
+        <v>5527000</v>
       </c>
       <c r="O6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4093,25 +3592,25 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W6">
         <v>90</v>
       </c>
       <c r="X6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y6">
         <v>90</v>
       </c>
       <c r="Z6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -4123,7 +3622,7 @@
         <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH6">
         <v>1</v>
@@ -4138,43 +3637,34 @@
         <v>9</v>
       </c>
       <c r="AL6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN6">
+        <v>90</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP6">
+        <v>90</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="s">
         <v>209</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN6">
-        <v>90</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP6">
-        <v>90</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS6">
-        <v>1</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>5500000</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>216</v>
-      </c>
-      <c r="AW6">
-        <v>55</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>208</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -4189,43 +3679,34 @@
         <v>9</v>
       </c>
       <c r="BC6" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE6">
+        <v>90</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG6">
+        <v>90</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="s">
         <v>209</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE6">
-        <v>90</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG6">
-        <v>90</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ6">
-        <v>1</v>
-      </c>
-      <c r="BK6">
-        <v>1</v>
-      </c>
-      <c r="BL6">
-        <v>1800000</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>219</v>
-      </c>
-      <c r="BN6">
-        <v>55</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>208</v>
       </c>
       <c r="BP6">
         <v>1</v>
@@ -4240,25 +3721,25 @@
         <v>9</v>
       </c>
       <c r="BT6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BU6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BV6">
         <v>90</v>
       </c>
       <c r="BW6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BX6">
         <v>90</v>
       </c>
       <c r="BY6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BZ6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CA6">
         <v>1</v>
@@ -4267,10 +3748,10 @@
         <v>1</v>
       </c>
       <c r="CC6">
-        <v>4000</v>
+        <v>7800</v>
       </c>
       <c r="CD6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="CE6">
         <v>0</v>
@@ -4282,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="CH6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="CI6">
         <v>1</v>
@@ -4297,37 +3778,37 @@
         <v>9</v>
       </c>
       <c r="CM6" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO6">
+        <v>90</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ6">
+        <v>90</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU6">
+        <v>0</v>
+      </c>
+      <c r="CV6">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="s">
         <v>209</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO6">
-        <v>90</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ6">
-        <v>90</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU6">
-        <v>0</v>
-      </c>
-      <c r="CV6">
-        <v>0</v>
-      </c>
-      <c r="CZ6" t="s">
-        <v>208</v>
       </c>
       <c r="DA6">
         <v>1</v>
@@ -4342,37 +3823,37 @@
         <v>9</v>
       </c>
       <c r="DE6" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF6" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG6">
+        <v>90</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI6">
+        <v>90</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM6">
+        <v>0</v>
+      </c>
+      <c r="DN6">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="s">
         <v>209</v>
-      </c>
-      <c r="DF6" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG6">
-        <v>90</v>
-      </c>
-      <c r="DH6" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI6">
-        <v>90</v>
-      </c>
-      <c r="DJ6" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK6" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL6" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM6">
-        <v>0</v>
-      </c>
-      <c r="DN6">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="s">
-        <v>208</v>
       </c>
       <c r="DS6">
         <v>1</v>
@@ -4387,28 +3868,28 @@
         <v>9</v>
       </c>
       <c r="DW6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY6">
         <v>90</v>
       </c>
       <c r="DZ6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA6">
         <v>90</v>
       </c>
       <c r="EB6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE6">
         <v>0</v>
@@ -4417,43 +3898,16 @@
         <v>0</v>
       </c>
       <c r="EI6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK6">
-        <v>1</v>
-      </c>
-      <c r="EL6" t="s">
-        <v>230</v>
-      </c>
-      <c r="EM6">
-        <v>50000</v>
-      </c>
-      <c r="EN6">
-        <v>7200</v>
-      </c>
-      <c r="EO6">
-        <v>7200</v>
-      </c>
-      <c r="EP6">
-        <v>50000</v>
-      </c>
-      <c r="EQ6">
-        <v>0.9</v>
-      </c>
-      <c r="ER6">
-        <v>0.8</v>
-      </c>
-      <c r="ES6" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET6" t="b">
         <v>0</v>
       </c>
       <c r="FD6" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE6">
         <v>0.05</v>
@@ -4468,13 +3922,13 @@
         <v>8.5</v>
       </c>
       <c r="FI6" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ6" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL6">
         <v>1</v>
@@ -4483,10 +3937,10 @@
         <v>1</v>
       </c>
       <c r="FN6">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="FO6">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="FP6">
         <v>0.95</v>
@@ -4501,7 +3955,7 @@
         <v>0</v>
       </c>
       <c r="FT6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU6">
         <v>0</v>
@@ -4510,28 +3964,28 @@
         <v>0</v>
       </c>
       <c r="GA6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB6" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC6" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD6">
         <v>86400</v>
       </c>
       <c r="GE6" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF6" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG6" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH6" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI6">
         <v>86400</v>
@@ -4540,7 +3994,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:192">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -4548,10 +4002,10 @@
         <v>196</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -4560,7 +4014,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4572,13 +4026,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3296000</v>
+        <v>3648000</v>
       </c>
       <c r="O7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -4593,25 +4047,25 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W7">
         <v>90</v>
       </c>
       <c r="X7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y7">
         <v>90</v>
       </c>
       <c r="Z7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB7">
         <v>0</v>
@@ -4623,7 +4077,7 @@
         <v>6</v>
       </c>
       <c r="AG7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH7">
         <v>1</v>
@@ -4638,43 +4092,34 @@
         <v>9</v>
       </c>
       <c r="AL7" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN7">
+        <v>90</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP7">
+        <v>90</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="s">
         <v>209</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN7">
-        <v>90</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP7">
-        <v>90</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS7">
-        <v>1</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>19500000</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>216</v>
-      </c>
-      <c r="AW7">
-        <v>35</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>208</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -4689,43 +4134,34 @@
         <v>9</v>
       </c>
       <c r="BC7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE7">
+        <v>90</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG7">
+        <v>90</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="s">
         <v>209</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE7">
-        <v>90</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG7">
-        <v>90</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ7">
-        <v>1</v>
-      </c>
-      <c r="BK7">
-        <v>1</v>
-      </c>
-      <c r="BL7">
-        <v>2800000</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>221</v>
-      </c>
-      <c r="BN7">
-        <v>55</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>208</v>
       </c>
       <c r="BP7">
         <v>1</v>
@@ -4740,49 +4176,49 @@
         <v>9</v>
       </c>
       <c r="BT7" t="s">
+        <v>210</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BV7">
+        <v>90</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BX7">
+        <v>90</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>212</v>
+      </c>
+      <c r="CA7">
+        <v>1</v>
+      </c>
+      <c r="CB7">
+        <v>1</v>
+      </c>
+      <c r="CC7">
+        <v>5000</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>213</v>
+      </c>
+      <c r="CE7">
+        <v>0</v>
+      </c>
+      <c r="CF7">
+        <v>40</v>
+      </c>
+      <c r="CG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH7" t="s">
         <v>209</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>210</v>
-      </c>
-      <c r="BV7">
-        <v>90</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>210</v>
-      </c>
-      <c r="BX7">
-        <v>90</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>210</v>
-      </c>
-      <c r="BZ7" t="s">
-        <v>211</v>
-      </c>
-      <c r="CA7">
-        <v>1</v>
-      </c>
-      <c r="CB7">
-        <v>1</v>
-      </c>
-      <c r="CC7">
-        <v>5900</v>
-      </c>
-      <c r="CD7" t="s">
-        <v>224</v>
-      </c>
-      <c r="CE7">
-        <v>-20</v>
-      </c>
-      <c r="CF7">
-        <v>50</v>
-      </c>
-      <c r="CG7" t="b">
-        <v>1</v>
-      </c>
-      <c r="CH7" t="s">
-        <v>208</v>
       </c>
       <c r="CI7">
         <v>1</v>
@@ -4797,37 +4233,37 @@
         <v>9</v>
       </c>
       <c r="CM7" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO7">
+        <v>90</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ7">
+        <v>90</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU7">
+        <v>0</v>
+      </c>
+      <c r="CV7">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="s">
         <v>209</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO7">
-        <v>90</v>
-      </c>
-      <c r="CP7" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ7">
-        <v>90</v>
-      </c>
-      <c r="CR7" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS7" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT7" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU7">
-        <v>0</v>
-      </c>
-      <c r="CV7">
-        <v>0</v>
-      </c>
-      <c r="CZ7" t="s">
-        <v>208</v>
       </c>
       <c r="DA7">
         <v>1</v>
@@ -4842,37 +4278,37 @@
         <v>9</v>
       </c>
       <c r="DE7" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF7" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG7">
+        <v>90</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI7">
+        <v>90</v>
+      </c>
+      <c r="DJ7" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK7" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL7" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM7">
+        <v>0</v>
+      </c>
+      <c r="DN7">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="s">
         <v>209</v>
-      </c>
-      <c r="DF7" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG7">
-        <v>90</v>
-      </c>
-      <c r="DH7" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI7">
-        <v>90</v>
-      </c>
-      <c r="DJ7" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK7" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL7" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM7">
-        <v>0</v>
-      </c>
-      <c r="DN7">
-        <v>0</v>
-      </c>
-      <c r="DR7" t="s">
-        <v>208</v>
       </c>
       <c r="DS7">
         <v>1</v>
@@ -4887,28 +4323,28 @@
         <v>9</v>
       </c>
       <c r="DW7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY7">
         <v>90</v>
       </c>
       <c r="DZ7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA7">
         <v>90</v>
       </c>
       <c r="EB7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE7">
         <v>0</v>
@@ -4917,43 +4353,16 @@
         <v>0</v>
       </c>
       <c r="EI7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK7">
-        <v>1</v>
-      </c>
-      <c r="EL7" t="s">
-        <v>228</v>
-      </c>
-      <c r="EM7">
-        <v>75000</v>
-      </c>
-      <c r="EN7">
-        <v>7200</v>
-      </c>
-      <c r="EO7">
-        <v>11000</v>
-      </c>
-      <c r="EP7">
-        <v>100000</v>
-      </c>
-      <c r="EQ7">
-        <v>0.9</v>
-      </c>
-      <c r="ER7">
-        <v>0.8</v>
-      </c>
-      <c r="ES7" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET7" t="b">
         <v>0</v>
       </c>
       <c r="FD7" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE7">
         <v>0.05</v>
@@ -4968,40 +4377,22 @@
         <v>8.5</v>
       </c>
       <c r="FI7" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ7" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FM7">
-        <v>1</v>
-      </c>
-      <c r="FN7">
-        <v>3300</v>
-      </c>
-      <c r="FO7">
-        <v>3300</v>
-      </c>
-      <c r="FP7">
-        <v>0.95</v>
-      </c>
-      <c r="FQ7">
-        <v>0.1</v>
-      </c>
-      <c r="FR7" t="b">
-        <v>0</v>
-      </c>
-      <c r="FS7" t="b">
         <v>0</v>
       </c>
       <c r="FT7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU7">
         <v>0</v>
@@ -5010,28 +4401,28 @@
         <v>0</v>
       </c>
       <c r="GA7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB7" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC7" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD7">
         <v>86400</v>
       </c>
       <c r="GE7" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF7" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG7" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH7" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI7">
         <v>86400</v>
@@ -5040,7 +4431,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:192">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -5072,13 +4463,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3564000</v>
+        <v>3125000</v>
       </c>
       <c r="O8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -5093,25 +4484,25 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W8">
         <v>90</v>
       </c>
       <c r="X8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y8">
         <v>90</v>
       </c>
       <c r="Z8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -5123,7 +4514,7 @@
         <v>6</v>
       </c>
       <c r="AG8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH8">
         <v>1</v>
@@ -5138,43 +4529,34 @@
         <v>9</v>
       </c>
       <c r="AL8" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN8">
+        <v>90</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP8">
+        <v>90</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="s">
         <v>209</v>
-      </c>
-      <c r="AM8" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN8">
-        <v>90</v>
-      </c>
-      <c r="AO8" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP8">
-        <v>90</v>
-      </c>
-      <c r="AQ8" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR8" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS8">
-        <v>1</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>5500000</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW8">
-        <v>55</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>208</v>
       </c>
       <c r="AY8">
         <v>1</v>
@@ -5189,43 +4571,34 @@
         <v>9</v>
       </c>
       <c r="BC8" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE8">
+        <v>90</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG8">
+        <v>90</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="s">
         <v>209</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE8">
-        <v>90</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG8">
-        <v>90</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI8" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ8">
-        <v>1</v>
-      </c>
-      <c r="BK8">
-        <v>1</v>
-      </c>
-      <c r="BL8">
-        <v>2100000</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>222</v>
-      </c>
-      <c r="BN8">
-        <v>55</v>
-      </c>
-      <c r="BO8" t="s">
-        <v>208</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -5240,25 +4613,25 @@
         <v>9</v>
       </c>
       <c r="BT8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BU8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BV8">
         <v>90</v>
       </c>
       <c r="BW8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BX8">
         <v>90</v>
       </c>
       <c r="BY8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BZ8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CA8">
         <v>1</v>
@@ -5267,10 +4640,10 @@
         <v>1</v>
       </c>
       <c r="CC8">
-        <v>4700</v>
+        <v>5400</v>
       </c>
       <c r="CD8" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="CE8">
         <v>-20</v>
@@ -5282,7 +4655,7 @@
         <v>1</v>
       </c>
       <c r="CH8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="CI8">
         <v>1</v>
@@ -5297,37 +4670,37 @@
         <v>9</v>
       </c>
       <c r="CM8" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN8" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO8">
+        <v>90</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ8">
+        <v>90</v>
+      </c>
+      <c r="CR8" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS8" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT8" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU8">
+        <v>0</v>
+      </c>
+      <c r="CV8">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="s">
         <v>209</v>
-      </c>
-      <c r="CN8" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO8">
-        <v>90</v>
-      </c>
-      <c r="CP8" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ8">
-        <v>90</v>
-      </c>
-      <c r="CR8" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS8" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT8" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU8">
-        <v>0</v>
-      </c>
-      <c r="CV8">
-        <v>0</v>
-      </c>
-      <c r="CZ8" t="s">
-        <v>208</v>
       </c>
       <c r="DA8">
         <v>1</v>
@@ -5342,37 +4715,37 @@
         <v>9</v>
       </c>
       <c r="DE8" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF8" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG8">
+        <v>90</v>
+      </c>
+      <c r="DH8" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI8">
+        <v>90</v>
+      </c>
+      <c r="DJ8" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK8" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL8" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM8">
+        <v>0</v>
+      </c>
+      <c r="DN8">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="s">
         <v>209</v>
-      </c>
-      <c r="DF8" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG8">
-        <v>90</v>
-      </c>
-      <c r="DH8" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI8">
-        <v>90</v>
-      </c>
-      <c r="DJ8" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK8" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL8" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM8">
-        <v>0</v>
-      </c>
-      <c r="DN8">
-        <v>0</v>
-      </c>
-      <c r="DR8" t="s">
-        <v>208</v>
       </c>
       <c r="DS8">
         <v>1</v>
@@ -5387,28 +4760,28 @@
         <v>9</v>
       </c>
       <c r="DW8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY8">
         <v>90</v>
       </c>
       <c r="DZ8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA8">
         <v>90</v>
       </c>
       <c r="EB8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED8" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE8">
         <v>0</v>
@@ -5417,43 +4790,16 @@
         <v>0</v>
       </c>
       <c r="EI8" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK8">
-        <v>1</v>
-      </c>
-      <c r="EL8" t="s">
-        <v>231</v>
-      </c>
-      <c r="EM8">
-        <v>100000</v>
-      </c>
-      <c r="EN8">
-        <v>11000</v>
-      </c>
-      <c r="EO8">
-        <v>22000</v>
-      </c>
-      <c r="EP8">
-        <v>200000</v>
-      </c>
-      <c r="EQ8">
-        <v>0.9</v>
-      </c>
-      <c r="ER8">
-        <v>0.8</v>
-      </c>
-      <c r="ES8" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET8" t="b">
         <v>0</v>
       </c>
       <c r="FD8" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE8">
         <v>0.05</v>
@@ -5468,13 +4814,13 @@
         <v>8.5</v>
       </c>
       <c r="FI8" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ8" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK8" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL8">
         <v>1</v>
@@ -5483,10 +4829,10 @@
         <v>1</v>
       </c>
       <c r="FN8">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="FO8">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="FP8">
         <v>0.95</v>
@@ -5501,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="FT8" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU8">
         <v>0</v>
@@ -5510,28 +4856,28 @@
         <v>0</v>
       </c>
       <c r="GA8" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB8" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC8" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD8">
         <v>86400</v>
       </c>
       <c r="GE8" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF8" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG8" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH8" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI8">
         <v>86400</v>
@@ -5540,7 +4886,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:192">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -5572,13 +4918,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3296000</v>
+        <v>2687000</v>
       </c>
       <c r="O9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -5593,25 +4939,25 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W9">
         <v>90</v>
       </c>
       <c r="X9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y9">
         <v>90</v>
       </c>
       <c r="Z9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -5623,7 +4969,7 @@
         <v>6</v>
       </c>
       <c r="AG9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH9">
         <v>1</v>
@@ -5638,43 +4984,34 @@
         <v>9</v>
       </c>
       <c r="AL9" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN9">
+        <v>90</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP9">
+        <v>90</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="s">
         <v>209</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN9">
-        <v>90</v>
-      </c>
-      <c r="AO9" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP9">
-        <v>90</v>
-      </c>
-      <c r="AQ9" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR9" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS9">
-        <v>1</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>19500000</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>216</v>
-      </c>
-      <c r="AW9">
-        <v>35</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>208</v>
       </c>
       <c r="AY9">
         <v>1</v>
@@ -5689,43 +5026,34 @@
         <v>9</v>
       </c>
       <c r="BC9" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE9">
+        <v>90</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG9">
+        <v>90</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ9">
+        <v>0</v>
+      </c>
+      <c r="BK9">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="s">
         <v>209</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE9">
-        <v>90</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG9">
-        <v>90</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ9">
-        <v>1</v>
-      </c>
-      <c r="BK9">
-        <v>1</v>
-      </c>
-      <c r="BL9">
-        <v>2400000</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>223</v>
-      </c>
-      <c r="BN9">
-        <v>55</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>208</v>
       </c>
       <c r="BP9">
         <v>1</v>
@@ -5740,25 +5068,25 @@
         <v>9</v>
       </c>
       <c r="BT9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BU9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BV9">
         <v>90</v>
       </c>
       <c r="BW9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BX9">
         <v>90</v>
       </c>
       <c r="BY9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BZ9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CA9">
         <v>1</v>
@@ -5767,10 +5095,10 @@
         <v>1</v>
       </c>
       <c r="CC9">
-        <v>5200</v>
+        <v>3800</v>
       </c>
       <c r="CD9" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="CE9">
         <v>0</v>
@@ -5782,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="CH9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="CI9">
         <v>1</v>
@@ -5797,37 +5125,37 @@
         <v>9</v>
       </c>
       <c r="CM9" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO9">
+        <v>90</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ9">
+        <v>90</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS9" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT9" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU9">
+        <v>0</v>
+      </c>
+      <c r="CV9">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="s">
         <v>209</v>
-      </c>
-      <c r="CN9" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO9">
-        <v>90</v>
-      </c>
-      <c r="CP9" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ9">
-        <v>90</v>
-      </c>
-      <c r="CR9" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS9" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT9" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU9">
-        <v>0</v>
-      </c>
-      <c r="CV9">
-        <v>0</v>
-      </c>
-      <c r="CZ9" t="s">
-        <v>208</v>
       </c>
       <c r="DA9">
         <v>1</v>
@@ -5842,37 +5170,37 @@
         <v>9</v>
       </c>
       <c r="DE9" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF9" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG9">
+        <v>90</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI9">
+        <v>90</v>
+      </c>
+      <c r="DJ9" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK9" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL9" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM9">
+        <v>0</v>
+      </c>
+      <c r="DN9">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="s">
         <v>209</v>
-      </c>
-      <c r="DF9" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG9">
-        <v>90</v>
-      </c>
-      <c r="DH9" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI9">
-        <v>90</v>
-      </c>
-      <c r="DJ9" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK9" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL9" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM9">
-        <v>0</v>
-      </c>
-      <c r="DN9">
-        <v>0</v>
-      </c>
-      <c r="DR9" t="s">
-        <v>208</v>
       </c>
       <c r="DS9">
         <v>1</v>
@@ -5887,28 +5215,28 @@
         <v>9</v>
       </c>
       <c r="DW9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY9">
         <v>90</v>
       </c>
       <c r="DZ9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA9">
         <v>90</v>
       </c>
       <c r="EB9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED9" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE9">
         <v>0</v>
@@ -5917,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="EI9" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ9">
         <v>1</v>
@@ -5926,25 +5254,25 @@
         <v>2</v>
       </c>
       <c r="EL9" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="EM9">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EN9">
         <v>7200</v>
       </c>
       <c r="EO9">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EP9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EQ9">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="ER9">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="ES9" t="b">
         <v>0</v>
@@ -5953,19 +5281,19 @@
         <v>0</v>
       </c>
       <c r="EU9" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="EV9">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EW9">
         <v>7200</v>
       </c>
       <c r="EX9">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EY9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EZ9">
         <v>90000</v>
@@ -5980,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="FD9" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE9">
         <v>0.05</v>
@@ -5995,13 +5323,13 @@
         <v>8.5</v>
       </c>
       <c r="FI9" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ9" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK9" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL9">
         <v>1</v>
@@ -6010,10 +5338,10 @@
         <v>1</v>
       </c>
       <c r="FN9">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="FO9">
-        <v>3300</v>
+        <v>2700</v>
       </c>
       <c r="FP9">
         <v>0.95</v>
@@ -6028,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="FT9" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU9">
         <v>0</v>
@@ -6037,28 +5365,28 @@
         <v>0</v>
       </c>
       <c r="GA9" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB9" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC9" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD9">
         <v>86400</v>
       </c>
       <c r="GE9" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF9" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG9" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH9" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI9">
         <v>86400</v>
@@ -6067,7 +5395,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:192">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -6075,10 +5403,10 @@
         <v>199</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -6087,7 +5415,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -6099,13 +5427,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>5527000</v>
+        <v>2262000</v>
       </c>
       <c r="O10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="P10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -6120,25 +5448,25 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W10">
         <v>90</v>
       </c>
       <c r="X10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y10">
         <v>90</v>
       </c>
       <c r="Z10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -6150,7 +5478,7 @@
         <v>6</v>
       </c>
       <c r="AG10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH10">
         <v>1</v>
@@ -6165,43 +5493,34 @@
         <v>9</v>
       </c>
       <c r="AL10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN10">
+        <v>90</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP10">
+        <v>90</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="s">
         <v>209</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN10">
-        <v>90</v>
-      </c>
-      <c r="AO10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP10">
-        <v>90</v>
-      </c>
-      <c r="AQ10" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR10" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS10">
-        <v>1</v>
-      </c>
-      <c r="AT10">
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <v>5500000</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>217</v>
-      </c>
-      <c r="AW10">
-        <v>35</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>208</v>
       </c>
       <c r="AY10">
         <v>1</v>
@@ -6216,43 +5535,34 @@
         <v>9</v>
       </c>
       <c r="BC10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE10">
+        <v>90</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG10">
+        <v>90</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="s">
         <v>209</v>
-      </c>
-      <c r="BD10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE10">
-        <v>90</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG10">
-        <v>90</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ10">
-        <v>1</v>
-      </c>
-      <c r="BK10">
-        <v>1</v>
-      </c>
-      <c r="BL10">
-        <v>2400000</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>219</v>
-      </c>
-      <c r="BN10">
-        <v>55</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>208</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -6267,49 +5577,34 @@
         <v>9</v>
       </c>
       <c r="BT10" t="s">
+        <v>210</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>211</v>
+      </c>
+      <c r="BV10">
+        <v>90</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>211</v>
+      </c>
+      <c r="BX10">
+        <v>90</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>211</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>212</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="s">
         <v>209</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BV10">
-        <v>90</v>
-      </c>
-      <c r="BW10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BX10">
-        <v>90</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>210</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>211</v>
-      </c>
-      <c r="CA10">
-        <v>1</v>
-      </c>
-      <c r="CB10">
-        <v>1</v>
-      </c>
-      <c r="CC10">
-        <v>7000</v>
-      </c>
-      <c r="CD10" t="s">
-        <v>224</v>
-      </c>
-      <c r="CE10">
-        <v>0</v>
-      </c>
-      <c r="CF10">
-        <v>40</v>
-      </c>
-      <c r="CG10" t="b">
-        <v>1</v>
-      </c>
-      <c r="CH10" t="s">
-        <v>208</v>
       </c>
       <c r="CI10">
         <v>1</v>
@@ -6324,37 +5619,37 @@
         <v>9</v>
       </c>
       <c r="CM10" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO10">
+        <v>90</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ10">
+        <v>90</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS10" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT10" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU10">
+        <v>0</v>
+      </c>
+      <c r="CV10">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="s">
         <v>209</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO10">
-        <v>90</v>
-      </c>
-      <c r="CP10" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ10">
-        <v>90</v>
-      </c>
-      <c r="CR10" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS10" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT10" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU10">
-        <v>0</v>
-      </c>
-      <c r="CV10">
-        <v>0</v>
-      </c>
-      <c r="CZ10" t="s">
-        <v>208</v>
       </c>
       <c r="DA10">
         <v>1</v>
@@ -6369,37 +5664,37 @@
         <v>9</v>
       </c>
       <c r="DE10" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF10" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG10">
+        <v>90</v>
+      </c>
+      <c r="DH10" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI10">
+        <v>90</v>
+      </c>
+      <c r="DJ10" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK10" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL10" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM10">
+        <v>0</v>
+      </c>
+      <c r="DN10">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="s">
         <v>209</v>
-      </c>
-      <c r="DF10" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG10">
-        <v>90</v>
-      </c>
-      <c r="DH10" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI10">
-        <v>90</v>
-      </c>
-      <c r="DJ10" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK10" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL10" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM10">
-        <v>0</v>
-      </c>
-      <c r="DN10">
-        <v>0</v>
-      </c>
-      <c r="DR10" t="s">
-        <v>208</v>
       </c>
       <c r="DS10">
         <v>1</v>
@@ -6414,28 +5709,28 @@
         <v>9</v>
       </c>
       <c r="DW10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY10">
         <v>90</v>
       </c>
       <c r="DZ10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA10">
         <v>90</v>
       </c>
       <c r="EB10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED10" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE10">
         <v>0</v>
@@ -6444,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="EI10" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ10">
         <v>1</v>
@@ -6453,25 +5748,25 @@
         <v>1</v>
       </c>
       <c r="EL10" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="EM10">
+        <v>75000</v>
+      </c>
+      <c r="EN10">
+        <v>7200</v>
+      </c>
+      <c r="EO10">
+        <v>11000</v>
+      </c>
+      <c r="EP10">
         <v>100000</v>
       </c>
-      <c r="EN10">
-        <v>11000</v>
-      </c>
-      <c r="EO10">
-        <v>22000</v>
-      </c>
-      <c r="EP10">
-        <v>200000</v>
-      </c>
       <c r="EQ10">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="ER10">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="ES10" t="b">
         <v>0</v>
@@ -6480,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="FD10" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE10">
         <v>0.05</v>
@@ -6495,40 +5790,22 @@
         <v>8.5</v>
       </c>
       <c r="FI10" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ10" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK10" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FM10">
-        <v>1</v>
-      </c>
-      <c r="FN10">
-        <v>5500</v>
-      </c>
-      <c r="FO10">
-        <v>5500</v>
-      </c>
-      <c r="FP10">
-        <v>0.95</v>
-      </c>
-      <c r="FQ10">
-        <v>0.1</v>
-      </c>
-      <c r="FR10" t="b">
-        <v>0</v>
-      </c>
-      <c r="FS10" t="b">
         <v>0</v>
       </c>
       <c r="FT10" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU10">
         <v>0</v>
@@ -6537,28 +5814,28 @@
         <v>0</v>
       </c>
       <c r="GA10" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB10" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC10" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD10">
         <v>86400</v>
       </c>
       <c r="GE10" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF10" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG10" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH10" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI10">
         <v>86400</v>
@@ -6567,7 +5844,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:192">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -6599,13 +5876,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>2896000</v>
+        <v>3863000</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -6620,25 +5897,25 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="V11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="W11">
         <v>90</v>
       </c>
       <c r="X11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y11">
         <v>90</v>
       </c>
       <c r="Z11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AA11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -6650,7 +5927,7 @@
         <v>6</v>
       </c>
       <c r="AG11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH11">
         <v>1</v>
@@ -6665,43 +5942,34 @@
         <v>9</v>
       </c>
       <c r="AL11" t="s">
+        <v>210</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>211</v>
+      </c>
+      <c r="AN11">
+        <v>90</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP11">
+        <v>90</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>211</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>212</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="s">
         <v>209</v>
-      </c>
-      <c r="AM11" t="s">
-        <v>210</v>
-      </c>
-      <c r="AN11">
-        <v>90</v>
-      </c>
-      <c r="AO11" t="s">
-        <v>210</v>
-      </c>
-      <c r="AP11">
-        <v>90</v>
-      </c>
-      <c r="AQ11" t="s">
-        <v>210</v>
-      </c>
-      <c r="AR11" t="s">
-        <v>211</v>
-      </c>
-      <c r="AS11">
-        <v>1</v>
-      </c>
-      <c r="AT11">
-        <v>1</v>
-      </c>
-      <c r="AU11">
-        <v>19500000</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>218</v>
-      </c>
-      <c r="AW11">
-        <v>55</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>208</v>
       </c>
       <c r="AY11">
         <v>1</v>
@@ -6716,43 +5984,34 @@
         <v>9</v>
       </c>
       <c r="BC11" t="s">
+        <v>210</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>211</v>
+      </c>
+      <c r="BE11">
+        <v>90</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>211</v>
+      </c>
+      <c r="BG11">
+        <v>90</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>211</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>212</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="s">
         <v>209</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>210</v>
-      </c>
-      <c r="BE11">
-        <v>90</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>210</v>
-      </c>
-      <c r="BG11">
-        <v>90</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>210</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>211</v>
-      </c>
-      <c r="BJ11">
-        <v>1</v>
-      </c>
-      <c r="BK11">
-        <v>1</v>
-      </c>
-      <c r="BL11">
-        <v>2800000</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>223</v>
-      </c>
-      <c r="BN11">
-        <v>55</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>208</v>
       </c>
       <c r="BP11">
         <v>1</v>
@@ -6767,25 +6026,25 @@
         <v>9</v>
       </c>
       <c r="BT11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BU11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BV11">
         <v>90</v>
       </c>
       <c r="BW11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BX11">
         <v>90</v>
       </c>
       <c r="BY11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="BZ11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="CA11">
         <v>1</v>
@@ -6794,10 +6053,10 @@
         <v>1</v>
       </c>
       <c r="CC11">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="CD11" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="CE11">
         <v>0</v>
@@ -6809,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="CH11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="CI11">
         <v>1</v>
@@ -6824,37 +6083,37 @@
         <v>9</v>
       </c>
       <c r="CM11" t="s">
+        <v>210</v>
+      </c>
+      <c r="CN11" t="s">
+        <v>211</v>
+      </c>
+      <c r="CO11">
+        <v>90</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>211</v>
+      </c>
+      <c r="CQ11">
+        <v>90</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>211</v>
+      </c>
+      <c r="CS11" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT11" t="s">
+        <v>214</v>
+      </c>
+      <c r="CU11">
+        <v>0</v>
+      </c>
+      <c r="CV11">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="s">
         <v>209</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>210</v>
-      </c>
-      <c r="CO11">
-        <v>90</v>
-      </c>
-      <c r="CP11" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ11">
-        <v>90</v>
-      </c>
-      <c r="CR11" t="s">
-        <v>210</v>
-      </c>
-      <c r="CS11" t="s">
-        <v>211</v>
-      </c>
-      <c r="CT11" t="s">
-        <v>225</v>
-      </c>
-      <c r="CU11">
-        <v>0</v>
-      </c>
-      <c r="CV11">
-        <v>0</v>
-      </c>
-      <c r="CZ11" t="s">
-        <v>208</v>
       </c>
       <c r="DA11">
         <v>1</v>
@@ -6869,37 +6128,37 @@
         <v>9</v>
       </c>
       <c r="DE11" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF11" t="s">
+        <v>211</v>
+      </c>
+      <c r="DG11">
+        <v>90</v>
+      </c>
+      <c r="DH11" t="s">
+        <v>211</v>
+      </c>
+      <c r="DI11">
+        <v>90</v>
+      </c>
+      <c r="DJ11" t="s">
+        <v>211</v>
+      </c>
+      <c r="DK11" t="s">
+        <v>212</v>
+      </c>
+      <c r="DL11" t="s">
+        <v>214</v>
+      </c>
+      <c r="DM11">
+        <v>0</v>
+      </c>
+      <c r="DN11">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="s">
         <v>209</v>
-      </c>
-      <c r="DF11" t="s">
-        <v>210</v>
-      </c>
-      <c r="DG11">
-        <v>90</v>
-      </c>
-      <c r="DH11" t="s">
-        <v>210</v>
-      </c>
-      <c r="DI11">
-        <v>90</v>
-      </c>
-      <c r="DJ11" t="s">
-        <v>210</v>
-      </c>
-      <c r="DK11" t="s">
-        <v>211</v>
-      </c>
-      <c r="DL11" t="s">
-        <v>225</v>
-      </c>
-      <c r="DM11">
-        <v>0</v>
-      </c>
-      <c r="DN11">
-        <v>0</v>
-      </c>
-      <c r="DR11" t="s">
-        <v>208</v>
       </c>
       <c r="DS11">
         <v>1</v>
@@ -6914,28 +6173,28 @@
         <v>9</v>
       </c>
       <c r="DW11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="DX11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="DY11">
         <v>90</v>
       </c>
       <c r="DZ11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EA11">
         <v>90</v>
       </c>
       <c r="EB11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="EC11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="ED11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EE11">
         <v>0</v>
@@ -6944,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="EI11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="EJ11">
         <v>1</v>
@@ -6953,25 +6212,25 @@
         <v>1</v>
       </c>
       <c r="EL11" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="EM11">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="EN11">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="EO11">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="EP11">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="EQ11">
-        <v>0.9</v>
+        <v>90000</v>
       </c>
       <c r="ER11">
-        <v>0.8</v>
+        <v>80000</v>
       </c>
       <c r="ES11" t="b">
         <v>0</v>
@@ -6980,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="FD11" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="FE11">
         <v>0.05</v>
@@ -6995,13 +6254,13 @@
         <v>8.5</v>
       </c>
       <c r="FI11" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="FJ11" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="FK11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FL11">
         <v>1</v>
@@ -7010,10 +6269,10 @@
         <v>1</v>
       </c>
       <c r="FN11">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="FO11">
-        <v>2900</v>
+        <v>3900</v>
       </c>
       <c r="FP11">
         <v>0.95</v>
@@ -7028,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="FT11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="FU11">
         <v>0</v>
@@ -7037,28 +6296,28 @@
         <v>0</v>
       </c>
       <c r="GA11" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="GB11" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GC11" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="GD11">
         <v>86400</v>
       </c>
       <c r="GE11" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="GF11" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="GG11" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GH11" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="GI11">
         <v>86400</v>
@@ -7073,11 +6332,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:GM1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:195" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:195">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7091,13 +6350,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -7667,11 +6926,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:ED1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:134" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:134">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7685,7 +6944,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7997,22 +7256,22 @@
         <v>158</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="DJ1" s="1" t="s">
         <v>163</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="DL1" s="1" t="s">
         <v>165</v>
@@ -8078,11 +7337,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:EM1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:143" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:143">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8096,7 +7355,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -8516,11 +7775,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:CB1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:80">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8765,11 +8024,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B1:AP1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:42" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:42">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8813,58 +8072,58 @@
         <v>174</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>182</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ge23nur\Documents\Python Scripts\HAMLET\02 - config\example_single_market\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDFA954-CCD5-47CB-8AFF-7921CCAD63CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="sfh" sheetId="1" r:id="rId1"/>
@@ -20,25 +14,12 @@
     <sheet name="producer" sheetId="5" r:id="rId5"/>
     <sheet name="storage" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1423" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="278">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -607,63 +588,84 @@
     <t>ems/market/fcast/wholesale</t>
   </si>
   <si>
-    <t>ems/fcasts/retraining_period</t>
-  </si>
-  <si>
-    <t>ems/fcasts/update_period</t>
-  </si>
-  <si>
-    <t>uzEoMpDvqUQmolk</t>
-  </si>
-  <si>
-    <t>DGzmAB9lHmVyQZv</t>
-  </si>
-  <si>
-    <t>TYMLJEa1KAhqE59</t>
-  </si>
-  <si>
-    <t>exVNgDckyloeKPg</t>
-  </si>
-  <si>
-    <t>KbSpjvHvz8Y5u7z</t>
-  </si>
-  <si>
-    <t>9ImCBUvCV7wFtHf</t>
-  </si>
-  <si>
-    <t>yHAIaE0rOHnBGoP</t>
-  </si>
-  <si>
-    <t>rNrxz3A1u6iRhO2</t>
-  </si>
-  <si>
-    <t>Ec93eXNNvTukTxN</t>
-  </si>
-  <si>
-    <t>ZzD5Fsx2AOCTX8N</t>
-  </si>
-  <si>
-    <t>hh_2532_0.csv</t>
+    <t>ems/market/fcast/retailer/energy</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/grid/local</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/grid/retail</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/levies</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/balancing</t>
+  </si>
+  <si>
+    <t>ems/fcasts/horizon</t>
+  </si>
+  <si>
+    <t>ems/fcasts/retraining</t>
+  </si>
+  <si>
+    <t>ems/fcasts/update</t>
+  </si>
+  <si>
+    <t>6qwgumJMmVbXDI7</t>
+  </si>
+  <si>
+    <t>4nnq3O1PEZp6dWM</t>
+  </si>
+  <si>
+    <t>BnqcT6hxtti70uH</t>
+  </si>
+  <si>
+    <t>9eFSrzr91OSowvp</t>
+  </si>
+  <si>
+    <t>0AzUwdxZZptibiO</t>
+  </si>
+  <si>
+    <t>geow5OY76tEO7e0</t>
+  </si>
+  <si>
+    <t>KATyPT8EDCK0ESt</t>
+  </si>
+  <si>
+    <t>E8G6EOAJkfvUjJH</t>
+  </si>
+  <si>
+    <t>NXvRT9GPioxZO0u</t>
+  </si>
+  <si>
+    <t>206Y66Ba67yqGSQ</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3564_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2012_3.csv</t>
+  </si>
+  <si>
+    <t>hh_2959_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3648_0.csv</t>
   </si>
   <si>
     <t>hh_3125_0.csv</t>
   </si>
   <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4402_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2896_0.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -676,40 +678,46 @@
     <t>[1, 0, 0]</t>
   </si>
   <si>
-    <t>heat_2532_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3125_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
   </si>
   <si>
     <t>heat_3296_0.csv</t>
   </si>
   <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2896_0.csv</t>
+    <t>heat_2012_3.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
   </si>
   <si>
     <t>dhw_gen_4_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
+    <t>dhw_gen_3_pu.csv</t>
   </si>
   <si>
     <t>pv_config.json</t>
@@ -721,31 +729,28 @@
     <t>local</t>
   </si>
   <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_1.csv</t>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
   </si>
   <si>
     <t>ev_parttime_89.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_46.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_47.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_42.csv</t>
+    <t>ev_freetime_3.csv</t>
   </si>
   <si>
     <t>ev_parttime_90.csv</t>
   </si>
   <si>
-    <t>ev_parttime_88.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_43.csv</t>
+    <t>ev_fulltime_44.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_41.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_49.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -763,10 +768,10 @@
     <t>['linear']</t>
   </si>
   <si>
-    <t>[10800, 21600, 32400, 43200]</t>
-  </si>
-  <si>
     <t>naive</t>
+  </si>
+  <si>
+    <t>['naive', 'naive']</t>
   </si>
   <si>
     <t>general/sub_id</t>
@@ -853,8 +858,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -917,21 +922,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -969,7 +966,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1003,7 +1000,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1038,10 +1034,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1214,204 +1209,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:GJ11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="1.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="31.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="28.90625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="26.90625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="29.81640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="31.36328125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="25" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="24.90625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="18" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="9" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="104" max="104" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="105" max="105" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="22" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="109" max="109" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="110" max="110" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="111" max="111" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="112" max="112" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="114" max="114" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="116" max="116" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="118" max="118" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="22.7265625" bestFit="1" customWidth="1"/>
-    <col min="120" max="120" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="121" max="121" width="27.453125" bestFit="1" customWidth="1"/>
-    <col min="122" max="122" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="123" max="123" width="25" bestFit="1" customWidth="1"/>
-    <col min="124" max="124" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="125" max="125" width="26.08984375" bestFit="1" customWidth="1"/>
-    <col min="126" max="126" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="127" max="127" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="129" max="129" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="130" max="130" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="132" max="132" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="133" max="133" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="134" max="134" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="135" max="135" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="136" max="136" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="138" max="138" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="140" max="140" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="142" max="142" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="144" max="144" width="24" bestFit="1" customWidth="1"/>
-    <col min="145" max="145" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="146" max="146" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="147" max="147" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="148" max="148" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="149" max="149" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="150" max="150" width="14" bestFit="1" customWidth="1"/>
-    <col min="151" max="151" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="152" max="152" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="153" max="153" width="24" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="156" max="156" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="157" max="157" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="158" max="158" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="159" max="159" width="14" bestFit="1" customWidth="1"/>
-    <col min="160" max="160" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="161" max="161" width="40.6328125" bestFit="1" customWidth="1"/>
-    <col min="162" max="162" width="29.26953125" bestFit="1" customWidth="1"/>
-    <col min="163" max="163" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="164" max="164" width="35.6328125" bestFit="1" customWidth="1"/>
-    <col min="165" max="165" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="166" max="166" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="168" max="168" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="169" max="169" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="170" max="170" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="171" max="171" width="22.26953125" bestFit="1" customWidth="1"/>
-    <col min="172" max="172" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="173" max="173" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="174" max="175" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="176" max="176" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="177" max="177" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="178" max="178" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="179" max="179" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="181" max="181" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="182" max="182" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="183" max="183" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="184" max="184" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="185" max="185" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="186" max="186" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="187" max="187" width="19" bestFit="1" customWidth="1"/>
-    <col min="188" max="188" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="189" max="189" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="190" max="190" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="191" max="191" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="192" max="192" width="23.453125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:GP11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:198">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1985,13 +1787,31 @@
       <c r="GJ1" s="1" t="s">
         <v>190</v>
       </c>
+      <c r="GK1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="GL1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="GM1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="GN1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="GO1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="GP1" s="1" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="2" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:198">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -2018,13 +1838,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>2532000</v>
+        <v>3863000</v>
       </c>
       <c r="O2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2039,25 +1859,25 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W2">
         <v>90</v>
       </c>
       <c r="X2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y2">
         <v>90</v>
       </c>
       <c r="Z2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB2">
         <v>0</v>
@@ -2069,7 +1889,7 @@
         <v>6</v>
       </c>
       <c r="AG2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH2">
         <v>1</v>
@@ -2084,25 +1904,25 @@
         <v>9</v>
       </c>
       <c r="AL2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN2">
         <v>90</v>
       </c>
       <c r="AO2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP2">
         <v>90</v>
       </c>
       <c r="AQ2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS2">
         <v>1</v>
@@ -2114,13 +1934,13 @@
         <v>19500000</v>
       </c>
       <c r="AV2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AW2">
         <v>55</v>
       </c>
       <c r="AX2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY2">
         <v>1</v>
@@ -2135,25 +1955,25 @@
         <v>9</v>
       </c>
       <c r="BC2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE2">
         <v>90</v>
       </c>
       <c r="BF2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG2">
         <v>90</v>
       </c>
       <c r="BH2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ2">
         <v>1</v>
@@ -2162,16 +1982,16 @@
         <v>1</v>
       </c>
       <c r="BL2">
-        <v>2800000</v>
+        <v>3200000</v>
       </c>
       <c r="BM2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="BN2">
         <v>55</v>
       </c>
       <c r="BO2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP2">
         <v>1</v>
@@ -2186,25 +2006,25 @@
         <v>9</v>
       </c>
       <c r="BT2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV2">
         <v>90</v>
       </c>
       <c r="BW2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA2">
         <v>1</v>
@@ -2213,22 +2033,22 @@
         <v>1</v>
       </c>
       <c r="CC2">
-        <v>3800</v>
+        <v>6500</v>
       </c>
       <c r="CD2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG2" t="b">
         <v>1</v>
       </c>
       <c r="CH2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI2">
         <v>1</v>
@@ -2243,28 +2063,28 @@
         <v>9</v>
       </c>
       <c r="CM2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO2">
         <v>90</v>
       </c>
       <c r="CP2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ2">
         <v>90</v>
       </c>
       <c r="CR2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU2">
         <v>0</v>
@@ -2273,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA2">
         <v>1</v>
@@ -2288,28 +2108,28 @@
         <v>9</v>
       </c>
       <c r="DE2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG2">
         <v>90</v>
       </c>
       <c r="DH2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI2">
         <v>90</v>
       </c>
       <c r="DJ2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM2">
         <v>0</v>
@@ -2318,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="DR2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS2">
         <v>1</v>
@@ -2333,28 +2153,28 @@
         <v>9</v>
       </c>
       <c r="DW2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY2">
         <v>90</v>
       </c>
       <c r="DZ2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA2">
         <v>90</v>
       </c>
       <c r="EB2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE2">
         <v>0</v>
@@ -2363,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="EI2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ2">
         <v>1</v>
@@ -2372,19 +2192,19 @@
         <v>1</v>
       </c>
       <c r="EL2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="EM2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="EN2">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="EO2">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="EP2">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="EQ2">
         <v>0.9</v>
@@ -2399,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="FD2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE2">
         <v>0.05</v>
@@ -2414,13 +2234,13 @@
         <v>8.5</v>
       </c>
       <c r="FI2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL2">
         <v>1</v>
@@ -2429,10 +2249,10 @@
         <v>1</v>
       </c>
       <c r="FN2">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="FO2">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="FP2">
         <v>0.95</v>
@@ -2447,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="FT2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU2">
         <v>0</v>
@@ -2456,48 +2276,66 @@
         <v>0</v>
       </c>
       <c r="GA2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD2">
         <v>86400</v>
       </c>
       <c r="GE2" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF2" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF2">
+        <v>86400</v>
       </c>
       <c r="GG2" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH2" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI2">
+        <v>249</v>
+      </c>
+      <c r="GI2" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ2" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK2" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL2" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM2" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN2">
         <v>86400</v>
       </c>
-      <c r="GJ2">
+      <c r="GO2">
+        <v>86400</v>
+      </c>
+      <c r="GP2">
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:198">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2506,7 +2344,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2518,13 +2356,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>3125000</v>
+        <v>3564000</v>
       </c>
       <c r="O3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2539,25 +2377,25 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W3">
         <v>90</v>
       </c>
       <c r="X3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y3">
         <v>90</v>
       </c>
       <c r="Z3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -2569,7 +2407,7 @@
         <v>6</v>
       </c>
       <c r="AG3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH3">
         <v>1</v>
@@ -2584,25 +2422,25 @@
         <v>9</v>
       </c>
       <c r="AL3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN3">
         <v>90</v>
       </c>
       <c r="AO3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP3">
         <v>90</v>
       </c>
       <c r="AQ3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS3">
         <v>1</v>
@@ -2611,16 +2449,16 @@
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AV3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AW3">
         <v>55</v>
       </c>
       <c r="AX3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY3">
         <v>1</v>
@@ -2635,25 +2473,25 @@
         <v>9</v>
       </c>
       <c r="BC3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE3">
         <v>90</v>
       </c>
       <c r="BF3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG3">
         <v>90</v>
       </c>
       <c r="BH3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ3">
         <v>1</v>
@@ -2665,13 +2503,13 @@
         <v>2400000</v>
       </c>
       <c r="BM3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="BN3">
         <v>55</v>
       </c>
       <c r="BO3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP3">
         <v>1</v>
@@ -2686,25 +2524,25 @@
         <v>9</v>
       </c>
       <c r="BT3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV3">
         <v>90</v>
       </c>
       <c r="BW3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX3">
         <v>90</v>
       </c>
       <c r="BY3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA3">
         <v>1</v>
@@ -2713,22 +2551,22 @@
         <v>1</v>
       </c>
       <c r="CC3">
-        <v>5400</v>
+        <v>5800</v>
       </c>
       <c r="CD3" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG3" t="b">
         <v>1</v>
       </c>
       <c r="CH3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI3">
         <v>1</v>
@@ -2743,28 +2581,28 @@
         <v>9</v>
       </c>
       <c r="CM3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO3">
         <v>90</v>
       </c>
       <c r="CP3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ3">
         <v>90</v>
       </c>
       <c r="CR3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU3">
         <v>0</v>
@@ -2773,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA3">
         <v>1</v>
@@ -2788,28 +2626,28 @@
         <v>9</v>
       </c>
       <c r="DE3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG3">
         <v>90</v>
       </c>
       <c r="DH3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI3">
         <v>90</v>
       </c>
       <c r="DJ3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM3">
         <v>0</v>
@@ -2818,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="DR3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS3">
         <v>1</v>
@@ -2833,28 +2671,28 @@
         <v>9</v>
       </c>
       <c r="DW3" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY3">
         <v>90</v>
       </c>
       <c r="DZ3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA3">
         <v>90</v>
       </c>
       <c r="EB3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE3">
         <v>0</v>
@@ -2863,28 +2701,28 @@
         <v>0</v>
       </c>
       <c r="EI3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ3">
         <v>1</v>
       </c>
       <c r="EK3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EL3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="EM3">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="EN3">
         <v>7200</v>
       </c>
       <c r="EO3">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="EP3">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="EQ3">
         <v>0.9</v>
@@ -2898,8 +2736,35 @@
       <c r="ET3" t="b">
         <v>0</v>
       </c>
+      <c r="EU3" t="s">
+        <v>243</v>
+      </c>
+      <c r="EV3">
+        <v>50000</v>
+      </c>
+      <c r="EW3">
+        <v>7200</v>
+      </c>
+      <c r="EX3">
+        <v>7200</v>
+      </c>
+      <c r="EY3">
+        <v>50000</v>
+      </c>
+      <c r="EZ3">
+        <v>0.9</v>
+      </c>
+      <c r="FA3">
+        <v>0.8</v>
+      </c>
+      <c r="FB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC3" t="b">
+        <v>0</v>
+      </c>
       <c r="FD3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE3">
         <v>0.05</v>
@@ -2914,13 +2779,13 @@
         <v>8.5</v>
       </c>
       <c r="FI3" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ3" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL3">
         <v>1</v>
@@ -2929,10 +2794,10 @@
         <v>1</v>
       </c>
       <c r="FN3">
-        <v>3100</v>
+        <v>3600</v>
       </c>
       <c r="FO3">
-        <v>3100</v>
+        <v>3600</v>
       </c>
       <c r="FP3">
         <v>0.95</v>
@@ -2947,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="FT3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU3">
         <v>0</v>
@@ -2956,48 +2821,66 @@
         <v>0</v>
       </c>
       <c r="GA3" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD3">
         <v>86400</v>
       </c>
       <c r="GE3" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF3" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF3">
+        <v>86400</v>
       </c>
       <c r="GG3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH3" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI3">
+        <v>249</v>
+      </c>
+      <c r="GI3" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ3" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK3" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL3" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM3" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN3">
         <v>86400</v>
       </c>
-      <c r="GJ3">
+      <c r="GO3">
+        <v>86400</v>
+      </c>
+      <c r="GP3">
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:198">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3006,7 +2889,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3021,10 +2904,10 @@
         <v>5527000</v>
       </c>
       <c r="O4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3039,25 +2922,25 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W4">
         <v>90</v>
       </c>
       <c r="X4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y4">
         <v>90</v>
       </c>
       <c r="Z4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -3069,7 +2952,7 @@
         <v>6</v>
       </c>
       <c r="AG4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH4">
         <v>1</v>
@@ -3084,25 +2967,25 @@
         <v>9</v>
       </c>
       <c r="AL4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN4">
         <v>90</v>
       </c>
       <c r="AO4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP4">
         <v>90</v>
       </c>
       <c r="AQ4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS4">
         <v>1</v>
@@ -3111,16 +2994,16 @@
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AV4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="AW4">
         <v>55</v>
       </c>
       <c r="AX4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY4">
         <v>1</v>
@@ -3135,25 +3018,25 @@
         <v>9</v>
       </c>
       <c r="BC4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE4">
         <v>90</v>
       </c>
       <c r="BF4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG4">
         <v>90</v>
       </c>
       <c r="BH4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ4">
         <v>1</v>
@@ -3165,13 +3048,13 @@
         <v>2400000</v>
       </c>
       <c r="BM4" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="BN4">
         <v>55</v>
       </c>
       <c r="BO4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP4">
         <v>1</v>
@@ -3186,25 +3069,25 @@
         <v>9</v>
       </c>
       <c r="BT4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV4">
         <v>90</v>
       </c>
       <c r="BW4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX4">
         <v>90</v>
       </c>
       <c r="BY4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA4">
         <v>1</v>
@@ -3213,10 +3096,10 @@
         <v>1</v>
       </c>
       <c r="CC4">
-        <v>7900</v>
+        <v>7000</v>
       </c>
       <c r="CD4" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE4">
         <v>0</v>
@@ -3228,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="CH4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI4">
         <v>1</v>
@@ -3243,28 +3126,28 @@
         <v>9</v>
       </c>
       <c r="CM4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO4">
         <v>90</v>
       </c>
       <c r="CP4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ4">
         <v>90</v>
       </c>
       <c r="CR4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT4" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU4">
         <v>0</v>
@@ -3273,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="CZ4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA4">
         <v>1</v>
@@ -3288,28 +3171,28 @@
         <v>9</v>
       </c>
       <c r="DE4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG4">
         <v>90</v>
       </c>
       <c r="DH4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI4">
         <v>90</v>
       </c>
       <c r="DJ4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL4" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM4">
         <v>0</v>
@@ -3318,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="DR4" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS4">
         <v>1</v>
@@ -3333,28 +3216,28 @@
         <v>9</v>
       </c>
       <c r="DW4" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY4">
         <v>90</v>
       </c>
       <c r="DZ4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA4">
         <v>90</v>
       </c>
       <c r="EB4" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC4" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE4">
         <v>0</v>
@@ -3363,16 +3246,16 @@
         <v>0</v>
       </c>
       <c r="EI4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ4">
         <v>1</v>
       </c>
       <c r="EK4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EL4" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="EM4">
         <v>75000</v>
@@ -3398,35 +3281,8 @@
       <c r="ET4" t="b">
         <v>0</v>
       </c>
-      <c r="EU4" t="s">
-        <v>234</v>
-      </c>
-      <c r="EV4">
-        <v>100000</v>
-      </c>
-      <c r="EW4">
-        <v>11000</v>
-      </c>
-      <c r="EX4">
-        <v>22000</v>
-      </c>
-      <c r="EY4">
-        <v>200000</v>
-      </c>
-      <c r="EZ4">
-        <v>90000</v>
-      </c>
-      <c r="FA4">
-        <v>80000</v>
-      </c>
-      <c r="FB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC4" t="b">
-        <v>0</v>
-      </c>
       <c r="FD4" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE4">
         <v>0.05</v>
@@ -3441,13 +3297,13 @@
         <v>8.5</v>
       </c>
       <c r="FI4" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ4" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL4">
         <v>1</v>
@@ -3474,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="FT4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU4">
         <v>0</v>
@@ -3483,42 +3339,60 @@
         <v>0</v>
       </c>
       <c r="GA4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC4" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD4">
         <v>86400</v>
       </c>
       <c r="GE4" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF4" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF4">
+        <v>86400</v>
       </c>
       <c r="GG4" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH4" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI4">
+        <v>249</v>
+      </c>
+      <c r="GI4" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ4" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK4" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL4" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM4" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN4">
         <v>86400</v>
       </c>
-      <c r="GJ4">
+      <c r="GO4">
+        <v>86400</v>
+      </c>
+      <c r="GP4">
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:198">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3545,13 +3419,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>4402000</v>
+        <v>3296000</v>
       </c>
       <c r="O5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -3566,25 +3440,25 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W5">
         <v>90</v>
       </c>
       <c r="X5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y5">
         <v>90</v>
       </c>
       <c r="Z5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -3596,7 +3470,7 @@
         <v>6</v>
       </c>
       <c r="AG5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -3611,25 +3485,25 @@
         <v>9</v>
       </c>
       <c r="AL5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN5">
         <v>90</v>
       </c>
       <c r="AO5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP5">
         <v>90</v>
       </c>
       <c r="AQ5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS5">
         <v>1</v>
@@ -3641,13 +3515,13 @@
         <v>5500000</v>
       </c>
       <c r="AV5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="AW5">
         <v>55</v>
       </c>
       <c r="AX5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY5">
         <v>1</v>
@@ -3662,25 +3536,25 @@
         <v>9</v>
       </c>
       <c r="BC5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE5">
         <v>90</v>
       </c>
       <c r="BF5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG5">
         <v>90</v>
       </c>
       <c r="BH5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ5">
         <v>1</v>
@@ -3689,16 +3563,16 @@
         <v>1</v>
       </c>
       <c r="BL5">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
       <c r="BM5" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="BN5">
         <v>55</v>
       </c>
       <c r="BO5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP5">
         <v>1</v>
@@ -3713,25 +3587,25 @@
         <v>9</v>
       </c>
       <c r="BT5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV5">
         <v>90</v>
       </c>
       <c r="BW5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX5">
         <v>90</v>
       </c>
       <c r="BY5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA5">
         <v>1</v>
@@ -3740,22 +3614,22 @@
         <v>1</v>
       </c>
       <c r="CC5">
-        <v>6900</v>
+        <v>4200</v>
       </c>
       <c r="CD5" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG5" t="b">
         <v>1</v>
       </c>
       <c r="CH5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI5">
         <v>1</v>
@@ -3770,28 +3644,28 @@
         <v>9</v>
       </c>
       <c r="CM5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO5">
         <v>90</v>
       </c>
       <c r="CP5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ5">
         <v>90</v>
       </c>
       <c r="CR5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU5">
         <v>0</v>
@@ -3800,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA5">
         <v>1</v>
@@ -3815,28 +3689,28 @@
         <v>9</v>
       </c>
       <c r="DE5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG5">
         <v>90</v>
       </c>
       <c r="DH5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI5">
         <v>90</v>
       </c>
       <c r="DJ5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM5">
         <v>0</v>
@@ -3845,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="DR5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS5">
         <v>1</v>
@@ -3860,28 +3734,28 @@
         <v>9</v>
       </c>
       <c r="DW5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY5">
         <v>90</v>
       </c>
       <c r="DZ5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA5">
         <v>90</v>
       </c>
       <c r="EB5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE5">
         <v>0</v>
@@ -3890,28 +3764,28 @@
         <v>0</v>
       </c>
       <c r="EI5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ5">
         <v>1</v>
       </c>
       <c r="EK5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EL5" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="EM5">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="EN5">
         <v>7200</v>
       </c>
       <c r="EO5">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="EP5">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="EQ5">
         <v>0.9</v>
@@ -3925,35 +3799,8 @@
       <c r="ET5" t="b">
         <v>0</v>
       </c>
-      <c r="EU5" t="s">
-        <v>235</v>
-      </c>
-      <c r="EV5">
-        <v>50000</v>
-      </c>
-      <c r="EW5">
-        <v>7200</v>
-      </c>
-      <c r="EX5">
-        <v>7200</v>
-      </c>
-      <c r="EY5">
-        <v>50000</v>
-      </c>
-      <c r="EZ5">
-        <v>90000</v>
-      </c>
-      <c r="FA5">
-        <v>80000</v>
-      </c>
-      <c r="FB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC5" t="b">
-        <v>0</v>
-      </c>
       <c r="FD5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE5">
         <v>0.05</v>
@@ -3968,13 +3815,13 @@
         <v>8.5</v>
       </c>
       <c r="FI5" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ5" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL5">
         <v>1</v>
@@ -3983,10 +3830,10 @@
         <v>1</v>
       </c>
       <c r="FN5">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="FO5">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="FP5">
         <v>0.95</v>
@@ -4001,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="FT5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU5">
         <v>0</v>
@@ -4010,48 +3857,66 @@
         <v>0</v>
       </c>
       <c r="GA5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB5" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC5" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD5">
         <v>86400</v>
       </c>
       <c r="GE5" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF5" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF5">
+        <v>86400</v>
       </c>
       <c r="GG5" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH5" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI5">
+        <v>249</v>
+      </c>
+      <c r="GI5" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ5" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK5" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL5" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM5" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN5">
         <v>86400</v>
       </c>
-      <c r="GJ5">
+      <c r="GO5">
+        <v>86400</v>
+      </c>
+      <c r="GP5">
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:198">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -4060,7 +3925,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4072,13 +3937,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>3296000</v>
+        <v>5527000</v>
       </c>
       <c r="O6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4093,25 +3958,25 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W6">
         <v>90</v>
       </c>
       <c r="X6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y6">
         <v>90</v>
       </c>
       <c r="Z6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -4123,7 +3988,7 @@
         <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH6">
         <v>1</v>
@@ -4138,25 +4003,25 @@
         <v>9</v>
       </c>
       <c r="AL6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN6">
         <v>90</v>
       </c>
       <c r="AO6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP6">
         <v>90</v>
       </c>
       <c r="AQ6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS6">
         <v>1</v>
@@ -4165,16 +4030,16 @@
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AV6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="AW6">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AX6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -4189,25 +4054,25 @@
         <v>9</v>
       </c>
       <c r="BC6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE6">
         <v>90</v>
       </c>
       <c r="BF6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG6">
         <v>90</v>
       </c>
       <c r="BH6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ6">
         <v>1</v>
@@ -4216,16 +4081,16 @@
         <v>1</v>
       </c>
       <c r="BL6">
-        <v>1800000</v>
+        <v>2800000</v>
       </c>
       <c r="BM6" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="BN6">
         <v>55</v>
       </c>
       <c r="BO6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP6">
         <v>1</v>
@@ -4240,25 +4105,25 @@
         <v>9</v>
       </c>
       <c r="BT6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV6">
         <v>90</v>
       </c>
       <c r="BW6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX6">
         <v>90</v>
       </c>
       <c r="BY6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA6">
         <v>1</v>
@@ -4267,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="CC6">
-        <v>4000</v>
+        <v>8900</v>
       </c>
       <c r="CD6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE6">
         <v>0</v>
@@ -4282,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="CH6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI6">
         <v>1</v>
@@ -4297,28 +4162,28 @@
         <v>9</v>
       </c>
       <c r="CM6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO6">
         <v>90</v>
       </c>
       <c r="CP6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ6">
         <v>90</v>
       </c>
       <c r="CR6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU6">
         <v>0</v>
@@ -4327,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA6">
         <v>1</v>
@@ -4342,28 +4207,28 @@
         <v>9</v>
       </c>
       <c r="DE6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG6">
         <v>90</v>
       </c>
       <c r="DH6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI6">
         <v>90</v>
       </c>
       <c r="DJ6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM6">
         <v>0</v>
@@ -4372,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="DR6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS6">
         <v>1</v>
@@ -4387,28 +4252,28 @@
         <v>9</v>
       </c>
       <c r="DW6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY6">
         <v>90</v>
       </c>
       <c r="DZ6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA6">
         <v>90</v>
       </c>
       <c r="EB6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED6" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE6">
         <v>0</v>
@@ -4417,16 +4282,16 @@
         <v>0</v>
       </c>
       <c r="EI6" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ6">
         <v>1</v>
       </c>
       <c r="EK6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EL6" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="EM6">
         <v>50000</v>
@@ -4452,8 +4317,35 @@
       <c r="ET6" t="b">
         <v>0</v>
       </c>
+      <c r="EU6" t="s">
+        <v>240</v>
+      </c>
+      <c r="EV6">
+        <v>75000</v>
+      </c>
+      <c r="EW6">
+        <v>7200</v>
+      </c>
+      <c r="EX6">
+        <v>11000</v>
+      </c>
+      <c r="EY6">
+        <v>100000</v>
+      </c>
+      <c r="EZ6">
+        <v>0.9</v>
+      </c>
+      <c r="FA6">
+        <v>0.8</v>
+      </c>
+      <c r="FB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC6" t="b">
+        <v>0</v>
+      </c>
       <c r="FD6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE6">
         <v>0.05</v>
@@ -4468,13 +4360,13 @@
         <v>8.5</v>
       </c>
       <c r="FI6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ6" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK6" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL6">
         <v>1</v>
@@ -4483,10 +4375,10 @@
         <v>1</v>
       </c>
       <c r="FN6">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="FO6">
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="FP6">
         <v>0.95</v>
@@ -4501,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="FT6" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU6">
         <v>0</v>
@@ -4510,42 +4402,60 @@
         <v>0</v>
       </c>
       <c r="GA6" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD6">
         <v>86400</v>
       </c>
       <c r="GE6" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF6" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF6">
+        <v>86400</v>
       </c>
       <c r="GG6" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH6" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI6">
+        <v>249</v>
+      </c>
+      <c r="GI6" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ6" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK6" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL6" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM6" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN6">
         <v>86400</v>
       </c>
-      <c r="GJ6">
+      <c r="GO6">
+        <v>86400</v>
+      </c>
+      <c r="GP6">
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:198">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F7">
         <v>4</v>
@@ -4572,13 +4482,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3296000</v>
+        <v>2012000</v>
       </c>
       <c r="O7" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -4593,25 +4503,25 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W7">
         <v>90</v>
       </c>
       <c r="X7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y7">
         <v>90</v>
       </c>
       <c r="Z7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB7">
         <v>0</v>
@@ -4623,7 +4533,7 @@
         <v>6</v>
       </c>
       <c r="AG7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH7">
         <v>1</v>
@@ -4638,25 +4548,25 @@
         <v>9</v>
       </c>
       <c r="AL7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN7">
         <v>90</v>
       </c>
       <c r="AO7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP7">
         <v>90</v>
       </c>
       <c r="AQ7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS7">
         <v>1</v>
@@ -4668,13 +4578,13 @@
         <v>19500000</v>
       </c>
       <c r="AV7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="AW7">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AX7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -4689,25 +4599,25 @@
         <v>9</v>
       </c>
       <c r="BC7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE7">
         <v>90</v>
       </c>
       <c r="BF7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG7">
         <v>90</v>
       </c>
       <c r="BH7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ7">
         <v>1</v>
@@ -4719,13 +4629,13 @@
         <v>2800000</v>
       </c>
       <c r="BM7" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="BN7">
         <v>55</v>
       </c>
       <c r="BO7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP7">
         <v>1</v>
@@ -4740,25 +4650,25 @@
         <v>9</v>
       </c>
       <c r="BT7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV7">
         <v>90</v>
       </c>
       <c r="BW7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX7">
         <v>90</v>
       </c>
       <c r="BY7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA7">
         <v>1</v>
@@ -4767,22 +4677,22 @@
         <v>1</v>
       </c>
       <c r="CC7">
-        <v>5900</v>
+        <v>3400</v>
       </c>
       <c r="CD7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE7">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG7" t="b">
         <v>1</v>
       </c>
       <c r="CH7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI7">
         <v>1</v>
@@ -4797,28 +4707,28 @@
         <v>9</v>
       </c>
       <c r="CM7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO7">
         <v>90</v>
       </c>
       <c r="CP7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ7">
         <v>90</v>
       </c>
       <c r="CR7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU7">
         <v>0</v>
@@ -4827,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA7">
         <v>1</v>
@@ -4842,28 +4752,28 @@
         <v>9</v>
       </c>
       <c r="DE7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG7">
         <v>90</v>
       </c>
       <c r="DH7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI7">
         <v>90</v>
       </c>
       <c r="DJ7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL7" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM7">
         <v>0</v>
@@ -4872,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="DR7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS7">
         <v>1</v>
@@ -4887,28 +4797,28 @@
         <v>9</v>
       </c>
       <c r="DW7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY7">
         <v>90</v>
       </c>
       <c r="DZ7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA7">
         <v>90</v>
       </c>
       <c r="EB7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED7" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE7">
         <v>0</v>
@@ -4917,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="EI7" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ7">
         <v>1</v>
@@ -4926,19 +4836,19 @@
         <v>1</v>
       </c>
       <c r="EL7" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="EM7">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EN7">
         <v>7200</v>
       </c>
       <c r="EO7">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EP7">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EQ7">
         <v>0.9</v>
@@ -4953,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="FD7" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE7">
         <v>0.05</v>
@@ -4968,13 +4878,13 @@
         <v>8.5</v>
       </c>
       <c r="FI7" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ7" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK7" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL7">
         <v>1</v>
@@ -4983,10 +4893,10 @@
         <v>1</v>
       </c>
       <c r="FN7">
-        <v>3300</v>
+        <v>2000</v>
       </c>
       <c r="FO7">
-        <v>3300</v>
+        <v>2000</v>
       </c>
       <c r="FP7">
         <v>0.95</v>
@@ -5001,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="FT7" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU7">
         <v>0</v>
@@ -5010,42 +4920,60 @@
         <v>0</v>
       </c>
       <c r="GA7" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB7" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC7" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD7">
         <v>86400</v>
       </c>
       <c r="GE7" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF7" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF7">
+        <v>86400</v>
       </c>
       <c r="GG7" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH7" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI7">
+        <v>249</v>
+      </c>
+      <c r="GI7" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM7" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN7">
         <v>86400</v>
       </c>
-      <c r="GJ7">
+      <c r="GO7">
+        <v>86400</v>
+      </c>
+      <c r="GP7">
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:198">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -5072,13 +5000,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3564000</v>
+        <v>2959000</v>
       </c>
       <c r="O8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="P8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -5093,25 +5021,25 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W8">
         <v>90</v>
       </c>
       <c r="X8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y8">
         <v>90</v>
       </c>
       <c r="Z8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -5123,7 +5051,7 @@
         <v>6</v>
       </c>
       <c r="AG8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH8">
         <v>1</v>
@@ -5138,25 +5066,25 @@
         <v>9</v>
       </c>
       <c r="AL8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN8">
         <v>90</v>
       </c>
       <c r="AO8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP8">
         <v>90</v>
       </c>
       <c r="AQ8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS8">
         <v>1</v>
@@ -5168,13 +5096,13 @@
         <v>5500000</v>
       </c>
       <c r="AV8" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="AW8">
         <v>55</v>
       </c>
       <c r="AX8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY8">
         <v>1</v>
@@ -5189,25 +5117,25 @@
         <v>9</v>
       </c>
       <c r="BC8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE8">
         <v>90</v>
       </c>
       <c r="BF8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG8">
         <v>90</v>
       </c>
       <c r="BH8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ8">
         <v>1</v>
@@ -5216,16 +5144,16 @@
         <v>1</v>
       </c>
       <c r="BL8">
-        <v>2100000</v>
+        <v>1800000</v>
       </c>
       <c r="BM8" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="BN8">
         <v>55</v>
       </c>
       <c r="BO8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -5240,25 +5168,25 @@
         <v>9</v>
       </c>
       <c r="BT8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV8">
         <v>90</v>
       </c>
       <c r="BW8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX8">
         <v>90</v>
       </c>
       <c r="BY8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA8">
         <v>1</v>
@@ -5267,22 +5195,22 @@
         <v>1</v>
       </c>
       <c r="CC8">
-        <v>4700</v>
+        <v>4000</v>
       </c>
       <c r="CD8" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE8">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF8">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG8" t="b">
         <v>1</v>
       </c>
       <c r="CH8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI8">
         <v>1</v>
@@ -5297,28 +5225,28 @@
         <v>9</v>
       </c>
       <c r="CM8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO8">
         <v>90</v>
       </c>
       <c r="CP8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ8">
         <v>90</v>
       </c>
       <c r="CR8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT8" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU8">
         <v>0</v>
@@ -5327,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA8">
         <v>1</v>
@@ -5342,28 +5270,28 @@
         <v>9</v>
       </c>
       <c r="DE8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG8">
         <v>90</v>
       </c>
       <c r="DH8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI8">
         <v>90</v>
       </c>
       <c r="DJ8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL8" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM8">
         <v>0</v>
@@ -5372,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="DR8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS8">
         <v>1</v>
@@ -5387,28 +5315,28 @@
         <v>9</v>
       </c>
       <c r="DW8" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY8">
         <v>90</v>
       </c>
       <c r="DZ8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA8">
         <v>90</v>
       </c>
       <c r="EB8" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC8" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE8">
         <v>0</v>
@@ -5417,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="EI8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ8">
         <v>1</v>
@@ -5426,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="EL8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="EM8">
         <v>100000</v>
@@ -5453,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="FD8" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE8">
         <v>0.05</v>
@@ -5468,13 +5396,13 @@
         <v>8.5</v>
       </c>
       <c r="FI8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL8">
         <v>1</v>
@@ -5483,10 +5411,10 @@
         <v>1</v>
       </c>
       <c r="FN8">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="FO8">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="FP8">
         <v>0.95</v>
@@ -5501,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="FT8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU8">
         <v>0</v>
@@ -5510,48 +5438,66 @@
         <v>0</v>
       </c>
       <c r="GA8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD8">
         <v>86400</v>
       </c>
       <c r="GE8" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF8" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF8">
+        <v>86400</v>
       </c>
       <c r="GG8" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH8" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI8">
+        <v>249</v>
+      </c>
+      <c r="GI8" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ8" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK8" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL8" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM8" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN8">
         <v>86400</v>
       </c>
-      <c r="GJ8">
+      <c r="GO8">
+        <v>86400</v>
+      </c>
+      <c r="GP8">
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:198">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -5560,7 +5506,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -5572,13 +5518,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3296000</v>
+        <v>3648000</v>
       </c>
       <c r="O9" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -5593,25 +5539,25 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W9">
         <v>90</v>
       </c>
       <c r="X9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y9">
         <v>90</v>
       </c>
       <c r="Z9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -5623,7 +5569,7 @@
         <v>6</v>
       </c>
       <c r="AG9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH9">
         <v>1</v>
@@ -5638,25 +5584,25 @@
         <v>9</v>
       </c>
       <c r="AL9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN9">
         <v>90</v>
       </c>
       <c r="AO9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP9">
         <v>90</v>
       </c>
       <c r="AQ9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS9">
         <v>1</v>
@@ -5665,16 +5611,16 @@
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AV9" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="AW9">
         <v>35</v>
       </c>
       <c r="AX9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY9">
         <v>1</v>
@@ -5689,25 +5635,25 @@
         <v>9</v>
       </c>
       <c r="BC9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE9">
         <v>90</v>
       </c>
       <c r="BF9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG9">
         <v>90</v>
       </c>
       <c r="BH9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ9">
         <v>1</v>
@@ -5716,16 +5662,16 @@
         <v>1</v>
       </c>
       <c r="BL9">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
       <c r="BM9" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="BN9">
         <v>55</v>
       </c>
       <c r="BO9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP9">
         <v>1</v>
@@ -5740,25 +5686,25 @@
         <v>9</v>
       </c>
       <c r="BT9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV9">
         <v>90</v>
       </c>
       <c r="BW9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX9">
         <v>90</v>
       </c>
       <c r="BY9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA9">
         <v>1</v>
@@ -5767,10 +5713,10 @@
         <v>1</v>
       </c>
       <c r="CC9">
-        <v>5200</v>
+        <v>5600</v>
       </c>
       <c r="CD9" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE9">
         <v>0</v>
@@ -5782,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="CH9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI9">
         <v>1</v>
@@ -5797,28 +5743,28 @@
         <v>9</v>
       </c>
       <c r="CM9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO9">
         <v>90</v>
       </c>
       <c r="CP9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ9">
         <v>90</v>
       </c>
       <c r="CR9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU9">
         <v>0</v>
@@ -5827,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA9">
         <v>1</v>
@@ -5842,28 +5788,28 @@
         <v>9</v>
       </c>
       <c r="DE9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG9">
         <v>90</v>
       </c>
       <c r="DH9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI9">
         <v>90</v>
       </c>
       <c r="DJ9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL9" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM9">
         <v>0</v>
@@ -5872,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="DR9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS9">
         <v>1</v>
@@ -5887,28 +5833,28 @@
         <v>9</v>
       </c>
       <c r="DW9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY9">
         <v>90</v>
       </c>
       <c r="DZ9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA9">
         <v>90</v>
       </c>
       <c r="EB9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE9">
         <v>0</v>
@@ -5917,16 +5863,16 @@
         <v>0</v>
       </c>
       <c r="EI9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ9">
         <v>1</v>
       </c>
       <c r="EK9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EL9" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="EM9">
         <v>75000</v>
@@ -5952,35 +5898,8 @@
       <c r="ET9" t="b">
         <v>0</v>
       </c>
-      <c r="EU9" t="s">
-        <v>230</v>
-      </c>
-      <c r="EV9">
-        <v>75000</v>
-      </c>
-      <c r="EW9">
-        <v>7200</v>
-      </c>
-      <c r="EX9">
-        <v>11000</v>
-      </c>
-      <c r="EY9">
-        <v>100000</v>
-      </c>
-      <c r="EZ9">
-        <v>90000</v>
-      </c>
-      <c r="FA9">
-        <v>80000</v>
-      </c>
-      <c r="FB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC9" t="b">
-        <v>0</v>
-      </c>
       <c r="FD9" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE9">
         <v>0.05</v>
@@ -5995,13 +5914,13 @@
         <v>8.5</v>
       </c>
       <c r="FI9" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ9" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL9">
         <v>1</v>
@@ -6010,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="FN9">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="FO9">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="FP9">
         <v>0.95</v>
@@ -6028,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="FT9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU9">
         <v>0</v>
@@ -6037,48 +5956,66 @@
         <v>0</v>
       </c>
       <c r="GA9" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB9" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC9" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD9">
         <v>86400</v>
       </c>
       <c r="GE9" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF9" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF9">
+        <v>86400</v>
       </c>
       <c r="GG9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH9" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI9">
+        <v>249</v>
+      </c>
+      <c r="GI9" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ9" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK9" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL9" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM9" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN9">
         <v>86400</v>
       </c>
-      <c r="GJ9">
+      <c r="GO9">
+        <v>86400</v>
+      </c>
+      <c r="GP9">
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:198">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -6087,7 +6024,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -6099,13 +6036,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>5527000</v>
+        <v>3863000</v>
       </c>
       <c r="O10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="P10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -6120,25 +6057,25 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W10">
         <v>90</v>
       </c>
       <c r="X10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y10">
         <v>90</v>
       </c>
       <c r="Z10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -6150,7 +6087,7 @@
         <v>6</v>
       </c>
       <c r="AG10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH10">
         <v>1</v>
@@ -6165,25 +6102,25 @@
         <v>9</v>
       </c>
       <c r="AL10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN10">
         <v>90</v>
       </c>
       <c r="AO10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP10">
         <v>90</v>
       </c>
       <c r="AQ10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS10">
         <v>1</v>
@@ -6192,16 +6129,16 @@
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="AV10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AW10">
         <v>35</v>
       </c>
       <c r="AX10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY10">
         <v>1</v>
@@ -6216,25 +6153,25 @@
         <v>9</v>
       </c>
       <c r="BC10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE10">
         <v>90</v>
       </c>
       <c r="BF10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG10">
         <v>90</v>
       </c>
       <c r="BH10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ10">
         <v>1</v>
@@ -6246,13 +6183,13 @@
         <v>2400000</v>
       </c>
       <c r="BM10" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="BN10">
         <v>55</v>
       </c>
       <c r="BO10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -6267,25 +6204,25 @@
         <v>9</v>
       </c>
       <c r="BT10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV10">
         <v>90</v>
       </c>
       <c r="BW10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX10">
         <v>90</v>
       </c>
       <c r="BY10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA10">
         <v>1</v>
@@ -6294,22 +6231,22 @@
         <v>1</v>
       </c>
       <c r="CC10">
-        <v>7000</v>
+        <v>5800</v>
       </c>
       <c r="CD10" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE10">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG10" t="b">
         <v>1</v>
       </c>
       <c r="CH10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI10">
         <v>1</v>
@@ -6324,28 +6261,28 @@
         <v>9</v>
       </c>
       <c r="CM10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO10">
         <v>90</v>
       </c>
       <c r="CP10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ10">
         <v>90</v>
       </c>
       <c r="CR10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT10" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU10">
         <v>0</v>
@@ -6354,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA10">
         <v>1</v>
@@ -6369,28 +6306,28 @@
         <v>9</v>
       </c>
       <c r="DE10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG10">
         <v>90</v>
       </c>
       <c r="DH10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI10">
         <v>90</v>
       </c>
       <c r="DJ10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL10" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM10">
         <v>0</v>
@@ -6399,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="DR10" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS10">
         <v>1</v>
@@ -6414,28 +6351,28 @@
         <v>9</v>
       </c>
       <c r="DW10" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY10">
         <v>90</v>
       </c>
       <c r="DZ10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA10">
         <v>90</v>
       </c>
       <c r="EB10" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC10" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE10">
         <v>0</v>
@@ -6444,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="EI10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ10">
         <v>1</v>
@@ -6453,19 +6390,19 @@
         <v>1</v>
       </c>
       <c r="EL10" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="EM10">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EN10">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EO10">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="EP10">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="EQ10">
         <v>0.9</v>
@@ -6480,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="FD10" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE10">
         <v>0.05</v>
@@ -6495,13 +6432,13 @@
         <v>8.5</v>
       </c>
       <c r="FI10" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ10" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL10">
         <v>1</v>
@@ -6510,10 +6447,10 @@
         <v>1</v>
       </c>
       <c r="FN10">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="FO10">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="FP10">
         <v>0.95</v>
@@ -6528,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="FT10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU10">
         <v>0</v>
@@ -6537,48 +6474,66 @@
         <v>0</v>
       </c>
       <c r="GA10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB10" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC10" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD10">
         <v>86400</v>
       </c>
       <c r="GE10" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF10" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF10">
+        <v>86400</v>
       </c>
       <c r="GG10" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH10" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI10">
+        <v>249</v>
+      </c>
+      <c r="GI10" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ10" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK10" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL10" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM10" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN10">
         <v>86400</v>
       </c>
-      <c r="GJ10">
+      <c r="GO10">
+        <v>86400</v>
+      </c>
+      <c r="GP10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:192" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:198">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -6587,7 +6542,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -6599,13 +6554,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>2896000</v>
+        <v>3125000</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -6620,25 +6575,25 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="V11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="W11">
         <v>90</v>
       </c>
       <c r="X11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="Y11">
         <v>90</v>
       </c>
       <c r="Z11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AA11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -6650,7 +6605,7 @@
         <v>6</v>
       </c>
       <c r="AG11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AH11">
         <v>1</v>
@@ -6665,25 +6620,25 @@
         <v>9</v>
       </c>
       <c r="AL11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AM11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AN11">
         <v>90</v>
       </c>
       <c r="AO11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AP11">
         <v>90</v>
       </c>
       <c r="AQ11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AR11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AS11">
         <v>1</v>
@@ -6692,16 +6647,16 @@
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="AV11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AW11">
         <v>55</v>
       </c>
       <c r="AX11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AY11">
         <v>1</v>
@@ -6716,25 +6671,25 @@
         <v>9</v>
       </c>
       <c r="BC11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BD11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BE11">
         <v>90</v>
       </c>
       <c r="BF11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BG11">
         <v>90</v>
       </c>
       <c r="BH11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BI11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="BJ11">
         <v>1</v>
@@ -6743,16 +6698,16 @@
         <v>1</v>
       </c>
       <c r="BL11">
-        <v>2800000</v>
+        <v>2400000</v>
       </c>
       <c r="BM11" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="BN11">
         <v>55</v>
       </c>
       <c r="BO11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="BP11">
         <v>1</v>
@@ -6767,25 +6722,25 @@
         <v>9</v>
       </c>
       <c r="BT11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="BU11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BV11">
         <v>90</v>
       </c>
       <c r="BW11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BX11">
         <v>90</v>
       </c>
       <c r="BY11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="BZ11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CA11">
         <v>1</v>
@@ -6794,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="CC11">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="CD11" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="CE11">
         <v>0</v>
@@ -6809,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="CH11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="CI11">
         <v>1</v>
@@ -6824,28 +6779,28 @@
         <v>9</v>
       </c>
       <c r="CM11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="CN11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CO11">
         <v>90</v>
       </c>
       <c r="CP11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CQ11">
         <v>90</v>
       </c>
       <c r="CR11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="CS11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="CT11" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="CU11">
         <v>0</v>
@@ -6854,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="CZ11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DA11">
         <v>1</v>
@@ -6869,28 +6824,28 @@
         <v>9</v>
       </c>
       <c r="DE11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DF11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DG11">
         <v>90</v>
       </c>
       <c r="DH11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DI11">
         <v>90</v>
       </c>
       <c r="DJ11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DK11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="DL11" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="DM11">
         <v>0</v>
@@ -6899,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="DR11" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="DS11">
         <v>1</v>
@@ -6914,28 +6869,28 @@
         <v>9</v>
       </c>
       <c r="DW11" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="DX11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="DY11">
         <v>90</v>
       </c>
       <c r="DZ11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EA11">
         <v>90</v>
       </c>
       <c r="EB11" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="EC11" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="ED11" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EE11">
         <v>0</v>
@@ -6944,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="EI11" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="EJ11">
         <v>1</v>
@@ -6953,19 +6908,19 @@
         <v>1</v>
       </c>
       <c r="EL11" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="EM11">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EN11">
         <v>7200</v>
       </c>
       <c r="EO11">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EP11">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EQ11">
         <v>0.9</v>
@@ -6980,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="FD11" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="FE11">
         <v>0.05</v>
@@ -6995,13 +6950,13 @@
         <v>8.5</v>
       </c>
       <c r="FI11" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="FJ11" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="FK11" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FL11">
         <v>1</v>
@@ -7010,10 +6965,10 @@
         <v>1</v>
       </c>
       <c r="FN11">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="FO11">
-        <v>2900</v>
+        <v>3100</v>
       </c>
       <c r="FP11">
         <v>0.95</v>
@@ -7028,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="FT11" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="FU11">
         <v>0</v>
@@ -7037,33 +6992,51 @@
         <v>0</v>
       </c>
       <c r="GA11" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="GB11" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GC11" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="GD11">
         <v>86400</v>
       </c>
       <c r="GE11" t="s">
-        <v>240</v>
-      </c>
-      <c r="GF11" t="s">
-        <v>241</v>
+        <v>248</v>
+      </c>
+      <c r="GF11">
+        <v>86400</v>
       </c>
       <c r="GG11" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="GH11" t="s">
-        <v>242</v>
-      </c>
-      <c r="GI11">
+        <v>249</v>
+      </c>
+      <c r="GI11" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ11" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK11" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL11" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM11" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN11">
         <v>86400</v>
       </c>
-      <c r="GJ11">
+      <c r="GO11">
+        <v>86400</v>
+      </c>
+      <c r="GP11">
         <v>3600</v>
       </c>
     </row>
@@ -7073,11 +7046,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:GM1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:GS1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:195" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:201">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7091,13 +7064,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -7659,6 +7632,24 @@
       </c>
       <c r="GM1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="GN1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="GO1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="GP1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="GQ1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="GR1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="GS1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -7667,11 +7658,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:ED1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:EJ1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:134" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:140">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7685,7 +7676,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7997,22 +7988,22 @@
         <v>158</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="DJ1" s="1" t="s">
         <v>163</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="DL1" s="1" t="s">
         <v>165</v>
@@ -8070,6 +8061,24 @@
       </c>
       <c r="ED1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="EE1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -8078,11 +8087,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:EM1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:ES1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:143" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:149">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8096,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -8508,6 +8517,24 @@
       </c>
       <c r="EM1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="EN1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="EO1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -8516,11 +8543,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B1:CB1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:CH1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:80" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:86">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8757,6 +8784,24 @@
       </c>
       <c r="CB1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -8765,11 +8810,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B1:AP1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:AV1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:42" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:48">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8813,58 +8858,58 @@
         <v>174</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>182</v>
@@ -8892,6 +8937,24 @@
       </c>
       <c r="AP1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1498" uniqueCount="278">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -588,40 +588,61 @@
     <t>ems/market/fcast/wholesale</t>
   </si>
   <si>
-    <t>ems/fcasts/retraining_period</t>
-  </si>
-  <si>
-    <t>ems/fcasts/update_period</t>
-  </si>
-  <si>
-    <t>1lIPbXNxrtcHbuq</t>
-  </si>
-  <si>
-    <t>1dMs8E6si6MYUqb</t>
-  </si>
-  <si>
-    <t>rZwqUNsMzDDl8Hy</t>
-  </si>
-  <si>
-    <t>n0w3DxDsc0KicUT</t>
-  </si>
-  <si>
-    <t>f9HuzbnqNCXzIlC</t>
-  </si>
-  <si>
-    <t>QRbLyCB6X1yb4BY</t>
-  </si>
-  <si>
-    <t>DbC1ILMdile5yIl</t>
-  </si>
-  <si>
-    <t>MdfdWyPPzFrkYvW</t>
-  </si>
-  <si>
-    <t>Nj2p967l9Vt9bjg</t>
-  </si>
-  <si>
-    <t>DubKsoLCiW6BzEv</t>
+    <t>ems/market/fcast/retailer/energy</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/grid/local</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/grid/retail</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/levies</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/balancing</t>
+  </si>
+  <si>
+    <t>ems/fcasts/horizon</t>
+  </si>
+  <si>
+    <t>ems/fcasts/retraining</t>
+  </si>
+  <si>
+    <t>ems/fcasts/update</t>
+  </si>
+  <si>
+    <t>6qwgumJMmVbXDI7</t>
+  </si>
+  <si>
+    <t>4nnq3O1PEZp6dWM</t>
+  </si>
+  <si>
+    <t>BnqcT6hxtti70uH</t>
+  </si>
+  <si>
+    <t>9eFSrzr91OSowvp</t>
+  </si>
+  <si>
+    <t>0AzUwdxZZptibiO</t>
+  </si>
+  <si>
+    <t>geow5OY76tEO7e0</t>
+  </si>
+  <si>
+    <t>KATyPT8EDCK0ESt</t>
+  </si>
+  <si>
+    <t>E8G6EOAJkfvUjJH</t>
+  </si>
+  <si>
+    <t>NXvRT9GPioxZO0u</t>
+  </si>
+  <si>
+    <t>206Y66Ba67yqGSQ</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
   </si>
   <si>
     <t>hh_3564_0.csv</t>
@@ -630,24 +651,21 @@
     <t>hh_5527_0.csv</t>
   </si>
   <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2012_3.csv</t>
+  </si>
+  <si>
+    <t>hh_2959_0.csv</t>
+  </si>
+  <si>
     <t>hh_3648_0.csv</t>
   </si>
   <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
     <t>hh_3125_0.csv</t>
   </si>
   <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3863_0.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -660,6 +678,48 @@
     <t>[1, 0, 0]</t>
   </si>
   <si>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2012_3.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
     <t>pv_config.json</t>
   </si>
   <si>
@@ -669,16 +729,28 @@
     <t>local</t>
   </si>
   <si>
-    <t>ev_freetime_1.csv</t>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_44.csv</t>
   </si>
   <si>
     <t>ev_fulltime_41.csv</t>
   </si>
   <si>
-    <t>ev_parttime_90.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_0.csv</t>
+    <t>ev_fulltime_49.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -696,10 +768,10 @@
     <t>['linear']</t>
   </si>
   <si>
-    <t>[10800, 21600, 32400, 43200]</t>
-  </si>
-  <si>
     <t>naive</t>
+  </si>
+  <si>
+    <t>['naive', 'naive']</t>
   </si>
   <si>
     <t>general/sub_id</t>
@@ -1138,10 +1210,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:GJ11"/>
+  <dimension ref="A1:GP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:192">
+    <row r="1" spans="1:198">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1715,19 +1787,37 @@
       <c r="GJ1" s="1" t="s">
         <v>190</v>
       </c>
+      <c r="GK1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="GL1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="GM1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="GN1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="GO1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="GP1" s="1" t="s">
+        <v>196</v>
+      </c>
     </row>
-    <row r="2" spans="1:192">
+    <row r="2" spans="1:198">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -1736,7 +1826,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1748,13 +1838,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>3564000</v>
+        <v>3863000</v>
       </c>
       <c r="O2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -1769,25 +1859,25 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W2">
         <v>90</v>
       </c>
       <c r="X2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y2">
         <v>90</v>
       </c>
       <c r="Z2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB2">
         <v>0</v>
@@ -1799,7 +1889,7 @@
         <v>6</v>
       </c>
       <c r="AG2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH2">
         <v>1</v>
@@ -1814,34 +1904,43 @@
         <v>9</v>
       </c>
       <c r="AL2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN2">
         <v>90</v>
       </c>
       <c r="AO2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP2">
         <v>90</v>
       </c>
       <c r="AQ2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <v>19500000</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>219</v>
+      </c>
+      <c r="AW2">
+        <v>55</v>
       </c>
       <c r="AX2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY2">
         <v>1</v>
@@ -1856,34 +1955,43 @@
         <v>9</v>
       </c>
       <c r="BC2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE2">
         <v>90</v>
       </c>
       <c r="BF2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG2">
         <v>90</v>
       </c>
       <c r="BH2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL2">
+        <v>3200000</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN2">
+        <v>55</v>
       </c>
       <c r="BO2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP2">
         <v>1</v>
@@ -1898,25 +2006,25 @@
         <v>9</v>
       </c>
       <c r="BT2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV2">
         <v>90</v>
       </c>
       <c r="BW2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA2">
         <v>1</v>
@@ -1925,22 +2033,22 @@
         <v>1</v>
       </c>
       <c r="CC2">
-        <v>5200</v>
+        <v>6500</v>
       </c>
       <c r="CD2" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CF2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="CG2" t="b">
         <v>1</v>
       </c>
       <c r="CH2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI2">
         <v>1</v>
@@ -1955,28 +2063,28 @@
         <v>9</v>
       </c>
       <c r="CM2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO2">
         <v>90</v>
       </c>
       <c r="CP2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ2">
         <v>90</v>
       </c>
       <c r="CR2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU2">
         <v>0</v>
@@ -1985,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="CZ2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA2">
         <v>1</v>
@@ -2000,28 +2108,28 @@
         <v>9</v>
       </c>
       <c r="DE2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG2">
         <v>90</v>
       </c>
       <c r="DH2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI2">
         <v>90</v>
       </c>
       <c r="DJ2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL2" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM2">
         <v>0</v>
@@ -2030,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="DR2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS2">
         <v>1</v>
@@ -2045,28 +2153,28 @@
         <v>9</v>
       </c>
       <c r="DW2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY2">
         <v>90</v>
       </c>
       <c r="DZ2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA2">
         <v>90</v>
       </c>
       <c r="EB2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE2">
         <v>0</v>
@@ -2075,16 +2183,43 @@
         <v>0</v>
       </c>
       <c r="EI2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK2">
+        <v>1</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>236</v>
+      </c>
+      <c r="EM2">
+        <v>100000</v>
+      </c>
+      <c r="EN2">
+        <v>11000</v>
+      </c>
+      <c r="EO2">
+        <v>22000</v>
+      </c>
+      <c r="EP2">
+        <v>200000</v>
+      </c>
+      <c r="EQ2">
+        <v>0.9</v>
+      </c>
+      <c r="ER2">
+        <v>0.8</v>
+      </c>
+      <c r="ES2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="b">
         <v>0</v>
       </c>
       <c r="FD2" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE2">
         <v>0.05</v>
@@ -2099,13 +2234,13 @@
         <v>8.5</v>
       </c>
       <c r="FI2" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ2" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL2">
         <v>1</v>
@@ -2114,10 +2249,10 @@
         <v>1</v>
       </c>
       <c r="FN2">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="FO2">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="FP2">
         <v>0.95</v>
@@ -2132,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="FT2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU2">
         <v>0</v>
@@ -2141,42 +2276,60 @@
         <v>0</v>
       </c>
       <c r="GA2" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB2" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC2" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD2">
         <v>86400</v>
       </c>
       <c r="GE2" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF2" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF2">
+        <v>86400</v>
       </c>
       <c r="GG2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH2" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI2">
+        <v>249</v>
+      </c>
+      <c r="GI2" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ2" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK2" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL2" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM2" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN2">
         <v>86400</v>
       </c>
-      <c r="GJ2">
+      <c r="GO2">
+        <v>86400</v>
+      </c>
+      <c r="GP2">
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:192">
+    <row r="3" spans="1:198">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -2203,13 +2356,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>5527000</v>
+        <v>3564000</v>
       </c>
       <c r="O3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2224,25 +2377,25 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W3">
         <v>90</v>
       </c>
       <c r="X3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y3">
         <v>90</v>
       </c>
       <c r="Z3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB3">
         <v>0</v>
@@ -2254,7 +2407,7 @@
         <v>6</v>
       </c>
       <c r="AG3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH3">
         <v>1</v>
@@ -2269,34 +2422,43 @@
         <v>9</v>
       </c>
       <c r="AL3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN3">
         <v>90</v>
       </c>
       <c r="AO3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP3">
         <v>90</v>
       </c>
       <c r="AQ3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU3">
+        <v>5500000</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>220</v>
+      </c>
+      <c r="AW3">
+        <v>55</v>
       </c>
       <c r="AX3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY3">
         <v>1</v>
@@ -2311,34 +2473,43 @@
         <v>9</v>
       </c>
       <c r="BC3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE3">
         <v>90</v>
       </c>
       <c r="BF3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG3">
         <v>90</v>
       </c>
       <c r="BH3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL3">
+        <v>2400000</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN3">
+        <v>55</v>
       </c>
       <c r="BO3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP3">
         <v>1</v>
@@ -2353,34 +2524,49 @@
         <v>9</v>
       </c>
       <c r="BT3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV3">
         <v>90</v>
       </c>
       <c r="BW3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX3">
         <v>90</v>
       </c>
       <c r="BY3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CC3">
+        <v>5800</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>233</v>
+      </c>
+      <c r="CE3">
+        <v>-20</v>
+      </c>
+      <c r="CF3">
+        <v>50</v>
+      </c>
+      <c r="CG3" t="b">
+        <v>1</v>
       </c>
       <c r="CH3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI3">
         <v>1</v>
@@ -2395,28 +2581,28 @@
         <v>9</v>
       </c>
       <c r="CM3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO3">
         <v>90</v>
       </c>
       <c r="CP3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ3">
         <v>90</v>
       </c>
       <c r="CR3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT3" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU3">
         <v>0</v>
@@ -2425,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="CZ3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA3">
         <v>1</v>
@@ -2440,28 +2626,28 @@
         <v>9</v>
       </c>
       <c r="DE3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG3">
         <v>90</v>
       </c>
       <c r="DH3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI3">
         <v>90</v>
       </c>
       <c r="DJ3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL3" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM3">
         <v>0</v>
@@ -2470,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="DR3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS3">
         <v>1</v>
@@ -2485,28 +2671,28 @@
         <v>9</v>
       </c>
       <c r="DW3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY3">
         <v>90</v>
       </c>
       <c r="DZ3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA3">
         <v>90</v>
       </c>
       <c r="EB3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED3" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE3">
         <v>0</v>
@@ -2515,43 +2701,70 @@
         <v>0</v>
       </c>
       <c r="EI3" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ3">
         <v>1</v>
       </c>
       <c r="EK3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EL3" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="EM3">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="EN3">
         <v>7200</v>
       </c>
       <c r="EO3">
+        <v>11000</v>
+      </c>
+      <c r="EP3">
+        <v>100000</v>
+      </c>
+      <c r="EQ3">
+        <v>0.9</v>
+      </c>
+      <c r="ER3">
+        <v>0.8</v>
+      </c>
+      <c r="ES3" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET3" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU3" t="s">
+        <v>243</v>
+      </c>
+      <c r="EV3">
+        <v>50000</v>
+      </c>
+      <c r="EW3">
         <v>7200</v>
       </c>
-      <c r="EP3">
+      <c r="EX3">
+        <v>7200</v>
+      </c>
+      <c r="EY3">
         <v>50000</v>
       </c>
-      <c r="EQ3">
-        <v>90000</v>
-      </c>
-      <c r="ER3">
-        <v>80000</v>
-      </c>
-      <c r="ES3" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET3" t="b">
+      <c r="EZ3">
+        <v>0.9</v>
+      </c>
+      <c r="FA3">
+        <v>0.8</v>
+      </c>
+      <c r="FB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC3" t="b">
         <v>0</v>
       </c>
       <c r="FD3" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE3">
         <v>0.05</v>
@@ -2566,22 +2779,40 @@
         <v>8.5</v>
       </c>
       <c r="FI3" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ3" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK3" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM3">
+        <v>1</v>
+      </c>
+      <c r="FN3">
+        <v>3600</v>
+      </c>
+      <c r="FO3">
+        <v>3600</v>
+      </c>
+      <c r="FP3">
+        <v>0.95</v>
+      </c>
+      <c r="FQ3">
+        <v>0.1</v>
+      </c>
+      <c r="FR3" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS3" t="b">
         <v>0</v>
       </c>
       <c r="FT3" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU3">
         <v>0</v>
@@ -2590,48 +2821,66 @@
         <v>0</v>
       </c>
       <c r="GA3" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB3" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC3" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD3">
         <v>86400</v>
       </c>
       <c r="GE3" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF3" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF3">
+        <v>86400</v>
       </c>
       <c r="GG3" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH3" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI3">
+        <v>249</v>
+      </c>
+      <c r="GI3" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ3" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK3" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL3" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM3" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN3">
         <v>86400</v>
       </c>
-      <c r="GJ3">
+      <c r="GO3">
+        <v>86400</v>
+      </c>
+      <c r="GP3">
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:192">
+    <row r="4" spans="1:198">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -2640,7 +2889,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2652,13 +2901,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>3648000</v>
+        <v>5527000</v>
       </c>
       <c r="O4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -2673,25 +2922,25 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W4">
         <v>90</v>
       </c>
       <c r="X4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y4">
         <v>90</v>
       </c>
       <c r="Z4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -2703,7 +2952,7 @@
         <v>6</v>
       </c>
       <c r="AG4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH4">
         <v>1</v>
@@ -2718,34 +2967,43 @@
         <v>9</v>
       </c>
       <c r="AL4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN4">
         <v>90</v>
       </c>
       <c r="AO4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP4">
         <v>90</v>
       </c>
       <c r="AQ4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <v>19500000</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>221</v>
+      </c>
+      <c r="AW4">
+        <v>55</v>
       </c>
       <c r="AX4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY4">
         <v>1</v>
@@ -2760,34 +3018,43 @@
         <v>9</v>
       </c>
       <c r="BC4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE4">
         <v>90</v>
       </c>
       <c r="BF4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG4">
         <v>90</v>
       </c>
       <c r="BH4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL4">
+        <v>2400000</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>228</v>
+      </c>
+      <c r="BN4">
+        <v>55</v>
       </c>
       <c r="BO4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP4">
         <v>1</v>
@@ -2802,25 +3069,25 @@
         <v>9</v>
       </c>
       <c r="BT4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV4">
         <v>90</v>
       </c>
       <c r="BW4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX4">
         <v>90</v>
       </c>
       <c r="BY4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA4">
         <v>1</v>
@@ -2829,22 +3096,22 @@
         <v>1</v>
       </c>
       <c r="CC4">
-        <v>5200</v>
+        <v>7000</v>
       </c>
       <c r="CD4" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE4">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG4" t="b">
         <v>1</v>
       </c>
       <c r="CH4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI4">
         <v>1</v>
@@ -2859,28 +3126,28 @@
         <v>9</v>
       </c>
       <c r="CM4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO4">
         <v>90</v>
       </c>
       <c r="CP4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ4">
         <v>90</v>
       </c>
       <c r="CR4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT4" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU4">
         <v>0</v>
@@ -2889,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="CZ4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA4">
         <v>1</v>
@@ -2904,28 +3171,28 @@
         <v>9</v>
       </c>
       <c r="DE4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG4">
         <v>90</v>
       </c>
       <c r="DH4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI4">
         <v>90</v>
       </c>
       <c r="DJ4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL4" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM4">
         <v>0</v>
@@ -2934,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="DR4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS4">
         <v>1</v>
@@ -2949,28 +3216,28 @@
         <v>9</v>
       </c>
       <c r="DW4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY4">
         <v>90</v>
       </c>
       <c r="DZ4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA4">
         <v>90</v>
       </c>
       <c r="EB4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED4" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE4">
         <v>0</v>
@@ -2979,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="EI4" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ4">
         <v>1</v>
@@ -2988,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="EL4" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="EM4">
         <v>75000</v>
@@ -3003,10 +3270,10 @@
         <v>100000</v>
       </c>
       <c r="EQ4">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER4">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES4" t="b">
         <v>0</v>
@@ -3015,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="FD4" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE4">
         <v>0.05</v>
@@ -3030,22 +3297,40 @@
         <v>8.5</v>
       </c>
       <c r="FI4" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ4" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK4" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM4">
+        <v>1</v>
+      </c>
+      <c r="FN4">
+        <v>5500</v>
+      </c>
+      <c r="FO4">
+        <v>5500</v>
+      </c>
+      <c r="FP4">
+        <v>0.95</v>
+      </c>
+      <c r="FQ4">
+        <v>0.1</v>
+      </c>
+      <c r="FR4" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="b">
         <v>0</v>
       </c>
       <c r="FT4" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU4">
         <v>0</v>
@@ -3054,48 +3339,66 @@
         <v>0</v>
       </c>
       <c r="GA4" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB4" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC4" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD4">
         <v>86400</v>
       </c>
       <c r="GE4" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF4" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF4">
+        <v>86400</v>
       </c>
       <c r="GG4" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH4" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI4">
+        <v>249</v>
+      </c>
+      <c r="GI4" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ4" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK4" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL4" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM4" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN4">
         <v>86400</v>
       </c>
-      <c r="GJ4">
+      <c r="GO4">
+        <v>86400</v>
+      </c>
+      <c r="GP4">
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:192">
+    <row r="5" spans="1:198">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3104,7 +3407,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3119,10 +3422,10 @@
         <v>3296000</v>
       </c>
       <c r="O5" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -3137,25 +3440,25 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W5">
         <v>90</v>
       </c>
       <c r="X5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y5">
         <v>90</v>
       </c>
       <c r="Z5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -3167,7 +3470,7 @@
         <v>6</v>
       </c>
       <c r="AG5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH5">
         <v>1</v>
@@ -3182,34 +3485,43 @@
         <v>9</v>
       </c>
       <c r="AL5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN5">
         <v>90</v>
       </c>
       <c r="AO5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP5">
         <v>90</v>
       </c>
       <c r="AQ5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU5">
+        <v>5500000</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>222</v>
+      </c>
+      <c r="AW5">
+        <v>55</v>
       </c>
       <c r="AX5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY5">
         <v>1</v>
@@ -3224,34 +3536,43 @@
         <v>9</v>
       </c>
       <c r="BC5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE5">
         <v>90</v>
       </c>
       <c r="BF5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG5">
         <v>90</v>
       </c>
       <c r="BH5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL5">
+        <v>2100000</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>229</v>
+      </c>
+      <c r="BN5">
+        <v>55</v>
       </c>
       <c r="BO5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP5">
         <v>1</v>
@@ -3266,25 +3587,25 @@
         <v>9</v>
       </c>
       <c r="BT5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV5">
         <v>90</v>
       </c>
       <c r="BW5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX5">
         <v>90</v>
       </c>
       <c r="BY5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA5">
         <v>1</v>
@@ -3293,10 +3614,10 @@
         <v>1</v>
       </c>
       <c r="CC5">
-        <v>5800</v>
+        <v>4200</v>
       </c>
       <c r="CD5" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE5">
         <v>0</v>
@@ -3308,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="CH5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI5">
         <v>1</v>
@@ -3323,28 +3644,28 @@
         <v>9</v>
       </c>
       <c r="CM5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO5">
         <v>90</v>
       </c>
       <c r="CP5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ5">
         <v>90</v>
       </c>
       <c r="CR5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT5" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU5">
         <v>0</v>
@@ -3353,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA5">
         <v>1</v>
@@ -3368,28 +3689,28 @@
         <v>9</v>
       </c>
       <c r="DE5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG5">
         <v>90</v>
       </c>
       <c r="DH5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI5">
         <v>90</v>
       </c>
       <c r="DJ5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL5" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM5">
         <v>0</v>
@@ -3398,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="DR5" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS5">
         <v>1</v>
@@ -3413,28 +3734,28 @@
         <v>9</v>
       </c>
       <c r="DW5" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY5">
         <v>90</v>
       </c>
       <c r="DZ5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA5">
         <v>90</v>
       </c>
       <c r="EB5" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC5" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED5" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE5">
         <v>0</v>
@@ -3443,16 +3764,43 @@
         <v>0</v>
       </c>
       <c r="EI5" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK5">
+        <v>1</v>
+      </c>
+      <c r="EL5" t="s">
+        <v>239</v>
+      </c>
+      <c r="EM5">
+        <v>75000</v>
+      </c>
+      <c r="EN5">
+        <v>7200</v>
+      </c>
+      <c r="EO5">
+        <v>11000</v>
+      </c>
+      <c r="EP5">
+        <v>100000</v>
+      </c>
+      <c r="EQ5">
+        <v>0.9</v>
+      </c>
+      <c r="ER5">
+        <v>0.8</v>
+      </c>
+      <c r="ES5" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="b">
         <v>0</v>
       </c>
       <c r="FD5" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE5">
         <v>0.05</v>
@@ -3467,13 +3815,13 @@
         <v>8.5</v>
       </c>
       <c r="FI5" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ5" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK5" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL5">
         <v>1</v>
@@ -3500,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="FT5" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU5">
         <v>0</v>
@@ -3509,42 +3857,60 @@
         <v>0</v>
       </c>
       <c r="GA5" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB5" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC5" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD5">
         <v>86400</v>
       </c>
       <c r="GE5" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF5" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF5">
+        <v>86400</v>
       </c>
       <c r="GG5" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH5" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI5">
+        <v>249</v>
+      </c>
+      <c r="GI5" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ5" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK5" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL5" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM5" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN5">
         <v>86400</v>
       </c>
-      <c r="GJ5">
+      <c r="GO5">
+        <v>86400</v>
+      </c>
+      <c r="GP5">
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:192">
+    <row r="6" spans="1:198">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -3574,10 +3940,10 @@
         <v>5527000</v>
       </c>
       <c r="O6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -3592,25 +3958,25 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W6">
         <v>90</v>
       </c>
       <c r="X6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y6">
         <v>90</v>
       </c>
       <c r="Z6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -3622,7 +3988,7 @@
         <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH6">
         <v>1</v>
@@ -3637,34 +4003,43 @@
         <v>9</v>
       </c>
       <c r="AL6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN6">
         <v>90</v>
       </c>
       <c r="AO6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP6">
         <v>90</v>
       </c>
       <c r="AQ6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <v>19500000</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>221</v>
+      </c>
+      <c r="AW6">
+        <v>35</v>
       </c>
       <c r="AX6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY6">
         <v>1</v>
@@ -3679,34 +4054,43 @@
         <v>9</v>
       </c>
       <c r="BC6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE6">
         <v>90</v>
       </c>
       <c r="BF6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG6">
         <v>90</v>
       </c>
       <c r="BH6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL6">
+        <v>2800000</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN6">
+        <v>55</v>
       </c>
       <c r="BO6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP6">
         <v>1</v>
@@ -3721,25 +4105,25 @@
         <v>9</v>
       </c>
       <c r="BT6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV6">
         <v>90</v>
       </c>
       <c r="BW6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX6">
         <v>90</v>
       </c>
       <c r="BY6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA6">
         <v>1</v>
@@ -3748,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="CC6">
-        <v>7800</v>
+        <v>8900</v>
       </c>
       <c r="CD6" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE6">
         <v>0</v>
@@ -3763,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="CH6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI6">
         <v>1</v>
@@ -3778,28 +4162,28 @@
         <v>9</v>
       </c>
       <c r="CM6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO6">
         <v>90</v>
       </c>
       <c r="CP6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ6">
         <v>90</v>
       </c>
       <c r="CR6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT6" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU6">
         <v>0</v>
@@ -3808,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA6">
         <v>1</v>
@@ -3823,28 +4207,28 @@
         <v>9</v>
       </c>
       <c r="DE6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG6">
         <v>90</v>
       </c>
       <c r="DH6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI6">
         <v>90</v>
       </c>
       <c r="DJ6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL6" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM6">
         <v>0</v>
@@ -3853,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="DR6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS6">
         <v>1</v>
@@ -3868,28 +4252,28 @@
         <v>9</v>
       </c>
       <c r="DW6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY6">
         <v>90</v>
       </c>
       <c r="DZ6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA6">
         <v>90</v>
       </c>
       <c r="EB6" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC6" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED6" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE6">
         <v>0</v>
@@ -3898,16 +4282,70 @@
         <v>0</v>
       </c>
       <c r="EI6" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK6">
+        <v>2</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>239</v>
+      </c>
+      <c r="EM6">
+        <v>50000</v>
+      </c>
+      <c r="EN6">
+        <v>7200</v>
+      </c>
+      <c r="EO6">
+        <v>7200</v>
+      </c>
+      <c r="EP6">
+        <v>50000</v>
+      </c>
+      <c r="EQ6">
+        <v>0.9</v>
+      </c>
+      <c r="ER6">
+        <v>0.8</v>
+      </c>
+      <c r="ES6" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET6" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU6" t="s">
+        <v>240</v>
+      </c>
+      <c r="EV6">
+        <v>75000</v>
+      </c>
+      <c r="EW6">
+        <v>7200</v>
+      </c>
+      <c r="EX6">
+        <v>11000</v>
+      </c>
+      <c r="EY6">
+        <v>100000</v>
+      </c>
+      <c r="EZ6">
+        <v>0.9</v>
+      </c>
+      <c r="FA6">
+        <v>0.8</v>
+      </c>
+      <c r="FB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC6" t="b">
         <v>0</v>
       </c>
       <c r="FD6" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE6">
         <v>0.05</v>
@@ -3922,13 +4360,13 @@
         <v>8.5</v>
       </c>
       <c r="FI6" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ6" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK6" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL6">
         <v>1</v>
@@ -3955,7 +4393,7 @@
         <v>0</v>
       </c>
       <c r="FT6" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU6">
         <v>0</v>
@@ -3964,48 +4402,66 @@
         <v>0</v>
       </c>
       <c r="GA6" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB6" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC6" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD6">
         <v>86400</v>
       </c>
       <c r="GE6" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF6" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF6">
+        <v>86400</v>
       </c>
       <c r="GG6" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH6" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI6">
+        <v>249</v>
+      </c>
+      <c r="GI6" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ6" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK6" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL6" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM6" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN6">
         <v>86400</v>
       </c>
-      <c r="GJ6">
+      <c r="GO6">
+        <v>86400</v>
+      </c>
+      <c r="GP6">
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:192">
+    <row r="7" spans="1:198">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -4014,7 +4470,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -4026,13 +4482,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3648000</v>
+        <v>2012000</v>
       </c>
       <c r="O7" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -4047,25 +4503,25 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W7">
         <v>90</v>
       </c>
       <c r="X7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y7">
         <v>90</v>
       </c>
       <c r="Z7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB7">
         <v>0</v>
@@ -4077,7 +4533,7 @@
         <v>6</v>
       </c>
       <c r="AG7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH7">
         <v>1</v>
@@ -4092,34 +4548,43 @@
         <v>9</v>
       </c>
       <c r="AL7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN7">
         <v>90</v>
       </c>
       <c r="AO7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP7">
         <v>90</v>
       </c>
       <c r="AQ7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <v>19500000</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>223</v>
+      </c>
+      <c r="AW7">
+        <v>55</v>
       </c>
       <c r="AX7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -4134,34 +4599,43 @@
         <v>9</v>
       </c>
       <c r="BC7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE7">
         <v>90</v>
       </c>
       <c r="BF7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG7">
         <v>90</v>
       </c>
       <c r="BH7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL7">
+        <v>2800000</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN7">
+        <v>55</v>
       </c>
       <c r="BO7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP7">
         <v>1</v>
@@ -4176,25 +4650,25 @@
         <v>9</v>
       </c>
       <c r="BT7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV7">
         <v>90</v>
       </c>
       <c r="BW7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX7">
         <v>90</v>
       </c>
       <c r="BY7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA7">
         <v>1</v>
@@ -4203,10 +4677,10 @@
         <v>1</v>
       </c>
       <c r="CC7">
-        <v>5000</v>
+        <v>3400</v>
       </c>
       <c r="CD7" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE7">
         <v>0</v>
@@ -4218,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="CH7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI7">
         <v>1</v>
@@ -4233,28 +4707,28 @@
         <v>9</v>
       </c>
       <c r="CM7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO7">
         <v>90</v>
       </c>
       <c r="CP7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ7">
         <v>90</v>
       </c>
       <c r="CR7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT7" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU7">
         <v>0</v>
@@ -4263,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA7">
         <v>1</v>
@@ -4278,28 +4752,28 @@
         <v>9</v>
       </c>
       <c r="DE7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG7">
         <v>90</v>
       </c>
       <c r="DH7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI7">
         <v>90</v>
       </c>
       <c r="DJ7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL7" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM7">
         <v>0</v>
@@ -4308,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="DR7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS7">
         <v>1</v>
@@ -4323,28 +4797,28 @@
         <v>9</v>
       </c>
       <c r="DW7" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY7">
         <v>90</v>
       </c>
       <c r="DZ7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA7">
         <v>90</v>
       </c>
       <c r="EB7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC7" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE7">
         <v>0</v>
@@ -4353,16 +4827,43 @@
         <v>0</v>
       </c>
       <c r="EI7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK7">
+        <v>1</v>
+      </c>
+      <c r="EL7" t="s">
+        <v>240</v>
+      </c>
+      <c r="EM7">
+        <v>50000</v>
+      </c>
+      <c r="EN7">
+        <v>7200</v>
+      </c>
+      <c r="EO7">
+        <v>7200</v>
+      </c>
+      <c r="EP7">
+        <v>50000</v>
+      </c>
+      <c r="EQ7">
+        <v>0.9</v>
+      </c>
+      <c r="ER7">
+        <v>0.8</v>
+      </c>
+      <c r="ES7" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET7" t="b">
         <v>0</v>
       </c>
       <c r="FD7" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE7">
         <v>0.05</v>
@@ -4377,22 +4878,40 @@
         <v>8.5</v>
       </c>
       <c r="FI7" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ7" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM7">
+        <v>1</v>
+      </c>
+      <c r="FN7">
+        <v>2000</v>
+      </c>
+      <c r="FO7">
+        <v>2000</v>
+      </c>
+      <c r="FP7">
+        <v>0.95</v>
+      </c>
+      <c r="FQ7">
+        <v>0.1</v>
+      </c>
+      <c r="FR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="b">
         <v>0</v>
       </c>
       <c r="FT7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU7">
         <v>0</v>
@@ -4401,42 +4920,60 @@
         <v>0</v>
       </c>
       <c r="GA7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB7" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC7" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD7">
         <v>86400</v>
       </c>
       <c r="GE7" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF7" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF7">
+        <v>86400</v>
       </c>
       <c r="GG7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH7" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI7">
+        <v>249</v>
+      </c>
+      <c r="GI7" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL7" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM7" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN7">
         <v>86400</v>
       </c>
-      <c r="GJ7">
+      <c r="GO7">
+        <v>86400</v>
+      </c>
+      <c r="GP7">
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:192">
+    <row r="8" spans="1:198">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -4463,13 +5000,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3125000</v>
+        <v>2959000</v>
       </c>
       <c r="O8" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -4484,25 +5021,25 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W8">
         <v>90</v>
       </c>
       <c r="X8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y8">
         <v>90</v>
       </c>
       <c r="Z8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB8">
         <v>0</v>
@@ -4514,7 +5051,7 @@
         <v>6</v>
       </c>
       <c r="AG8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH8">
         <v>1</v>
@@ -4529,34 +5066,43 @@
         <v>9</v>
       </c>
       <c r="AL8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN8">
         <v>90</v>
       </c>
       <c r="AO8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP8">
         <v>90</v>
       </c>
       <c r="AQ8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>5500000</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>224</v>
+      </c>
+      <c r="AW8">
+        <v>55</v>
       </c>
       <c r="AX8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY8">
         <v>1</v>
@@ -4571,34 +5117,43 @@
         <v>9</v>
       </c>
       <c r="BC8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE8">
         <v>90</v>
       </c>
       <c r="BF8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG8">
         <v>90</v>
       </c>
       <c r="BH8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL8">
+        <v>1800000</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>232</v>
+      </c>
+      <c r="BN8">
+        <v>55</v>
       </c>
       <c r="BO8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP8">
         <v>1</v>
@@ -4613,25 +5168,25 @@
         <v>9</v>
       </c>
       <c r="BT8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV8">
         <v>90</v>
       </c>
       <c r="BW8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX8">
         <v>90</v>
       </c>
       <c r="BY8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA8">
         <v>1</v>
@@ -4640,22 +5195,22 @@
         <v>1</v>
       </c>
       <c r="CC8">
-        <v>5400</v>
+        <v>4000</v>
       </c>
       <c r="CD8" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE8">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CF8">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CG8" t="b">
         <v>1</v>
       </c>
       <c r="CH8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI8">
         <v>1</v>
@@ -4670,28 +5225,28 @@
         <v>9</v>
       </c>
       <c r="CM8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO8">
         <v>90</v>
       </c>
       <c r="CP8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ8">
         <v>90</v>
       </c>
       <c r="CR8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT8" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU8">
         <v>0</v>
@@ -4700,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA8">
         <v>1</v>
@@ -4715,28 +5270,28 @@
         <v>9</v>
       </c>
       <c r="DE8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG8">
         <v>90</v>
       </c>
       <c r="DH8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI8">
         <v>90</v>
       </c>
       <c r="DJ8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL8" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM8">
         <v>0</v>
@@ -4745,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="DR8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS8">
         <v>1</v>
@@ -4760,28 +5315,28 @@
         <v>9</v>
       </c>
       <c r="DW8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY8">
         <v>90</v>
       </c>
       <c r="DZ8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA8">
         <v>90</v>
       </c>
       <c r="EB8" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED8" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE8">
         <v>0</v>
@@ -4790,16 +5345,43 @@
         <v>0</v>
       </c>
       <c r="EI8" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK8">
+        <v>1</v>
+      </c>
+      <c r="EL8" t="s">
+        <v>241</v>
+      </c>
+      <c r="EM8">
+        <v>100000</v>
+      </c>
+      <c r="EN8">
+        <v>11000</v>
+      </c>
+      <c r="EO8">
+        <v>22000</v>
+      </c>
+      <c r="EP8">
+        <v>200000</v>
+      </c>
+      <c r="EQ8">
+        <v>0.9</v>
+      </c>
+      <c r="ER8">
+        <v>0.8</v>
+      </c>
+      <c r="ES8" t="b">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="b">
         <v>0</v>
       </c>
       <c r="FD8" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE8">
         <v>0.05</v>
@@ -4814,13 +5396,13 @@
         <v>8.5</v>
       </c>
       <c r="FI8" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ8" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK8" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL8">
         <v>1</v>
@@ -4829,10 +5411,10 @@
         <v>1</v>
       </c>
       <c r="FN8">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="FO8">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="FP8">
         <v>0.95</v>
@@ -4847,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="FT8" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU8">
         <v>0</v>
@@ -4856,48 +5438,66 @@
         <v>0</v>
       </c>
       <c r="GA8" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB8" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC8" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD8">
         <v>86400</v>
       </c>
       <c r="GE8" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF8" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF8">
+        <v>86400</v>
       </c>
       <c r="GG8" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH8" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI8">
+        <v>249</v>
+      </c>
+      <c r="GI8" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ8" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK8" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL8" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM8" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN8">
         <v>86400</v>
       </c>
-      <c r="GJ8">
+      <c r="GO8">
+        <v>86400</v>
+      </c>
+      <c r="GP8">
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:192">
+    <row r="9" spans="1:198">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -4906,7 +5506,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -4918,13 +5518,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>2687000</v>
+        <v>3648000</v>
       </c>
       <c r="O9" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -4939,25 +5539,25 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W9">
         <v>90</v>
       </c>
       <c r="X9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y9">
         <v>90</v>
       </c>
       <c r="Z9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB9">
         <v>0</v>
@@ -4969,7 +5569,7 @@
         <v>6</v>
       </c>
       <c r="AG9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH9">
         <v>1</v>
@@ -4984,34 +5584,43 @@
         <v>9</v>
       </c>
       <c r="AL9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN9">
         <v>90</v>
       </c>
       <c r="AO9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP9">
         <v>90</v>
       </c>
       <c r="AQ9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <v>5500000</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>225</v>
+      </c>
+      <c r="AW9">
+        <v>35</v>
       </c>
       <c r="AX9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY9">
         <v>1</v>
@@ -5026,34 +5635,43 @@
         <v>9</v>
       </c>
       <c r="BC9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE9">
         <v>90</v>
       </c>
       <c r="BF9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG9">
         <v>90</v>
       </c>
       <c r="BH9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL9">
+        <v>2100000</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>227</v>
+      </c>
+      <c r="BN9">
+        <v>55</v>
       </c>
       <c r="BO9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP9">
         <v>1</v>
@@ -5068,25 +5686,25 @@
         <v>9</v>
       </c>
       <c r="BT9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV9">
         <v>90</v>
       </c>
       <c r="BW9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX9">
         <v>90</v>
       </c>
       <c r="BY9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA9">
         <v>1</v>
@@ -5095,10 +5713,10 @@
         <v>1</v>
       </c>
       <c r="CC9">
-        <v>3800</v>
+        <v>5600</v>
       </c>
       <c r="CD9" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE9">
         <v>0</v>
@@ -5110,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="CH9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI9">
         <v>1</v>
@@ -5125,28 +5743,28 @@
         <v>9</v>
       </c>
       <c r="CM9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO9">
         <v>90</v>
       </c>
       <c r="CP9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ9">
         <v>90</v>
       </c>
       <c r="CR9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT9" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU9">
         <v>0</v>
@@ -5155,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA9">
         <v>1</v>
@@ -5170,28 +5788,28 @@
         <v>9</v>
       </c>
       <c r="DE9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG9">
         <v>90</v>
       </c>
       <c r="DH9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI9">
         <v>90</v>
       </c>
       <c r="DJ9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL9" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM9">
         <v>0</v>
@@ -5200,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="DR9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS9">
         <v>1</v>
@@ -5215,28 +5833,28 @@
         <v>9</v>
       </c>
       <c r="DW9" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY9">
         <v>90</v>
       </c>
       <c r="DZ9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA9">
         <v>90</v>
       </c>
       <c r="EB9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED9" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE9">
         <v>0</v>
@@ -5245,34 +5863,34 @@
         <v>0</v>
       </c>
       <c r="EI9" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ9">
         <v>1</v>
       </c>
       <c r="EK9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="EL9" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="EM9">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="EN9">
         <v>7200</v>
       </c>
       <c r="EO9">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="EP9">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="EQ9">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER9">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES9" t="b">
         <v>0</v>
@@ -5280,35 +5898,8 @@
       <c r="ET9" t="b">
         <v>0</v>
       </c>
-      <c r="EU9" t="s">
-        <v>219</v>
-      </c>
-      <c r="EV9">
-        <v>50000</v>
-      </c>
-      <c r="EW9">
-        <v>7200</v>
-      </c>
-      <c r="EX9">
-        <v>7200</v>
-      </c>
-      <c r="EY9">
-        <v>50000</v>
-      </c>
-      <c r="EZ9">
-        <v>90000</v>
-      </c>
-      <c r="FA9">
-        <v>80000</v>
-      </c>
-      <c r="FB9" t="b">
-        <v>0</v>
-      </c>
-      <c r="FC9" t="b">
-        <v>0</v>
-      </c>
       <c r="FD9" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE9">
         <v>0.05</v>
@@ -5323,13 +5914,13 @@
         <v>8.5</v>
       </c>
       <c r="FI9" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ9" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK9" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL9">
         <v>1</v>
@@ -5338,10 +5929,10 @@
         <v>1</v>
       </c>
       <c r="FN9">
-        <v>2700</v>
+        <v>3600</v>
       </c>
       <c r="FO9">
-        <v>2700</v>
+        <v>3600</v>
       </c>
       <c r="FP9">
         <v>0.95</v>
@@ -5356,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="FT9" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU9">
         <v>0</v>
@@ -5365,42 +5956,60 @@
         <v>0</v>
       </c>
       <c r="GA9" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB9" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC9" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD9">
         <v>86400</v>
       </c>
       <c r="GE9" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF9" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF9">
+        <v>86400</v>
       </c>
       <c r="GG9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH9" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI9">
+        <v>249</v>
+      </c>
+      <c r="GI9" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ9" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK9" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL9" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM9" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN9">
         <v>86400</v>
       </c>
-      <c r="GJ9">
+      <c r="GO9">
+        <v>86400</v>
+      </c>
+      <c r="GP9">
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:192">
+    <row r="10" spans="1:198">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -5427,13 +6036,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>2262000</v>
+        <v>3863000</v>
       </c>
       <c r="O10" t="s">
         <v>207</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -5448,25 +6057,25 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W10">
         <v>90</v>
       </c>
       <c r="X10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y10">
         <v>90</v>
       </c>
       <c r="Z10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB10">
         <v>0</v>
@@ -5478,7 +6087,7 @@
         <v>6</v>
       </c>
       <c r="AG10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH10">
         <v>1</v>
@@ -5493,34 +6102,43 @@
         <v>9</v>
       </c>
       <c r="AL10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN10">
         <v>90</v>
       </c>
       <c r="AO10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP10">
         <v>90</v>
       </c>
       <c r="AQ10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <v>19500000</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>219</v>
+      </c>
+      <c r="AW10">
+        <v>35</v>
       </c>
       <c r="AX10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY10">
         <v>1</v>
@@ -5535,34 +6153,43 @@
         <v>9</v>
       </c>
       <c r="BC10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE10">
         <v>90</v>
       </c>
       <c r="BF10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG10">
         <v>90</v>
       </c>
       <c r="BH10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL10">
+        <v>2400000</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>230</v>
+      </c>
+      <c r="BN10">
+        <v>55</v>
       </c>
       <c r="BO10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP10">
         <v>1</v>
@@ -5577,34 +6204,49 @@
         <v>9</v>
       </c>
       <c r="BT10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV10">
         <v>90</v>
       </c>
       <c r="BW10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX10">
         <v>90</v>
       </c>
       <c r="BY10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="CC10">
+        <v>5800</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>233</v>
+      </c>
+      <c r="CE10">
+        <v>-20</v>
+      </c>
+      <c r="CF10">
+        <v>50</v>
+      </c>
+      <c r="CG10" t="b">
+        <v>1</v>
       </c>
       <c r="CH10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI10">
         <v>1</v>
@@ -5619,28 +6261,28 @@
         <v>9</v>
       </c>
       <c r="CM10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO10">
         <v>90</v>
       </c>
       <c r="CP10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ10">
         <v>90</v>
       </c>
       <c r="CR10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT10" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU10">
         <v>0</v>
@@ -5649,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA10">
         <v>1</v>
@@ -5664,28 +6306,28 @@
         <v>9</v>
       </c>
       <c r="DE10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG10">
         <v>90</v>
       </c>
       <c r="DH10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI10">
         <v>90</v>
       </c>
       <c r="DJ10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL10" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM10">
         <v>0</v>
@@ -5694,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="DR10" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS10">
         <v>1</v>
@@ -5709,28 +6351,28 @@
         <v>9</v>
       </c>
       <c r="DW10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY10">
         <v>90</v>
       </c>
       <c r="DZ10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA10">
         <v>90</v>
       </c>
       <c r="EB10" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED10" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE10">
         <v>0</v>
@@ -5739,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="EI10" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ10">
         <v>1</v>
@@ -5748,25 +6390,25 @@
         <v>1</v>
       </c>
       <c r="EL10" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="EM10">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="EN10">
         <v>7200</v>
       </c>
       <c r="EO10">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EP10">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EQ10">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER10">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES10" t="b">
         <v>0</v>
@@ -5775,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="FD10" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE10">
         <v>0.05</v>
@@ -5790,22 +6432,40 @@
         <v>8.5</v>
       </c>
       <c r="FI10" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ10" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK10" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FM10">
+        <v>1</v>
+      </c>
+      <c r="FN10">
+        <v>3900</v>
+      </c>
+      <c r="FO10">
+        <v>3900</v>
+      </c>
+      <c r="FP10">
+        <v>0.95</v>
+      </c>
+      <c r="FQ10">
+        <v>0.1</v>
+      </c>
+      <c r="FR10" t="b">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="b">
         <v>0</v>
       </c>
       <c r="FT10" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU10">
         <v>0</v>
@@ -5814,48 +6474,66 @@
         <v>0</v>
       </c>
       <c r="GA10" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB10" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC10" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD10">
         <v>86400</v>
       </c>
       <c r="GE10" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF10" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF10">
+        <v>86400</v>
       </c>
       <c r="GG10" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH10" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI10">
+        <v>249</v>
+      </c>
+      <c r="GI10" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ10" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK10" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL10" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM10" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN10">
         <v>86400</v>
       </c>
-      <c r="GJ10">
+      <c r="GO10">
+        <v>86400</v>
+      </c>
+      <c r="GP10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:192">
+    <row r="11" spans="1:198">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -5864,7 +6542,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -5876,13 +6554,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>3863000</v>
+        <v>3125000</v>
       </c>
       <c r="O11" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="P11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -5897,25 +6575,25 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="V11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="W11">
         <v>90</v>
       </c>
       <c r="X11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y11">
         <v>90</v>
       </c>
       <c r="Z11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AA11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AB11">
         <v>0</v>
@@ -5927,7 +6605,7 @@
         <v>6</v>
       </c>
       <c r="AG11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AH11">
         <v>1</v>
@@ -5942,34 +6620,43 @@
         <v>9</v>
       </c>
       <c r="AL11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AM11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AN11">
         <v>90</v>
       </c>
       <c r="AO11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AP11">
         <v>90</v>
       </c>
       <c r="AQ11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AR11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <v>5500000</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>226</v>
+      </c>
+      <c r="AW11">
+        <v>55</v>
       </c>
       <c r="AX11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AY11">
         <v>1</v>
@@ -5984,34 +6671,43 @@
         <v>9</v>
       </c>
       <c r="BC11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BD11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BE11">
         <v>90</v>
       </c>
       <c r="BF11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BG11">
         <v>90</v>
       </c>
       <c r="BH11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BI11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="BL11">
+        <v>2400000</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>231</v>
+      </c>
+      <c r="BN11">
+        <v>55</v>
       </c>
       <c r="BO11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="BP11">
         <v>1</v>
@@ -6026,25 +6722,25 @@
         <v>9</v>
       </c>
       <c r="BT11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="BU11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BV11">
         <v>90</v>
       </c>
       <c r="BW11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BX11">
         <v>90</v>
       </c>
       <c r="BY11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BZ11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CA11">
         <v>1</v>
@@ -6053,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="CC11">
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="CD11" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="CE11">
         <v>0</v>
@@ -6068,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="CH11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="CI11">
         <v>1</v>
@@ -6083,28 +6779,28 @@
         <v>9</v>
       </c>
       <c r="CM11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="CN11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CO11">
         <v>90</v>
       </c>
       <c r="CP11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CQ11">
         <v>90</v>
       </c>
       <c r="CR11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="CS11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="CT11" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="CU11">
         <v>0</v>
@@ -6113,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="CZ11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DA11">
         <v>1</v>
@@ -6128,28 +6824,28 @@
         <v>9</v>
       </c>
       <c r="DE11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DF11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DG11">
         <v>90</v>
       </c>
       <c r="DH11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DI11">
         <v>90</v>
       </c>
       <c r="DJ11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DK11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="DL11" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="DM11">
         <v>0</v>
@@ -6158,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="DR11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="DS11">
         <v>1</v>
@@ -6173,28 +6869,28 @@
         <v>9</v>
       </c>
       <c r="DW11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="DX11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="DY11">
         <v>90</v>
       </c>
       <c r="DZ11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EA11">
         <v>90</v>
       </c>
       <c r="EB11" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="EC11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="ED11" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EE11">
         <v>0</v>
@@ -6203,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="EI11" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="EJ11">
         <v>1</v>
@@ -6212,25 +6908,25 @@
         <v>1</v>
       </c>
       <c r="EL11" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="EM11">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="EN11">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="EO11">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="EP11">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="EQ11">
-        <v>90000</v>
+        <v>0.9</v>
       </c>
       <c r="ER11">
-        <v>80000</v>
+        <v>0.8</v>
       </c>
       <c r="ES11" t="b">
         <v>0</v>
@@ -6239,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="FD11" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="FE11">
         <v>0.05</v>
@@ -6254,13 +6950,13 @@
         <v>8.5</v>
       </c>
       <c r="FI11" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="FJ11" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="FK11" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FL11">
         <v>1</v>
@@ -6269,10 +6965,10 @@
         <v>1</v>
       </c>
       <c r="FN11">
-        <v>3900</v>
+        <v>3100</v>
       </c>
       <c r="FO11">
-        <v>3900</v>
+        <v>3100</v>
       </c>
       <c r="FP11">
         <v>0.95</v>
@@ -6287,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="FT11" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="FU11">
         <v>0</v>
@@ -6296,33 +6992,51 @@
         <v>0</v>
       </c>
       <c r="GA11" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="GB11" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GC11" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="GD11">
         <v>86400</v>
       </c>
       <c r="GE11" t="s">
-        <v>224</v>
-      </c>
-      <c r="GF11" t="s">
-        <v>225</v>
+        <v>248</v>
+      </c>
+      <c r="GF11">
+        <v>86400</v>
       </c>
       <c r="GG11" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="GH11" t="s">
-        <v>226</v>
-      </c>
-      <c r="GI11">
+        <v>249</v>
+      </c>
+      <c r="GI11" t="s">
+        <v>250</v>
+      </c>
+      <c r="GJ11" t="s">
+        <v>249</v>
+      </c>
+      <c r="GK11" t="s">
+        <v>249</v>
+      </c>
+      <c r="GL11" t="s">
+        <v>249</v>
+      </c>
+      <c r="GM11" t="s">
+        <v>250</v>
+      </c>
+      <c r="GN11">
         <v>86400</v>
       </c>
-      <c r="GJ11">
+      <c r="GO11">
+        <v>86400</v>
+      </c>
+      <c r="GP11">
         <v>3600</v>
       </c>
     </row>
@@ -6333,10 +7047,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:GM1"/>
+  <dimension ref="B1:GS1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:195">
+    <row r="1" spans="2:201">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6350,13 +7064,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -6918,6 +7632,24 @@
       </c>
       <c r="GM1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="GN1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="GO1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="GP1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="GQ1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="GR1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="GS1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -6927,10 +7659,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:ED1"/>
+  <dimension ref="B1:EJ1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:134">
+    <row r="1" spans="2:140">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6944,7 +7676,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7256,22 +7988,22 @@
         <v>158</v>
       </c>
       <c r="DF1" s="1" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="DG1" s="1" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="DH1" s="1" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="DI1" s="1" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="DJ1" s="1" t="s">
         <v>163</v>
       </c>
       <c r="DK1" s="1" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="DL1" s="1" t="s">
         <v>165</v>
@@ -7329,6 +8061,24 @@
       </c>
       <c r="ED1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="EE1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -7338,10 +8088,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:EM1"/>
+  <dimension ref="B1:ES1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:143">
+    <row r="1" spans="2:149">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7355,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -7767,6 +8517,24 @@
       </c>
       <c r="EM1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="EN1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="EO1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -7776,10 +8544,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:CB1"/>
+  <dimension ref="B1:CH1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:80">
+    <row r="1" spans="2:86">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8016,6 +8784,24 @@
       </c>
       <c r="CB1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -8025,10 +8811,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:AP1"/>
+  <dimension ref="B1:AV1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:42">
+    <row r="1" spans="2:48">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8072,58 +8858,58 @@
         <v>174</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>182</v>
@@ -8151,6 +8937,24 @@
       </c>
       <c r="AP1" s="1" t="s">
         <v>190</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="320">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -717,54 +717,60 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>AiAVqbLxriY9rjA</t>
-  </si>
-  <si>
-    <t>mvWCYJg2v4k5jfT</t>
-  </si>
-  <si>
-    <t>1R2RodLeMOThH8a</t>
-  </si>
-  <si>
-    <t>LdjQVpYWOOU1AFV</t>
-  </si>
-  <si>
-    <t>F1LEVSr9AlPrA13</t>
-  </si>
-  <si>
-    <t>3ggHJl2QsI6I6lY</t>
-  </si>
-  <si>
-    <t>R1X3lcBByP6o9rl</t>
-  </si>
-  <si>
-    <t>yOzvJCxV1YSchjY</t>
-  </si>
-  <si>
-    <t>tBGZl2VmSEMvbUm</t>
-  </si>
-  <si>
-    <t>WlaIGNabXASq7fB</t>
+    <t>AqWXE9DEO8hByue</t>
+  </si>
+  <si>
+    <t>aM0cFJcGazmTn74</t>
+  </si>
+  <si>
+    <t>dGjALyULMFUj8m3</t>
+  </si>
+  <si>
+    <t>g2wXSWhRgXPfwXM</t>
+  </si>
+  <si>
+    <t>V0ADANY7ClQZ4lm</t>
+  </si>
+  <si>
+    <t>wuhhnp1FBrx3XSL</t>
+  </si>
+  <si>
+    <t>QVlvnKyFkva8qU4</t>
+  </si>
+  <si>
+    <t>Xdq8WMnHTivaCxj</t>
+  </si>
+  <si>
+    <t>zsgQNT5cOwiWLqg</t>
+  </si>
+  <si>
+    <t>kn47c0hnjvJ11j0</t>
+  </si>
+  <si>
+    <t>hh_2262_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3564_0.csv</t>
   </si>
   <si>
     <t>hh_4402_0.csv</t>
   </si>
   <si>
-    <t>hh_3648_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
+    <t>hh_5527_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
   </si>
   <si>
     <t>hh_4536_0.csv</t>
   </si>
   <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
     <t>hh_3125_0.csv</t>
   </si>
   <si>
+    <t>hh_2687_0.csv</t>
+  </si>
+  <si>
     <t>perfect</t>
   </si>
   <si>
@@ -780,51 +786,48 @@
     <t>rfr</t>
   </si>
   <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
     <t>heat_4402_0.csv</t>
   </si>
   <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2262_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_5_pu.csv</t>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3863_0.csv</t>
   </si>
   <si>
     <t>heat_4536_0.csv</t>
   </si>
   <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3125_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_2_pu.csv</t>
+    <t>heat_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_2687_0.csv</t>
   </si>
   <si>
     <t>naive</t>
   </si>
   <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
     <t>dhw_gen_2_pu.csv</t>
   </si>
   <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
     <t>dhw_gen_4_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -834,43 +837,49 @@
     <t>green_local</t>
   </si>
   <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
   </si>
   <si>
     <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
   </si>
   <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
+    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
   </si>
   <si>
     <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
   </si>
   <si>
-    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
-  </si>
-  <si>
     <t>rnn</t>
   </si>
   <si>
     <t>local</t>
   </si>
   <si>
-    <t>ev_fulltime_48.csv</t>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_46.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_43.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_42.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_45.csv</t>
   </si>
   <si>
     <t>ev_freetime_0.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_42.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_89.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_44.csv</t>
+    <t>ev_parttime_90.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -2060,13 +2069,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>4402000</v>
+        <v>2262000</v>
       </c>
       <c r="O2" t="s">
         <v>242</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2081,10 +2090,10 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W2">
         <v>3</v>
@@ -2096,7 +2105,7 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA2">
         <v>3</v>
@@ -2108,13 +2117,13 @@
         <v>20</v>
       </c>
       <c r="AD2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE2">
         <v>3</v>
       </c>
       <c r="AF2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2126,7 +2135,7 @@
         <v>6</v>
       </c>
       <c r="AL2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM2">
         <v>1</v>
@@ -2141,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="AQ2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS2">
         <v>3</v>
@@ -2156,7 +2165,7 @@
         <v>20</v>
       </c>
       <c r="AV2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW2">
         <v>3</v>
@@ -2168,13 +2177,13 @@
         <v>20</v>
       </c>
       <c r="AZ2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA2">
         <v>3</v>
       </c>
       <c r="BB2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC2">
         <v>1</v>
@@ -2186,10 +2195,10 @@
         <v>5500000</v>
       </c>
       <c r="BF2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BG2">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH2" t="s">
         <v>262</v>
@@ -2207,10 +2216,10 @@
         <v>9</v>
       </c>
       <c r="BM2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO2">
         <v>3</v>
@@ -2222,7 +2231,7 @@
         <v>20</v>
       </c>
       <c r="BR2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS2">
         <v>3</v>
@@ -2234,13 +2243,13 @@
         <v>20</v>
       </c>
       <c r="BV2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW2">
         <v>3</v>
       </c>
       <c r="BX2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY2">
         <v>1</v>
@@ -2258,7 +2267,7 @@
         <v>55</v>
       </c>
       <c r="CD2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE2">
         <v>1</v>
@@ -2273,10 +2282,10 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK2">
         <v>3</v>
@@ -2288,7 +2297,7 @@
         <v>20</v>
       </c>
       <c r="CN2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO2">
         <v>3</v>
@@ -2300,13 +2309,13 @@
         <v>20</v>
       </c>
       <c r="CR2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS2">
         <v>3</v>
       </c>
       <c r="CT2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU2">
         <v>1</v>
@@ -2315,10 +2324,10 @@
         <v>1</v>
       </c>
       <c r="CW2">
-        <v>6900</v>
+        <v>3700</v>
       </c>
       <c r="CX2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY2">
         <v>-20</v>
@@ -2330,7 +2339,7 @@
         <v>1</v>
       </c>
       <c r="DB2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC2">
         <v>1</v>
@@ -2345,10 +2354,10 @@
         <v>9</v>
       </c>
       <c r="DG2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI2">
         <v>3</v>
@@ -2360,7 +2369,7 @@
         <v>20</v>
       </c>
       <c r="DL2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM2">
         <v>3</v>
@@ -2372,16 +2381,16 @@
         <v>20</v>
       </c>
       <c r="DP2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ2">
         <v>3</v>
       </c>
       <c r="DR2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -2390,16 +2399,16 @@
         <v>1</v>
       </c>
       <c r="DV2">
-        <v>3600</v>
+        <v>1400</v>
       </c>
       <c r="DW2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="DX2" t="b">
         <v>1</v>
       </c>
       <c r="DY2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ2">
         <v>1</v>
@@ -2414,10 +2423,10 @@
         <v>9</v>
       </c>
       <c r="ED2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF2">
         <v>3</v>
@@ -2429,7 +2438,7 @@
         <v>20</v>
       </c>
       <c r="EI2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ2">
         <v>3</v>
@@ -2441,16 +2450,16 @@
         <v>20</v>
       </c>
       <c r="EM2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN2">
         <v>3</v>
       </c>
       <c r="EO2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ2">
         <v>0</v>
@@ -2459,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="EV2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW2">
         <v>1</v>
@@ -2474,10 +2483,10 @@
         <v>9</v>
       </c>
       <c r="FA2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC2">
         <v>3</v>
@@ -2489,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="FF2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG2">
         <v>3</v>
@@ -2501,16 +2510,16 @@
         <v>20</v>
       </c>
       <c r="FJ2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK2">
         <v>3</v>
       </c>
       <c r="FL2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2519,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="FR2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS2">
         <v>1</v>
@@ -2528,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="FU2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="FV2">
         <v>75000</v>
@@ -2555,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="GM2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN2">
         <v>0.05</v>
@@ -2570,13 +2579,13 @@
         <v>8.5</v>
       </c>
       <c r="GR2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU2">
         <v>1</v>
@@ -2585,10 +2594,10 @@
         <v>1</v>
       </c>
       <c r="GW2">
-        <v>4400</v>
+        <v>2300</v>
       </c>
       <c r="GX2">
-        <v>4400</v>
+        <v>2300</v>
       </c>
       <c r="GY2">
         <v>0.95</v>
@@ -2603,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="HC2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD2">
         <v>0</v>
@@ -2612,19 +2621,19 @@
         <v>0</v>
       </c>
       <c r="HJ2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM2">
         <v>86400</v>
       </c>
       <c r="HN2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO2">
         <v>86400</v>
@@ -2636,7 +2645,7 @@
         <v>262</v>
       </c>
       <c r="HR2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS2" t="s">
         <v>262</v>
@@ -2648,7 +2657,7 @@
         <v>262</v>
       </c>
       <c r="HV2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW2">
         <v>86400</v>
@@ -2692,13 +2701,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>3648000</v>
+        <v>3564000</v>
       </c>
       <c r="O3" t="s">
         <v>243</v>
       </c>
       <c r="P3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2713,10 +2722,10 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -2728,7 +2737,7 @@
         <v>20</v>
       </c>
       <c r="Z3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA3">
         <v>3</v>
@@ -2740,13 +2749,13 @@
         <v>20</v>
       </c>
       <c r="AD3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE3">
         <v>3</v>
       </c>
       <c r="AF3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -2758,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="AL3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM3">
         <v>1</v>
@@ -2773,10 +2782,10 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS3">
         <v>3</v>
@@ -2788,7 +2797,7 @@
         <v>20</v>
       </c>
       <c r="AV3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW3">
         <v>3</v>
@@ -2800,13 +2809,13 @@
         <v>20</v>
       </c>
       <c r="AZ3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA3">
         <v>3</v>
       </c>
       <c r="BB3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC3">
         <v>1</v>
@@ -2818,7 +2827,7 @@
         <v>19500000</v>
       </c>
       <c r="BF3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="BG3">
         <v>55</v>
@@ -2839,10 +2848,10 @@
         <v>9</v>
       </c>
       <c r="BM3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO3">
         <v>3</v>
@@ -2854,7 +2863,7 @@
         <v>20</v>
       </c>
       <c r="BR3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS3">
         <v>3</v>
@@ -2866,13 +2875,13 @@
         <v>20</v>
       </c>
       <c r="BV3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW3">
         <v>3</v>
       </c>
       <c r="BX3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY3">
         <v>1</v>
@@ -2881,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="CA3">
-        <v>2800000</v>
+        <v>2400000</v>
       </c>
       <c r="CB3" t="s">
         <v>264</v>
@@ -2890,7 +2899,7 @@
         <v>55</v>
       </c>
       <c r="CD3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE3">
         <v>1</v>
@@ -2905,10 +2914,10 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK3">
         <v>3</v>
@@ -2920,7 +2929,7 @@
         <v>20</v>
       </c>
       <c r="CN3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO3">
         <v>3</v>
@@ -2932,13 +2941,13 @@
         <v>20</v>
       </c>
       <c r="CR3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS3">
         <v>3</v>
       </c>
       <c r="CT3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU3">
         <v>1</v>
@@ -2947,10 +2956,10 @@
         <v>1</v>
       </c>
       <c r="CW3">
-        <v>4900</v>
+        <v>4500</v>
       </c>
       <c r="CX3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY3">
         <v>0</v>
@@ -2962,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="DB3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC3">
         <v>1</v>
@@ -2977,10 +2986,10 @@
         <v>9</v>
       </c>
       <c r="DG3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI3">
         <v>3</v>
@@ -2992,7 +3001,7 @@
         <v>20</v>
       </c>
       <c r="DL3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM3">
         <v>3</v>
@@ -3004,16 +3013,16 @@
         <v>20</v>
       </c>
       <c r="DP3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ3">
         <v>3</v>
       </c>
       <c r="DR3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT3">
         <v>1</v>
@@ -3022,16 +3031,16 @@
         <v>1</v>
       </c>
       <c r="DV3">
-        <v>2900</v>
+        <v>2700</v>
       </c>
       <c r="DW3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="DX3" t="b">
         <v>1</v>
       </c>
       <c r="DY3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ3">
         <v>1</v>
@@ -3046,10 +3055,10 @@
         <v>9</v>
       </c>
       <c r="ED3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF3">
         <v>3</v>
@@ -3061,7 +3070,7 @@
         <v>20</v>
       </c>
       <c r="EI3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ3">
         <v>3</v>
@@ -3073,16 +3082,16 @@
         <v>20</v>
       </c>
       <c r="EM3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN3">
         <v>3</v>
       </c>
       <c r="EO3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ3">
         <v>0</v>
@@ -3091,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="EV3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW3">
         <v>1</v>
@@ -3106,10 +3115,10 @@
         <v>9</v>
       </c>
       <c r="FA3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC3">
         <v>3</v>
@@ -3121,7 +3130,7 @@
         <v>20</v>
       </c>
       <c r="FF3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG3">
         <v>3</v>
@@ -3133,16 +3142,16 @@
         <v>20</v>
       </c>
       <c r="FJ3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK3">
         <v>3</v>
       </c>
       <c r="FL3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN3">
         <v>0</v>
@@ -3151,28 +3160,28 @@
         <v>0</v>
       </c>
       <c r="FR3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS3">
         <v>1</v>
       </c>
       <c r="FT3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="FU3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="FV3">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FW3">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX3">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="FY3">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="FZ3">
         <v>0.9</v>
@@ -3186,8 +3195,35 @@
       <c r="GC3" t="b">
         <v>0</v>
       </c>
+      <c r="GD3" t="s">
+        <v>286</v>
+      </c>
+      <c r="GE3">
+        <v>100000</v>
+      </c>
+      <c r="GF3">
+        <v>11000</v>
+      </c>
+      <c r="GG3">
+        <v>22000</v>
+      </c>
+      <c r="GH3">
+        <v>200000</v>
+      </c>
+      <c r="GI3">
+        <v>0.9</v>
+      </c>
+      <c r="GJ3">
+        <v>0.8</v>
+      </c>
+      <c r="GK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL3" t="b">
+        <v>0</v>
+      </c>
       <c r="GM3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN3">
         <v>0.05</v>
@@ -3202,13 +3238,13 @@
         <v>8.5</v>
       </c>
       <c r="GR3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU3">
         <v>1</v>
@@ -3235,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="HC3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD3">
         <v>0</v>
@@ -3244,19 +3280,19 @@
         <v>0</v>
       </c>
       <c r="HJ3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM3">
         <v>86400</v>
       </c>
       <c r="HN3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO3">
         <v>86400</v>
@@ -3268,7 +3304,7 @@
         <v>262</v>
       </c>
       <c r="HR3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS3" t="s">
         <v>262</v>
@@ -3280,7 +3316,7 @@
         <v>262</v>
       </c>
       <c r="HV3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW3">
         <v>86400</v>
@@ -3324,13 +3360,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>2262000</v>
+        <v>4402000</v>
       </c>
       <c r="O4" t="s">
         <v>244</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3345,10 +3381,10 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -3360,7 +3396,7 @@
         <v>20</v>
       </c>
       <c r="Z4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA4">
         <v>3</v>
@@ -3372,13 +3408,13 @@
         <v>20</v>
       </c>
       <c r="AD4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
       <c r="AF4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3390,7 +3426,7 @@
         <v>6</v>
       </c>
       <c r="AL4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM4">
         <v>1</v>
@@ -3405,10 +3441,10 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS4">
         <v>3</v>
@@ -3420,7 +3456,7 @@
         <v>20</v>
       </c>
       <c r="AV4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW4">
         <v>3</v>
@@ -3432,13 +3468,13 @@
         <v>20</v>
       </c>
       <c r="AZ4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA4">
         <v>3</v>
       </c>
       <c r="BB4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC4">
         <v>1</v>
@@ -3450,10 +3486,10 @@
         <v>19500000</v>
       </c>
       <c r="BF4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="BG4">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH4" t="s">
         <v>262</v>
@@ -3471,10 +3507,10 @@
         <v>9</v>
       </c>
       <c r="BM4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO4">
         <v>3</v>
@@ -3486,7 +3522,7 @@
         <v>20</v>
       </c>
       <c r="BR4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS4">
         <v>3</v>
@@ -3498,13 +3534,13 @@
         <v>20</v>
       </c>
       <c r="BV4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW4">
         <v>3</v>
       </c>
       <c r="BX4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY4">
         <v>1</v>
@@ -3513,16 +3549,16 @@
         <v>1</v>
       </c>
       <c r="CA4">
-        <v>3200000</v>
+        <v>2800000</v>
       </c>
       <c r="CB4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="CC4">
         <v>55</v>
       </c>
       <c r="CD4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE4">
         <v>1</v>
@@ -3537,10 +3573,10 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK4">
         <v>3</v>
@@ -3552,7 +3588,7 @@
         <v>20</v>
       </c>
       <c r="CN4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO4">
         <v>3</v>
@@ -3564,13 +3600,13 @@
         <v>20</v>
       </c>
       <c r="CR4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS4">
         <v>3</v>
       </c>
       <c r="CT4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU4">
         <v>1</v>
@@ -3579,10 +3615,10 @@
         <v>1</v>
       </c>
       <c r="CW4">
-        <v>3200</v>
+        <v>6300</v>
       </c>
       <c r="CX4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY4">
         <v>0</v>
@@ -3594,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="DB4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC4">
         <v>1</v>
@@ -3609,10 +3645,10 @@
         <v>9</v>
       </c>
       <c r="DG4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI4">
         <v>3</v>
@@ -3624,7 +3660,7 @@
         <v>20</v>
       </c>
       <c r="DL4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM4">
         <v>3</v>
@@ -3636,16 +3672,16 @@
         <v>20</v>
       </c>
       <c r="DP4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ4">
         <v>3</v>
       </c>
       <c r="DR4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT4">
         <v>1</v>
@@ -3654,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="DV4">
-        <v>1800</v>
+        <v>2900</v>
       </c>
       <c r="DW4" t="s">
         <v>273</v>
@@ -3663,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="DY4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ4">
         <v>1</v>
@@ -3678,10 +3714,10 @@
         <v>9</v>
       </c>
       <c r="ED4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF4">
         <v>3</v>
@@ -3693,7 +3729,7 @@
         <v>20</v>
       </c>
       <c r="EI4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ4">
         <v>3</v>
@@ -3705,16 +3741,16 @@
         <v>20</v>
       </c>
       <c r="EM4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN4">
         <v>3</v>
       </c>
       <c r="EO4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ4">
         <v>0</v>
@@ -3723,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="EV4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW4">
         <v>1</v>
@@ -3738,10 +3774,10 @@
         <v>9</v>
       </c>
       <c r="FA4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC4">
         <v>3</v>
@@ -3753,7 +3789,7 @@
         <v>20</v>
       </c>
       <c r="FF4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG4">
         <v>3</v>
@@ -3765,16 +3801,16 @@
         <v>20</v>
       </c>
       <c r="FJ4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK4">
         <v>3</v>
       </c>
       <c r="FL4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN4">
         <v>0</v>
@@ -3783,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="FR4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS4">
         <v>1</v>
@@ -3792,19 +3828,19 @@
         <v>1</v>
       </c>
       <c r="FU4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="FV4">
+        <v>75000</v>
+      </c>
+      <c r="FW4">
+        <v>7200</v>
+      </c>
+      <c r="FX4">
+        <v>11000</v>
+      </c>
+      <c r="FY4">
         <v>100000</v>
-      </c>
-      <c r="FW4">
-        <v>11000</v>
-      </c>
-      <c r="FX4">
-        <v>22000</v>
-      </c>
-      <c r="FY4">
-        <v>200000</v>
       </c>
       <c r="FZ4">
         <v>0.9</v>
@@ -3819,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="GM4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN4">
         <v>0.05</v>
@@ -3834,13 +3870,13 @@
         <v>8.5</v>
       </c>
       <c r="GR4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU4">
         <v>1</v>
@@ -3849,10 +3885,10 @@
         <v>1</v>
       </c>
       <c r="GW4">
-        <v>2300</v>
+        <v>4400</v>
       </c>
       <c r="GX4">
-        <v>2300</v>
+        <v>4400</v>
       </c>
       <c r="GY4">
         <v>0.95</v>
@@ -3867,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="HC4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD4">
         <v>0</v>
@@ -3876,19 +3912,19 @@
         <v>0</v>
       </c>
       <c r="HJ4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM4">
         <v>86400</v>
       </c>
       <c r="HN4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO4">
         <v>86400</v>
@@ -3900,7 +3936,7 @@
         <v>262</v>
       </c>
       <c r="HR4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS4" t="s">
         <v>262</v>
@@ -3912,7 +3948,7 @@
         <v>262</v>
       </c>
       <c r="HV4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW4">
         <v>86400</v>
@@ -3932,10 +3968,10 @@
         <v>235</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3944,7 +3980,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3956,13 +3992,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>4402000</v>
+        <v>5527000</v>
       </c>
       <c r="O5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="P5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -3977,10 +4013,10 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -3992,7 +4028,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA5">
         <v>3</v>
@@ -4004,13 +4040,13 @@
         <v>20</v>
       </c>
       <c r="AD5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE5">
         <v>3</v>
       </c>
       <c r="AF5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -4022,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="AL5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM5">
         <v>1</v>
@@ -4037,10 +4073,10 @@
         <v>9</v>
       </c>
       <c r="AQ5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS5">
         <v>3</v>
@@ -4052,7 +4088,7 @@
         <v>20</v>
       </c>
       <c r="AV5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW5">
         <v>3</v>
@@ -4064,13 +4100,13 @@
         <v>20</v>
       </c>
       <c r="AZ5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA5">
         <v>3</v>
       </c>
       <c r="BB5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC5">
         <v>1</v>
@@ -4079,10 +4115,10 @@
         <v>1</v>
       </c>
       <c r="BE5">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BG5">
         <v>55</v>
@@ -4103,10 +4139,10 @@
         <v>9</v>
       </c>
       <c r="BM5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO5">
         <v>3</v>
@@ -4118,7 +4154,7 @@
         <v>20</v>
       </c>
       <c r="BR5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS5">
         <v>3</v>
@@ -4130,13 +4166,13 @@
         <v>20</v>
       </c>
       <c r="BV5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW5">
         <v>3</v>
       </c>
       <c r="BX5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY5">
         <v>1</v>
@@ -4145,16 +4181,16 @@
         <v>1</v>
       </c>
       <c r="CA5">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="CB5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="CC5">
         <v>55</v>
       </c>
       <c r="CD5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE5">
         <v>1</v>
@@ -4169,10 +4205,10 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK5">
         <v>3</v>
@@ -4184,7 +4220,7 @@
         <v>20</v>
       </c>
       <c r="CN5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO5">
         <v>3</v>
@@ -4196,13 +4232,13 @@
         <v>20</v>
       </c>
       <c r="CR5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS5">
         <v>3</v>
       </c>
       <c r="CT5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU5">
         <v>1</v>
@@ -4211,22 +4247,22 @@
         <v>1</v>
       </c>
       <c r="CW5">
-        <v>7500</v>
+        <v>7400</v>
       </c>
       <c r="CX5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY5">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA5" t="b">
         <v>1</v>
       </c>
       <c r="DB5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC5">
         <v>1</v>
@@ -4241,10 +4277,10 @@
         <v>9</v>
       </c>
       <c r="DG5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI5">
         <v>3</v>
@@ -4256,7 +4292,7 @@
         <v>20</v>
       </c>
       <c r="DL5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM5">
         <v>3</v>
@@ -4268,16 +4304,16 @@
         <v>20</v>
       </c>
       <c r="DP5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ5">
         <v>3</v>
       </c>
       <c r="DR5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT5">
         <v>1</v>
@@ -4286,16 +4322,16 @@
         <v>1</v>
       </c>
       <c r="DV5">
-        <v>2100</v>
+        <v>2600</v>
       </c>
       <c r="DW5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="DX5" t="b">
         <v>1</v>
       </c>
       <c r="DY5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ5">
         <v>1</v>
@@ -4310,10 +4346,10 @@
         <v>9</v>
       </c>
       <c r="ED5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF5">
         <v>3</v>
@@ -4325,7 +4361,7 @@
         <v>20</v>
       </c>
       <c r="EI5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ5">
         <v>3</v>
@@ -4337,16 +4373,16 @@
         <v>20</v>
       </c>
       <c r="EM5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN5">
         <v>3</v>
       </c>
       <c r="EO5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ5">
         <v>0</v>
@@ -4355,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="EV5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW5">
         <v>1</v>
@@ -4370,10 +4406,10 @@
         <v>9</v>
       </c>
       <c r="FA5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC5">
         <v>3</v>
@@ -4385,7 +4421,7 @@
         <v>20</v>
       </c>
       <c r="FF5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG5">
         <v>3</v>
@@ -4397,16 +4433,16 @@
         <v>20</v>
       </c>
       <c r="FJ5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK5">
         <v>3</v>
       </c>
       <c r="FL5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN5">
         <v>0</v>
@@ -4415,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="FR5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS5">
         <v>1</v>
@@ -4424,19 +4460,19 @@
         <v>1</v>
       </c>
       <c r="FU5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="FV5">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="FW5">
         <v>7200</v>
       </c>
       <c r="FX5">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FY5">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FZ5">
         <v>0.9</v>
@@ -4451,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="GM5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN5">
         <v>0.05</v>
@@ -4466,13 +4502,13 @@
         <v>8.5</v>
       </c>
       <c r="GR5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU5">
         <v>1</v>
@@ -4481,10 +4517,10 @@
         <v>1</v>
       </c>
       <c r="GW5">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="GX5">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="GY5">
         <v>0.95</v>
@@ -4499,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="HC5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD5">
         <v>0</v>
@@ -4508,19 +4544,19 @@
         <v>0</v>
       </c>
       <c r="HJ5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM5">
         <v>86400</v>
       </c>
       <c r="HN5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO5">
         <v>86400</v>
@@ -4532,7 +4568,7 @@
         <v>262</v>
       </c>
       <c r="HR5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS5" t="s">
         <v>262</v>
@@ -4544,7 +4580,7 @@
         <v>262</v>
       </c>
       <c r="HV5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW5">
         <v>86400</v>
@@ -4564,10 +4600,10 @@
         <v>236</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -4576,7 +4612,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4588,13 +4624,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>4536000</v>
+        <v>4402000</v>
       </c>
       <c r="O6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4609,10 +4645,10 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W6">
         <v>3</v>
@@ -4624,7 +4660,7 @@
         <v>20</v>
       </c>
       <c r="Z6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -4636,13 +4672,13 @@
         <v>20</v>
       </c>
       <c r="AD6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE6">
         <v>3</v>
       </c>
       <c r="AF6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG6">
         <v>0</v>
@@ -4654,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="AL6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM6">
         <v>1</v>
@@ -4669,10 +4705,10 @@
         <v>9</v>
       </c>
       <c r="AQ6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS6">
         <v>3</v>
@@ -4684,7 +4720,7 @@
         <v>20</v>
       </c>
       <c r="AV6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW6">
         <v>3</v>
@@ -4696,13 +4732,13 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA6">
         <v>3</v>
       </c>
       <c r="BB6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC6">
         <v>1</v>
@@ -4711,13 +4747,13 @@
         <v>1</v>
       </c>
       <c r="BE6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BG6">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH6" t="s">
         <v>262</v>
@@ -4735,10 +4771,10 @@
         <v>9</v>
       </c>
       <c r="BM6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO6">
         <v>3</v>
@@ -4750,7 +4786,7 @@
         <v>20</v>
       </c>
       <c r="BR6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS6">
         <v>3</v>
@@ -4762,13 +4798,13 @@
         <v>20</v>
       </c>
       <c r="BV6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW6">
         <v>3</v>
       </c>
       <c r="BX6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY6">
         <v>1</v>
@@ -4777,16 +4813,16 @@
         <v>1</v>
       </c>
       <c r="CA6">
-        <v>2800000</v>
+        <v>2100000</v>
       </c>
       <c r="CB6" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="CC6">
         <v>55</v>
       </c>
       <c r="CD6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE6">
         <v>1</v>
@@ -4801,10 +4837,10 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK6">
         <v>3</v>
@@ -4816,7 +4852,7 @@
         <v>20</v>
       </c>
       <c r="CN6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO6">
         <v>3</v>
@@ -4828,13 +4864,13 @@
         <v>20</v>
       </c>
       <c r="CR6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS6">
         <v>3</v>
       </c>
       <c r="CT6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU6">
         <v>1</v>
@@ -4843,22 +4879,22 @@
         <v>1</v>
       </c>
       <c r="CW6">
-        <v>7900</v>
+        <v>6000</v>
       </c>
       <c r="CX6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY6">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA6" t="b">
         <v>1</v>
       </c>
       <c r="DB6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC6">
         <v>1</v>
@@ -4873,10 +4909,10 @@
         <v>9</v>
       </c>
       <c r="DG6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI6">
         <v>3</v>
@@ -4888,7 +4924,7 @@
         <v>20</v>
       </c>
       <c r="DL6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM6">
         <v>3</v>
@@ -4900,16 +4936,16 @@
         <v>20</v>
       </c>
       <c r="DP6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ6">
         <v>3</v>
       </c>
       <c r="DR6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT6">
         <v>1</v>
@@ -4918,16 +4954,16 @@
         <v>1</v>
       </c>
       <c r="DV6">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="DW6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="DX6" t="b">
         <v>1</v>
       </c>
       <c r="DY6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ6">
         <v>1</v>
@@ -4942,10 +4978,10 @@
         <v>9</v>
       </c>
       <c r="ED6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF6">
         <v>3</v>
@@ -4957,7 +4993,7 @@
         <v>20</v>
       </c>
       <c r="EI6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ6">
         <v>3</v>
@@ -4969,16 +5005,16 @@
         <v>20</v>
       </c>
       <c r="EM6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN6">
         <v>3</v>
       </c>
       <c r="EO6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ6">
         <v>0</v>
@@ -4987,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="EV6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW6">
         <v>1</v>
@@ -5002,10 +5038,10 @@
         <v>9</v>
       </c>
       <c r="FA6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC6">
         <v>3</v>
@@ -5017,7 +5053,7 @@
         <v>20</v>
       </c>
       <c r="FF6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG6">
         <v>3</v>
@@ -5029,16 +5065,16 @@
         <v>20</v>
       </c>
       <c r="FJ6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK6">
         <v>3</v>
       </c>
       <c r="FL6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN6">
         <v>0</v>
@@ -5047,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="FR6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS6">
         <v>1</v>
@@ -5056,19 +5092,19 @@
         <v>1</v>
       </c>
       <c r="FU6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="FV6">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="FW6">
         <v>7200</v>
       </c>
       <c r="FX6">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FY6">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FZ6">
         <v>0.9</v>
@@ -5083,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="GM6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN6">
         <v>0.05</v>
@@ -5098,13 +5134,13 @@
         <v>8.5</v>
       </c>
       <c r="GR6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS6" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU6">
         <v>1</v>
@@ -5113,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="GW6">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="GX6">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="GY6">
         <v>0.95</v>
@@ -5131,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="HC6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD6">
         <v>0</v>
@@ -5140,19 +5176,19 @@
         <v>0</v>
       </c>
       <c r="HJ6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM6">
         <v>86400</v>
       </c>
       <c r="HN6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO6">
         <v>86400</v>
@@ -5164,7 +5200,7 @@
         <v>262</v>
       </c>
       <c r="HR6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS6" t="s">
         <v>262</v>
@@ -5176,7 +5212,7 @@
         <v>262</v>
       </c>
       <c r="HV6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW6">
         <v>86400</v>
@@ -5220,13 +5256,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>5527000</v>
+        <v>3863000</v>
       </c>
       <c r="O7" t="s">
         <v>246</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5241,10 +5277,10 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W7">
         <v>3</v>
@@ -5256,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="Z7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA7">
         <v>3</v>
@@ -5268,13 +5304,13 @@
         <v>20</v>
       </c>
       <c r="AD7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE7">
         <v>3</v>
       </c>
       <c r="AF7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG7">
         <v>0</v>
@@ -5286,7 +5322,7 @@
         <v>6</v>
       </c>
       <c r="AL7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM7">
         <v>1</v>
@@ -5301,10 +5337,10 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS7">
         <v>3</v>
@@ -5316,7 +5352,7 @@
         <v>20</v>
       </c>
       <c r="AV7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW7">
         <v>3</v>
@@ -5328,13 +5364,13 @@
         <v>20</v>
       </c>
       <c r="AZ7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA7">
         <v>3</v>
       </c>
       <c r="BB7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC7">
         <v>1</v>
@@ -5349,7 +5385,7 @@
         <v>258</v>
       </c>
       <c r="BG7">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH7" t="s">
         <v>262</v>
@@ -5367,10 +5403,10 @@
         <v>9</v>
       </c>
       <c r="BM7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO7">
         <v>3</v>
@@ -5382,7 +5418,7 @@
         <v>20</v>
       </c>
       <c r="BR7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS7">
         <v>3</v>
@@ -5394,13 +5430,13 @@
         <v>20</v>
       </c>
       <c r="BV7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW7">
         <v>3</v>
       </c>
       <c r="BX7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY7">
         <v>1</v>
@@ -5409,16 +5445,16 @@
         <v>1</v>
       </c>
       <c r="CA7">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
       <c r="CB7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="CC7">
         <v>55</v>
       </c>
       <c r="CD7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE7">
         <v>1</v>
@@ -5433,10 +5469,10 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK7">
         <v>3</v>
@@ -5448,7 +5484,7 @@
         <v>20</v>
       </c>
       <c r="CN7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO7">
         <v>3</v>
@@ -5460,13 +5496,13 @@
         <v>20</v>
       </c>
       <c r="CR7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS7">
         <v>3</v>
       </c>
       <c r="CT7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU7">
         <v>1</v>
@@ -5475,10 +5511,10 @@
         <v>1</v>
       </c>
       <c r="CW7">
-        <v>9900</v>
+        <v>6100</v>
       </c>
       <c r="CX7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY7">
         <v>0</v>
@@ -5490,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="DB7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC7">
         <v>1</v>
@@ -5505,10 +5541,10 @@
         <v>9</v>
       </c>
       <c r="DG7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI7">
         <v>3</v>
@@ -5520,7 +5556,7 @@
         <v>20</v>
       </c>
       <c r="DL7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM7">
         <v>3</v>
@@ -5532,16 +5568,16 @@
         <v>20</v>
       </c>
       <c r="DP7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ7">
         <v>3</v>
       </c>
       <c r="DR7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT7">
         <v>1</v>
@@ -5550,16 +5586,16 @@
         <v>1</v>
       </c>
       <c r="DV7">
-        <v>2600</v>
+        <v>1700</v>
       </c>
       <c r="DW7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="DX7" t="b">
         <v>1</v>
       </c>
       <c r="DY7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ7">
         <v>1</v>
@@ -5574,10 +5610,10 @@
         <v>9</v>
       </c>
       <c r="ED7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF7">
         <v>3</v>
@@ -5589,7 +5625,7 @@
         <v>20</v>
       </c>
       <c r="EI7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ7">
         <v>3</v>
@@ -5601,16 +5637,16 @@
         <v>20</v>
       </c>
       <c r="EM7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN7">
         <v>3</v>
       </c>
       <c r="EO7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ7">
         <v>0</v>
@@ -5619,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="EV7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW7">
         <v>1</v>
@@ -5634,10 +5670,10 @@
         <v>9</v>
       </c>
       <c r="FA7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC7">
         <v>3</v>
@@ -5649,7 +5685,7 @@
         <v>20</v>
       </c>
       <c r="FF7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG7">
         <v>3</v>
@@ -5661,16 +5697,16 @@
         <v>20</v>
       </c>
       <c r="FJ7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK7">
         <v>3</v>
       </c>
       <c r="FL7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN7">
         <v>0</v>
@@ -5679,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="FR7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS7">
         <v>1</v>
@@ -5688,19 +5724,19 @@
         <v>1</v>
       </c>
       <c r="FU7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="FV7">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FW7">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FX7">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="FY7">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="FZ7">
         <v>0.9</v>
@@ -5715,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="GM7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN7">
         <v>0.05</v>
@@ -5730,13 +5766,13 @@
         <v>8.5</v>
       </c>
       <c r="GR7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU7">
         <v>1</v>
@@ -5745,10 +5781,10 @@
         <v>1</v>
       </c>
       <c r="GW7">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="GX7">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="GY7">
         <v>0.95</v>
@@ -5763,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="HC7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD7">
         <v>0</v>
@@ -5772,19 +5808,19 @@
         <v>0</v>
       </c>
       <c r="HJ7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM7">
         <v>86400</v>
       </c>
       <c r="HN7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO7">
         <v>86400</v>
@@ -5796,7 +5832,7 @@
         <v>262</v>
       </c>
       <c r="HR7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS7" t="s">
         <v>262</v>
@@ -5808,7 +5844,7 @@
         <v>262</v>
       </c>
       <c r="HV7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW7">
         <v>86400</v>
@@ -5852,13 +5888,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3125000</v>
+        <v>4536000</v>
       </c>
       <c r="O8" t="s">
         <v>247</v>
       </c>
       <c r="P8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -5873,10 +5909,10 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W8">
         <v>3</v>
@@ -5888,7 +5924,7 @@
         <v>20</v>
       </c>
       <c r="Z8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA8">
         <v>3</v>
@@ -5900,13 +5936,13 @@
         <v>20</v>
       </c>
       <c r="AD8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE8">
         <v>3</v>
       </c>
       <c r="AF8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG8">
         <v>0</v>
@@ -5918,7 +5954,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM8">
         <v>1</v>
@@ -5933,10 +5969,10 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS8">
         <v>3</v>
@@ -5948,7 +5984,7 @@
         <v>20</v>
       </c>
       <c r="AV8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW8">
         <v>3</v>
@@ -5960,13 +5996,13 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA8">
         <v>3</v>
       </c>
       <c r="BB8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC8">
         <v>1</v>
@@ -5999,10 +6035,10 @@
         <v>9</v>
       </c>
       <c r="BM8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO8">
         <v>3</v>
@@ -6014,7 +6050,7 @@
         <v>20</v>
       </c>
       <c r="BR8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS8">
         <v>3</v>
@@ -6026,13 +6062,13 @@
         <v>20</v>
       </c>
       <c r="BV8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW8">
         <v>3</v>
       </c>
       <c r="BX8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY8">
         <v>1</v>
@@ -6041,16 +6077,16 @@
         <v>1</v>
       </c>
       <c r="CA8">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="CB8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="CC8">
         <v>55</v>
       </c>
       <c r="CD8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE8">
         <v>1</v>
@@ -6065,10 +6101,10 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK8">
         <v>3</v>
@@ -6080,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="CN8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO8">
         <v>3</v>
@@ -6092,13 +6128,13 @@
         <v>20</v>
       </c>
       <c r="CR8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS8">
         <v>3</v>
       </c>
       <c r="CT8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU8">
         <v>1</v>
@@ -6107,22 +6143,22 @@
         <v>1</v>
       </c>
       <c r="CW8">
-        <v>4700</v>
+        <v>5900</v>
       </c>
       <c r="CX8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY8">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ8">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA8" t="b">
         <v>1</v>
       </c>
       <c r="DB8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC8">
         <v>1</v>
@@ -6137,10 +6173,10 @@
         <v>9</v>
       </c>
       <c r="DG8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI8">
         <v>3</v>
@@ -6152,7 +6188,7 @@
         <v>20</v>
       </c>
       <c r="DL8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM8">
         <v>3</v>
@@ -6164,16 +6200,16 @@
         <v>20</v>
       </c>
       <c r="DP8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ8">
         <v>3</v>
       </c>
       <c r="DR8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT8">
         <v>1</v>
@@ -6182,16 +6218,16 @@
         <v>1</v>
       </c>
       <c r="DV8">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="DW8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="DX8" t="b">
         <v>1</v>
       </c>
       <c r="DY8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ8">
         <v>1</v>
@@ -6206,10 +6242,10 @@
         <v>9</v>
       </c>
       <c r="ED8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF8">
         <v>3</v>
@@ -6221,7 +6257,7 @@
         <v>20</v>
       </c>
       <c r="EI8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ8">
         <v>3</v>
@@ -6233,16 +6269,16 @@
         <v>20</v>
       </c>
       <c r="EM8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN8">
         <v>3</v>
       </c>
       <c r="EO8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ8">
         <v>0</v>
@@ -6251,7 +6287,7 @@
         <v>0</v>
       </c>
       <c r="EV8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW8">
         <v>1</v>
@@ -6266,10 +6302,10 @@
         <v>9</v>
       </c>
       <c r="FA8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC8">
         <v>3</v>
@@ -6281,7 +6317,7 @@
         <v>20</v>
       </c>
       <c r="FF8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG8">
         <v>3</v>
@@ -6293,16 +6329,16 @@
         <v>20</v>
       </c>
       <c r="FJ8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK8">
         <v>3</v>
       </c>
       <c r="FL8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN8">
         <v>0</v>
@@ -6311,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="FR8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS8">
         <v>1</v>
@@ -6320,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="FU8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="FV8">
         <v>75000</v>
@@ -6347,7 +6383,7 @@
         <v>0</v>
       </c>
       <c r="GM8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN8">
         <v>0.05</v>
@@ -6362,13 +6398,13 @@
         <v>8.5</v>
       </c>
       <c r="GR8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU8">
         <v>1</v>
@@ -6377,10 +6413,10 @@
         <v>1</v>
       </c>
       <c r="GW8">
-        <v>3100</v>
+        <v>4500</v>
       </c>
       <c r="GX8">
-        <v>3100</v>
+        <v>4500</v>
       </c>
       <c r="GY8">
         <v>0.95</v>
@@ -6395,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="HC8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD8">
         <v>0</v>
@@ -6404,19 +6440,19 @@
         <v>0</v>
       </c>
       <c r="HJ8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL8" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM8">
         <v>86400</v>
       </c>
       <c r="HN8" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO8">
         <v>86400</v>
@@ -6428,7 +6464,7 @@
         <v>262</v>
       </c>
       <c r="HR8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS8" t="s">
         <v>262</v>
@@ -6440,7 +6476,7 @@
         <v>262</v>
       </c>
       <c r="HV8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW8">
         <v>86400</v>
@@ -6460,10 +6496,10 @@
         <v>239</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -6472,7 +6508,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -6484,13 +6520,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>2262000</v>
+        <v>3125000</v>
       </c>
       <c r="O9" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="P9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6505,10 +6541,10 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W9">
         <v>3</v>
@@ -6520,7 +6556,7 @@
         <v>20</v>
       </c>
       <c r="Z9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA9">
         <v>3</v>
@@ -6532,13 +6568,13 @@
         <v>20</v>
       </c>
       <c r="AD9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE9">
         <v>3</v>
       </c>
       <c r="AF9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG9">
         <v>0</v>
@@ -6550,7 +6586,7 @@
         <v>6</v>
       </c>
       <c r="AL9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM9">
         <v>1</v>
@@ -6565,10 +6601,10 @@
         <v>9</v>
       </c>
       <c r="AQ9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS9">
         <v>3</v>
@@ -6580,7 +6616,7 @@
         <v>20</v>
       </c>
       <c r="AV9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW9">
         <v>3</v>
@@ -6592,13 +6628,13 @@
         <v>20</v>
       </c>
       <c r="AZ9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA9">
         <v>3</v>
       </c>
       <c r="BB9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC9">
         <v>1</v>
@@ -6607,7 +6643,7 @@
         <v>1</v>
       </c>
       <c r="BE9">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF9" t="s">
         <v>260</v>
@@ -6631,10 +6667,10 @@
         <v>9</v>
       </c>
       <c r="BM9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO9">
         <v>3</v>
@@ -6646,7 +6682,7 @@
         <v>20</v>
       </c>
       <c r="BR9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS9">
         <v>3</v>
@@ -6658,13 +6694,13 @@
         <v>20</v>
       </c>
       <c r="BV9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW9">
         <v>3</v>
       </c>
       <c r="BX9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY9">
         <v>1</v>
@@ -6673,16 +6709,16 @@
         <v>1</v>
       </c>
       <c r="CA9">
-        <v>2400000</v>
+        <v>2800000</v>
       </c>
       <c r="CB9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="CC9">
         <v>55</v>
       </c>
       <c r="CD9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE9">
         <v>1</v>
@@ -6697,10 +6733,10 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK9">
         <v>3</v>
@@ -6712,7 +6748,7 @@
         <v>20</v>
       </c>
       <c r="CN9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO9">
         <v>3</v>
@@ -6724,13 +6760,13 @@
         <v>20</v>
       </c>
       <c r="CR9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS9">
         <v>3</v>
       </c>
       <c r="CT9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU9">
         <v>1</v>
@@ -6739,10 +6775,10 @@
         <v>1</v>
       </c>
       <c r="CW9">
-        <v>3200</v>
+        <v>4800</v>
       </c>
       <c r="CX9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY9">
         <v>0</v>
@@ -6754,7 +6790,7 @@
         <v>1</v>
       </c>
       <c r="DB9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC9">
         <v>1</v>
@@ -6769,10 +6805,10 @@
         <v>9</v>
       </c>
       <c r="DG9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI9">
         <v>3</v>
@@ -6784,7 +6820,7 @@
         <v>20</v>
       </c>
       <c r="DL9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM9">
         <v>3</v>
@@ -6796,16 +6832,16 @@
         <v>20</v>
       </c>
       <c r="DP9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ9">
         <v>3</v>
       </c>
       <c r="DR9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT9">
         <v>1</v>
@@ -6814,16 +6850,16 @@
         <v>1</v>
       </c>
       <c r="DV9">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="DW9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="DX9" t="b">
         <v>1</v>
       </c>
       <c r="DY9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ9">
         <v>1</v>
@@ -6838,10 +6874,10 @@
         <v>9</v>
       </c>
       <c r="ED9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF9">
         <v>3</v>
@@ -6853,7 +6889,7 @@
         <v>20</v>
       </c>
       <c r="EI9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ9">
         <v>3</v>
@@ -6865,16 +6901,16 @@
         <v>20</v>
       </c>
       <c r="EM9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN9">
         <v>3</v>
       </c>
       <c r="EO9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ9">
         <v>0</v>
@@ -6883,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="EV9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW9">
         <v>1</v>
@@ -6898,10 +6934,10 @@
         <v>9</v>
       </c>
       <c r="FA9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC9">
         <v>3</v>
@@ -6913,7 +6949,7 @@
         <v>20</v>
       </c>
       <c r="FF9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG9">
         <v>3</v>
@@ -6925,16 +6961,16 @@
         <v>20</v>
       </c>
       <c r="FJ9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK9">
         <v>3</v>
       </c>
       <c r="FL9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN9">
         <v>0</v>
@@ -6943,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="FR9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS9">
         <v>1</v>
@@ -6952,19 +6988,19 @@
         <v>1</v>
       </c>
       <c r="FU9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="FV9">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="FW9">
         <v>7200</v>
       </c>
       <c r="FX9">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FY9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FZ9">
         <v>0.9</v>
@@ -6979,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="GM9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN9">
         <v>0.05</v>
@@ -6994,13 +7030,13 @@
         <v>8.5</v>
       </c>
       <c r="GR9" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU9">
         <v>1</v>
@@ -7009,10 +7045,10 @@
         <v>1</v>
       </c>
       <c r="GW9">
-        <v>2300</v>
+        <v>3100</v>
       </c>
       <c r="GX9">
-        <v>2300</v>
+        <v>3100</v>
       </c>
       <c r="GY9">
         <v>0.95</v>
@@ -7027,7 +7063,7 @@
         <v>0</v>
       </c>
       <c r="HC9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD9">
         <v>0</v>
@@ -7036,19 +7072,19 @@
         <v>0</v>
       </c>
       <c r="HJ9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL9" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM9">
         <v>86400</v>
       </c>
       <c r="HN9" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO9">
         <v>86400</v>
@@ -7060,7 +7096,7 @@
         <v>262</v>
       </c>
       <c r="HR9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS9" t="s">
         <v>262</v>
@@ -7072,7 +7108,7 @@
         <v>262</v>
       </c>
       <c r="HV9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW9">
         <v>86400</v>
@@ -7116,13 +7152,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>5527000</v>
+        <v>2687000</v>
       </c>
       <c r="O10" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -7137,10 +7173,10 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W10">
         <v>3</v>
@@ -7152,7 +7188,7 @@
         <v>20</v>
       </c>
       <c r="Z10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA10">
         <v>3</v>
@@ -7164,13 +7200,13 @@
         <v>20</v>
       </c>
       <c r="AD10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE10">
         <v>3</v>
       </c>
       <c r="AF10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG10">
         <v>0</v>
@@ -7182,7 +7218,7 @@
         <v>6</v>
       </c>
       <c r="AL10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM10">
         <v>1</v>
@@ -7197,10 +7233,10 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS10">
         <v>3</v>
@@ -7212,7 +7248,7 @@
         <v>20</v>
       </c>
       <c r="AV10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW10">
         <v>3</v>
@@ -7224,13 +7260,13 @@
         <v>20</v>
       </c>
       <c r="AZ10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA10">
         <v>3</v>
       </c>
       <c r="BB10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC10">
         <v>1</v>
@@ -7242,10 +7278,10 @@
         <v>5500000</v>
       </c>
       <c r="BF10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="BG10">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH10" t="s">
         <v>262</v>
@@ -7263,10 +7299,10 @@
         <v>9</v>
       </c>
       <c r="BM10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO10">
         <v>3</v>
@@ -7278,7 +7314,7 @@
         <v>20</v>
       </c>
       <c r="BR10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS10">
         <v>3</v>
@@ -7290,13 +7326,13 @@
         <v>20</v>
       </c>
       <c r="BV10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW10">
         <v>3</v>
       </c>
       <c r="BX10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY10">
         <v>1</v>
@@ -7305,16 +7341,16 @@
         <v>1</v>
       </c>
       <c r="CA10">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="CB10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="CC10">
         <v>55</v>
       </c>
       <c r="CD10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE10">
         <v>1</v>
@@ -7329,10 +7365,10 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK10">
         <v>3</v>
@@ -7344,7 +7380,7 @@
         <v>20</v>
       </c>
       <c r="CN10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO10">
         <v>3</v>
@@ -7356,13 +7392,13 @@
         <v>20</v>
       </c>
       <c r="CR10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS10">
         <v>3</v>
       </c>
       <c r="CT10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU10">
         <v>1</v>
@@ -7371,10 +7407,10 @@
         <v>1</v>
       </c>
       <c r="CW10">
-        <v>8800</v>
+        <v>4800</v>
       </c>
       <c r="CX10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY10">
         <v>0</v>
@@ -7386,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="DB10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC10">
         <v>1</v>
@@ -7401,10 +7437,10 @@
         <v>9</v>
       </c>
       <c r="DG10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI10">
         <v>3</v>
@@ -7416,7 +7452,7 @@
         <v>20</v>
       </c>
       <c r="DL10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM10">
         <v>3</v>
@@ -7428,16 +7464,16 @@
         <v>20</v>
       </c>
       <c r="DP10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ10">
         <v>3</v>
       </c>
       <c r="DR10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT10">
         <v>1</v>
@@ -7446,16 +7482,16 @@
         <v>1</v>
       </c>
       <c r="DV10">
-        <v>4300</v>
+        <v>2100</v>
       </c>
       <c r="DW10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DX10" t="b">
         <v>1</v>
       </c>
       <c r="DY10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ10">
         <v>1</v>
@@ -7470,10 +7506,10 @@
         <v>9</v>
       </c>
       <c r="ED10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF10">
         <v>3</v>
@@ -7485,7 +7521,7 @@
         <v>20</v>
       </c>
       <c r="EI10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ10">
         <v>3</v>
@@ -7497,16 +7533,16 @@
         <v>20</v>
       </c>
       <c r="EM10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN10">
         <v>3</v>
       </c>
       <c r="EO10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ10">
         <v>0</v>
@@ -7515,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="EV10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW10">
         <v>1</v>
@@ -7530,10 +7566,10 @@
         <v>9</v>
       </c>
       <c r="FA10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC10">
         <v>3</v>
@@ -7545,7 +7581,7 @@
         <v>20</v>
       </c>
       <c r="FF10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG10">
         <v>3</v>
@@ -7557,16 +7593,16 @@
         <v>20</v>
       </c>
       <c r="FJ10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK10">
         <v>3</v>
       </c>
       <c r="FL10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN10">
         <v>0</v>
@@ -7575,7 +7611,7 @@
         <v>0</v>
       </c>
       <c r="FR10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS10">
         <v>1</v>
@@ -7584,7 +7620,7 @@
         <v>1</v>
       </c>
       <c r="FU10" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="FV10">
         <v>50000</v>
@@ -7611,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="GM10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN10">
         <v>0.05</v>
@@ -7626,13 +7662,13 @@
         <v>8.5</v>
       </c>
       <c r="GR10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU10">
         <v>1</v>
@@ -7641,10 +7677,10 @@
         <v>1</v>
       </c>
       <c r="GW10">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="GX10">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="GY10">
         <v>0.95</v>
@@ -7659,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="HC10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD10">
         <v>0</v>
@@ -7668,19 +7704,19 @@
         <v>0</v>
       </c>
       <c r="HJ10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK10" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL10" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM10">
         <v>86400</v>
       </c>
       <c r="HN10" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO10">
         <v>86400</v>
@@ -7692,7 +7728,7 @@
         <v>262</v>
       </c>
       <c r="HR10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS10" t="s">
         <v>262</v>
@@ -7704,7 +7740,7 @@
         <v>262</v>
       </c>
       <c r="HV10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW10">
         <v>86400</v>
@@ -7724,10 +7760,10 @@
         <v>241</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -7736,7 +7772,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7748,13 +7784,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>4536000</v>
+        <v>5527000</v>
       </c>
       <c r="O11" t="s">
         <v>245</v>
       </c>
       <c r="P11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -7769,10 +7805,10 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="V11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="W11">
         <v>3</v>
@@ -7784,7 +7820,7 @@
         <v>20</v>
       </c>
       <c r="Z11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA11">
         <v>3</v>
@@ -7796,13 +7832,13 @@
         <v>20</v>
       </c>
       <c r="AD11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AE11">
         <v>3</v>
       </c>
       <c r="AF11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AG11">
         <v>0</v>
@@ -7814,7 +7850,7 @@
         <v>6</v>
       </c>
       <c r="AL11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM11">
         <v>1</v>
@@ -7829,10 +7865,10 @@
         <v>9</v>
       </c>
       <c r="AQ11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AR11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AS11">
         <v>3</v>
@@ -7844,7 +7880,7 @@
         <v>20</v>
       </c>
       <c r="AV11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AW11">
         <v>3</v>
@@ -7856,13 +7892,13 @@
         <v>20</v>
       </c>
       <c r="AZ11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BA11">
         <v>3</v>
       </c>
       <c r="BB11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BC11">
         <v>1</v>
@@ -7871,13 +7907,13 @@
         <v>1</v>
       </c>
       <c r="BE11">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="BG11">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH11" t="s">
         <v>262</v>
@@ -7895,10 +7931,10 @@
         <v>9</v>
       </c>
       <c r="BM11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BN11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BO11">
         <v>3</v>
@@ -7910,7 +7946,7 @@
         <v>20</v>
       </c>
       <c r="BR11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BS11">
         <v>3</v>
@@ -7922,13 +7958,13 @@
         <v>20</v>
       </c>
       <c r="BV11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BW11">
         <v>3</v>
       </c>
       <c r="BX11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BY11">
         <v>1</v>
@@ -7940,13 +7976,13 @@
         <v>2400000</v>
       </c>
       <c r="CB11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="CC11">
         <v>55</v>
       </c>
       <c r="CD11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="CE11">
         <v>1</v>
@@ -7961,10 +7997,10 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="CJ11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CK11">
         <v>3</v>
@@ -7976,7 +8012,7 @@
         <v>20</v>
       </c>
       <c r="CN11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CO11">
         <v>3</v>
@@ -7988,13 +8024,13 @@
         <v>20</v>
       </c>
       <c r="CR11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CS11">
         <v>3</v>
       </c>
       <c r="CT11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CU11">
         <v>1</v>
@@ -8003,22 +8039,22 @@
         <v>1</v>
       </c>
       <c r="CW11">
-        <v>6100</v>
+        <v>9400</v>
       </c>
       <c r="CX11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="CY11">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA11" t="b">
         <v>1</v>
       </c>
       <c r="DB11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DC11">
         <v>1</v>
@@ -8033,10 +8069,10 @@
         <v>9</v>
       </c>
       <c r="DG11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="DH11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DI11">
         <v>3</v>
@@ -8048,7 +8084,7 @@
         <v>20</v>
       </c>
       <c r="DL11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DM11">
         <v>3</v>
@@ -8060,16 +8096,16 @@
         <v>20</v>
       </c>
       <c r="DP11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DQ11">
         <v>3</v>
       </c>
       <c r="DR11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DS11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="DT11">
         <v>1</v>
@@ -8078,16 +8114,16 @@
         <v>1</v>
       </c>
       <c r="DV11">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="DW11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="DX11" t="b">
         <v>1</v>
       </c>
       <c r="DY11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="DZ11">
         <v>1</v>
@@ -8102,10 +8138,10 @@
         <v>9</v>
       </c>
       <c r="ED11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="EE11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EF11">
         <v>3</v>
@@ -8117,7 +8153,7 @@
         <v>20</v>
       </c>
       <c r="EI11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EJ11">
         <v>3</v>
@@ -8129,16 +8165,16 @@
         <v>20</v>
       </c>
       <c r="EM11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EN11">
         <v>3</v>
       </c>
       <c r="EO11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EP11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="EQ11">
         <v>0</v>
@@ -8147,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="EV11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="EW11">
         <v>1</v>
@@ -8162,10 +8198,10 @@
         <v>9</v>
       </c>
       <c r="FA11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="FB11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FC11">
         <v>3</v>
@@ -8177,7 +8213,7 @@
         <v>20</v>
       </c>
       <c r="FF11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FG11">
         <v>3</v>
@@ -8189,16 +8225,16 @@
         <v>20</v>
       </c>
       <c r="FJ11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FK11">
         <v>3</v>
       </c>
       <c r="FL11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FM11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FN11">
         <v>0</v>
@@ -8207,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="FR11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FS11">
         <v>1</v>
@@ -8216,19 +8252,19 @@
         <v>1</v>
       </c>
       <c r="FU11" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="FV11">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FW11">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX11">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="FY11">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="FZ11">
         <v>0.9</v>
@@ -8243,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="GM11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="GN11">
         <v>0.05</v>
@@ -8258,13 +8294,13 @@
         <v>8.5</v>
       </c>
       <c r="GR11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="GS11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="GT11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="GU11">
         <v>1</v>
@@ -8273,10 +8309,10 @@
         <v>1</v>
       </c>
       <c r="GW11">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="GX11">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="GY11">
         <v>0.95</v>
@@ -8291,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="HC11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HD11">
         <v>0</v>
@@ -8300,19 +8336,19 @@
         <v>0</v>
       </c>
       <c r="HJ11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="HK11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HL11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="HM11">
         <v>86400</v>
       </c>
       <c r="HN11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="HO11">
         <v>86400</v>
@@ -8324,7 +8360,7 @@
         <v>262</v>
       </c>
       <c r="HR11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HS11" t="s">
         <v>262</v>
@@ -8336,7 +8372,7 @@
         <v>262</v>
       </c>
       <c r="HV11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="HW11">
         <v>86400</v>
@@ -8372,13 +8408,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -9089,7 +9125,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9476,22 +9512,22 @@
         <v>193</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="EI1" s="1" t="s">
         <v>198</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="EK1" s="1" t="s">
         <v>200</v>
@@ -9593,7 +9629,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -10466,58 +10502,58 @@
         <v>209</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>217</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="320">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -717,60 +717,57 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>AqWXE9DEO8hByue</t>
-  </si>
-  <si>
-    <t>aM0cFJcGazmTn74</t>
-  </si>
-  <si>
-    <t>dGjALyULMFUj8m3</t>
-  </si>
-  <si>
-    <t>g2wXSWhRgXPfwXM</t>
-  </si>
-  <si>
-    <t>V0ADANY7ClQZ4lm</t>
-  </si>
-  <si>
-    <t>wuhhnp1FBrx3XSL</t>
-  </si>
-  <si>
-    <t>QVlvnKyFkva8qU4</t>
-  </si>
-  <si>
-    <t>Xdq8WMnHTivaCxj</t>
-  </si>
-  <si>
-    <t>zsgQNT5cOwiWLqg</t>
-  </si>
-  <si>
-    <t>kn47c0hnjvJ11j0</t>
+    <t>Xsg719VWbzc8WGq</t>
+  </si>
+  <si>
+    <t>tlndEuosN2YTsfi</t>
+  </si>
+  <si>
+    <t>eSoMCS0UISzmJjZ</t>
+  </si>
+  <si>
+    <t>zc3xI9GvdO0JEmA</t>
+  </si>
+  <si>
+    <t>A3GbC1RuCSzwfsB</t>
+  </si>
+  <si>
+    <t>b1LwgBQqloIH4Ia</t>
+  </si>
+  <si>
+    <t>EWHJ2Ztf4uf7kXD</t>
+  </si>
+  <si>
+    <t>WWosr6A645WT33L</t>
+  </si>
+  <si>
+    <t>rnExJsXYZDHNtOh</t>
+  </si>
+  <si>
+    <t>xiEjT08QnVwRPwo</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
   </si>
   <si>
     <t>hh_2262_0.csv</t>
   </si>
   <si>
-    <t>hh_3564_0.csv</t>
+    <t>hh_2012_3.csv</t>
+  </si>
+  <si>
+    <t>hh_4536_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
   </si>
   <si>
     <t>hh_4402_0.csv</t>
   </si>
   <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3863_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4536_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
     <t>perfect</t>
   </si>
   <si>
@@ -786,48 +783,51 @@
     <t>rfr</t>
   </si>
   <si>
-    <t>heat_gen_5_pu.csv</t>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2262_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2012_3.csv</t>
+  </si>
+  <si>
+    <t>heat_4536_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_4_pu.csv</t>
   </si>
   <si>
     <t>heat_4402_0.csv</t>
   </si>
   <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3863_0.csv</t>
-  </si>
-  <si>
-    <t>heat_4536_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_2687_0.csv</t>
-  </si>
-  <si>
     <t>naive</t>
   </si>
   <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
     <t>dhw_gen_3_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
     <t>dhw_gen_1_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -837,49 +837,49 @@
     <t>green_local</t>
   </si>
   <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
     <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
   </si>
   <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
     <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
   </si>
   <si>
-    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
-  </si>
-  <si>
-    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
-  </si>
-  <si>
-    <t>rnn</t>
+    <t>arima</t>
   </si>
   <si>
     <t>local</t>
   </si>
   <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_47.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
     <t>ev_freetime_3.csv</t>
   </si>
   <si>
     <t>ev_fulltime_46.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_43.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_42.csv</t>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_1.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_44.csv</t>
   </si>
   <si>
     <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_0.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_90.csv</t>
   </si>
   <si>
     <t>price_sensitive</t>
@@ -2069,13 +2069,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>2262000</v>
+        <v>3863000</v>
       </c>
       <c r="O2" t="s">
         <v>242</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2090,40 +2090,40 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V2" t="s">
+        <v>251</v>
+      </c>
+      <c r="W2">
+        <v>3</v>
+      </c>
+      <c r="X2">
+        <v>20</v>
+      </c>
+      <c r="Y2">
+        <v>20</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>20</v>
+      </c>
+      <c r="AC2">
+        <v>20</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE2">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="s">
         <v>252</v>
-      </c>
-      <c r="W2">
-        <v>3</v>
-      </c>
-      <c r="X2">
-        <v>20</v>
-      </c>
-      <c r="Y2">
-        <v>20</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA2">
-        <v>3</v>
-      </c>
-      <c r="AB2">
-        <v>20</v>
-      </c>
-      <c r="AC2">
-        <v>20</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE2">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>253</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2135,7 +2135,7 @@
         <v>6</v>
       </c>
       <c r="AL2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM2">
         <v>1</v>
@@ -2150,40 +2150,40 @@
         <v>9</v>
       </c>
       <c r="AQ2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS2">
+        <v>3</v>
+      </c>
+      <c r="AT2">
+        <v>20</v>
+      </c>
+      <c r="AU2">
+        <v>20</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW2">
+        <v>3</v>
+      </c>
+      <c r="AX2">
+        <v>20</v>
+      </c>
+      <c r="AY2">
+        <v>20</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA2">
+        <v>3</v>
+      </c>
+      <c r="BB2" t="s">
         <v>252</v>
-      </c>
-      <c r="AS2">
-        <v>3</v>
-      </c>
-      <c r="AT2">
-        <v>20</v>
-      </c>
-      <c r="AU2">
-        <v>20</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW2">
-        <v>3</v>
-      </c>
-      <c r="AX2">
-        <v>20</v>
-      </c>
-      <c r="AY2">
-        <v>20</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA2">
-        <v>3</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>253</v>
       </c>
       <c r="BC2">
         <v>1</v>
@@ -2195,13 +2195,13 @@
         <v>5500000</v>
       </c>
       <c r="BF2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI2">
         <v>1</v>
@@ -2216,40 +2216,40 @@
         <v>9</v>
       </c>
       <c r="BM2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO2">
+        <v>3</v>
+      </c>
+      <c r="BP2">
+        <v>20</v>
+      </c>
+      <c r="BQ2">
+        <v>20</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS2">
+        <v>3</v>
+      </c>
+      <c r="BT2">
+        <v>20</v>
+      </c>
+      <c r="BU2">
+        <v>20</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW2">
+        <v>3</v>
+      </c>
+      <c r="BX2" t="s">
         <v>252</v>
-      </c>
-      <c r="BO2">
-        <v>3</v>
-      </c>
-      <c r="BP2">
-        <v>20</v>
-      </c>
-      <c r="BQ2">
-        <v>20</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS2">
-        <v>3</v>
-      </c>
-      <c r="BT2">
-        <v>20</v>
-      </c>
-      <c r="BU2">
-        <v>20</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW2">
-        <v>3</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>253</v>
       </c>
       <c r="BY2">
         <v>1</v>
@@ -2261,7 +2261,7 @@
         <v>1800000</v>
       </c>
       <c r="CB2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="CC2">
         <v>55</v>
@@ -2282,41 +2282,41 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ2" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK2">
+        <v>3</v>
+      </c>
+      <c r="CL2">
+        <v>20</v>
+      </c>
+      <c r="CM2">
+        <v>20</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO2">
+        <v>3</v>
+      </c>
+      <c r="CP2">
+        <v>20</v>
+      </c>
+      <c r="CQ2">
+        <v>20</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS2">
+        <v>3</v>
+      </c>
+      <c r="CT2" t="s">
         <v>252</v>
       </c>
-      <c r="CK2">
-        <v>3</v>
-      </c>
-      <c r="CL2">
-        <v>20</v>
-      </c>
-      <c r="CM2">
-        <v>20</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO2">
-        <v>3</v>
-      </c>
-      <c r="CP2">
-        <v>20</v>
-      </c>
-      <c r="CQ2">
-        <v>20</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS2">
-        <v>3</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>253</v>
-      </c>
       <c r="CU2">
         <v>1</v>
       </c>
@@ -2324,22 +2324,22 @@
         <v>1</v>
       </c>
       <c r="CW2">
-        <v>3700</v>
+        <v>6200</v>
       </c>
       <c r="CX2" t="s">
         <v>270</v>
       </c>
       <c r="CY2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA2" t="b">
         <v>1</v>
       </c>
       <c r="DB2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC2">
         <v>1</v>
@@ -2354,40 +2354,40 @@
         <v>9</v>
       </c>
       <c r="DG2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH2" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI2">
+        <v>3</v>
+      </c>
+      <c r="DJ2">
+        <v>20</v>
+      </c>
+      <c r="DK2">
+        <v>20</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM2">
+        <v>3</v>
+      </c>
+      <c r="DN2">
+        <v>20</v>
+      </c>
+      <c r="DO2">
+        <v>20</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ2">
+        <v>3</v>
+      </c>
+      <c r="DR2" t="s">
         <v>252</v>
-      </c>
-      <c r="DI2">
-        <v>3</v>
-      </c>
-      <c r="DJ2">
-        <v>20</v>
-      </c>
-      <c r="DK2">
-        <v>20</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM2">
-        <v>3</v>
-      </c>
-      <c r="DN2">
-        <v>20</v>
-      </c>
-      <c r="DO2">
-        <v>20</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ2">
-        <v>3</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>253</v>
       </c>
       <c r="DS2" t="s">
         <v>271</v>
@@ -2399,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="DV2">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="DW2" t="s">
         <v>272</v>
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="DY2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ2">
         <v>1</v>
@@ -2423,40 +2423,40 @@
         <v>9</v>
       </c>
       <c r="ED2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE2" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF2">
+        <v>3</v>
+      </c>
+      <c r="EG2">
+        <v>20</v>
+      </c>
+      <c r="EH2">
+        <v>20</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ2">
+        <v>3</v>
+      </c>
+      <c r="EK2">
+        <v>20</v>
+      </c>
+      <c r="EL2">
+        <v>20</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN2">
+        <v>3</v>
+      </c>
+      <c r="EO2" t="s">
         <v>252</v>
-      </c>
-      <c r="EF2">
-        <v>3</v>
-      </c>
-      <c r="EG2">
-        <v>20</v>
-      </c>
-      <c r="EH2">
-        <v>20</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ2">
-        <v>3</v>
-      </c>
-      <c r="EK2">
-        <v>20</v>
-      </c>
-      <c r="EL2">
-        <v>20</v>
-      </c>
-      <c r="EM2" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN2">
-        <v>3</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>253</v>
       </c>
       <c r="EP2" t="s">
         <v>271</v>
@@ -2483,73 +2483,73 @@
         <v>9</v>
       </c>
       <c r="FA2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB2" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC2">
+        <v>3</v>
+      </c>
+      <c r="FD2">
+        <v>20</v>
+      </c>
+      <c r="FE2">
+        <v>20</v>
+      </c>
+      <c r="FF2" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG2">
+        <v>3</v>
+      </c>
+      <c r="FH2">
+        <v>20</v>
+      </c>
+      <c r="FI2">
+        <v>20</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK2">
+        <v>3</v>
+      </c>
+      <c r="FL2" t="s">
         <v>252</v>
       </c>
-      <c r="FC2">
-        <v>3</v>
-      </c>
-      <c r="FD2">
-        <v>20</v>
-      </c>
-      <c r="FE2">
-        <v>20</v>
-      </c>
-      <c r="FF2" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG2">
-        <v>3</v>
-      </c>
-      <c r="FH2">
-        <v>20</v>
-      </c>
-      <c r="FI2">
-        <v>20</v>
-      </c>
-      <c r="FJ2" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK2">
-        <v>3</v>
-      </c>
-      <c r="FL2" t="s">
-        <v>253</v>
-      </c>
       <c r="FM2" t="s">
+        <v>277</v>
+      </c>
+      <c r="FN2">
+        <v>0</v>
+      </c>
+      <c r="FO2">
+        <v>0</v>
+      </c>
+      <c r="FR2" t="s">
+        <v>277</v>
+      </c>
+      <c r="FS2">
+        <v>1</v>
+      </c>
+      <c r="FT2">
+        <v>2</v>
+      </c>
+      <c r="FU2" t="s">
         <v>278</v>
       </c>
-      <c r="FN2">
-        <v>0</v>
-      </c>
-      <c r="FO2">
-        <v>0</v>
-      </c>
-      <c r="FR2" t="s">
-        <v>278</v>
-      </c>
-      <c r="FS2">
-        <v>1</v>
-      </c>
-      <c r="FT2">
-        <v>1</v>
-      </c>
-      <c r="FU2" t="s">
-        <v>279</v>
-      </c>
       <c r="FV2">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="FW2">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX2">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="FY2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="FZ2">
         <v>0.9</v>
@@ -2563,6 +2563,33 @@
       <c r="GC2" t="b">
         <v>0</v>
       </c>
+      <c r="GD2" t="s">
+        <v>286</v>
+      </c>
+      <c r="GE2">
+        <v>75000</v>
+      </c>
+      <c r="GF2">
+        <v>7200</v>
+      </c>
+      <c r="GG2">
+        <v>11000</v>
+      </c>
+      <c r="GH2">
+        <v>100000</v>
+      </c>
+      <c r="GI2">
+        <v>0.9</v>
+      </c>
+      <c r="GJ2">
+        <v>0.8</v>
+      </c>
+      <c r="GK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL2" t="b">
+        <v>0</v>
+      </c>
       <c r="GM2" t="s">
         <v>287</v>
       </c>
@@ -2585,7 +2612,7 @@
         <v>289</v>
       </c>
       <c r="GT2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU2">
         <v>1</v>
@@ -2594,10 +2621,10 @@
         <v>1</v>
       </c>
       <c r="GW2">
-        <v>2300</v>
+        <v>3900</v>
       </c>
       <c r="GX2">
-        <v>2300</v>
+        <v>3900</v>
       </c>
       <c r="GY2">
         <v>0.95</v>
@@ -2612,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="HC2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD2">
         <v>0</v>
@@ -2621,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="HJ2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK2" t="s">
         <v>290</v>
@@ -2639,22 +2666,22 @@
         <v>86400</v>
       </c>
       <c r="HP2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR2" t="s">
         <v>292</v>
       </c>
       <c r="HS2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV2" t="s">
         <v>292</v>
@@ -2677,10 +2704,10 @@
         <v>233</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2689,7 +2716,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2701,13 +2728,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>3564000</v>
+        <v>2262000</v>
       </c>
       <c r="O3" t="s">
         <v>243</v>
       </c>
       <c r="P3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2722,40 +2749,40 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V3" t="s">
+        <v>251</v>
+      </c>
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3">
+        <v>20</v>
+      </c>
+      <c r="Y3">
+        <v>20</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
+        <v>20</v>
+      </c>
+      <c r="AC3">
+        <v>20</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE3">
+        <v>3</v>
+      </c>
+      <c r="AF3" t="s">
         <v>252</v>
-      </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3">
-        <v>20</v>
-      </c>
-      <c r="Y3">
-        <v>20</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA3">
-        <v>3</v>
-      </c>
-      <c r="AB3">
-        <v>20</v>
-      </c>
-      <c r="AC3">
-        <v>20</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE3">
-        <v>3</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>253</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -2767,7 +2794,7 @@
         <v>6</v>
       </c>
       <c r="AL3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM3">
         <v>1</v>
@@ -2782,41 +2809,41 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS3">
+        <v>3</v>
+      </c>
+      <c r="AT3">
+        <v>20</v>
+      </c>
+      <c r="AU3">
+        <v>20</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW3">
+        <v>3</v>
+      </c>
+      <c r="AX3">
+        <v>20</v>
+      </c>
+      <c r="AY3">
+        <v>20</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA3">
+        <v>3</v>
+      </c>
+      <c r="BB3" t="s">
         <v>252</v>
       </c>
-      <c r="AS3">
-        <v>3</v>
-      </c>
-      <c r="AT3">
-        <v>20</v>
-      </c>
-      <c r="AU3">
-        <v>20</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW3">
-        <v>3</v>
-      </c>
-      <c r="AX3">
-        <v>20</v>
-      </c>
-      <c r="AY3">
-        <v>20</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA3">
-        <v>3</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>253</v>
-      </c>
       <c r="BC3">
         <v>1</v>
       </c>
@@ -2824,7 +2851,7 @@
         <v>1</v>
       </c>
       <c r="BE3">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF3" t="s">
         <v>255</v>
@@ -2833,7 +2860,7 @@
         <v>55</v>
       </c>
       <c r="BH3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI3">
         <v>1</v>
@@ -2848,41 +2875,41 @@
         <v>9</v>
       </c>
       <c r="BM3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN3" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO3">
+        <v>3</v>
+      </c>
+      <c r="BP3">
+        <v>20</v>
+      </c>
+      <c r="BQ3">
+        <v>20</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS3">
+        <v>3</v>
+      </c>
+      <c r="BT3">
+        <v>20</v>
+      </c>
+      <c r="BU3">
+        <v>20</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW3">
+        <v>3</v>
+      </c>
+      <c r="BX3" t="s">
         <v>252</v>
       </c>
-      <c r="BO3">
-        <v>3</v>
-      </c>
-      <c r="BP3">
-        <v>20</v>
-      </c>
-      <c r="BQ3">
-        <v>20</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS3">
-        <v>3</v>
-      </c>
-      <c r="BT3">
-        <v>20</v>
-      </c>
-      <c r="BU3">
-        <v>20</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW3">
-        <v>3</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>253</v>
-      </c>
       <c r="BY3">
         <v>1</v>
       </c>
@@ -2890,10 +2917,10 @@
         <v>1</v>
       </c>
       <c r="CA3">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="CB3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="CC3">
         <v>55</v>
@@ -2914,41 +2941,41 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ3" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK3">
+        <v>3</v>
+      </c>
+      <c r="CL3">
+        <v>20</v>
+      </c>
+      <c r="CM3">
+        <v>20</v>
+      </c>
+      <c r="CN3" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO3">
+        <v>3</v>
+      </c>
+      <c r="CP3">
+        <v>20</v>
+      </c>
+      <c r="CQ3">
+        <v>20</v>
+      </c>
+      <c r="CR3" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS3">
+        <v>3</v>
+      </c>
+      <c r="CT3" t="s">
         <v>252</v>
       </c>
-      <c r="CK3">
-        <v>3</v>
-      </c>
-      <c r="CL3">
-        <v>20</v>
-      </c>
-      <c r="CM3">
-        <v>20</v>
-      </c>
-      <c r="CN3" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO3">
-        <v>3</v>
-      </c>
-      <c r="CP3">
-        <v>20</v>
-      </c>
-      <c r="CQ3">
-        <v>20</v>
-      </c>
-      <c r="CR3" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS3">
-        <v>3</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>253</v>
-      </c>
       <c r="CU3">
         <v>1</v>
       </c>
@@ -2956,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="CW3">
-        <v>4500</v>
+        <v>3400</v>
       </c>
       <c r="CX3" t="s">
         <v>270</v>
@@ -2971,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="DB3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC3">
         <v>1</v>
@@ -2986,40 +3013,40 @@
         <v>9</v>
       </c>
       <c r="DG3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH3" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI3">
+        <v>3</v>
+      </c>
+      <c r="DJ3">
+        <v>20</v>
+      </c>
+      <c r="DK3">
+        <v>20</v>
+      </c>
+      <c r="DL3" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM3">
+        <v>3</v>
+      </c>
+      <c r="DN3">
+        <v>20</v>
+      </c>
+      <c r="DO3">
+        <v>20</v>
+      </c>
+      <c r="DP3" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ3">
+        <v>3</v>
+      </c>
+      <c r="DR3" t="s">
         <v>252</v>
-      </c>
-      <c r="DI3">
-        <v>3</v>
-      </c>
-      <c r="DJ3">
-        <v>20</v>
-      </c>
-      <c r="DK3">
-        <v>20</v>
-      </c>
-      <c r="DL3" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM3">
-        <v>3</v>
-      </c>
-      <c r="DN3">
-        <v>20</v>
-      </c>
-      <c r="DO3">
-        <v>20</v>
-      </c>
-      <c r="DP3" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ3">
-        <v>3</v>
-      </c>
-      <c r="DR3" t="s">
-        <v>253</v>
       </c>
       <c r="DS3" t="s">
         <v>271</v>
@@ -3031,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="DV3">
-        <v>2700</v>
+        <v>1100</v>
       </c>
       <c r="DW3" t="s">
         <v>273</v>
@@ -3040,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="DY3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ3">
         <v>1</v>
@@ -3055,40 +3082,40 @@
         <v>9</v>
       </c>
       <c r="ED3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE3" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF3">
+        <v>3</v>
+      </c>
+      <c r="EG3">
+        <v>20</v>
+      </c>
+      <c r="EH3">
+        <v>20</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ3">
+        <v>3</v>
+      </c>
+      <c r="EK3">
+        <v>20</v>
+      </c>
+      <c r="EL3">
+        <v>20</v>
+      </c>
+      <c r="EM3" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN3">
+        <v>3</v>
+      </c>
+      <c r="EO3" t="s">
         <v>252</v>
-      </c>
-      <c r="EF3">
-        <v>3</v>
-      </c>
-      <c r="EG3">
-        <v>20</v>
-      </c>
-      <c r="EH3">
-        <v>20</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ3">
-        <v>3</v>
-      </c>
-      <c r="EK3">
-        <v>20</v>
-      </c>
-      <c r="EL3">
-        <v>20</v>
-      </c>
-      <c r="EM3" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN3">
-        <v>3</v>
-      </c>
-      <c r="EO3" t="s">
-        <v>253</v>
       </c>
       <c r="EP3" t="s">
         <v>271</v>
@@ -3115,43 +3142,43 @@
         <v>9</v>
       </c>
       <c r="FA3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB3" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC3">
+        <v>3</v>
+      </c>
+      <c r="FD3">
+        <v>20</v>
+      </c>
+      <c r="FE3">
+        <v>20</v>
+      </c>
+      <c r="FF3" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG3">
+        <v>3</v>
+      </c>
+      <c r="FH3">
+        <v>20</v>
+      </c>
+      <c r="FI3">
+        <v>20</v>
+      </c>
+      <c r="FJ3" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK3">
+        <v>3</v>
+      </c>
+      <c r="FL3" t="s">
         <v>252</v>
       </c>
-      <c r="FC3">
-        <v>3</v>
-      </c>
-      <c r="FD3">
-        <v>20</v>
-      </c>
-      <c r="FE3">
-        <v>20</v>
-      </c>
-      <c r="FF3" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG3">
-        <v>3</v>
-      </c>
-      <c r="FH3">
-        <v>20</v>
-      </c>
-      <c r="FI3">
-        <v>20</v>
-      </c>
-      <c r="FJ3" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK3">
-        <v>3</v>
-      </c>
-      <c r="FL3" t="s">
-        <v>253</v>
-      </c>
       <c r="FM3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN3">
         <v>0</v>
@@ -3160,28 +3187,28 @@
         <v>0</v>
       </c>
       <c r="FR3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS3">
         <v>1</v>
       </c>
       <c r="FT3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="FU3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="FV3">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FW3">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FX3">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="FY3">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="FZ3">
         <v>0.9</v>
@@ -3195,33 +3222,6 @@
       <c r="GC3" t="b">
         <v>0</v>
       </c>
-      <c r="GD3" t="s">
-        <v>286</v>
-      </c>
-      <c r="GE3">
-        <v>100000</v>
-      </c>
-      <c r="GF3">
-        <v>11000</v>
-      </c>
-      <c r="GG3">
-        <v>22000</v>
-      </c>
-      <c r="GH3">
-        <v>200000</v>
-      </c>
-      <c r="GI3">
-        <v>0.9</v>
-      </c>
-      <c r="GJ3">
-        <v>0.8</v>
-      </c>
-      <c r="GK3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GL3" t="b">
-        <v>0</v>
-      </c>
       <c r="GM3" t="s">
         <v>287</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>289</v>
       </c>
       <c r="GT3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU3">
         <v>1</v>
@@ -3253,10 +3253,10 @@
         <v>1</v>
       </c>
       <c r="GW3">
-        <v>3600</v>
+        <v>2300</v>
       </c>
       <c r="GX3">
-        <v>3600</v>
+        <v>2300</v>
       </c>
       <c r="GY3">
         <v>0.95</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="HC3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD3">
         <v>0</v>
@@ -3280,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="HJ3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK3" t="s">
         <v>290</v>
@@ -3298,22 +3298,22 @@
         <v>86400</v>
       </c>
       <c r="HP3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR3" t="s">
         <v>292</v>
       </c>
       <c r="HS3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV3" t="s">
         <v>292</v>
@@ -3360,13 +3360,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>4402000</v>
+        <v>2012000</v>
       </c>
       <c r="O4" t="s">
         <v>244</v>
       </c>
       <c r="P4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3381,40 +3381,40 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V4" t="s">
+        <v>251</v>
+      </c>
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4">
+        <v>20</v>
+      </c>
+      <c r="Y4">
+        <v>20</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <v>20</v>
+      </c>
+      <c r="AC4">
+        <v>20</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE4">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="s">
         <v>252</v>
-      </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-      <c r="X4">
-        <v>20</v>
-      </c>
-      <c r="Y4">
-        <v>20</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
-      <c r="AB4">
-        <v>20</v>
-      </c>
-      <c r="AC4">
-        <v>20</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE4">
-        <v>3</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>253</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3426,7 +3426,7 @@
         <v>6</v>
       </c>
       <c r="AL4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM4">
         <v>1</v>
@@ -3441,40 +3441,40 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS4">
+        <v>3</v>
+      </c>
+      <c r="AT4">
+        <v>20</v>
+      </c>
+      <c r="AU4">
+        <v>20</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW4">
+        <v>3</v>
+      </c>
+      <c r="AX4">
+        <v>20</v>
+      </c>
+      <c r="AY4">
+        <v>20</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA4">
+        <v>3</v>
+      </c>
+      <c r="BB4" t="s">
         <v>252</v>
-      </c>
-      <c r="AS4">
-        <v>3</v>
-      </c>
-      <c r="AT4">
-        <v>20</v>
-      </c>
-      <c r="AU4">
-        <v>20</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW4">
-        <v>3</v>
-      </c>
-      <c r="AX4">
-        <v>20</v>
-      </c>
-      <c r="AY4">
-        <v>20</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA4">
-        <v>3</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>253</v>
       </c>
       <c r="BC4">
         <v>1</v>
@@ -3492,7 +3492,7 @@
         <v>35</v>
       </c>
       <c r="BH4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI4">
         <v>1</v>
@@ -3507,40 +3507,40 @@
         <v>9</v>
       </c>
       <c r="BM4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO4">
+        <v>3</v>
+      </c>
+      <c r="BP4">
+        <v>20</v>
+      </c>
+      <c r="BQ4">
+        <v>20</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS4">
+        <v>3</v>
+      </c>
+      <c r="BT4">
+        <v>20</v>
+      </c>
+      <c r="BU4">
+        <v>20</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW4">
+        <v>3</v>
+      </c>
+      <c r="BX4" t="s">
         <v>252</v>
-      </c>
-      <c r="BO4">
-        <v>3</v>
-      </c>
-      <c r="BP4">
-        <v>20</v>
-      </c>
-      <c r="BQ4">
-        <v>20</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS4">
-        <v>3</v>
-      </c>
-      <c r="BT4">
-        <v>20</v>
-      </c>
-      <c r="BU4">
-        <v>20</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW4">
-        <v>3</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>253</v>
       </c>
       <c r="BY4">
         <v>1</v>
@@ -3573,41 +3573,41 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ4" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK4">
+        <v>3</v>
+      </c>
+      <c r="CL4">
+        <v>20</v>
+      </c>
+      <c r="CM4">
+        <v>20</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO4">
+        <v>3</v>
+      </c>
+      <c r="CP4">
+        <v>20</v>
+      </c>
+      <c r="CQ4">
+        <v>20</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS4">
+        <v>3</v>
+      </c>
+      <c r="CT4" t="s">
         <v>252</v>
       </c>
-      <c r="CK4">
-        <v>3</v>
-      </c>
-      <c r="CL4">
-        <v>20</v>
-      </c>
-      <c r="CM4">
-        <v>20</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO4">
-        <v>3</v>
-      </c>
-      <c r="CP4">
-        <v>20</v>
-      </c>
-      <c r="CQ4">
-        <v>20</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS4">
-        <v>3</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>253</v>
-      </c>
       <c r="CU4">
         <v>1</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>1</v>
       </c>
       <c r="CW4">
-        <v>6300</v>
+        <v>3200</v>
       </c>
       <c r="CX4" t="s">
         <v>270</v>
@@ -3630,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="DB4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC4">
         <v>1</v>
@@ -3645,40 +3645,40 @@
         <v>9</v>
       </c>
       <c r="DG4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH4" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI4">
+        <v>3</v>
+      </c>
+      <c r="DJ4">
+        <v>20</v>
+      </c>
+      <c r="DK4">
+        <v>20</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM4">
+        <v>3</v>
+      </c>
+      <c r="DN4">
+        <v>20</v>
+      </c>
+      <c r="DO4">
+        <v>20</v>
+      </c>
+      <c r="DP4" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ4">
+        <v>3</v>
+      </c>
+      <c r="DR4" t="s">
         <v>252</v>
-      </c>
-      <c r="DI4">
-        <v>3</v>
-      </c>
-      <c r="DJ4">
-        <v>20</v>
-      </c>
-      <c r="DK4">
-        <v>20</v>
-      </c>
-      <c r="DL4" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM4">
-        <v>3</v>
-      </c>
-      <c r="DN4">
-        <v>20</v>
-      </c>
-      <c r="DO4">
-        <v>20</v>
-      </c>
-      <c r="DP4" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ4">
-        <v>3</v>
-      </c>
-      <c r="DR4" t="s">
-        <v>253</v>
       </c>
       <c r="DS4" t="s">
         <v>271</v>
@@ -3690,16 +3690,16 @@
         <v>1</v>
       </c>
       <c r="DV4">
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="DW4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="DX4" t="b">
         <v>1</v>
       </c>
       <c r="DY4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ4">
         <v>1</v>
@@ -3714,40 +3714,40 @@
         <v>9</v>
       </c>
       <c r="ED4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE4" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF4">
+        <v>3</v>
+      </c>
+      <c r="EG4">
+        <v>20</v>
+      </c>
+      <c r="EH4">
+        <v>20</v>
+      </c>
+      <c r="EI4" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ4">
+        <v>3</v>
+      </c>
+      <c r="EK4">
+        <v>20</v>
+      </c>
+      <c r="EL4">
+        <v>20</v>
+      </c>
+      <c r="EM4" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN4">
+        <v>3</v>
+      </c>
+      <c r="EO4" t="s">
         <v>252</v>
-      </c>
-      <c r="EF4">
-        <v>3</v>
-      </c>
-      <c r="EG4">
-        <v>20</v>
-      </c>
-      <c r="EH4">
-        <v>20</v>
-      </c>
-      <c r="EI4" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ4">
-        <v>3</v>
-      </c>
-      <c r="EK4">
-        <v>20</v>
-      </c>
-      <c r="EL4">
-        <v>20</v>
-      </c>
-      <c r="EM4" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN4">
-        <v>3</v>
-      </c>
-      <c r="EO4" t="s">
-        <v>253</v>
       </c>
       <c r="EP4" t="s">
         <v>271</v>
@@ -3774,43 +3774,43 @@
         <v>9</v>
       </c>
       <c r="FA4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB4" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC4">
+        <v>3</v>
+      </c>
+      <c r="FD4">
+        <v>20</v>
+      </c>
+      <c r="FE4">
+        <v>20</v>
+      </c>
+      <c r="FF4" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG4">
+        <v>3</v>
+      </c>
+      <c r="FH4">
+        <v>20</v>
+      </c>
+      <c r="FI4">
+        <v>20</v>
+      </c>
+      <c r="FJ4" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK4">
+        <v>3</v>
+      </c>
+      <c r="FL4" t="s">
         <v>252</v>
       </c>
-      <c r="FC4">
-        <v>3</v>
-      </c>
-      <c r="FD4">
-        <v>20</v>
-      </c>
-      <c r="FE4">
-        <v>20</v>
-      </c>
-      <c r="FF4" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG4">
-        <v>3</v>
-      </c>
-      <c r="FH4">
-        <v>20</v>
-      </c>
-      <c r="FI4">
-        <v>20</v>
-      </c>
-      <c r="FJ4" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK4">
-        <v>3</v>
-      </c>
-      <c r="FL4" t="s">
-        <v>253</v>
-      </c>
       <c r="FM4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN4">
         <v>0</v>
@@ -3819,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="FR4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS4">
         <v>1</v>
@@ -3828,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="FU4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="FV4">
         <v>75000</v>
@@ -3876,7 +3876,7 @@
         <v>289</v>
       </c>
       <c r="GT4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU4">
         <v>1</v>
@@ -3885,10 +3885,10 @@
         <v>1</v>
       </c>
       <c r="GW4">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="GX4">
-        <v>4400</v>
+        <v>2000</v>
       </c>
       <c r="GY4">
         <v>0.95</v>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="HC4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD4">
         <v>0</v>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="HJ4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK4" t="s">
         <v>290</v>
@@ -3930,22 +3930,22 @@
         <v>86400</v>
       </c>
       <c r="HP4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR4" t="s">
         <v>292</v>
       </c>
       <c r="HS4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV4" t="s">
         <v>292</v>
@@ -3968,10 +3968,10 @@
         <v>235</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3980,7 +3980,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3992,13 +3992,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>5527000</v>
+        <v>4536000</v>
       </c>
       <c r="O5" t="s">
         <v>245</v>
       </c>
       <c r="P5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4013,40 +4013,40 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V5" t="s">
+        <v>251</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>20</v>
+      </c>
+      <c r="Y5">
+        <v>20</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
+      <c r="AB5">
+        <v>20</v>
+      </c>
+      <c r="AC5">
+        <v>20</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE5">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="s">
         <v>252</v>
-      </c>
-      <c r="W5">
-        <v>3</v>
-      </c>
-      <c r="X5">
-        <v>20</v>
-      </c>
-      <c r="Y5">
-        <v>20</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>20</v>
-      </c>
-      <c r="AC5">
-        <v>20</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE5">
-        <v>3</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>253</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>6</v>
       </c>
       <c r="AL5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM5">
         <v>1</v>
@@ -4073,41 +4073,41 @@
         <v>9</v>
       </c>
       <c r="AQ5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS5">
+        <v>3</v>
+      </c>
+      <c r="AT5">
+        <v>20</v>
+      </c>
+      <c r="AU5">
+        <v>20</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW5">
+        <v>3</v>
+      </c>
+      <c r="AX5">
+        <v>20</v>
+      </c>
+      <c r="AY5">
+        <v>20</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA5">
+        <v>3</v>
+      </c>
+      <c r="BB5" t="s">
         <v>252</v>
       </c>
-      <c r="AS5">
-        <v>3</v>
-      </c>
-      <c r="AT5">
-        <v>20</v>
-      </c>
-      <c r="AU5">
-        <v>20</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW5">
-        <v>3</v>
-      </c>
-      <c r="AX5">
-        <v>20</v>
-      </c>
-      <c r="AY5">
-        <v>20</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA5">
-        <v>3</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>253</v>
-      </c>
       <c r="BC5">
         <v>1</v>
       </c>
@@ -4115,16 +4115,16 @@
         <v>1</v>
       </c>
       <c r="BE5">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF5" t="s">
         <v>257</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI5">
         <v>1</v>
@@ -4139,41 +4139,41 @@
         <v>9</v>
       </c>
       <c r="BM5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO5">
+        <v>3</v>
+      </c>
+      <c r="BP5">
+        <v>20</v>
+      </c>
+      <c r="BQ5">
+        <v>20</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS5">
+        <v>3</v>
+      </c>
+      <c r="BT5">
+        <v>20</v>
+      </c>
+      <c r="BU5">
+        <v>20</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW5">
+        <v>3</v>
+      </c>
+      <c r="BX5" t="s">
         <v>252</v>
       </c>
-      <c r="BO5">
-        <v>3</v>
-      </c>
-      <c r="BP5">
-        <v>20</v>
-      </c>
-      <c r="BQ5">
-        <v>20</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS5">
-        <v>3</v>
-      </c>
-      <c r="BT5">
-        <v>20</v>
-      </c>
-      <c r="BU5">
-        <v>20</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW5">
-        <v>3</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>253</v>
-      </c>
       <c r="BY5">
         <v>1</v>
       </c>
@@ -4181,10 +4181,10 @@
         <v>1</v>
       </c>
       <c r="CA5">
-        <v>2400000</v>
+        <v>2100000</v>
       </c>
       <c r="CB5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="CC5">
         <v>55</v>
@@ -4205,41 +4205,41 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ5" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK5">
+        <v>3</v>
+      </c>
+      <c r="CL5">
+        <v>20</v>
+      </c>
+      <c r="CM5">
+        <v>20</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO5">
+        <v>3</v>
+      </c>
+      <c r="CP5">
+        <v>20</v>
+      </c>
+      <c r="CQ5">
+        <v>20</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS5">
+        <v>3</v>
+      </c>
+      <c r="CT5" t="s">
         <v>252</v>
       </c>
-      <c r="CK5">
-        <v>3</v>
-      </c>
-      <c r="CL5">
-        <v>20</v>
-      </c>
-      <c r="CM5">
-        <v>20</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO5">
-        <v>3</v>
-      </c>
-      <c r="CP5">
-        <v>20</v>
-      </c>
-      <c r="CQ5">
-        <v>20</v>
-      </c>
-      <c r="CR5" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS5">
-        <v>3</v>
-      </c>
-      <c r="CT5" t="s">
-        <v>253</v>
-      </c>
       <c r="CU5">
         <v>1</v>
       </c>
@@ -4247,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="CW5">
-        <v>7400</v>
+        <v>5700</v>
       </c>
       <c r="CX5" t="s">
         <v>270</v>
@@ -4262,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="DB5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC5">
         <v>1</v>
@@ -4277,40 +4277,40 @@
         <v>9</v>
       </c>
       <c r="DG5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH5" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI5">
+        <v>3</v>
+      </c>
+      <c r="DJ5">
+        <v>20</v>
+      </c>
+      <c r="DK5">
+        <v>20</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM5">
+        <v>3</v>
+      </c>
+      <c r="DN5">
+        <v>20</v>
+      </c>
+      <c r="DO5">
+        <v>20</v>
+      </c>
+      <c r="DP5" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ5">
+        <v>3</v>
+      </c>
+      <c r="DR5" t="s">
         <v>252</v>
-      </c>
-      <c r="DI5">
-        <v>3</v>
-      </c>
-      <c r="DJ5">
-        <v>20</v>
-      </c>
-      <c r="DK5">
-        <v>20</v>
-      </c>
-      <c r="DL5" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM5">
-        <v>3</v>
-      </c>
-      <c r="DN5">
-        <v>20</v>
-      </c>
-      <c r="DO5">
-        <v>20</v>
-      </c>
-      <c r="DP5" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ5">
-        <v>3</v>
-      </c>
-      <c r="DR5" t="s">
-        <v>253</v>
       </c>
       <c r="DS5" t="s">
         <v>271</v>
@@ -4322,16 +4322,16 @@
         <v>1</v>
       </c>
       <c r="DV5">
-        <v>2600</v>
+        <v>3500</v>
       </c>
       <c r="DW5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="DX5" t="b">
         <v>1</v>
       </c>
       <c r="DY5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ5">
         <v>1</v>
@@ -4346,40 +4346,40 @@
         <v>9</v>
       </c>
       <c r="ED5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE5" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF5">
+        <v>3</v>
+      </c>
+      <c r="EG5">
+        <v>20</v>
+      </c>
+      <c r="EH5">
+        <v>20</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ5">
+        <v>3</v>
+      </c>
+      <c r="EK5">
+        <v>20</v>
+      </c>
+      <c r="EL5">
+        <v>20</v>
+      </c>
+      <c r="EM5" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN5">
+        <v>3</v>
+      </c>
+      <c r="EO5" t="s">
         <v>252</v>
-      </c>
-      <c r="EF5">
-        <v>3</v>
-      </c>
-      <c r="EG5">
-        <v>20</v>
-      </c>
-      <c r="EH5">
-        <v>20</v>
-      </c>
-      <c r="EI5" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ5">
-        <v>3</v>
-      </c>
-      <c r="EK5">
-        <v>20</v>
-      </c>
-      <c r="EL5">
-        <v>20</v>
-      </c>
-      <c r="EM5" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN5">
-        <v>3</v>
-      </c>
-      <c r="EO5" t="s">
-        <v>253</v>
       </c>
       <c r="EP5" t="s">
         <v>271</v>
@@ -4406,43 +4406,43 @@
         <v>9</v>
       </c>
       <c r="FA5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB5" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC5">
+        <v>3</v>
+      </c>
+      <c r="FD5">
+        <v>20</v>
+      </c>
+      <c r="FE5">
+        <v>20</v>
+      </c>
+      <c r="FF5" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG5">
+        <v>3</v>
+      </c>
+      <c r="FH5">
+        <v>20</v>
+      </c>
+      <c r="FI5">
+        <v>20</v>
+      </c>
+      <c r="FJ5" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK5">
+        <v>3</v>
+      </c>
+      <c r="FL5" t="s">
         <v>252</v>
       </c>
-      <c r="FC5">
-        <v>3</v>
-      </c>
-      <c r="FD5">
-        <v>20</v>
-      </c>
-      <c r="FE5">
-        <v>20</v>
-      </c>
-      <c r="FF5" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG5">
-        <v>3</v>
-      </c>
-      <c r="FH5">
-        <v>20</v>
-      </c>
-      <c r="FI5">
-        <v>20</v>
-      </c>
-      <c r="FJ5" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK5">
-        <v>3</v>
-      </c>
-      <c r="FL5" t="s">
-        <v>253</v>
-      </c>
       <c r="FM5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN5">
         <v>0</v>
@@ -4451,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="FR5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS5">
         <v>1</v>
@@ -4460,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="FU5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="FV5">
         <v>75000</v>
@@ -4508,7 +4508,7 @@
         <v>289</v>
       </c>
       <c r="GT5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU5">
         <v>1</v>
@@ -4517,10 +4517,10 @@
         <v>1</v>
       </c>
       <c r="GW5">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="GX5">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="GY5">
         <v>0.95</v>
@@ -4535,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="HC5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD5">
         <v>0</v>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="HJ5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK5" t="s">
         <v>290</v>
@@ -4562,22 +4562,22 @@
         <v>86400</v>
       </c>
       <c r="HP5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR5" t="s">
         <v>292</v>
       </c>
       <c r="HS5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV5" t="s">
         <v>292</v>
@@ -4624,13 +4624,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>4402000</v>
+        <v>3296000</v>
       </c>
       <c r="O6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4645,40 +4645,40 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V6" t="s">
+        <v>251</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>20</v>
+      </c>
+      <c r="Y6">
+        <v>20</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>20</v>
+      </c>
+      <c r="AC6">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE6">
+        <v>3</v>
+      </c>
+      <c r="AF6" t="s">
         <v>252</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
-      <c r="X6">
-        <v>20</v>
-      </c>
-      <c r="Y6">
-        <v>20</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA6">
-        <v>3</v>
-      </c>
-      <c r="AB6">
-        <v>20</v>
-      </c>
-      <c r="AC6">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE6">
-        <v>3</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>253</v>
       </c>
       <c r="AG6">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="AL6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM6">
         <v>1</v>
@@ -4705,40 +4705,40 @@
         <v>9</v>
       </c>
       <c r="AQ6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS6">
+        <v>3</v>
+      </c>
+      <c r="AT6">
+        <v>20</v>
+      </c>
+      <c r="AU6">
+        <v>20</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW6">
+        <v>3</v>
+      </c>
+      <c r="AX6">
+        <v>20</v>
+      </c>
+      <c r="AY6">
+        <v>20</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA6">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="s">
         <v>252</v>
-      </c>
-      <c r="AS6">
-        <v>3</v>
-      </c>
-      <c r="AT6">
-        <v>20</v>
-      </c>
-      <c r="AU6">
-        <v>20</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW6">
-        <v>3</v>
-      </c>
-      <c r="AX6">
-        <v>20</v>
-      </c>
-      <c r="AY6">
-        <v>20</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA6">
-        <v>3</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>253</v>
       </c>
       <c r="BC6">
         <v>1</v>
@@ -4750,13 +4750,13 @@
         <v>5500000</v>
       </c>
       <c r="BF6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="BG6">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI6">
         <v>1</v>
@@ -4771,41 +4771,41 @@
         <v>9</v>
       </c>
       <c r="BM6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN6" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO6">
+        <v>3</v>
+      </c>
+      <c r="BP6">
+        <v>20</v>
+      </c>
+      <c r="BQ6">
+        <v>20</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS6">
+        <v>3</v>
+      </c>
+      <c r="BT6">
+        <v>20</v>
+      </c>
+      <c r="BU6">
+        <v>20</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW6">
+        <v>3</v>
+      </c>
+      <c r="BX6" t="s">
         <v>252</v>
       </c>
-      <c r="BO6">
-        <v>3</v>
-      </c>
-      <c r="BP6">
-        <v>20</v>
-      </c>
-      <c r="BQ6">
-        <v>20</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS6">
-        <v>3</v>
-      </c>
-      <c r="BT6">
-        <v>20</v>
-      </c>
-      <c r="BU6">
-        <v>20</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW6">
-        <v>3</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>253</v>
-      </c>
       <c r="BY6">
         <v>1</v>
       </c>
@@ -4813,10 +4813,10 @@
         <v>1</v>
       </c>
       <c r="CA6">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="CB6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="CC6">
         <v>55</v>
@@ -4837,41 +4837,41 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ6" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK6">
+        <v>3</v>
+      </c>
+      <c r="CL6">
+        <v>20</v>
+      </c>
+      <c r="CM6">
+        <v>20</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO6">
+        <v>3</v>
+      </c>
+      <c r="CP6">
+        <v>20</v>
+      </c>
+      <c r="CQ6">
+        <v>20</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS6">
+        <v>3</v>
+      </c>
+      <c r="CT6" t="s">
         <v>252</v>
       </c>
-      <c r="CK6">
-        <v>3</v>
-      </c>
-      <c r="CL6">
-        <v>20</v>
-      </c>
-      <c r="CM6">
-        <v>20</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO6">
-        <v>3</v>
-      </c>
-      <c r="CP6">
-        <v>20</v>
-      </c>
-      <c r="CQ6">
-        <v>20</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS6">
-        <v>3</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>253</v>
-      </c>
       <c r="CU6">
         <v>1</v>
       </c>
@@ -4879,22 +4879,22 @@
         <v>1</v>
       </c>
       <c r="CW6">
-        <v>6000</v>
+        <v>5600</v>
       </c>
       <c r="CX6" t="s">
         <v>270</v>
       </c>
       <c r="CY6">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA6" t="b">
         <v>1</v>
       </c>
       <c r="DB6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC6">
         <v>1</v>
@@ -4909,40 +4909,40 @@
         <v>9</v>
       </c>
       <c r="DG6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH6" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI6">
+        <v>3</v>
+      </c>
+      <c r="DJ6">
+        <v>20</v>
+      </c>
+      <c r="DK6">
+        <v>20</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM6">
+        <v>3</v>
+      </c>
+      <c r="DN6">
+        <v>20</v>
+      </c>
+      <c r="DO6">
+        <v>20</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ6">
+        <v>3</v>
+      </c>
+      <c r="DR6" t="s">
         <v>252</v>
-      </c>
-      <c r="DI6">
-        <v>3</v>
-      </c>
-      <c r="DJ6">
-        <v>20</v>
-      </c>
-      <c r="DK6">
-        <v>20</v>
-      </c>
-      <c r="DL6" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM6">
-        <v>3</v>
-      </c>
-      <c r="DN6">
-        <v>20</v>
-      </c>
-      <c r="DO6">
-        <v>20</v>
-      </c>
-      <c r="DP6" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ6">
-        <v>3</v>
-      </c>
-      <c r="DR6" t="s">
-        <v>253</v>
       </c>
       <c r="DS6" t="s">
         <v>271</v>
@@ -4954,16 +4954,16 @@
         <v>1</v>
       </c>
       <c r="DV6">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="DW6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="DX6" t="b">
         <v>1</v>
       </c>
       <c r="DY6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ6">
         <v>1</v>
@@ -4978,40 +4978,40 @@
         <v>9</v>
       </c>
       <c r="ED6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE6" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF6">
+        <v>3</v>
+      </c>
+      <c r="EG6">
+        <v>20</v>
+      </c>
+      <c r="EH6">
+        <v>20</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ6">
+        <v>3</v>
+      </c>
+      <c r="EK6">
+        <v>20</v>
+      </c>
+      <c r="EL6">
+        <v>20</v>
+      </c>
+      <c r="EM6" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN6">
+        <v>3</v>
+      </c>
+      <c r="EO6" t="s">
         <v>252</v>
-      </c>
-      <c r="EF6">
-        <v>3</v>
-      </c>
-      <c r="EG6">
-        <v>20</v>
-      </c>
-      <c r="EH6">
-        <v>20</v>
-      </c>
-      <c r="EI6" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ6">
-        <v>3</v>
-      </c>
-      <c r="EK6">
-        <v>20</v>
-      </c>
-      <c r="EL6">
-        <v>20</v>
-      </c>
-      <c r="EM6" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN6">
-        <v>3</v>
-      </c>
-      <c r="EO6" t="s">
-        <v>253</v>
       </c>
       <c r="EP6" t="s">
         <v>271</v>
@@ -5038,43 +5038,43 @@
         <v>9</v>
       </c>
       <c r="FA6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB6" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC6">
+        <v>3</v>
+      </c>
+      <c r="FD6">
+        <v>20</v>
+      </c>
+      <c r="FE6">
+        <v>20</v>
+      </c>
+      <c r="FF6" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG6">
+        <v>3</v>
+      </c>
+      <c r="FH6">
+        <v>20</v>
+      </c>
+      <c r="FI6">
+        <v>20</v>
+      </c>
+      <c r="FJ6" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK6">
+        <v>3</v>
+      </c>
+      <c r="FL6" t="s">
         <v>252</v>
       </c>
-      <c r="FC6">
-        <v>3</v>
-      </c>
-      <c r="FD6">
-        <v>20</v>
-      </c>
-      <c r="FE6">
-        <v>20</v>
-      </c>
-      <c r="FF6" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG6">
-        <v>3</v>
-      </c>
-      <c r="FH6">
-        <v>20</v>
-      </c>
-      <c r="FI6">
-        <v>20</v>
-      </c>
-      <c r="FJ6" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK6">
-        <v>3</v>
-      </c>
-      <c r="FL6" t="s">
-        <v>253</v>
-      </c>
       <c r="FM6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN6">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="FR6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS6">
         <v>1</v>
@@ -5140,7 +5140,7 @@
         <v>289</v>
       </c>
       <c r="GT6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU6">
         <v>1</v>
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="GW6">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="GX6">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="GY6">
         <v>0.95</v>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="HC6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD6">
         <v>0</v>
@@ -5176,7 +5176,7 @@
         <v>0</v>
       </c>
       <c r="HJ6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK6" t="s">
         <v>290</v>
@@ -5194,22 +5194,22 @@
         <v>86400</v>
       </c>
       <c r="HP6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR6" t="s">
         <v>292</v>
       </c>
       <c r="HS6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV6" t="s">
         <v>292</v>
@@ -5232,10 +5232,10 @@
         <v>237</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -5244,7 +5244,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -5256,13 +5256,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3863000</v>
+        <v>3296000</v>
       </c>
       <c r="O7" t="s">
         <v>246</v>
       </c>
       <c r="P7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5277,40 +5277,40 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V7" t="s">
+        <v>251</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="X7">
+        <v>20</v>
+      </c>
+      <c r="Y7">
+        <v>20</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>20</v>
+      </c>
+      <c r="AC7">
+        <v>20</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE7">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="s">
         <v>252</v>
-      </c>
-      <c r="W7">
-        <v>3</v>
-      </c>
-      <c r="X7">
-        <v>20</v>
-      </c>
-      <c r="Y7">
-        <v>20</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7">
-        <v>20</v>
-      </c>
-      <c r="AC7">
-        <v>20</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE7">
-        <v>3</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>253</v>
       </c>
       <c r="AG7">
         <v>0</v>
@@ -5322,7 +5322,7 @@
         <v>6</v>
       </c>
       <c r="AL7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM7">
         <v>1</v>
@@ -5337,41 +5337,41 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS7">
+        <v>3</v>
+      </c>
+      <c r="AT7">
+        <v>20</v>
+      </c>
+      <c r="AU7">
+        <v>20</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW7">
+        <v>3</v>
+      </c>
+      <c r="AX7">
+        <v>20</v>
+      </c>
+      <c r="AY7">
+        <v>20</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA7">
+        <v>3</v>
+      </c>
+      <c r="BB7" t="s">
         <v>252</v>
       </c>
-      <c r="AS7">
-        <v>3</v>
-      </c>
-      <c r="AT7">
-        <v>20</v>
-      </c>
-      <c r="AU7">
-        <v>20</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW7">
-        <v>3</v>
-      </c>
-      <c r="AX7">
-        <v>20</v>
-      </c>
-      <c r="AY7">
-        <v>20</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA7">
-        <v>3</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>253</v>
-      </c>
       <c r="BC7">
         <v>1</v>
       </c>
@@ -5379,16 +5379,16 @@
         <v>1</v>
       </c>
       <c r="BE7">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BG7">
         <v>55</v>
       </c>
       <c r="BH7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI7">
         <v>1</v>
@@ -5403,41 +5403,41 @@
         <v>9</v>
       </c>
       <c r="BM7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO7">
+        <v>3</v>
+      </c>
+      <c r="BP7">
+        <v>20</v>
+      </c>
+      <c r="BQ7">
+        <v>20</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS7">
+        <v>3</v>
+      </c>
+      <c r="BT7">
+        <v>20</v>
+      </c>
+      <c r="BU7">
+        <v>20</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW7">
+        <v>3</v>
+      </c>
+      <c r="BX7" t="s">
         <v>252</v>
       </c>
-      <c r="BO7">
-        <v>3</v>
-      </c>
-      <c r="BP7">
-        <v>20</v>
-      </c>
-      <c r="BQ7">
-        <v>20</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS7">
-        <v>3</v>
-      </c>
-      <c r="BT7">
-        <v>20</v>
-      </c>
-      <c r="BU7">
-        <v>20</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW7">
-        <v>3</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>253</v>
-      </c>
       <c r="BY7">
         <v>1</v>
       </c>
@@ -5445,10 +5445,10 @@
         <v>1</v>
       </c>
       <c r="CA7">
-        <v>2100000</v>
+        <v>2800000</v>
       </c>
       <c r="CB7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="CC7">
         <v>55</v>
@@ -5469,41 +5469,41 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK7">
+        <v>3</v>
+      </c>
+      <c r="CL7">
+        <v>20</v>
+      </c>
+      <c r="CM7">
+        <v>20</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO7">
+        <v>3</v>
+      </c>
+      <c r="CP7">
+        <v>20</v>
+      </c>
+      <c r="CQ7">
+        <v>20</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS7">
+        <v>3</v>
+      </c>
+      <c r="CT7" t="s">
         <v>252</v>
       </c>
-      <c r="CK7">
-        <v>3</v>
-      </c>
-      <c r="CL7">
-        <v>20</v>
-      </c>
-      <c r="CM7">
-        <v>20</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO7">
-        <v>3</v>
-      </c>
-      <c r="CP7">
-        <v>20</v>
-      </c>
-      <c r="CQ7">
-        <v>20</v>
-      </c>
-      <c r="CR7" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS7">
-        <v>3</v>
-      </c>
-      <c r="CT7" t="s">
-        <v>253</v>
-      </c>
       <c r="CU7">
         <v>1</v>
       </c>
@@ -5511,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="CW7">
-        <v>6100</v>
+        <v>4400</v>
       </c>
       <c r="CX7" t="s">
         <v>270</v>
@@ -5526,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="DB7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC7">
         <v>1</v>
@@ -5541,40 +5541,40 @@
         <v>9</v>
       </c>
       <c r="DG7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI7">
+        <v>3</v>
+      </c>
+      <c r="DJ7">
+        <v>20</v>
+      </c>
+      <c r="DK7">
+        <v>20</v>
+      </c>
+      <c r="DL7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM7">
+        <v>3</v>
+      </c>
+      <c r="DN7">
+        <v>20</v>
+      </c>
+      <c r="DO7">
+        <v>20</v>
+      </c>
+      <c r="DP7" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ7">
+        <v>3</v>
+      </c>
+      <c r="DR7" t="s">
         <v>252</v>
-      </c>
-      <c r="DI7">
-        <v>3</v>
-      </c>
-      <c r="DJ7">
-        <v>20</v>
-      </c>
-      <c r="DK7">
-        <v>20</v>
-      </c>
-      <c r="DL7" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM7">
-        <v>3</v>
-      </c>
-      <c r="DN7">
-        <v>20</v>
-      </c>
-      <c r="DO7">
-        <v>20</v>
-      </c>
-      <c r="DP7" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ7">
-        <v>3</v>
-      </c>
-      <c r="DR7" t="s">
-        <v>253</v>
       </c>
       <c r="DS7" t="s">
         <v>271</v>
@@ -5589,13 +5589,13 @@
         <v>1700</v>
       </c>
       <c r="DW7" t="s">
+        <v>273</v>
+      </c>
+      <c r="DX7" t="b">
+        <v>1</v>
+      </c>
+      <c r="DY7" t="s">
         <v>276</v>
-      </c>
-      <c r="DX7" t="b">
-        <v>1</v>
-      </c>
-      <c r="DY7" t="s">
-        <v>277</v>
       </c>
       <c r="DZ7">
         <v>1</v>
@@ -5610,40 +5610,40 @@
         <v>9</v>
       </c>
       <c r="ED7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF7">
+        <v>3</v>
+      </c>
+      <c r="EG7">
+        <v>20</v>
+      </c>
+      <c r="EH7">
+        <v>20</v>
+      </c>
+      <c r="EI7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ7">
+        <v>3</v>
+      </c>
+      <c r="EK7">
+        <v>20</v>
+      </c>
+      <c r="EL7">
+        <v>20</v>
+      </c>
+      <c r="EM7" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN7">
+        <v>3</v>
+      </c>
+      <c r="EO7" t="s">
         <v>252</v>
-      </c>
-      <c r="EF7">
-        <v>3</v>
-      </c>
-      <c r="EG7">
-        <v>20</v>
-      </c>
-      <c r="EH7">
-        <v>20</v>
-      </c>
-      <c r="EI7" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ7">
-        <v>3</v>
-      </c>
-      <c r="EK7">
-        <v>20</v>
-      </c>
-      <c r="EL7">
-        <v>20</v>
-      </c>
-      <c r="EM7" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN7">
-        <v>3</v>
-      </c>
-      <c r="EO7" t="s">
-        <v>253</v>
       </c>
       <c r="EP7" t="s">
         <v>271</v>
@@ -5670,43 +5670,43 @@
         <v>9</v>
       </c>
       <c r="FA7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC7">
+        <v>3</v>
+      </c>
+      <c r="FD7">
+        <v>20</v>
+      </c>
+      <c r="FE7">
+        <v>20</v>
+      </c>
+      <c r="FF7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG7">
+        <v>3</v>
+      </c>
+      <c r="FH7">
+        <v>20</v>
+      </c>
+      <c r="FI7">
+        <v>20</v>
+      </c>
+      <c r="FJ7" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK7">
+        <v>3</v>
+      </c>
+      <c r="FL7" t="s">
         <v>252</v>
       </c>
-      <c r="FC7">
-        <v>3</v>
-      </c>
-      <c r="FD7">
-        <v>20</v>
-      </c>
-      <c r="FE7">
-        <v>20</v>
-      </c>
-      <c r="FF7" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG7">
-        <v>3</v>
-      </c>
-      <c r="FH7">
-        <v>20</v>
-      </c>
-      <c r="FI7">
-        <v>20</v>
-      </c>
-      <c r="FJ7" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK7">
-        <v>3</v>
-      </c>
-      <c r="FL7" t="s">
-        <v>253</v>
-      </c>
       <c r="FM7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN7">
         <v>0</v>
@@ -5715,16 +5715,16 @@
         <v>0</v>
       </c>
       <c r="FR7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS7">
         <v>1</v>
       </c>
       <c r="FT7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="FU7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="FV7">
         <v>50000</v>
@@ -5750,6 +5750,33 @@
       <c r="GC7" t="b">
         <v>0</v>
       </c>
+      <c r="GD7" t="s">
+        <v>281</v>
+      </c>
+      <c r="GE7">
+        <v>50000</v>
+      </c>
+      <c r="GF7">
+        <v>7200</v>
+      </c>
+      <c r="GG7">
+        <v>7200</v>
+      </c>
+      <c r="GH7">
+        <v>50000</v>
+      </c>
+      <c r="GI7">
+        <v>0.9</v>
+      </c>
+      <c r="GJ7">
+        <v>0.8</v>
+      </c>
+      <c r="GK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL7" t="b">
+        <v>0</v>
+      </c>
       <c r="GM7" t="s">
         <v>287</v>
       </c>
@@ -5772,7 +5799,7 @@
         <v>289</v>
       </c>
       <c r="GT7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU7">
         <v>1</v>
@@ -5781,10 +5808,10 @@
         <v>1</v>
       </c>
       <c r="GW7">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="GX7">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="GY7">
         <v>0.95</v>
@@ -5799,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="HC7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD7">
         <v>0</v>
@@ -5808,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="HJ7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK7" t="s">
         <v>290</v>
@@ -5826,22 +5853,22 @@
         <v>86400</v>
       </c>
       <c r="HP7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR7" t="s">
         <v>292</v>
       </c>
       <c r="HS7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV7" t="s">
         <v>292</v>
@@ -5888,13 +5915,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>4536000</v>
+        <v>5527000</v>
       </c>
       <c r="O8" t="s">
         <v>247</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -5909,40 +5936,40 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V8" t="s">
+        <v>251</v>
+      </c>
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>20</v>
+      </c>
+      <c r="Y8">
+        <v>20</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
+      <c r="AB8">
+        <v>20</v>
+      </c>
+      <c r="AC8">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE8">
+        <v>3</v>
+      </c>
+      <c r="AF8" t="s">
         <v>252</v>
-      </c>
-      <c r="W8">
-        <v>3</v>
-      </c>
-      <c r="X8">
-        <v>20</v>
-      </c>
-      <c r="Y8">
-        <v>20</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA8">
-        <v>3</v>
-      </c>
-      <c r="AB8">
-        <v>20</v>
-      </c>
-      <c r="AC8">
-        <v>20</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE8">
-        <v>3</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>253</v>
       </c>
       <c r="AG8">
         <v>0</v>
@@ -5954,7 +5981,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM8">
         <v>1</v>
@@ -5969,40 +5996,40 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR8" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS8">
+        <v>3</v>
+      </c>
+      <c r="AT8">
+        <v>20</v>
+      </c>
+      <c r="AU8">
+        <v>20</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW8">
+        <v>3</v>
+      </c>
+      <c r="AX8">
+        <v>20</v>
+      </c>
+      <c r="AY8">
+        <v>20</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA8">
+        <v>3</v>
+      </c>
+      <c r="BB8" t="s">
         <v>252</v>
-      </c>
-      <c r="AS8">
-        <v>3</v>
-      </c>
-      <c r="AT8">
-        <v>20</v>
-      </c>
-      <c r="AU8">
-        <v>20</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW8">
-        <v>3</v>
-      </c>
-      <c r="AX8">
-        <v>20</v>
-      </c>
-      <c r="AY8">
-        <v>20</v>
-      </c>
-      <c r="AZ8" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA8">
-        <v>3</v>
-      </c>
-      <c r="BB8" t="s">
-        <v>253</v>
       </c>
       <c r="BC8">
         <v>1</v>
@@ -6014,13 +6041,13 @@
         <v>19500000</v>
       </c>
       <c r="BF8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BG8">
         <v>55</v>
       </c>
       <c r="BH8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI8">
         <v>1</v>
@@ -6035,41 +6062,41 @@
         <v>9</v>
       </c>
       <c r="BM8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO8">
+        <v>3</v>
+      </c>
+      <c r="BP8">
+        <v>20</v>
+      </c>
+      <c r="BQ8">
+        <v>20</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS8">
+        <v>3</v>
+      </c>
+      <c r="BT8">
+        <v>20</v>
+      </c>
+      <c r="BU8">
+        <v>20</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW8">
+        <v>3</v>
+      </c>
+      <c r="BX8" t="s">
         <v>252</v>
       </c>
-      <c r="BO8">
-        <v>3</v>
-      </c>
-      <c r="BP8">
-        <v>20</v>
-      </c>
-      <c r="BQ8">
-        <v>20</v>
-      </c>
-      <c r="BR8" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS8">
-        <v>3</v>
-      </c>
-      <c r="BT8">
-        <v>20</v>
-      </c>
-      <c r="BU8">
-        <v>20</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW8">
-        <v>3</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>253</v>
-      </c>
       <c r="BY8">
         <v>1</v>
       </c>
@@ -6077,10 +6104,10 @@
         <v>1</v>
       </c>
       <c r="CA8">
-        <v>3200000</v>
+        <v>2400000</v>
       </c>
       <c r="CB8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="CC8">
         <v>55</v>
@@ -6101,41 +6128,41 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ8" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK8">
+        <v>3</v>
+      </c>
+      <c r="CL8">
+        <v>20</v>
+      </c>
+      <c r="CM8">
+        <v>20</v>
+      </c>
+      <c r="CN8" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO8">
+        <v>3</v>
+      </c>
+      <c r="CP8">
+        <v>20</v>
+      </c>
+      <c r="CQ8">
+        <v>20</v>
+      </c>
+      <c r="CR8" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS8">
+        <v>3</v>
+      </c>
+      <c r="CT8" t="s">
         <v>252</v>
       </c>
-      <c r="CK8">
-        <v>3</v>
-      </c>
-      <c r="CL8">
-        <v>20</v>
-      </c>
-      <c r="CM8">
-        <v>20</v>
-      </c>
-      <c r="CN8" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO8">
-        <v>3</v>
-      </c>
-      <c r="CP8">
-        <v>20</v>
-      </c>
-      <c r="CQ8">
-        <v>20</v>
-      </c>
-      <c r="CR8" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS8">
-        <v>3</v>
-      </c>
-      <c r="CT8" t="s">
-        <v>253</v>
-      </c>
       <c r="CU8">
         <v>1</v>
       </c>
@@ -6143,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="CW8">
-        <v>5900</v>
+        <v>7000</v>
       </c>
       <c r="CX8" t="s">
         <v>270</v>
@@ -6158,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="DB8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC8">
         <v>1</v>
@@ -6173,40 +6200,40 @@
         <v>9</v>
       </c>
       <c r="DG8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH8" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI8">
+        <v>3</v>
+      </c>
+      <c r="DJ8">
+        <v>20</v>
+      </c>
+      <c r="DK8">
+        <v>20</v>
+      </c>
+      <c r="DL8" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM8">
+        <v>3</v>
+      </c>
+      <c r="DN8">
+        <v>20</v>
+      </c>
+      <c r="DO8">
+        <v>20</v>
+      </c>
+      <c r="DP8" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ8">
+        <v>3</v>
+      </c>
+      <c r="DR8" t="s">
         <v>252</v>
-      </c>
-      <c r="DI8">
-        <v>3</v>
-      </c>
-      <c r="DJ8">
-        <v>20</v>
-      </c>
-      <c r="DK8">
-        <v>20</v>
-      </c>
-      <c r="DL8" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM8">
-        <v>3</v>
-      </c>
-      <c r="DN8">
-        <v>20</v>
-      </c>
-      <c r="DO8">
-        <v>20</v>
-      </c>
-      <c r="DP8" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ8">
-        <v>3</v>
-      </c>
-      <c r="DR8" t="s">
-        <v>253</v>
       </c>
       <c r="DS8" t="s">
         <v>271</v>
@@ -6218,16 +6245,16 @@
         <v>1</v>
       </c>
       <c r="DV8">
-        <v>2600</v>
+        <v>4000</v>
       </c>
       <c r="DW8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="DX8" t="b">
         <v>1</v>
       </c>
       <c r="DY8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ8">
         <v>1</v>
@@ -6242,40 +6269,40 @@
         <v>9</v>
       </c>
       <c r="ED8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE8" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF8">
+        <v>3</v>
+      </c>
+      <c r="EG8">
+        <v>20</v>
+      </c>
+      <c r="EH8">
+        <v>20</v>
+      </c>
+      <c r="EI8" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ8">
+        <v>3</v>
+      </c>
+      <c r="EK8">
+        <v>20</v>
+      </c>
+      <c r="EL8">
+        <v>20</v>
+      </c>
+      <c r="EM8" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN8">
+        <v>3</v>
+      </c>
+      <c r="EO8" t="s">
         <v>252</v>
-      </c>
-      <c r="EF8">
-        <v>3</v>
-      </c>
-      <c r="EG8">
-        <v>20</v>
-      </c>
-      <c r="EH8">
-        <v>20</v>
-      </c>
-      <c r="EI8" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ8">
-        <v>3</v>
-      </c>
-      <c r="EK8">
-        <v>20</v>
-      </c>
-      <c r="EL8">
-        <v>20</v>
-      </c>
-      <c r="EM8" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN8">
-        <v>3</v>
-      </c>
-      <c r="EO8" t="s">
-        <v>253</v>
       </c>
       <c r="EP8" t="s">
         <v>271</v>
@@ -6302,43 +6329,43 @@
         <v>9</v>
       </c>
       <c r="FA8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB8" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC8">
+        <v>3</v>
+      </c>
+      <c r="FD8">
+        <v>20</v>
+      </c>
+      <c r="FE8">
+        <v>20</v>
+      </c>
+      <c r="FF8" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG8">
+        <v>3</v>
+      </c>
+      <c r="FH8">
+        <v>20</v>
+      </c>
+      <c r="FI8">
+        <v>20</v>
+      </c>
+      <c r="FJ8" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK8">
+        <v>3</v>
+      </c>
+      <c r="FL8" t="s">
         <v>252</v>
       </c>
-      <c r="FC8">
-        <v>3</v>
-      </c>
-      <c r="FD8">
-        <v>20</v>
-      </c>
-      <c r="FE8">
-        <v>20</v>
-      </c>
-      <c r="FF8" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG8">
-        <v>3</v>
-      </c>
-      <c r="FH8">
-        <v>20</v>
-      </c>
-      <c r="FI8">
-        <v>20</v>
-      </c>
-      <c r="FJ8" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK8">
-        <v>3</v>
-      </c>
-      <c r="FL8" t="s">
-        <v>253</v>
-      </c>
       <c r="FM8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN8">
         <v>0</v>
@@ -6347,7 +6374,7 @@
         <v>0</v>
       </c>
       <c r="FR8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS8">
         <v>1</v>
@@ -6359,16 +6386,16 @@
         <v>283</v>
       </c>
       <c r="FV8">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="FW8">
         <v>7200</v>
       </c>
       <c r="FX8">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FY8">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FZ8">
         <v>0.9</v>
@@ -6404,7 +6431,7 @@
         <v>289</v>
       </c>
       <c r="GT8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU8">
         <v>1</v>
@@ -6413,10 +6440,10 @@
         <v>1</v>
       </c>
       <c r="GW8">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="GX8">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="GY8">
         <v>0.95</v>
@@ -6431,7 +6458,7 @@
         <v>0</v>
       </c>
       <c r="HC8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD8">
         <v>0</v>
@@ -6440,7 +6467,7 @@
         <v>0</v>
       </c>
       <c r="HJ8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK8" t="s">
         <v>290</v>
@@ -6458,22 +6485,22 @@
         <v>86400</v>
       </c>
       <c r="HP8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR8" t="s">
         <v>292</v>
       </c>
       <c r="HS8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV8" t="s">
         <v>292</v>
@@ -6496,10 +6523,10 @@
         <v>239</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -6508,7 +6535,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -6520,13 +6547,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3125000</v>
+        <v>3863000</v>
       </c>
       <c r="O9" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6541,40 +6568,40 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V9" t="s">
+        <v>251</v>
+      </c>
+      <c r="W9">
+        <v>3</v>
+      </c>
+      <c r="X9">
+        <v>20</v>
+      </c>
+      <c r="Y9">
+        <v>20</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AB9">
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <v>20</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE9">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="s">
         <v>252</v>
-      </c>
-      <c r="W9">
-        <v>3</v>
-      </c>
-      <c r="X9">
-        <v>20</v>
-      </c>
-      <c r="Y9">
-        <v>20</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA9">
-        <v>3</v>
-      </c>
-      <c r="AB9">
-        <v>20</v>
-      </c>
-      <c r="AC9">
-        <v>20</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE9">
-        <v>3</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>253</v>
       </c>
       <c r="AG9">
         <v>0</v>
@@ -6586,7 +6613,7 @@
         <v>6</v>
       </c>
       <c r="AL9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM9">
         <v>1</v>
@@ -6601,41 +6628,41 @@
         <v>9</v>
       </c>
       <c r="AQ9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR9" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS9">
+        <v>3</v>
+      </c>
+      <c r="AT9">
+        <v>20</v>
+      </c>
+      <c r="AU9">
+        <v>20</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW9">
+        <v>3</v>
+      </c>
+      <c r="AX9">
+        <v>20</v>
+      </c>
+      <c r="AY9">
+        <v>20</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA9">
+        <v>3</v>
+      </c>
+      <c r="BB9" t="s">
         <v>252</v>
       </c>
-      <c r="AS9">
-        <v>3</v>
-      </c>
-      <c r="AT9">
-        <v>20</v>
-      </c>
-      <c r="AU9">
-        <v>20</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW9">
-        <v>3</v>
-      </c>
-      <c r="AX9">
-        <v>20</v>
-      </c>
-      <c r="AY9">
-        <v>20</v>
-      </c>
-      <c r="AZ9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA9">
-        <v>3</v>
-      </c>
-      <c r="BB9" t="s">
-        <v>253</v>
-      </c>
       <c r="BC9">
         <v>1</v>
       </c>
@@ -6643,16 +6670,16 @@
         <v>1</v>
       </c>
       <c r="BE9">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BG9">
         <v>55</v>
       </c>
       <c r="BH9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI9">
         <v>1</v>
@@ -6667,41 +6694,41 @@
         <v>9</v>
       </c>
       <c r="BM9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN9" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO9">
+        <v>3</v>
+      </c>
+      <c r="BP9">
+        <v>20</v>
+      </c>
+      <c r="BQ9">
+        <v>20</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS9">
+        <v>3</v>
+      </c>
+      <c r="BT9">
+        <v>20</v>
+      </c>
+      <c r="BU9">
+        <v>20</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW9">
+        <v>3</v>
+      </c>
+      <c r="BX9" t="s">
         <v>252</v>
       </c>
-      <c r="BO9">
-        <v>3</v>
-      </c>
-      <c r="BP9">
-        <v>20</v>
-      </c>
-      <c r="BQ9">
-        <v>20</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS9">
-        <v>3</v>
-      </c>
-      <c r="BT9">
-        <v>20</v>
-      </c>
-      <c r="BU9">
-        <v>20</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW9">
-        <v>3</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>253</v>
-      </c>
       <c r="BY9">
         <v>1</v>
       </c>
@@ -6709,10 +6736,10 @@
         <v>1</v>
       </c>
       <c r="CA9">
-        <v>2800000</v>
+        <v>2100000</v>
       </c>
       <c r="CB9" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="CC9">
         <v>55</v>
@@ -6733,41 +6760,41 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ9" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK9">
+        <v>3</v>
+      </c>
+      <c r="CL9">
+        <v>20</v>
+      </c>
+      <c r="CM9">
+        <v>20</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO9">
+        <v>3</v>
+      </c>
+      <c r="CP9">
+        <v>20</v>
+      </c>
+      <c r="CQ9">
+        <v>20</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS9">
+        <v>3</v>
+      </c>
+      <c r="CT9" t="s">
         <v>252</v>
       </c>
-      <c r="CK9">
-        <v>3</v>
-      </c>
-      <c r="CL9">
-        <v>20</v>
-      </c>
-      <c r="CM9">
-        <v>20</v>
-      </c>
-      <c r="CN9" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO9">
-        <v>3</v>
-      </c>
-      <c r="CP9">
-        <v>20</v>
-      </c>
-      <c r="CQ9">
-        <v>20</v>
-      </c>
-      <c r="CR9" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS9">
-        <v>3</v>
-      </c>
-      <c r="CT9" t="s">
-        <v>253</v>
-      </c>
       <c r="CU9">
         <v>1</v>
       </c>
@@ -6775,7 +6802,7 @@
         <v>1</v>
       </c>
       <c r="CW9">
-        <v>4800</v>
+        <v>5600</v>
       </c>
       <c r="CX9" t="s">
         <v>270</v>
@@ -6790,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="DB9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC9">
         <v>1</v>
@@ -6805,40 +6832,40 @@
         <v>9</v>
       </c>
       <c r="DG9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH9" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI9">
+        <v>3</v>
+      </c>
+      <c r="DJ9">
+        <v>20</v>
+      </c>
+      <c r="DK9">
+        <v>20</v>
+      </c>
+      <c r="DL9" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM9">
+        <v>3</v>
+      </c>
+      <c r="DN9">
+        <v>20</v>
+      </c>
+      <c r="DO9">
+        <v>20</v>
+      </c>
+      <c r="DP9" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ9">
+        <v>3</v>
+      </c>
+      <c r="DR9" t="s">
         <v>252</v>
-      </c>
-      <c r="DI9">
-        <v>3</v>
-      </c>
-      <c r="DJ9">
-        <v>20</v>
-      </c>
-      <c r="DK9">
-        <v>20</v>
-      </c>
-      <c r="DL9" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM9">
-        <v>3</v>
-      </c>
-      <c r="DN9">
-        <v>20</v>
-      </c>
-      <c r="DO9">
-        <v>20</v>
-      </c>
-      <c r="DP9" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ9">
-        <v>3</v>
-      </c>
-      <c r="DR9" t="s">
-        <v>253</v>
       </c>
       <c r="DS9" t="s">
         <v>271</v>
@@ -6850,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="DV9">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="DW9" t="s">
         <v>272</v>
@@ -6859,7 +6886,7 @@
         <v>1</v>
       </c>
       <c r="DY9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ9">
         <v>1</v>
@@ -6874,40 +6901,40 @@
         <v>9</v>
       </c>
       <c r="ED9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE9" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF9">
+        <v>3</v>
+      </c>
+      <c r="EG9">
+        <v>20</v>
+      </c>
+      <c r="EH9">
+        <v>20</v>
+      </c>
+      <c r="EI9" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ9">
+        <v>3</v>
+      </c>
+      <c r="EK9">
+        <v>20</v>
+      </c>
+      <c r="EL9">
+        <v>20</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN9">
+        <v>3</v>
+      </c>
+      <c r="EO9" t="s">
         <v>252</v>
-      </c>
-      <c r="EF9">
-        <v>3</v>
-      </c>
-      <c r="EG9">
-        <v>20</v>
-      </c>
-      <c r="EH9">
-        <v>20</v>
-      </c>
-      <c r="EI9" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ9">
-        <v>3</v>
-      </c>
-      <c r="EK9">
-        <v>20</v>
-      </c>
-      <c r="EL9">
-        <v>20</v>
-      </c>
-      <c r="EM9" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN9">
-        <v>3</v>
-      </c>
-      <c r="EO9" t="s">
-        <v>253</v>
       </c>
       <c r="EP9" t="s">
         <v>271</v>
@@ -6934,43 +6961,43 @@
         <v>9</v>
       </c>
       <c r="FA9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB9" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC9">
+        <v>3</v>
+      </c>
+      <c r="FD9">
+        <v>20</v>
+      </c>
+      <c r="FE9">
+        <v>20</v>
+      </c>
+      <c r="FF9" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG9">
+        <v>3</v>
+      </c>
+      <c r="FH9">
+        <v>20</v>
+      </c>
+      <c r="FI9">
+        <v>20</v>
+      </c>
+      <c r="FJ9" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK9">
+        <v>3</v>
+      </c>
+      <c r="FL9" t="s">
         <v>252</v>
       </c>
-      <c r="FC9">
-        <v>3</v>
-      </c>
-      <c r="FD9">
-        <v>20</v>
-      </c>
-      <c r="FE9">
-        <v>20</v>
-      </c>
-      <c r="FF9" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG9">
-        <v>3</v>
-      </c>
-      <c r="FH9">
-        <v>20</v>
-      </c>
-      <c r="FI9">
-        <v>20</v>
-      </c>
-      <c r="FJ9" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK9">
-        <v>3</v>
-      </c>
-      <c r="FL9" t="s">
-        <v>253</v>
-      </c>
       <c r="FM9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN9">
         <v>0</v>
@@ -6979,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="FR9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS9">
         <v>1</v>
@@ -6991,16 +7018,16 @@
         <v>284</v>
       </c>
       <c r="FV9">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FW9">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX9">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="FY9">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="FZ9">
         <v>0.9</v>
@@ -7036,7 +7063,7 @@
         <v>289</v>
       </c>
       <c r="GT9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU9">
         <v>1</v>
@@ -7045,10 +7072,10 @@
         <v>1</v>
       </c>
       <c r="GW9">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="GX9">
-        <v>3100</v>
+        <v>3900</v>
       </c>
       <c r="GY9">
         <v>0.95</v>
@@ -7063,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="HC9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD9">
         <v>0</v>
@@ -7072,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="HJ9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK9" t="s">
         <v>290</v>
@@ -7090,22 +7117,22 @@
         <v>86400</v>
       </c>
       <c r="HP9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR9" t="s">
         <v>292</v>
       </c>
       <c r="HS9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV9" t="s">
         <v>292</v>
@@ -7128,10 +7155,10 @@
         <v>240</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -7140,7 +7167,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7152,13 +7179,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>2687000</v>
+        <v>5527000</v>
       </c>
       <c r="O10" t="s">
+        <v>247</v>
+      </c>
+      <c r="P10" t="s">
         <v>249</v>
-      </c>
-      <c r="P10" t="s">
-        <v>250</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -7173,40 +7200,40 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V10" t="s">
+        <v>251</v>
+      </c>
+      <c r="W10">
+        <v>3</v>
+      </c>
+      <c r="X10">
+        <v>20</v>
+      </c>
+      <c r="Y10">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>20</v>
+      </c>
+      <c r="AC10">
+        <v>20</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE10">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="s">
         <v>252</v>
-      </c>
-      <c r="W10">
-        <v>3</v>
-      </c>
-      <c r="X10">
-        <v>20</v>
-      </c>
-      <c r="Y10">
-        <v>20</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA10">
-        <v>3</v>
-      </c>
-      <c r="AB10">
-        <v>20</v>
-      </c>
-      <c r="AC10">
-        <v>20</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE10">
-        <v>3</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>253</v>
       </c>
       <c r="AG10">
         <v>0</v>
@@ -7218,7 +7245,7 @@
         <v>6</v>
       </c>
       <c r="AL10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM10">
         <v>1</v>
@@ -7233,41 +7260,41 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS10">
+        <v>3</v>
+      </c>
+      <c r="AT10">
+        <v>20</v>
+      </c>
+      <c r="AU10">
+        <v>20</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW10">
+        <v>3</v>
+      </c>
+      <c r="AX10">
+        <v>20</v>
+      </c>
+      <c r="AY10">
+        <v>20</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA10">
+        <v>3</v>
+      </c>
+      <c r="BB10" t="s">
         <v>252</v>
       </c>
-      <c r="AS10">
-        <v>3</v>
-      </c>
-      <c r="AT10">
-        <v>20</v>
-      </c>
-      <c r="AU10">
-        <v>20</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW10">
-        <v>3</v>
-      </c>
-      <c r="AX10">
-        <v>20</v>
-      </c>
-      <c r="AY10">
-        <v>20</v>
-      </c>
-      <c r="AZ10" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA10">
-        <v>3</v>
-      </c>
-      <c r="BB10" t="s">
-        <v>253</v>
-      </c>
       <c r="BC10">
         <v>1</v>
       </c>
@@ -7275,16 +7302,16 @@
         <v>1</v>
       </c>
       <c r="BE10">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF10" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="BG10">
         <v>55</v>
       </c>
       <c r="BH10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI10">
         <v>1</v>
@@ -7299,41 +7326,41 @@
         <v>9</v>
       </c>
       <c r="BM10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN10" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO10">
+        <v>3</v>
+      </c>
+      <c r="BP10">
+        <v>20</v>
+      </c>
+      <c r="BQ10">
+        <v>20</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS10">
+        <v>3</v>
+      </c>
+      <c r="BT10">
+        <v>20</v>
+      </c>
+      <c r="BU10">
+        <v>20</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW10">
+        <v>3</v>
+      </c>
+      <c r="BX10" t="s">
         <v>252</v>
       </c>
-      <c r="BO10">
-        <v>3</v>
-      </c>
-      <c r="BP10">
-        <v>20</v>
-      </c>
-      <c r="BQ10">
-        <v>20</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS10">
-        <v>3</v>
-      </c>
-      <c r="BT10">
-        <v>20</v>
-      </c>
-      <c r="BU10">
-        <v>20</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW10">
-        <v>3</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>253</v>
-      </c>
       <c r="BY10">
         <v>1</v>
       </c>
@@ -7341,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="CA10">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="CB10" t="s">
         <v>268</v>
@@ -7365,41 +7392,41 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ10" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK10">
+        <v>3</v>
+      </c>
+      <c r="CL10">
+        <v>20</v>
+      </c>
+      <c r="CM10">
+        <v>20</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO10">
+        <v>3</v>
+      </c>
+      <c r="CP10">
+        <v>20</v>
+      </c>
+      <c r="CQ10">
+        <v>20</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS10">
+        <v>3</v>
+      </c>
+      <c r="CT10" t="s">
         <v>252</v>
       </c>
-      <c r="CK10">
-        <v>3</v>
-      </c>
-      <c r="CL10">
-        <v>20</v>
-      </c>
-      <c r="CM10">
-        <v>20</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO10">
-        <v>3</v>
-      </c>
-      <c r="CP10">
-        <v>20</v>
-      </c>
-      <c r="CQ10">
-        <v>20</v>
-      </c>
-      <c r="CR10" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS10">
-        <v>3</v>
-      </c>
-      <c r="CT10" t="s">
-        <v>253</v>
-      </c>
       <c r="CU10">
         <v>1</v>
       </c>
@@ -7407,7 +7434,7 @@
         <v>1</v>
       </c>
       <c r="CW10">
-        <v>4800</v>
+        <v>8500</v>
       </c>
       <c r="CX10" t="s">
         <v>270</v>
@@ -7422,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="DB10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC10">
         <v>1</v>
@@ -7437,40 +7464,40 @@
         <v>9</v>
       </c>
       <c r="DG10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH10" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI10">
+        <v>3</v>
+      </c>
+      <c r="DJ10">
+        <v>20</v>
+      </c>
+      <c r="DK10">
+        <v>20</v>
+      </c>
+      <c r="DL10" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM10">
+        <v>3</v>
+      </c>
+      <c r="DN10">
+        <v>20</v>
+      </c>
+      <c r="DO10">
+        <v>20</v>
+      </c>
+      <c r="DP10" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ10">
+        <v>3</v>
+      </c>
+      <c r="DR10" t="s">
         <v>252</v>
-      </c>
-      <c r="DI10">
-        <v>3</v>
-      </c>
-      <c r="DJ10">
-        <v>20</v>
-      </c>
-      <c r="DK10">
-        <v>20</v>
-      </c>
-      <c r="DL10" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM10">
-        <v>3</v>
-      </c>
-      <c r="DN10">
-        <v>20</v>
-      </c>
-      <c r="DO10">
-        <v>20</v>
-      </c>
-      <c r="DP10" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ10">
-        <v>3</v>
-      </c>
-      <c r="DR10" t="s">
-        <v>253</v>
       </c>
       <c r="DS10" t="s">
         <v>271</v>
@@ -7482,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="DV10">
-        <v>2100</v>
+        <v>4200</v>
       </c>
       <c r="DW10" t="s">
         <v>275</v>
@@ -7491,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="DY10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ10">
         <v>1</v>
@@ -7506,40 +7533,40 @@
         <v>9</v>
       </c>
       <c r="ED10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE10" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF10">
+        <v>3</v>
+      </c>
+      <c r="EG10">
+        <v>20</v>
+      </c>
+      <c r="EH10">
+        <v>20</v>
+      </c>
+      <c r="EI10" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ10">
+        <v>3</v>
+      </c>
+      <c r="EK10">
+        <v>20</v>
+      </c>
+      <c r="EL10">
+        <v>20</v>
+      </c>
+      <c r="EM10" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN10">
+        <v>3</v>
+      </c>
+      <c r="EO10" t="s">
         <v>252</v>
-      </c>
-      <c r="EF10">
-        <v>3</v>
-      </c>
-      <c r="EG10">
-        <v>20</v>
-      </c>
-      <c r="EH10">
-        <v>20</v>
-      </c>
-      <c r="EI10" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ10">
-        <v>3</v>
-      </c>
-      <c r="EK10">
-        <v>20</v>
-      </c>
-      <c r="EL10">
-        <v>20</v>
-      </c>
-      <c r="EM10" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN10">
-        <v>3</v>
-      </c>
-      <c r="EO10" t="s">
-        <v>253</v>
       </c>
       <c r="EP10" t="s">
         <v>271</v>
@@ -7566,43 +7593,43 @@
         <v>9</v>
       </c>
       <c r="FA10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB10" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC10">
+        <v>3</v>
+      </c>
+      <c r="FD10">
+        <v>20</v>
+      </c>
+      <c r="FE10">
+        <v>20</v>
+      </c>
+      <c r="FF10" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG10">
+        <v>3</v>
+      </c>
+      <c r="FH10">
+        <v>20</v>
+      </c>
+      <c r="FI10">
+        <v>20</v>
+      </c>
+      <c r="FJ10" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK10">
+        <v>3</v>
+      </c>
+      <c r="FL10" t="s">
         <v>252</v>
       </c>
-      <c r="FC10">
-        <v>3</v>
-      </c>
-      <c r="FD10">
-        <v>20</v>
-      </c>
-      <c r="FE10">
-        <v>20</v>
-      </c>
-      <c r="FF10" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG10">
-        <v>3</v>
-      </c>
-      <c r="FH10">
-        <v>20</v>
-      </c>
-      <c r="FI10">
-        <v>20</v>
-      </c>
-      <c r="FJ10" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK10">
-        <v>3</v>
-      </c>
-      <c r="FL10" t="s">
-        <v>253</v>
-      </c>
       <c r="FM10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN10">
         <v>0</v>
@@ -7611,28 +7638,28 @@
         <v>0</v>
       </c>
       <c r="FR10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS10">
         <v>1</v>
       </c>
       <c r="FT10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="FU10" t="s">
         <v>285</v>
       </c>
       <c r="FV10">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="FW10">
         <v>7200</v>
       </c>
       <c r="FX10">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FY10">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FZ10">
         <v>0.9</v>
@@ -7646,6 +7673,33 @@
       <c r="GC10" t="b">
         <v>0</v>
       </c>
+      <c r="GD10" t="s">
+        <v>279</v>
+      </c>
+      <c r="GE10">
+        <v>100000</v>
+      </c>
+      <c r="GF10">
+        <v>11000</v>
+      </c>
+      <c r="GG10">
+        <v>22000</v>
+      </c>
+      <c r="GH10">
+        <v>200000</v>
+      </c>
+      <c r="GI10">
+        <v>0.9</v>
+      </c>
+      <c r="GJ10">
+        <v>0.8</v>
+      </c>
+      <c r="GK10" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL10" t="b">
+        <v>0</v>
+      </c>
       <c r="GM10" t="s">
         <v>287</v>
       </c>
@@ -7668,7 +7722,7 @@
         <v>289</v>
       </c>
       <c r="GT10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU10">
         <v>1</v>
@@ -7677,10 +7731,10 @@
         <v>1</v>
       </c>
       <c r="GW10">
-        <v>2700</v>
+        <v>5500</v>
       </c>
       <c r="GX10">
-        <v>2700</v>
+        <v>5500</v>
       </c>
       <c r="GY10">
         <v>0.95</v>
@@ -7695,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="HC10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD10">
         <v>0</v>
@@ -7704,7 +7758,7 @@
         <v>0</v>
       </c>
       <c r="HJ10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK10" t="s">
         <v>290</v>
@@ -7722,22 +7776,22 @@
         <v>86400</v>
       </c>
       <c r="HP10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR10" t="s">
         <v>292</v>
       </c>
       <c r="HS10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV10" t="s">
         <v>292</v>
@@ -7760,10 +7814,10 @@
         <v>241</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -7772,7 +7826,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7784,13 +7838,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>5527000</v>
+        <v>4402000</v>
       </c>
       <c r="O11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -7805,40 +7859,40 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="V11" t="s">
+        <v>251</v>
+      </c>
+      <c r="W11">
+        <v>3</v>
+      </c>
+      <c r="X11">
+        <v>20</v>
+      </c>
+      <c r="Y11">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>251</v>
+      </c>
+      <c r="AA11">
+        <v>3</v>
+      </c>
+      <c r="AB11">
+        <v>20</v>
+      </c>
+      <c r="AC11">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE11">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="s">
         <v>252</v>
-      </c>
-      <c r="W11">
-        <v>3</v>
-      </c>
-      <c r="X11">
-        <v>20</v>
-      </c>
-      <c r="Y11">
-        <v>20</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>252</v>
-      </c>
-      <c r="AA11">
-        <v>3</v>
-      </c>
-      <c r="AB11">
-        <v>20</v>
-      </c>
-      <c r="AC11">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>252</v>
-      </c>
-      <c r="AE11">
-        <v>3</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>253</v>
       </c>
       <c r="AG11">
         <v>0</v>
@@ -7850,7 +7904,7 @@
         <v>6</v>
       </c>
       <c r="AL11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM11">
         <v>1</v>
@@ -7865,41 +7919,41 @@
         <v>9</v>
       </c>
       <c r="AQ11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AR11" t="s">
+        <v>251</v>
+      </c>
+      <c r="AS11">
+        <v>3</v>
+      </c>
+      <c r="AT11">
+        <v>20</v>
+      </c>
+      <c r="AU11">
+        <v>20</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>251</v>
+      </c>
+      <c r="AW11">
+        <v>3</v>
+      </c>
+      <c r="AX11">
+        <v>20</v>
+      </c>
+      <c r="AY11">
+        <v>20</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BA11">
+        <v>3</v>
+      </c>
+      <c r="BB11" t="s">
         <v>252</v>
       </c>
-      <c r="AS11">
-        <v>3</v>
-      </c>
-      <c r="AT11">
-        <v>20</v>
-      </c>
-      <c r="AU11">
-        <v>20</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>252</v>
-      </c>
-      <c r="AW11">
-        <v>3</v>
-      </c>
-      <c r="AX11">
-        <v>20</v>
-      </c>
-      <c r="AY11">
-        <v>20</v>
-      </c>
-      <c r="AZ11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA11">
-        <v>3</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>253</v>
-      </c>
       <c r="BC11">
         <v>1</v>
       </c>
@@ -7907,16 +7961,16 @@
         <v>1</v>
       </c>
       <c r="BE11">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="BG11">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI11">
         <v>1</v>
@@ -7931,41 +7985,41 @@
         <v>9</v>
       </c>
       <c r="BM11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BN11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BO11">
+        <v>3</v>
+      </c>
+      <c r="BP11">
+        <v>20</v>
+      </c>
+      <c r="BQ11">
+        <v>20</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BS11">
+        <v>3</v>
+      </c>
+      <c r="BT11">
+        <v>20</v>
+      </c>
+      <c r="BU11">
+        <v>20</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>251</v>
+      </c>
+      <c r="BW11">
+        <v>3</v>
+      </c>
+      <c r="BX11" t="s">
         <v>252</v>
       </c>
-      <c r="BO11">
-        <v>3</v>
-      </c>
-      <c r="BP11">
-        <v>20</v>
-      </c>
-      <c r="BQ11">
-        <v>20</v>
-      </c>
-      <c r="BR11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BS11">
-        <v>3</v>
-      </c>
-      <c r="BT11">
-        <v>20</v>
-      </c>
-      <c r="BU11">
-        <v>20</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>252</v>
-      </c>
-      <c r="BW11">
-        <v>3</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>253</v>
-      </c>
       <c r="BY11">
         <v>1</v>
       </c>
@@ -7973,10 +8027,10 @@
         <v>1</v>
       </c>
       <c r="CA11">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="CB11" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="CC11">
         <v>55</v>
@@ -7997,41 +8051,41 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="CJ11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CK11">
+        <v>3</v>
+      </c>
+      <c r="CL11">
+        <v>20</v>
+      </c>
+      <c r="CM11">
+        <v>20</v>
+      </c>
+      <c r="CN11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CO11">
+        <v>3</v>
+      </c>
+      <c r="CP11">
+        <v>20</v>
+      </c>
+      <c r="CQ11">
+        <v>20</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>251</v>
+      </c>
+      <c r="CS11">
+        <v>3</v>
+      </c>
+      <c r="CT11" t="s">
         <v>252</v>
       </c>
-      <c r="CK11">
-        <v>3</v>
-      </c>
-      <c r="CL11">
-        <v>20</v>
-      </c>
-      <c r="CM11">
-        <v>20</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CO11">
-        <v>3</v>
-      </c>
-      <c r="CP11">
-        <v>20</v>
-      </c>
-      <c r="CQ11">
-        <v>20</v>
-      </c>
-      <c r="CR11" t="s">
-        <v>252</v>
-      </c>
-      <c r="CS11">
-        <v>3</v>
-      </c>
-      <c r="CT11" t="s">
-        <v>253</v>
-      </c>
       <c r="CU11">
         <v>1</v>
       </c>
@@ -8039,7 +8093,7 @@
         <v>1</v>
       </c>
       <c r="CW11">
-        <v>9400</v>
+        <v>7800</v>
       </c>
       <c r="CX11" t="s">
         <v>270</v>
@@ -8054,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="DB11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="DC11">
         <v>1</v>
@@ -8069,40 +8123,40 @@
         <v>9</v>
       </c>
       <c r="DG11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="DH11" t="s">
+        <v>251</v>
+      </c>
+      <c r="DI11">
+        <v>3</v>
+      </c>
+      <c r="DJ11">
+        <v>20</v>
+      </c>
+      <c r="DK11">
+        <v>20</v>
+      </c>
+      <c r="DL11" t="s">
+        <v>251</v>
+      </c>
+      <c r="DM11">
+        <v>3</v>
+      </c>
+      <c r="DN11">
+        <v>20</v>
+      </c>
+      <c r="DO11">
+        <v>20</v>
+      </c>
+      <c r="DP11" t="s">
+        <v>251</v>
+      </c>
+      <c r="DQ11">
+        <v>3</v>
+      </c>
+      <c r="DR11" t="s">
         <v>252</v>
-      </c>
-      <c r="DI11">
-        <v>3</v>
-      </c>
-      <c r="DJ11">
-        <v>20</v>
-      </c>
-      <c r="DK11">
-        <v>20</v>
-      </c>
-      <c r="DL11" t="s">
-        <v>252</v>
-      </c>
-      <c r="DM11">
-        <v>3</v>
-      </c>
-      <c r="DN11">
-        <v>20</v>
-      </c>
-      <c r="DO11">
-        <v>20</v>
-      </c>
-      <c r="DP11" t="s">
-        <v>252</v>
-      </c>
-      <c r="DQ11">
-        <v>3</v>
-      </c>
-      <c r="DR11" t="s">
-        <v>253</v>
       </c>
       <c r="DS11" t="s">
         <v>271</v>
@@ -8114,16 +8168,16 @@
         <v>1</v>
       </c>
       <c r="DV11">
-        <v>3900</v>
+        <v>2800</v>
       </c>
       <c r="DW11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="DX11" t="b">
         <v>1</v>
       </c>
       <c r="DY11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DZ11">
         <v>1</v>
@@ -8138,40 +8192,40 @@
         <v>9</v>
       </c>
       <c r="ED11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="EE11" t="s">
+        <v>251</v>
+      </c>
+      <c r="EF11">
+        <v>3</v>
+      </c>
+      <c r="EG11">
+        <v>20</v>
+      </c>
+      <c r="EH11">
+        <v>20</v>
+      </c>
+      <c r="EI11" t="s">
+        <v>251</v>
+      </c>
+      <c r="EJ11">
+        <v>3</v>
+      </c>
+      <c r="EK11">
+        <v>20</v>
+      </c>
+      <c r="EL11">
+        <v>20</v>
+      </c>
+      <c r="EM11" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN11">
+        <v>3</v>
+      </c>
+      <c r="EO11" t="s">
         <v>252</v>
-      </c>
-      <c r="EF11">
-        <v>3</v>
-      </c>
-      <c r="EG11">
-        <v>20</v>
-      </c>
-      <c r="EH11">
-        <v>20</v>
-      </c>
-      <c r="EI11" t="s">
-        <v>252</v>
-      </c>
-      <c r="EJ11">
-        <v>3</v>
-      </c>
-      <c r="EK11">
-        <v>20</v>
-      </c>
-      <c r="EL11">
-        <v>20</v>
-      </c>
-      <c r="EM11" t="s">
-        <v>252</v>
-      </c>
-      <c r="EN11">
-        <v>3</v>
-      </c>
-      <c r="EO11" t="s">
-        <v>253</v>
       </c>
       <c r="EP11" t="s">
         <v>271</v>
@@ -8198,43 +8252,43 @@
         <v>9</v>
       </c>
       <c r="FA11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="FB11" t="s">
+        <v>251</v>
+      </c>
+      <c r="FC11">
+        <v>3</v>
+      </c>
+      <c r="FD11">
+        <v>20</v>
+      </c>
+      <c r="FE11">
+        <v>20</v>
+      </c>
+      <c r="FF11" t="s">
+        <v>251</v>
+      </c>
+      <c r="FG11">
+        <v>3</v>
+      </c>
+      <c r="FH11">
+        <v>20</v>
+      </c>
+      <c r="FI11">
+        <v>20</v>
+      </c>
+      <c r="FJ11" t="s">
+        <v>251</v>
+      </c>
+      <c r="FK11">
+        <v>3</v>
+      </c>
+      <c r="FL11" t="s">
         <v>252</v>
       </c>
-      <c r="FC11">
-        <v>3</v>
-      </c>
-      <c r="FD11">
-        <v>20</v>
-      </c>
-      <c r="FE11">
-        <v>20</v>
-      </c>
-      <c r="FF11" t="s">
-        <v>252</v>
-      </c>
-      <c r="FG11">
-        <v>3</v>
-      </c>
-      <c r="FH11">
-        <v>20</v>
-      </c>
-      <c r="FI11">
-        <v>20</v>
-      </c>
-      <c r="FJ11" t="s">
-        <v>252</v>
-      </c>
-      <c r="FK11">
-        <v>3</v>
-      </c>
-      <c r="FL11" t="s">
-        <v>253</v>
-      </c>
       <c r="FM11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FN11">
         <v>0</v>
@@ -8243,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="FR11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="FS11">
         <v>1</v>
@@ -8252,19 +8306,19 @@
         <v>1</v>
       </c>
       <c r="FU11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="FV11">
+        <v>75000</v>
+      </c>
+      <c r="FW11">
+        <v>7200</v>
+      </c>
+      <c r="FX11">
+        <v>11000</v>
+      </c>
+      <c r="FY11">
         <v>100000</v>
-      </c>
-      <c r="FW11">
-        <v>11000</v>
-      </c>
-      <c r="FX11">
-        <v>22000</v>
-      </c>
-      <c r="FY11">
-        <v>200000</v>
       </c>
       <c r="FZ11">
         <v>0.9</v>
@@ -8300,7 +8354,7 @@
         <v>289</v>
       </c>
       <c r="GT11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="GU11">
         <v>1</v>
@@ -8309,10 +8363,10 @@
         <v>1</v>
       </c>
       <c r="GW11">
-        <v>5500</v>
+        <v>4400</v>
       </c>
       <c r="GX11">
-        <v>5500</v>
+        <v>4400</v>
       </c>
       <c r="GY11">
         <v>0.95</v>
@@ -8327,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="HC11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HD11">
         <v>0</v>
@@ -8336,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="HJ11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="HK11" t="s">
         <v>290</v>
@@ -8354,22 +8408,22 @@
         <v>86400</v>
       </c>
       <c r="HP11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HQ11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HR11" t="s">
         <v>292</v>
       </c>
       <c r="HS11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HT11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HU11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="HV11" t="s">
         <v>292</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="322">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -717,57 +717,57 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>Xsg719VWbzc8WGq</t>
-  </si>
-  <si>
-    <t>tlndEuosN2YTsfi</t>
-  </si>
-  <si>
-    <t>eSoMCS0UISzmJjZ</t>
-  </si>
-  <si>
-    <t>zc3xI9GvdO0JEmA</t>
-  </si>
-  <si>
-    <t>A3GbC1RuCSzwfsB</t>
-  </si>
-  <si>
-    <t>b1LwgBQqloIH4Ia</t>
-  </si>
-  <si>
-    <t>EWHJ2Ztf4uf7kXD</t>
-  </si>
-  <si>
-    <t>WWosr6A645WT33L</t>
-  </si>
-  <si>
-    <t>rnExJsXYZDHNtOh</t>
-  </si>
-  <si>
-    <t>xiEjT08QnVwRPwo</t>
-  </si>
-  <si>
-    <t>hh_3863_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
+    <t>rW9Bi4f1AbGBCtO</t>
+  </si>
+  <si>
+    <t>Jq4Y5Afz7yd3pjK</t>
+  </si>
+  <si>
+    <t>S6DjdLlEFYi5V5p</t>
+  </si>
+  <si>
+    <t>ZPaCL1szWJW6uw8</t>
+  </si>
+  <si>
+    <t>pL6jAjPWyJofFLv</t>
+  </si>
+  <si>
+    <t>1Vr1dXuWgexa3Zr</t>
+  </si>
+  <si>
+    <t>UcyV1AOXfAmBPSw</t>
+  </si>
+  <si>
+    <t>d5uiSwAOqPU9zwX</t>
+  </si>
+  <si>
+    <t>6G9Udy7Ll56HIud</t>
+  </si>
+  <si>
+    <t>UkKBPJGYQw9gFHU</t>
+  </si>
+  <si>
+    <t>hh_2687_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3564_0.csv</t>
   </si>
   <si>
     <t>hh_2012_3.csv</t>
   </si>
   <si>
-    <t>hh_4536_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4402_0.csv</t>
   </si>
   <si>
     <t>hh_5527_0.csv</t>
   </si>
   <si>
-    <t>hh_4402_0.csv</t>
-  </si>
-  <si>
     <t>perfect</t>
   </si>
   <si>
@@ -783,106 +783,112 @@
     <t>rfr</t>
   </si>
   <si>
-    <t>heat_3863_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2262_0.csv</t>
+    <t>heat_2687_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3296_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3564_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
   </si>
   <si>
     <t>heat_2012_3.csv</t>
   </si>
   <si>
-    <t>heat_4536_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_3296_0.csv</t>
+    <t>heat_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_4402_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
   </si>
   <si>
     <t>heat_5527_0.csv</t>
   </si>
   <si>
-    <t>heat_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4402_0.csv</t>
-  </si>
-  <si>
     <t>naive</t>
   </si>
   <si>
-    <t>dhw_gen_2_pu.csv</t>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
   </si>
   <si>
     <t>dhw_gen_6_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
     <t>dhw_gen_3_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
-    <t>pv_config.json</t>
+    <t>pv_3_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_1_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_2_pu.csv</t>
   </si>
   <si>
     <t>green_local</t>
   </si>
   <si>
+    <t>wind_Nordex_MM92_3300000_131.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
     <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
   </si>
   <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
-  </si>
-  <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>arima</t>
-  </si>
-  <si>
     <t>local</t>
   </si>
   <si>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_44.csv</t>
+  </si>
+  <si>
     <t>ev_fulltime_45.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_47.csv</t>
-  </si>
-  <si>
     <t>ev_parttime_88.csv</t>
   </si>
   <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_46.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_90.csv</t>
+    <t>ev_fulltime_49.csv</t>
   </si>
   <si>
     <t>ev_freetime_1.csv</t>
   </si>
   <si>
-    <t>ev_fulltime_44.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>price_sensitive</t>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_0.csv</t>
+  </si>
+  <si>
+    <t>min_soc</t>
   </si>
   <si>
     <t>arrival</t>
@@ -894,7 +900,7 @@
     <t>linopy</t>
   </si>
   <si>
-    <t>['linear']</t>
+    <t>linear</t>
   </si>
   <si>
     <t>['naive', 'naive']</t>
@@ -2045,10 +2051,10 @@
         <v>232</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -2057,7 +2063,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -2069,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>3863000</v>
+        <v>2687000</v>
       </c>
       <c r="O2" t="s">
         <v>242</v>
@@ -2192,13 +2198,13 @@
         <v>1</v>
       </c>
       <c r="BE2">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF2" t="s">
         <v>254</v>
       </c>
       <c r="BG2">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH2" t="s">
         <v>263</v>
@@ -2258,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="CA2">
-        <v>1800000</v>
+        <v>2800000</v>
       </c>
       <c r="CB2" t="s">
         <v>264</v>
@@ -2324,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="CW2">
-        <v>6200</v>
+        <v>4000</v>
       </c>
       <c r="CX2" t="s">
         <v>270</v>
@@ -2390,7 +2396,7 @@
         <v>252</v>
       </c>
       <c r="DS2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -2399,16 +2405,16 @@
         <v>1</v>
       </c>
       <c r="DV2">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="DW2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="DX2" t="b">
         <v>1</v>
       </c>
       <c r="DY2" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ2">
         <v>1</v>
@@ -2459,7 +2465,7 @@
         <v>252</v>
       </c>
       <c r="EP2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ2">
         <v>0</v>
@@ -2519,7 +2525,7 @@
         <v>252</v>
       </c>
       <c r="FM2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN2">
         <v>0</v>
@@ -2528,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="FR2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS2">
         <v>1</v>
@@ -2537,19 +2543,19 @@
         <v>2</v>
       </c>
       <c r="FU2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="FV2">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FW2">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FX2">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="FY2">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="FZ2">
         <v>0.9</v>
@@ -2564,19 +2570,19 @@
         <v>0</v>
       </c>
       <c r="GD2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="GE2">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="GF2">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GG2">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="GH2">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="GI2">
         <v>0.9</v>
@@ -2591,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="GM2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN2">
         <v>0.05</v>
@@ -2606,13 +2612,13 @@
         <v>8.5</v>
       </c>
       <c r="GR2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU2">
         <v>1</v>
@@ -2621,10 +2627,10 @@
         <v>1</v>
       </c>
       <c r="GW2">
-        <v>3900</v>
+        <v>2700</v>
       </c>
       <c r="GX2">
-        <v>3900</v>
+        <v>2700</v>
       </c>
       <c r="GY2">
         <v>0.95</v>
@@ -2639,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="HC2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD2">
         <v>0</v>
@@ -2648,19 +2654,19 @@
         <v>0</v>
       </c>
       <c r="HJ2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM2">
         <v>86400</v>
       </c>
       <c r="HN2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO2">
         <v>86400</v>
@@ -2672,7 +2678,7 @@
         <v>263</v>
       </c>
       <c r="HR2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS2" t="s">
         <v>263</v>
@@ -2684,7 +2690,7 @@
         <v>263</v>
       </c>
       <c r="HV2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW2">
         <v>86400</v>
@@ -2728,7 +2734,7 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>2262000</v>
+        <v>3296000</v>
       </c>
       <c r="O3" t="s">
         <v>243</v>
@@ -2857,7 +2863,7 @@
         <v>255</v>
       </c>
       <c r="BG3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH3" t="s">
         <v>263</v>
@@ -2983,7 +2989,7 @@
         <v>1</v>
       </c>
       <c r="CW3">
-        <v>3400</v>
+        <v>5100</v>
       </c>
       <c r="CX3" t="s">
         <v>270</v>
@@ -3049,7 +3055,7 @@
         <v>252</v>
       </c>
       <c r="DS3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT3">
         <v>1</v>
@@ -3058,16 +3064,16 @@
         <v>1</v>
       </c>
       <c r="DV3">
-        <v>1100</v>
+        <v>1900</v>
       </c>
       <c r="DW3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DX3" t="b">
         <v>1</v>
       </c>
       <c r="DY3" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ3">
         <v>1</v>
@@ -3118,7 +3124,7 @@
         <v>252</v>
       </c>
       <c r="EP3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ3">
         <v>0</v>
@@ -3178,7 +3184,7 @@
         <v>252</v>
       </c>
       <c r="FM3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN3">
         <v>0</v>
@@ -3187,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="FR3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS3">
         <v>1</v>
@@ -3196,19 +3202,19 @@
         <v>1</v>
       </c>
       <c r="FU3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="FV3">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FW3">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX3">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="FY3">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="FZ3">
         <v>0.9</v>
@@ -3223,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="GM3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN3">
         <v>0.05</v>
@@ -3238,13 +3244,13 @@
         <v>8.5</v>
       </c>
       <c r="GR3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU3">
         <v>1</v>
@@ -3253,10 +3259,10 @@
         <v>1</v>
       </c>
       <c r="GW3">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="GX3">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="GY3">
         <v>0.95</v>
@@ -3271,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="HC3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD3">
         <v>0</v>
@@ -3280,19 +3286,19 @@
         <v>0</v>
       </c>
       <c r="HJ3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM3">
         <v>86400</v>
       </c>
       <c r="HN3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO3">
         <v>86400</v>
@@ -3304,7 +3310,7 @@
         <v>263</v>
       </c>
       <c r="HR3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS3" t="s">
         <v>263</v>
@@ -3316,7 +3322,7 @@
         <v>263</v>
       </c>
       <c r="HV3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW3">
         <v>86400</v>
@@ -3360,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>2012000</v>
+        <v>3564000</v>
       </c>
       <c r="O4" t="s">
         <v>244</v>
@@ -3552,7 +3558,7 @@
         <v>2800000</v>
       </c>
       <c r="CB4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="CC4">
         <v>55</v>
@@ -3615,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="CW4">
-        <v>3200</v>
+        <v>5100</v>
       </c>
       <c r="CX4" t="s">
         <v>270</v>
@@ -3681,7 +3687,7 @@
         <v>252</v>
       </c>
       <c r="DS4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT4">
         <v>1</v>
@@ -3690,16 +3696,16 @@
         <v>1</v>
       </c>
       <c r="DV4">
-        <v>1700</v>
+        <v>2900</v>
       </c>
       <c r="DW4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="DX4" t="b">
         <v>1</v>
       </c>
       <c r="DY4" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ4">
         <v>1</v>
@@ -3750,7 +3756,7 @@
         <v>252</v>
       </c>
       <c r="EP4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ4">
         <v>0</v>
@@ -3810,7 +3816,7 @@
         <v>252</v>
       </c>
       <c r="FM4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN4">
         <v>0</v>
@@ -3819,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="FR4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS4">
         <v>1</v>
@@ -3828,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="FU4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="FV4">
         <v>75000</v>
@@ -3855,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="GM4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN4">
         <v>0.05</v>
@@ -3870,13 +3876,13 @@
         <v>8.5</v>
       </c>
       <c r="GR4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU4">
         <v>1</v>
@@ -3885,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="GW4">
-        <v>2000</v>
+        <v>3600</v>
       </c>
       <c r="GX4">
-        <v>2000</v>
+        <v>3600</v>
       </c>
       <c r="GY4">
         <v>0.95</v>
@@ -3903,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="HC4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD4">
         <v>0</v>
@@ -3912,19 +3918,19 @@
         <v>0</v>
       </c>
       <c r="HJ4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM4">
         <v>86400</v>
       </c>
       <c r="HN4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO4">
         <v>86400</v>
@@ -3936,7 +3942,7 @@
         <v>263</v>
       </c>
       <c r="HR4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS4" t="s">
         <v>263</v>
@@ -3948,7 +3954,7 @@
         <v>263</v>
       </c>
       <c r="HV4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW4">
         <v>86400</v>
@@ -3968,10 +3974,10 @@
         <v>235</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -3980,7 +3986,7 @@
         <v>2.6</v>
       </c>
       <c r="J5">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -3992,10 +3998,10 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>4536000</v>
+        <v>3564000</v>
       </c>
       <c r="O5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P5" t="s">
         <v>249</v>
@@ -4115,13 +4121,13 @@
         <v>1</v>
       </c>
       <c r="BE5">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF5" t="s">
         <v>257</v>
       </c>
       <c r="BG5">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH5" t="s">
         <v>263</v>
@@ -4181,10 +4187,10 @@
         <v>1</v>
       </c>
       <c r="CA5">
-        <v>2100000</v>
+        <v>3200000</v>
       </c>
       <c r="CB5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="CC5">
         <v>55</v>
@@ -4247,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="CW5">
-        <v>5700</v>
+        <v>6100</v>
       </c>
       <c r="CX5" t="s">
         <v>270</v>
@@ -4313,7 +4319,7 @@
         <v>252</v>
       </c>
       <c r="DS5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT5">
         <v>1</v>
@@ -4322,16 +4328,16 @@
         <v>1</v>
       </c>
       <c r="DV5">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="DW5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="DX5" t="b">
         <v>1</v>
       </c>
       <c r="DY5" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ5">
         <v>1</v>
@@ -4382,7 +4388,7 @@
         <v>252</v>
       </c>
       <c r="EP5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ5">
         <v>0</v>
@@ -4442,7 +4448,7 @@
         <v>252</v>
       </c>
       <c r="FM5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN5">
         <v>0</v>
@@ -4451,16 +4457,16 @@
         <v>0</v>
       </c>
       <c r="FR5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS5">
         <v>1</v>
       </c>
       <c r="FT5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="FU5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="FV5">
         <v>75000</v>
@@ -4486,8 +4492,35 @@
       <c r="GC5" t="b">
         <v>0</v>
       </c>
+      <c r="GD5" t="s">
+        <v>281</v>
+      </c>
+      <c r="GE5">
+        <v>75000</v>
+      </c>
+      <c r="GF5">
+        <v>7200</v>
+      </c>
+      <c r="GG5">
+        <v>11000</v>
+      </c>
+      <c r="GH5">
+        <v>100000</v>
+      </c>
+      <c r="GI5">
+        <v>0.9</v>
+      </c>
+      <c r="GJ5">
+        <v>0.8</v>
+      </c>
+      <c r="GK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL5" t="b">
+        <v>0</v>
+      </c>
       <c r="GM5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN5">
         <v>0.05</v>
@@ -4502,13 +4535,13 @@
         <v>8.5</v>
       </c>
       <c r="GR5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU5">
         <v>1</v>
@@ -4517,10 +4550,10 @@
         <v>1</v>
       </c>
       <c r="GW5">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="GX5">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="GY5">
         <v>0.95</v>
@@ -4535,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="HC5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD5">
         <v>0</v>
@@ -4544,19 +4577,19 @@
         <v>0</v>
       </c>
       <c r="HJ5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM5">
         <v>86400</v>
       </c>
       <c r="HN5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO5">
         <v>86400</v>
@@ -4568,7 +4601,7 @@
         <v>263</v>
       </c>
       <c r="HR5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS5" t="s">
         <v>263</v>
@@ -4580,7 +4613,7 @@
         <v>263</v>
       </c>
       <c r="HV5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW5">
         <v>86400</v>
@@ -4600,10 +4633,10 @@
         <v>236</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -4612,7 +4645,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4624,10 +4657,10 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>3296000</v>
+        <v>2012000</v>
       </c>
       <c r="O6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P6" t="s">
         <v>249</v>
@@ -4747,13 +4780,13 @@
         <v>1</v>
       </c>
       <c r="BE6">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF6" t="s">
         <v>258</v>
       </c>
       <c r="BG6">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH6" t="s">
         <v>263</v>
@@ -4816,7 +4849,7 @@
         <v>2400000</v>
       </c>
       <c r="CB6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="CC6">
         <v>55</v>
@@ -4879,16 +4912,16 @@
         <v>1</v>
       </c>
       <c r="CW6">
-        <v>5600</v>
+        <v>2800</v>
       </c>
       <c r="CX6" t="s">
         <v>270</v>
       </c>
       <c r="CY6">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA6" t="b">
         <v>1</v>
@@ -4945,7 +4978,7 @@
         <v>252</v>
       </c>
       <c r="DS6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT6">
         <v>1</v>
@@ -4954,16 +4987,16 @@
         <v>1</v>
       </c>
       <c r="DV6">
-        <v>2100</v>
+        <v>1500</v>
       </c>
       <c r="DW6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="DX6" t="b">
         <v>1</v>
       </c>
       <c r="DY6" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ6">
         <v>1</v>
@@ -5014,7 +5047,7 @@
         <v>252</v>
       </c>
       <c r="EP6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ6">
         <v>0</v>
@@ -5074,7 +5107,7 @@
         <v>252</v>
       </c>
       <c r="FM6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN6">
         <v>0</v>
@@ -5083,16 +5116,16 @@
         <v>0</v>
       </c>
       <c r="FR6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS6">
         <v>1</v>
       </c>
       <c r="FT6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="FU6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="FV6">
         <v>50000</v>
@@ -5118,8 +5151,35 @@
       <c r="GC6" t="b">
         <v>0</v>
       </c>
+      <c r="GD6" t="s">
+        <v>286</v>
+      </c>
+      <c r="GE6">
+        <v>50000</v>
+      </c>
+      <c r="GF6">
+        <v>7200</v>
+      </c>
+      <c r="GG6">
+        <v>7200</v>
+      </c>
+      <c r="GH6">
+        <v>50000</v>
+      </c>
+      <c r="GI6">
+        <v>0.9</v>
+      </c>
+      <c r="GJ6">
+        <v>0.8</v>
+      </c>
+      <c r="GK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL6" t="b">
+        <v>0</v>
+      </c>
       <c r="GM6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN6">
         <v>0.05</v>
@@ -5134,13 +5194,13 @@
         <v>8.5</v>
       </c>
       <c r="GR6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU6">
         <v>1</v>
@@ -5149,10 +5209,10 @@
         <v>1</v>
       </c>
       <c r="GW6">
-        <v>3300</v>
+        <v>2000</v>
       </c>
       <c r="GX6">
-        <v>3300</v>
+        <v>2000</v>
       </c>
       <c r="GY6">
         <v>0.95</v>
@@ -5167,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="HC6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD6">
         <v>0</v>
@@ -5176,19 +5236,19 @@
         <v>0</v>
       </c>
       <c r="HJ6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM6">
         <v>86400</v>
       </c>
       <c r="HN6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO6">
         <v>86400</v>
@@ -5200,7 +5260,7 @@
         <v>263</v>
       </c>
       <c r="HR6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS6" t="s">
         <v>263</v>
@@ -5212,7 +5272,7 @@
         <v>263</v>
       </c>
       <c r="HV6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW6">
         <v>86400</v>
@@ -5256,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3296000</v>
+        <v>3125000</v>
       </c>
       <c r="O7" t="s">
         <v>246</v>
@@ -5445,10 +5505,10 @@
         <v>1</v>
       </c>
       <c r="CA7">
-        <v>2800000</v>
+        <v>3200000</v>
       </c>
       <c r="CB7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="CC7">
         <v>55</v>
@@ -5511,16 +5571,16 @@
         <v>1</v>
       </c>
       <c r="CW7">
-        <v>4400</v>
+        <v>4700</v>
       </c>
       <c r="CX7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="CY7">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
@@ -5577,7 +5637,7 @@
         <v>252</v>
       </c>
       <c r="DS7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT7">
         <v>1</v>
@@ -5586,16 +5646,16 @@
         <v>1</v>
       </c>
       <c r="DV7">
-        <v>1700</v>
+        <v>2400</v>
       </c>
       <c r="DW7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DX7" t="b">
         <v>1</v>
       </c>
       <c r="DY7" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ7">
         <v>1</v>
@@ -5646,7 +5706,7 @@
         <v>252</v>
       </c>
       <c r="EP7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ7">
         <v>0</v>
@@ -5706,7 +5766,7 @@
         <v>252</v>
       </c>
       <c r="FM7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN7">
         <v>0</v>
@@ -5715,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="FR7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS7">
         <v>1</v>
       </c>
       <c r="FT7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="FU7" t="s">
         <v>283</v>
       </c>
       <c r="FV7">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="FW7">
         <v>7200</v>
       </c>
       <c r="FX7">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FY7">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FZ7">
         <v>0.9</v>
@@ -5750,35 +5810,8 @@
       <c r="GC7" t="b">
         <v>0</v>
       </c>
-      <c r="GD7" t="s">
-        <v>281</v>
-      </c>
-      <c r="GE7">
-        <v>50000</v>
-      </c>
-      <c r="GF7">
-        <v>7200</v>
-      </c>
-      <c r="GG7">
-        <v>7200</v>
-      </c>
-      <c r="GH7">
-        <v>50000</v>
-      </c>
-      <c r="GI7">
-        <v>0.9</v>
-      </c>
-      <c r="GJ7">
-        <v>0.8</v>
-      </c>
-      <c r="GK7" t="b">
-        <v>0</v>
-      </c>
-      <c r="GL7" t="b">
-        <v>0</v>
-      </c>
       <c r="GM7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN7">
         <v>0.05</v>
@@ -5793,13 +5826,13 @@
         <v>8.5</v>
       </c>
       <c r="GR7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU7">
         <v>1</v>
@@ -5808,10 +5841,10 @@
         <v>1</v>
       </c>
       <c r="GW7">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="GX7">
-        <v>3300</v>
+        <v>3100</v>
       </c>
       <c r="GY7">
         <v>0.95</v>
@@ -5826,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="HC7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD7">
         <v>0</v>
@@ -5835,19 +5868,19 @@
         <v>0</v>
       </c>
       <c r="HJ7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM7">
         <v>86400</v>
       </c>
       <c r="HN7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO7">
         <v>86400</v>
@@ -5859,7 +5892,7 @@
         <v>263</v>
       </c>
       <c r="HR7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS7" t="s">
         <v>263</v>
@@ -5871,7 +5904,7 @@
         <v>263</v>
       </c>
       <c r="HV7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW7">
         <v>86400</v>
@@ -5891,10 +5924,10 @@
         <v>238</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -5903,7 +5936,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -5915,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>5527000</v>
+        <v>4402000</v>
       </c>
       <c r="O8" t="s">
         <v>247</v>
@@ -6038,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="BE8">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF8" t="s">
         <v>260</v>
@@ -6104,10 +6137,10 @@
         <v>1</v>
       </c>
       <c r="CA8">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="CB8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="CC8">
         <v>55</v>
@@ -6170,10 +6203,10 @@
         <v>1</v>
       </c>
       <c r="CW8">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="CX8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="CY8">
         <v>0</v>
@@ -6236,7 +6269,7 @@
         <v>252</v>
       </c>
       <c r="DS8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT8">
         <v>1</v>
@@ -6245,16 +6278,16 @@
         <v>1</v>
       </c>
       <c r="DV8">
-        <v>4000</v>
+        <v>2200</v>
       </c>
       <c r="DW8" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="DX8" t="b">
         <v>1</v>
       </c>
       <c r="DY8" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ8">
         <v>1</v>
@@ -6305,7 +6338,7 @@
         <v>252</v>
       </c>
       <c r="EP8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ8">
         <v>0</v>
@@ -6365,7 +6398,7 @@
         <v>252</v>
       </c>
       <c r="FM8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN8">
         <v>0</v>
@@ -6374,7 +6407,7 @@
         <v>0</v>
       </c>
       <c r="FR8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS8">
         <v>1</v>
@@ -6383,19 +6416,19 @@
         <v>1</v>
       </c>
       <c r="FU8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="FV8">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FW8">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX8">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="FY8">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="FZ8">
         <v>0.9</v>
@@ -6410,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="GM8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN8">
         <v>0.05</v>
@@ -6425,13 +6458,13 @@
         <v>8.5</v>
       </c>
       <c r="GR8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU8">
         <v>1</v>
@@ -6440,10 +6473,10 @@
         <v>1</v>
       </c>
       <c r="GW8">
-        <v>5500</v>
+        <v>4400</v>
       </c>
       <c r="GX8">
-        <v>5500</v>
+        <v>4400</v>
       </c>
       <c r="GY8">
         <v>0.95</v>
@@ -6458,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="HC8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD8">
         <v>0</v>
@@ -6467,19 +6500,19 @@
         <v>0</v>
       </c>
       <c r="HJ8" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM8">
         <v>86400</v>
       </c>
       <c r="HN8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO8">
         <v>86400</v>
@@ -6491,7 +6524,7 @@
         <v>263</v>
       </c>
       <c r="HR8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS8" t="s">
         <v>263</v>
@@ -6503,7 +6536,7 @@
         <v>263</v>
       </c>
       <c r="HV8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW8">
         <v>86400</v>
@@ -6547,10 +6580,10 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3863000</v>
+        <v>3564000</v>
       </c>
       <c r="O9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P9" t="s">
         <v>249</v>
@@ -6673,7 +6706,7 @@
         <v>5500000</v>
       </c>
       <c r="BF9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="BG9">
         <v>55</v>
@@ -6802,16 +6835,16 @@
         <v>1</v>
       </c>
       <c r="CW9">
-        <v>5600</v>
+        <v>4700</v>
       </c>
       <c r="CX9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="CY9">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA9" t="b">
         <v>1</v>
@@ -6868,7 +6901,7 @@
         <v>252</v>
       </c>
       <c r="DS9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT9">
         <v>1</v>
@@ -6877,16 +6910,16 @@
         <v>1</v>
       </c>
       <c r="DV9">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="DW9" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="DX9" t="b">
         <v>1</v>
       </c>
       <c r="DY9" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ9">
         <v>1</v>
@@ -6937,7 +6970,7 @@
         <v>252</v>
       </c>
       <c r="EP9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ9">
         <v>0</v>
@@ -6997,7 +7030,7 @@
         <v>252</v>
       </c>
       <c r="FM9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN9">
         <v>0</v>
@@ -7006,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="FR9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS9">
         <v>1</v>
@@ -7015,19 +7048,19 @@
         <v>1</v>
       </c>
       <c r="FU9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="FV9">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FW9">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FX9">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="FY9">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="FZ9">
         <v>0.9</v>
@@ -7042,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="GM9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN9">
         <v>0.05</v>
@@ -7057,13 +7090,13 @@
         <v>8.5</v>
       </c>
       <c r="GR9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU9">
         <v>1</v>
@@ -7072,10 +7105,10 @@
         <v>1</v>
       </c>
       <c r="GW9">
-        <v>3900</v>
+        <v>3600</v>
       </c>
       <c r="GX9">
-        <v>3900</v>
+        <v>3600</v>
       </c>
       <c r="GY9">
         <v>0.95</v>
@@ -7090,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="HC9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD9">
         <v>0</v>
@@ -7099,19 +7132,19 @@
         <v>0</v>
       </c>
       <c r="HJ9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM9">
         <v>86400</v>
       </c>
       <c r="HN9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO9">
         <v>86400</v>
@@ -7123,7 +7156,7 @@
         <v>263</v>
       </c>
       <c r="HR9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS9" t="s">
         <v>263</v>
@@ -7135,7 +7168,7 @@
         <v>263</v>
       </c>
       <c r="HV9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW9">
         <v>86400</v>
@@ -7155,10 +7188,10 @@
         <v>240</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -7167,7 +7200,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7182,7 +7215,7 @@
         <v>5527000</v>
       </c>
       <c r="O10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P10" t="s">
         <v>249</v>
@@ -7302,10 +7335,10 @@
         <v>1</v>
       </c>
       <c r="BE10">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="BG10">
         <v>55</v>
@@ -7368,7 +7401,7 @@
         <v>1</v>
       </c>
       <c r="CA10">
-        <v>3200000</v>
+        <v>2100000</v>
       </c>
       <c r="CB10" t="s">
         <v>268</v>
@@ -7434,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="CW10">
-        <v>8500</v>
+        <v>9900</v>
       </c>
       <c r="CX10" t="s">
         <v>270</v>
@@ -7500,7 +7533,7 @@
         <v>252</v>
       </c>
       <c r="DS10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT10">
         <v>1</v>
@@ -7509,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="DV10">
-        <v>4200</v>
+        <v>3900</v>
       </c>
       <c r="DW10" t="s">
         <v>275</v>
@@ -7518,7 +7551,7 @@
         <v>1</v>
       </c>
       <c r="DY10" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ10">
         <v>1</v>
@@ -7569,7 +7602,7 @@
         <v>252</v>
       </c>
       <c r="EP10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ10">
         <v>0</v>
@@ -7629,7 +7662,7 @@
         <v>252</v>
       </c>
       <c r="FM10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN10">
         <v>0</v>
@@ -7638,16 +7671,16 @@
         <v>0</v>
       </c>
       <c r="FR10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS10">
         <v>1</v>
       </c>
       <c r="FT10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="FU10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FV10">
         <v>75000</v>
@@ -7673,35 +7706,8 @@
       <c r="GC10" t="b">
         <v>0</v>
       </c>
-      <c r="GD10" t="s">
-        <v>279</v>
-      </c>
-      <c r="GE10">
-        <v>100000</v>
-      </c>
-      <c r="GF10">
-        <v>11000</v>
-      </c>
-      <c r="GG10">
-        <v>22000</v>
-      </c>
-      <c r="GH10">
-        <v>200000</v>
-      </c>
-      <c r="GI10">
-        <v>0.9</v>
-      </c>
-      <c r="GJ10">
-        <v>0.8</v>
-      </c>
-      <c r="GK10" t="b">
-        <v>0</v>
-      </c>
-      <c r="GL10" t="b">
-        <v>0</v>
-      </c>
       <c r="GM10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN10">
         <v>0.05</v>
@@ -7716,13 +7722,13 @@
         <v>8.5</v>
       </c>
       <c r="GR10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU10">
         <v>1</v>
@@ -7749,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="HC10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD10">
         <v>0</v>
@@ -7758,19 +7764,19 @@
         <v>0</v>
       </c>
       <c r="HJ10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM10">
         <v>86400</v>
       </c>
       <c r="HN10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO10">
         <v>86400</v>
@@ -7782,7 +7788,7 @@
         <v>263</v>
       </c>
       <c r="HR10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS10" t="s">
         <v>263</v>
@@ -7794,7 +7800,7 @@
         <v>263</v>
       </c>
       <c r="HV10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW10">
         <v>86400</v>
@@ -7814,10 +7820,10 @@
         <v>241</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -7826,7 +7832,7 @@
         <v>2.6</v>
       </c>
       <c r="J11">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7838,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>4402000</v>
+        <v>5527000</v>
       </c>
       <c r="O11" t="s">
         <v>248</v>
@@ -7961,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="BE11">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF11" t="s">
         <v>262</v>
@@ -8027,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="CA11">
-        <v>3200000</v>
+        <v>2400000</v>
       </c>
       <c r="CB11" t="s">
         <v>268</v>
@@ -8093,16 +8099,16 @@
         <v>1</v>
       </c>
       <c r="CW11">
-        <v>7800</v>
+        <v>7100</v>
       </c>
       <c r="CX11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="CY11">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ11">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA11" t="b">
         <v>1</v>
@@ -8159,7 +8165,7 @@
         <v>252</v>
       </c>
       <c r="DS11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="DT11">
         <v>1</v>
@@ -8168,16 +8174,16 @@
         <v>1</v>
       </c>
       <c r="DV11">
-        <v>2800</v>
+        <v>4400</v>
       </c>
       <c r="DW11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="DX11" t="b">
         <v>1</v>
       </c>
       <c r="DY11" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="DZ11">
         <v>1</v>
@@ -8228,7 +8234,7 @@
         <v>252</v>
       </c>
       <c r="EP11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="EQ11">
         <v>0</v>
@@ -8288,7 +8294,7 @@
         <v>252</v>
       </c>
       <c r="FM11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FN11">
         <v>0</v>
@@ -8297,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="FR11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="FS11">
         <v>1</v>
@@ -8306,19 +8312,19 @@
         <v>1</v>
       </c>
       <c r="FU11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="FV11">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="FW11">
         <v>7200</v>
       </c>
       <c r="FX11">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FY11">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FZ11">
         <v>0.9</v>
@@ -8333,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="GM11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GN11">
         <v>0.05</v>
@@ -8348,13 +8354,13 @@
         <v>8.5</v>
       </c>
       <c r="GR11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GS11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GT11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="GU11">
         <v>1</v>
@@ -8363,10 +8369,10 @@
         <v>1</v>
       </c>
       <c r="GW11">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="GX11">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="GY11">
         <v>0.95</v>
@@ -8381,7 +8387,7 @@
         <v>0</v>
       </c>
       <c r="HC11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HD11">
         <v>0</v>
@@ -8390,19 +8396,19 @@
         <v>0</v>
       </c>
       <c r="HJ11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="HK11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HL11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="HM11">
         <v>86400</v>
       </c>
       <c r="HN11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="HO11">
         <v>86400</v>
@@ -8414,7 +8420,7 @@
         <v>263</v>
       </c>
       <c r="HR11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HS11" t="s">
         <v>263</v>
@@ -8426,7 +8432,7 @@
         <v>263</v>
       </c>
       <c r="HV11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HW11">
         <v>86400</v>
@@ -8462,13 +8468,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -9179,7 +9185,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9566,22 +9572,22 @@
         <v>193</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="EI1" s="1" t="s">
         <v>198</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="EK1" s="1" t="s">
         <v>200</v>
@@ -9683,7 +9689,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -10556,58 +10562,58 @@
         <v>209</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>217</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="326">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -687,232 +687,244 @@
     <t>ems/market/horizon</t>
   </si>
   <si>
+    <t>ems/market/fcast/local/method</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/local/naive/offset</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/wholesale/method</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/wholesale/naive/offset</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/energy</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/grid/local</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/grid/retail</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/levies</t>
+  </si>
+  <si>
+    <t>ems/market/fcast/retailer/balancing</t>
+  </si>
+  <si>
+    <t>ems/fcasts/horizon</t>
+  </si>
+  <si>
+    <t>ems/fcasts/retraining</t>
+  </si>
+  <si>
+    <t>ems/fcasts/update</t>
+  </si>
+  <si>
+    <t>jyFGsACyxp4M2bF</t>
+  </si>
+  <si>
+    <t>NF1R1X5xLHc5oai</t>
+  </si>
+  <si>
+    <t>f6gRFkqafMoslOh</t>
+  </si>
+  <si>
+    <t>I60jAo0thuY7TM6</t>
+  </si>
+  <si>
+    <t>w5LxCx7amBPhKab</t>
+  </si>
+  <si>
+    <t>NmWj0SV2dIIMv1Q</t>
+  </si>
+  <si>
+    <t>HC22h0DOauutOsq</t>
+  </si>
+  <si>
+    <t>gLGXThmj1lHuDe9</t>
+  </si>
+  <si>
+    <t>RiFtEzMHKOmLYK4</t>
+  </si>
+  <si>
+    <t>h2L2NbbwFFcbX5m</t>
+  </si>
+  <si>
+    <t>hh_2896_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4536_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3648_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3863_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2959_0.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
+  </si>
+  <si>
+    <t>perfect</t>
+  </si>
+  <si>
+    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
+  </si>
+  <si>
+    <t>['temp', 'time']</t>
+  </si>
+  <si>
+    <t>[1, 0, 0]</t>
+  </si>
+  <si>
+    <t>rfr</t>
+  </si>
+  <si>
+    <t>heat_gen_5_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_4536_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3125_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_3863_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2959_0.csv</t>
+  </si>
+  <si>
+    <t>heat_5527_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>naive</t>
+  </si>
+  <si>
+    <t>dhw_gen_2_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_3_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_6_pu.csv</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>pv_3_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_1_pu.csv</t>
+  </si>
+  <si>
+    <t>pv_2_pu.csv</t>
+  </si>
+  <si>
+    <t>green_local</t>
+  </si>
+  <si>
+    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
+  </si>
+  <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_47.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_43.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_44.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_2.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_90.csv</t>
+  </si>
+  <si>
+    <t>min_soc</t>
+  </si>
+  <si>
+    <t>arrival</t>
+  </si>
+  <si>
+    <t>['time']</t>
+  </si>
+  <si>
+    <t>linopy</t>
+  </si>
+  <si>
+    <t>linear</t>
+  </si>
+  <si>
+    <t>['naive', 'naive']</t>
+  </si>
+  <si>
+    <t>general/sub_id</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments_independent</t>
+  </si>
+  <si>
+    <t>general/parameters/apartments</t>
+  </si>
+  <si>
     <t>ems/market/fcast/local</t>
   </si>
   <si>
     <t>ems/market/fcast/wholesale</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/retailer/energy</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/retailer/grid/local</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/retailer/grid/retail</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/retailer/levies</t>
-  </si>
-  <si>
-    <t>ems/market/fcast/retailer/balancing</t>
-  </si>
-  <si>
-    <t>ems/fcasts/horizon</t>
-  </si>
-  <si>
-    <t>ems/fcasts/retraining</t>
-  </si>
-  <si>
-    <t>ems/fcasts/update</t>
-  </si>
-  <si>
-    <t>rW9Bi4f1AbGBCtO</t>
-  </si>
-  <si>
-    <t>Jq4Y5Afz7yd3pjK</t>
-  </si>
-  <si>
-    <t>S6DjdLlEFYi5V5p</t>
-  </si>
-  <si>
-    <t>ZPaCL1szWJW6uw8</t>
-  </si>
-  <si>
-    <t>pL6jAjPWyJofFLv</t>
-  </si>
-  <si>
-    <t>1Vr1dXuWgexa3Zr</t>
-  </si>
-  <si>
-    <t>UcyV1AOXfAmBPSw</t>
-  </si>
-  <si>
-    <t>d5uiSwAOqPU9zwX</t>
-  </si>
-  <si>
-    <t>6G9Udy7Ll56HIud</t>
-  </si>
-  <si>
-    <t>UkKBPJGYQw9gFHU</t>
-  </si>
-  <si>
-    <t>hh_2687_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3296_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3564_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_3125_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4402_0.csv</t>
-  </si>
-  <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>perfect</t>
-  </si>
-  <si>
-    <t>[2, 0, 2, 2, 0, 0, 96, 2, 0, 0, 672]</t>
-  </si>
-  <si>
-    <t>['temp', 'time']</t>
-  </si>
-  <si>
-    <t>[1, 0, 0]</t>
-  </si>
-  <si>
-    <t>rfr</t>
-  </si>
-  <si>
-    <t>heat_2687_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3296_0.csv</t>
-  </si>
-  <si>
-    <t>heat_3564_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_2012_3.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4402_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>naive</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_3_pu.csv</t>
-  </si>
-  <si>
-    <t>average</t>
-  </si>
-  <si>
-    <t>pv_3_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_1_pu.csv</t>
-  </si>
-  <si>
-    <t>pv_2_pu.csv</t>
-  </si>
-  <si>
-    <t>green_local</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
-  </si>
-  <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
-  </si>
-  <si>
-    <t>local</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_44.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_88.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_49.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_1.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_48.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_0.csv</t>
-  </si>
-  <si>
-    <t>min_soc</t>
-  </si>
-  <si>
-    <t>arrival</t>
-  </si>
-  <si>
-    <t>['time']</t>
-  </si>
-  <si>
-    <t>linopy</t>
-  </si>
-  <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>['naive', 'naive']</t>
-  </si>
-  <si>
-    <t>general/sub_id</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments_independent</t>
-  </si>
-  <si>
-    <t>general/parameters/apartments</t>
   </si>
   <si>
     <t>general/parameters/type</t>
@@ -1342,10 +1354,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HY11"/>
+  <dimension ref="A1:IA11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:233">
+    <row r="1" spans="1:235">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2042,13 +2054,19 @@
       <c r="HY1" s="1" t="s">
         <v>231</v>
       </c>
+      <c r="HZ1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="IA1" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="2" spans="1:233">
+    <row r="2" spans="1:235">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -2075,13 +2093,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>2687000</v>
+        <v>2896000</v>
       </c>
       <c r="O2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2096,10 +2114,10 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W2">
         <v>3</v>
@@ -2111,7 +2129,7 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA2">
         <v>3</v>
@@ -2123,13 +2141,13 @@
         <v>20</v>
       </c>
       <c r="AD2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE2">
         <v>3</v>
       </c>
       <c r="AF2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG2">
         <v>0</v>
@@ -2141,7 +2159,7 @@
         <v>6</v>
       </c>
       <c r="AL2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM2">
         <v>1</v>
@@ -2156,10 +2174,10 @@
         <v>9</v>
       </c>
       <c r="AQ2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS2">
         <v>3</v>
@@ -2171,7 +2189,7 @@
         <v>20</v>
       </c>
       <c r="AV2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW2">
         <v>3</v>
@@ -2183,13 +2201,13 @@
         <v>20</v>
       </c>
       <c r="AZ2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA2">
         <v>3</v>
       </c>
       <c r="BB2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC2">
         <v>1</v>
@@ -2201,13 +2219,13 @@
         <v>19500000</v>
       </c>
       <c r="BF2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="BG2">
         <v>55</v>
       </c>
       <c r="BH2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI2">
         <v>1</v>
@@ -2222,10 +2240,10 @@
         <v>9</v>
       </c>
       <c r="BM2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO2">
         <v>3</v>
@@ -2237,7 +2255,7 @@
         <v>20</v>
       </c>
       <c r="BR2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS2">
         <v>3</v>
@@ -2249,13 +2267,13 @@
         <v>20</v>
       </c>
       <c r="BV2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW2">
         <v>3</v>
       </c>
       <c r="BX2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY2">
         <v>1</v>
@@ -2264,16 +2282,16 @@
         <v>1</v>
       </c>
       <c r="CA2">
-        <v>2800000</v>
+        <v>3200000</v>
       </c>
       <c r="CB2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="CC2">
         <v>55</v>
       </c>
       <c r="CD2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE2">
         <v>1</v>
@@ -2288,10 +2306,10 @@
         <v>9</v>
       </c>
       <c r="CI2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK2">
         <v>3</v>
@@ -2303,7 +2321,7 @@
         <v>20</v>
       </c>
       <c r="CN2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO2">
         <v>3</v>
@@ -2315,13 +2333,13 @@
         <v>20</v>
       </c>
       <c r="CR2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS2">
         <v>3</v>
       </c>
       <c r="CT2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU2">
         <v>1</v>
@@ -2330,10 +2348,10 @@
         <v>1</v>
       </c>
       <c r="CW2">
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="CX2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="CY2">
         <v>0</v>
@@ -2345,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="DB2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC2">
         <v>1</v>
@@ -2360,10 +2378,10 @@
         <v>9</v>
       </c>
       <c r="DG2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI2">
         <v>3</v>
@@ -2375,7 +2393,7 @@
         <v>20</v>
       </c>
       <c r="DL2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM2">
         <v>3</v>
@@ -2387,16 +2405,16 @@
         <v>20</v>
       </c>
       <c r="DP2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ2">
         <v>3</v>
       </c>
       <c r="DR2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT2">
         <v>1</v>
@@ -2408,13 +2426,13 @@
         <v>2000</v>
       </c>
       <c r="DW2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="DX2" t="b">
         <v>1</v>
       </c>
       <c r="DY2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ2">
         <v>1</v>
@@ -2429,10 +2447,10 @@
         <v>9</v>
       </c>
       <c r="ED2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF2">
         <v>3</v>
@@ -2444,7 +2462,7 @@
         <v>20</v>
       </c>
       <c r="EI2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ2">
         <v>3</v>
@@ -2456,16 +2474,16 @@
         <v>20</v>
       </c>
       <c r="EM2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN2">
         <v>3</v>
       </c>
       <c r="EO2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ2">
         <v>0</v>
@@ -2474,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="EV2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW2">
         <v>1</v>
@@ -2489,10 +2507,10 @@
         <v>9</v>
       </c>
       <c r="FA2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC2">
         <v>3</v>
@@ -2504,7 +2522,7 @@
         <v>20</v>
       </c>
       <c r="FF2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG2">
         <v>3</v>
@@ -2516,13 +2534,13 @@
         <v>20</v>
       </c>
       <c r="FJ2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK2">
         <v>3</v>
       </c>
       <c r="FL2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM2" t="s">
         <v>280</v>
@@ -2540,22 +2558,22 @@
         <v>1</v>
       </c>
       <c r="FT2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="FU2" t="s">
         <v>281</v>
       </c>
       <c r="FV2">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="FW2">
         <v>7200</v>
       </c>
       <c r="FX2">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FY2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FZ2">
         <v>0.9</v>
@@ -2569,35 +2587,8 @@
       <c r="GC2" t="b">
         <v>0</v>
       </c>
-      <c r="GD2" t="s">
-        <v>288</v>
-      </c>
-      <c r="GE2">
-        <v>100000</v>
-      </c>
-      <c r="GF2">
-        <v>11000</v>
-      </c>
-      <c r="GG2">
-        <v>22000</v>
-      </c>
-      <c r="GH2">
-        <v>200000</v>
-      </c>
-      <c r="GI2">
-        <v>0.9</v>
-      </c>
-      <c r="GJ2">
-        <v>0.8</v>
-      </c>
-      <c r="GK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="GL2" t="b">
-        <v>0</v>
-      </c>
       <c r="GM2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN2">
         <v>0.05</v>
@@ -2612,10 +2603,10 @@
         <v>8.5</v>
       </c>
       <c r="GR2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT2" t="s">
         <v>280</v>
@@ -2627,10 +2618,10 @@
         <v>1</v>
       </c>
       <c r="GW2">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="GX2">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="GY2">
         <v>0.95</v>
@@ -2657,57 +2648,63 @@
         <v>280</v>
       </c>
       <c r="HK2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM2">
         <v>86400</v>
       </c>
       <c r="HN2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO2">
         <v>86400</v>
       </c>
       <c r="HP2" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ2" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ2">
+        <v>1</v>
       </c>
       <c r="HR2" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS2" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS2">
+        <v>1</v>
       </c>
       <c r="HT2" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV2" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW2">
+        <v>265</v>
+      </c>
+      <c r="HW2" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX2" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY2">
         <v>86400</v>
       </c>
-      <c r="HX2">
+      <c r="HZ2">
         <v>86400</v>
       </c>
-      <c r="HY2">
+      <c r="IA2">
         <v>3600</v>
       </c>
     </row>
-    <row r="3" spans="1:233">
+    <row r="3" spans="1:235">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -2734,13 +2731,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>3296000</v>
+        <v>4536000</v>
       </c>
       <c r="O3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2755,10 +2752,10 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -2770,7 +2767,7 @@
         <v>20</v>
       </c>
       <c r="Z3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA3">
         <v>3</v>
@@ -2782,13 +2779,13 @@
         <v>20</v>
       </c>
       <c r="AD3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE3">
         <v>3</v>
       </c>
       <c r="AF3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG3">
         <v>0</v>
@@ -2800,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="AL3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM3">
         <v>1</v>
@@ -2815,10 +2812,10 @@
         <v>9</v>
       </c>
       <c r="AQ3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS3">
         <v>3</v>
@@ -2830,7 +2827,7 @@
         <v>20</v>
       </c>
       <c r="AV3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW3">
         <v>3</v>
@@ -2842,13 +2839,13 @@
         <v>20</v>
       </c>
       <c r="AZ3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA3">
         <v>3</v>
       </c>
       <c r="BB3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC3">
         <v>1</v>
@@ -2860,13 +2857,13 @@
         <v>5500000</v>
       </c>
       <c r="BF3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="BG3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI3">
         <v>1</v>
@@ -2881,10 +2878,10 @@
         <v>9</v>
       </c>
       <c r="BM3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO3">
         <v>3</v>
@@ -2896,7 +2893,7 @@
         <v>20</v>
       </c>
       <c r="BR3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS3">
         <v>3</v>
@@ -2908,13 +2905,13 @@
         <v>20</v>
       </c>
       <c r="BV3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW3">
         <v>3</v>
       </c>
       <c r="BX3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY3">
         <v>1</v>
@@ -2923,16 +2920,16 @@
         <v>1</v>
       </c>
       <c r="CA3">
-        <v>1800000</v>
+        <v>2100000</v>
       </c>
       <c r="CB3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="CC3">
         <v>55</v>
       </c>
       <c r="CD3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE3">
         <v>1</v>
@@ -2947,10 +2944,10 @@
         <v>9</v>
       </c>
       <c r="CI3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK3">
         <v>3</v>
@@ -2962,7 +2959,7 @@
         <v>20</v>
       </c>
       <c r="CN3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO3">
         <v>3</v>
@@ -2974,13 +2971,13 @@
         <v>20</v>
       </c>
       <c r="CR3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS3">
         <v>3</v>
       </c>
       <c r="CT3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU3">
         <v>1</v>
@@ -2989,10 +2986,10 @@
         <v>1</v>
       </c>
       <c r="CW3">
-        <v>5100</v>
+        <v>7500</v>
       </c>
       <c r="CX3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="CY3">
         <v>0</v>
@@ -3004,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="DB3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC3">
         <v>1</v>
@@ -3019,10 +3016,10 @@
         <v>9</v>
       </c>
       <c r="DG3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI3">
         <v>3</v>
@@ -3034,7 +3031,7 @@
         <v>20</v>
       </c>
       <c r="DL3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM3">
         <v>3</v>
@@ -3046,16 +3043,16 @@
         <v>20</v>
       </c>
       <c r="DP3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ3">
         <v>3</v>
       </c>
       <c r="DR3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT3">
         <v>1</v>
@@ -3064,16 +3061,16 @@
         <v>1</v>
       </c>
       <c r="DV3">
-        <v>1900</v>
+        <v>2200</v>
       </c>
       <c r="DW3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="DX3" t="b">
         <v>1</v>
       </c>
       <c r="DY3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ3">
         <v>1</v>
@@ -3088,10 +3085,10 @@
         <v>9</v>
       </c>
       <c r="ED3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF3">
         <v>3</v>
@@ -3103,7 +3100,7 @@
         <v>20</v>
       </c>
       <c r="EI3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ3">
         <v>3</v>
@@ -3115,16 +3112,16 @@
         <v>20</v>
       </c>
       <c r="EM3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN3">
         <v>3</v>
       </c>
       <c r="EO3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ3">
         <v>0</v>
@@ -3133,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="EV3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW3">
         <v>1</v>
@@ -3148,10 +3145,10 @@
         <v>9</v>
       </c>
       <c r="FA3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC3">
         <v>3</v>
@@ -3163,7 +3160,7 @@
         <v>20</v>
       </c>
       <c r="FF3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG3">
         <v>3</v>
@@ -3175,13 +3172,13 @@
         <v>20</v>
       </c>
       <c r="FJ3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK3">
         <v>3</v>
       </c>
       <c r="FL3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM3" t="s">
         <v>280</v>
@@ -3205,16 +3202,16 @@
         <v>282</v>
       </c>
       <c r="FV3">
+        <v>75000</v>
+      </c>
+      <c r="FW3">
+        <v>7200</v>
+      </c>
+      <c r="FX3">
+        <v>11000</v>
+      </c>
+      <c r="FY3">
         <v>100000</v>
-      </c>
-      <c r="FW3">
-        <v>11000</v>
-      </c>
-      <c r="FX3">
-        <v>22000</v>
-      </c>
-      <c r="FY3">
-        <v>200000</v>
       </c>
       <c r="FZ3">
         <v>0.9</v>
@@ -3229,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="GM3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN3">
         <v>0.05</v>
@@ -3244,10 +3241,10 @@
         <v>8.5</v>
       </c>
       <c r="GR3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT3" t="s">
         <v>280</v>
@@ -3259,10 +3256,10 @@
         <v>1</v>
       </c>
       <c r="GW3">
-        <v>3300</v>
+        <v>4500</v>
       </c>
       <c r="GX3">
-        <v>3300</v>
+        <v>4500</v>
       </c>
       <c r="GY3">
         <v>0.95</v>
@@ -3289,63 +3286,69 @@
         <v>280</v>
       </c>
       <c r="HK3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM3">
         <v>86400</v>
       </c>
       <c r="HN3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO3">
         <v>86400</v>
       </c>
       <c r="HP3" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ3" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ3">
+        <v>1</v>
       </c>
       <c r="HR3" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS3" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS3">
+        <v>1</v>
       </c>
       <c r="HT3" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV3" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW3">
+        <v>265</v>
+      </c>
+      <c r="HW3" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX3" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY3">
         <v>86400</v>
       </c>
-      <c r="HX3">
+      <c r="HZ3">
         <v>86400</v>
       </c>
-      <c r="HY3">
+      <c r="IA3">
         <v>3600</v>
       </c>
     </row>
-    <row r="4" spans="1:233">
+    <row r="4" spans="1:235">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3354,7 +3357,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3366,13 +3369,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>3564000</v>
+        <v>3125000</v>
       </c>
       <c r="O4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3387,10 +3390,10 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -3402,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="Z4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA4">
         <v>3</v>
@@ -3414,13 +3417,13 @@
         <v>20</v>
       </c>
       <c r="AD4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
       <c r="AF4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG4">
         <v>0</v>
@@ -3432,7 +3435,7 @@
         <v>6</v>
       </c>
       <c r="AL4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM4">
         <v>1</v>
@@ -3447,10 +3450,10 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS4">
         <v>3</v>
@@ -3462,7 +3465,7 @@
         <v>20</v>
       </c>
       <c r="AV4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW4">
         <v>3</v>
@@ -3474,13 +3477,13 @@
         <v>20</v>
       </c>
       <c r="AZ4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA4">
         <v>3</v>
       </c>
       <c r="BB4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC4">
         <v>1</v>
@@ -3489,16 +3492,16 @@
         <v>1</v>
       </c>
       <c r="BE4">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="BG4">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BH4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI4">
         <v>1</v>
@@ -3513,10 +3516,10 @@
         <v>9</v>
       </c>
       <c r="BM4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO4">
         <v>3</v>
@@ -3528,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="BR4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS4">
         <v>3</v>
@@ -3540,13 +3543,13 @@
         <v>20</v>
       </c>
       <c r="BV4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW4">
         <v>3</v>
       </c>
       <c r="BX4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY4">
         <v>1</v>
@@ -3555,16 +3558,16 @@
         <v>1</v>
       </c>
       <c r="CA4">
-        <v>2800000</v>
+        <v>2400000</v>
       </c>
       <c r="CB4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="CC4">
         <v>55</v>
       </c>
       <c r="CD4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE4">
         <v>1</v>
@@ -3579,10 +3582,10 @@
         <v>9</v>
       </c>
       <c r="CI4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK4">
         <v>3</v>
@@ -3594,7 +3597,7 @@
         <v>20</v>
       </c>
       <c r="CN4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO4">
         <v>3</v>
@@ -3606,13 +3609,13 @@
         <v>20</v>
       </c>
       <c r="CR4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS4">
         <v>3</v>
       </c>
       <c r="CT4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU4">
         <v>1</v>
@@ -3621,22 +3624,22 @@
         <v>1</v>
       </c>
       <c r="CW4">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="CX4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="CY4">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA4" t="b">
         <v>1</v>
       </c>
       <c r="DB4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC4">
         <v>1</v>
@@ -3651,10 +3654,10 @@
         <v>9</v>
       </c>
       <c r="DG4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI4">
         <v>3</v>
@@ -3666,7 +3669,7 @@
         <v>20</v>
       </c>
       <c r="DL4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM4">
         <v>3</v>
@@ -3678,16 +3681,16 @@
         <v>20</v>
       </c>
       <c r="DP4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ4">
         <v>3</v>
       </c>
       <c r="DR4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT4">
         <v>1</v>
@@ -3696,16 +3699,16 @@
         <v>1</v>
       </c>
       <c r="DV4">
-        <v>2900</v>
+        <v>1400</v>
       </c>
       <c r="DW4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="DX4" t="b">
         <v>1</v>
       </c>
       <c r="DY4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ4">
         <v>1</v>
@@ -3720,10 +3723,10 @@
         <v>9</v>
       </c>
       <c r="ED4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF4">
         <v>3</v>
@@ -3735,7 +3738,7 @@
         <v>20</v>
       </c>
       <c r="EI4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ4">
         <v>3</v>
@@ -3747,16 +3750,16 @@
         <v>20</v>
       </c>
       <c r="EM4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN4">
         <v>3</v>
       </c>
       <c r="EO4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ4">
         <v>0</v>
@@ -3765,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="EV4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW4">
         <v>1</v>
@@ -3780,10 +3783,10 @@
         <v>9</v>
       </c>
       <c r="FA4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC4">
         <v>3</v>
@@ -3795,7 +3798,7 @@
         <v>20</v>
       </c>
       <c r="FF4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG4">
         <v>3</v>
@@ -3807,13 +3810,13 @@
         <v>20</v>
       </c>
       <c r="FJ4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK4">
         <v>3</v>
       </c>
       <c r="FL4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM4" t="s">
         <v>280</v>
@@ -3837,16 +3840,16 @@
         <v>283</v>
       </c>
       <c r="FV4">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="FW4">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX4">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="FY4">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="FZ4">
         <v>0.9</v>
@@ -3861,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="GM4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN4">
         <v>0.05</v>
@@ -3876,10 +3879,10 @@
         <v>8.5</v>
       </c>
       <c r="GR4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT4" t="s">
         <v>280</v>
@@ -3891,10 +3894,10 @@
         <v>1</v>
       </c>
       <c r="GW4">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="GX4">
-        <v>3600</v>
+        <v>3100</v>
       </c>
       <c r="GY4">
         <v>0.95</v>
@@ -3921,57 +3924,63 @@
         <v>280</v>
       </c>
       <c r="HK4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM4">
         <v>86400</v>
       </c>
       <c r="HN4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO4">
         <v>86400</v>
       </c>
       <c r="HP4" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ4" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ4">
+        <v>1</v>
       </c>
       <c r="HR4" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS4" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS4">
+        <v>1</v>
       </c>
       <c r="HT4" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV4" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW4">
+        <v>265</v>
+      </c>
+      <c r="HW4" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX4" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY4">
         <v>86400</v>
       </c>
-      <c r="HX4">
+      <c r="HZ4">
         <v>86400</v>
       </c>
-      <c r="HY4">
+      <c r="IA4">
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:233">
+    <row r="5" spans="1:235">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -3998,13 +4007,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>3564000</v>
+        <v>3648000</v>
       </c>
       <c r="O5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="P5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4019,10 +4028,10 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -4034,7 +4043,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA5">
         <v>3</v>
@@ -4046,13 +4055,13 @@
         <v>20</v>
       </c>
       <c r="AD5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE5">
         <v>3</v>
       </c>
       <c r="AF5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG5">
         <v>0</v>
@@ -4064,7 +4073,7 @@
         <v>6</v>
       </c>
       <c r="AL5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM5">
         <v>1</v>
@@ -4079,10 +4088,10 @@
         <v>9</v>
       </c>
       <c r="AQ5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS5">
         <v>3</v>
@@ -4094,7 +4103,7 @@
         <v>20</v>
       </c>
       <c r="AV5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW5">
         <v>3</v>
@@ -4106,13 +4115,13 @@
         <v>20</v>
       </c>
       <c r="AZ5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA5">
         <v>3</v>
       </c>
       <c r="BB5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC5">
         <v>1</v>
@@ -4124,13 +4133,13 @@
         <v>19500000</v>
       </c>
       <c r="BF5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI5">
         <v>1</v>
@@ -4145,10 +4154,10 @@
         <v>9</v>
       </c>
       <c r="BM5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO5">
         <v>3</v>
@@ -4160,7 +4169,7 @@
         <v>20</v>
       </c>
       <c r="BR5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS5">
         <v>3</v>
@@ -4172,13 +4181,13 @@
         <v>20</v>
       </c>
       <c r="BV5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW5">
         <v>3</v>
       </c>
       <c r="BX5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY5">
         <v>1</v>
@@ -4187,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="CA5">
-        <v>3200000</v>
+        <v>2800000</v>
       </c>
       <c r="CB5" t="s">
         <v>267</v>
@@ -4196,7 +4205,7 @@
         <v>55</v>
       </c>
       <c r="CD5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE5">
         <v>1</v>
@@ -4211,10 +4220,10 @@
         <v>9</v>
       </c>
       <c r="CI5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK5">
         <v>3</v>
@@ -4226,7 +4235,7 @@
         <v>20</v>
       </c>
       <c r="CN5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO5">
         <v>3</v>
@@ -4238,13 +4247,13 @@
         <v>20</v>
       </c>
       <c r="CR5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS5">
         <v>3</v>
       </c>
       <c r="CT5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU5">
         <v>1</v>
@@ -4253,22 +4262,22 @@
         <v>1</v>
       </c>
       <c r="CW5">
-        <v>6100</v>
+        <v>5600</v>
       </c>
       <c r="CX5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="CY5">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA5" t="b">
         <v>1</v>
       </c>
       <c r="DB5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC5">
         <v>1</v>
@@ -4283,10 +4292,10 @@
         <v>9</v>
       </c>
       <c r="DG5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI5">
         <v>3</v>
@@ -4298,7 +4307,7 @@
         <v>20</v>
       </c>
       <c r="DL5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM5">
         <v>3</v>
@@ -4310,16 +4319,16 @@
         <v>20</v>
       </c>
       <c r="DP5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ5">
         <v>3</v>
       </c>
       <c r="DR5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT5">
         <v>1</v>
@@ -4328,16 +4337,16 @@
         <v>1</v>
       </c>
       <c r="DV5">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="DW5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="DX5" t="b">
         <v>1</v>
       </c>
       <c r="DY5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ5">
         <v>1</v>
@@ -4352,10 +4361,10 @@
         <v>9</v>
       </c>
       <c r="ED5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF5">
         <v>3</v>
@@ -4367,7 +4376,7 @@
         <v>20</v>
       </c>
       <c r="EI5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ5">
         <v>3</v>
@@ -4379,16 +4388,16 @@
         <v>20</v>
       </c>
       <c r="EM5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN5">
         <v>3</v>
       </c>
       <c r="EO5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ5">
         <v>0</v>
@@ -4397,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="EV5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW5">
         <v>1</v>
@@ -4412,10 +4421,10 @@
         <v>9</v>
       </c>
       <c r="FA5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC5">
         <v>3</v>
@@ -4427,7 +4436,7 @@
         <v>20</v>
       </c>
       <c r="FF5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG5">
         <v>3</v>
@@ -4439,13 +4448,13 @@
         <v>20</v>
       </c>
       <c r="FJ5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK5">
         <v>3</v>
       </c>
       <c r="FL5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM5" t="s">
         <v>280</v>
@@ -4463,22 +4472,22 @@
         <v>1</v>
       </c>
       <c r="FT5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="FU5" t="s">
         <v>284</v>
       </c>
       <c r="FV5">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="FW5">
         <v>7200</v>
       </c>
       <c r="FX5">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FY5">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FZ5">
         <v>0.9</v>
@@ -4492,35 +4501,8 @@
       <c r="GC5" t="b">
         <v>0</v>
       </c>
-      <c r="GD5" t="s">
-        <v>281</v>
-      </c>
-      <c r="GE5">
-        <v>75000</v>
-      </c>
-      <c r="GF5">
-        <v>7200</v>
-      </c>
-      <c r="GG5">
-        <v>11000</v>
-      </c>
-      <c r="GH5">
-        <v>100000</v>
-      </c>
-      <c r="GI5">
-        <v>0.9</v>
-      </c>
-      <c r="GJ5">
-        <v>0.8</v>
-      </c>
-      <c r="GK5" t="b">
-        <v>0</v>
-      </c>
-      <c r="GL5" t="b">
-        <v>0</v>
-      </c>
       <c r="GM5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN5">
         <v>0.05</v>
@@ -4535,10 +4517,10 @@
         <v>8.5</v>
       </c>
       <c r="GR5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT5" t="s">
         <v>280</v>
@@ -4580,63 +4562,69 @@
         <v>280</v>
       </c>
       <c r="HK5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM5">
         <v>86400</v>
       </c>
       <c r="HN5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO5">
         <v>86400</v>
       </c>
       <c r="HP5" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ5" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ5">
+        <v>1</v>
       </c>
       <c r="HR5" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS5" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS5">
+        <v>1</v>
       </c>
       <c r="HT5" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV5" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW5">
+        <v>265</v>
+      </c>
+      <c r="HW5" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX5" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY5">
         <v>86400</v>
       </c>
-      <c r="HX5">
+      <c r="HZ5">
         <v>86400</v>
       </c>
-      <c r="HY5">
+      <c r="IA5">
         <v>3600</v>
       </c>
     </row>
-    <row r="6" spans="1:233">
+    <row r="6" spans="1:235">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -4645,7 +4633,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4657,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>2012000</v>
+        <v>3863000</v>
       </c>
       <c r="O6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4678,10 +4666,10 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W6">
         <v>3</v>
@@ -4693,7 +4681,7 @@
         <v>20</v>
       </c>
       <c r="Z6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -4705,13 +4693,13 @@
         <v>20</v>
       </c>
       <c r="AD6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE6">
         <v>3</v>
       </c>
       <c r="AF6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG6">
         <v>0</v>
@@ -4723,7 +4711,7 @@
         <v>6</v>
       </c>
       <c r="AL6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM6">
         <v>1</v>
@@ -4738,10 +4726,10 @@
         <v>9</v>
       </c>
       <c r="AQ6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS6">
         <v>3</v>
@@ -4753,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="AV6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW6">
         <v>3</v>
@@ -4765,13 +4753,13 @@
         <v>20</v>
       </c>
       <c r="AZ6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA6">
         <v>3</v>
       </c>
       <c r="BB6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC6">
         <v>1</v>
@@ -4780,16 +4768,16 @@
         <v>1</v>
       </c>
       <c r="BE6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BG6">
         <v>35</v>
       </c>
       <c r="BH6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI6">
         <v>1</v>
@@ -4804,10 +4792,10 @@
         <v>9</v>
       </c>
       <c r="BM6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO6">
         <v>3</v>
@@ -4819,7 +4807,7 @@
         <v>20</v>
       </c>
       <c r="BR6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS6">
         <v>3</v>
@@ -4831,13 +4819,13 @@
         <v>20</v>
       </c>
       <c r="BV6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW6">
         <v>3</v>
       </c>
       <c r="BX6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY6">
         <v>1</v>
@@ -4846,16 +4834,16 @@
         <v>1</v>
       </c>
       <c r="CA6">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="CB6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="CC6">
         <v>55</v>
       </c>
       <c r="CD6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE6">
         <v>1</v>
@@ -4870,10 +4858,10 @@
         <v>9</v>
       </c>
       <c r="CI6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK6">
         <v>3</v>
@@ -4885,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="CN6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO6">
         <v>3</v>
@@ -4897,13 +4885,13 @@
         <v>20</v>
       </c>
       <c r="CR6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS6">
         <v>3</v>
       </c>
       <c r="CT6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU6">
         <v>1</v>
@@ -4912,10 +4900,10 @@
         <v>1</v>
       </c>
       <c r="CW6">
-        <v>2800</v>
+        <v>6900</v>
       </c>
       <c r="CX6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="CY6">
         <v>0</v>
@@ -4927,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="DB6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC6">
         <v>1</v>
@@ -4942,10 +4930,10 @@
         <v>9</v>
       </c>
       <c r="DG6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI6">
         <v>3</v>
@@ -4957,7 +4945,7 @@
         <v>20</v>
       </c>
       <c r="DL6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM6">
         <v>3</v>
@@ -4969,16 +4957,16 @@
         <v>20</v>
       </c>
       <c r="DP6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ6">
         <v>3</v>
       </c>
       <c r="DR6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT6">
         <v>1</v>
@@ -4987,16 +4975,16 @@
         <v>1</v>
       </c>
       <c r="DV6">
-        <v>1500</v>
+        <v>3200</v>
       </c>
       <c r="DW6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DX6" t="b">
         <v>1</v>
       </c>
       <c r="DY6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ6">
         <v>1</v>
@@ -5011,10 +4999,10 @@
         <v>9</v>
       </c>
       <c r="ED6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF6">
         <v>3</v>
@@ -5026,7 +5014,7 @@
         <v>20</v>
       </c>
       <c r="EI6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ6">
         <v>3</v>
@@ -5038,16 +5026,16 @@
         <v>20</v>
       </c>
       <c r="EM6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN6">
         <v>3</v>
       </c>
       <c r="EO6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ6">
         <v>0</v>
@@ -5056,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="EV6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW6">
         <v>1</v>
@@ -5071,10 +5059,10 @@
         <v>9</v>
       </c>
       <c r="FA6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC6">
         <v>3</v>
@@ -5086,7 +5074,7 @@
         <v>20</v>
       </c>
       <c r="FF6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG6">
         <v>3</v>
@@ -5098,13 +5086,13 @@
         <v>20</v>
       </c>
       <c r="FJ6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK6">
         <v>3</v>
       </c>
       <c r="FL6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM6" t="s">
         <v>280</v>
@@ -5152,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="GD6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="GE6">
         <v>50000</v>
@@ -5179,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="GM6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN6">
         <v>0.05</v>
@@ -5194,10 +5182,10 @@
         <v>8.5</v>
       </c>
       <c r="GR6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT6" t="s">
         <v>280</v>
@@ -5209,10 +5197,10 @@
         <v>1</v>
       </c>
       <c r="GW6">
-        <v>2000</v>
+        <v>3900</v>
       </c>
       <c r="GX6">
-        <v>2000</v>
+        <v>3900</v>
       </c>
       <c r="GY6">
         <v>0.95</v>
@@ -5239,63 +5227,69 @@
         <v>280</v>
       </c>
       <c r="HK6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM6">
         <v>86400</v>
       </c>
       <c r="HN6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO6">
         <v>86400</v>
       </c>
       <c r="HP6" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ6" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ6">
+        <v>1</v>
       </c>
       <c r="HR6" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS6" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS6">
+        <v>1</v>
       </c>
       <c r="HT6" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV6" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW6">
+        <v>265</v>
+      </c>
+      <c r="HW6" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX6" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY6">
         <v>86400</v>
       </c>
-      <c r="HX6">
+      <c r="HZ6">
         <v>86400</v>
       </c>
-      <c r="HY6">
+      <c r="IA6">
         <v>3600</v>
       </c>
     </row>
-    <row r="7" spans="1:233">
+    <row r="7" spans="1:235">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -5304,7 +5298,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -5316,13 +5310,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>3125000</v>
+        <v>2959000</v>
       </c>
       <c r="O7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5337,10 +5331,10 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W7">
         <v>3</v>
@@ -5352,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="Z7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA7">
         <v>3</v>
@@ -5364,13 +5358,13 @@
         <v>20</v>
       </c>
       <c r="AD7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE7">
         <v>3</v>
       </c>
       <c r="AF7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG7">
         <v>0</v>
@@ -5382,7 +5376,7 @@
         <v>6</v>
       </c>
       <c r="AL7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM7">
         <v>1</v>
@@ -5397,10 +5391,10 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS7">
         <v>3</v>
@@ -5412,7 +5406,7 @@
         <v>20</v>
       </c>
       <c r="AV7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW7">
         <v>3</v>
@@ -5424,13 +5418,13 @@
         <v>20</v>
       </c>
       <c r="AZ7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA7">
         <v>3</v>
       </c>
       <c r="BB7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC7">
         <v>1</v>
@@ -5439,16 +5433,16 @@
         <v>1</v>
       </c>
       <c r="BE7">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BF7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BH7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI7">
         <v>1</v>
@@ -5463,10 +5457,10 @@
         <v>9</v>
       </c>
       <c r="BM7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO7">
         <v>3</v>
@@ -5478,7 +5472,7 @@
         <v>20</v>
       </c>
       <c r="BR7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS7">
         <v>3</v>
@@ -5490,13 +5484,13 @@
         <v>20</v>
       </c>
       <c r="BV7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW7">
         <v>3</v>
       </c>
       <c r="BX7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY7">
         <v>1</v>
@@ -5505,16 +5499,16 @@
         <v>1</v>
       </c>
       <c r="CA7">
-        <v>3200000</v>
+        <v>2100000</v>
       </c>
       <c r="CB7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="CC7">
         <v>55</v>
       </c>
       <c r="CD7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE7">
         <v>1</v>
@@ -5529,10 +5523,10 @@
         <v>9</v>
       </c>
       <c r="CI7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK7">
         <v>3</v>
@@ -5544,7 +5538,7 @@
         <v>20</v>
       </c>
       <c r="CN7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO7">
         <v>3</v>
@@ -5556,13 +5550,13 @@
         <v>20</v>
       </c>
       <c r="CR7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS7">
         <v>3</v>
       </c>
       <c r="CT7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU7">
         <v>1</v>
@@ -5574,19 +5568,19 @@
         <v>4700</v>
       </c>
       <c r="CX7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="CY7">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ7">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA7" t="b">
         <v>1</v>
       </c>
       <c r="DB7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC7">
         <v>1</v>
@@ -5601,10 +5595,10 @@
         <v>9</v>
       </c>
       <c r="DG7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI7">
         <v>3</v>
@@ -5616,7 +5610,7 @@
         <v>20</v>
       </c>
       <c r="DL7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM7">
         <v>3</v>
@@ -5628,16 +5622,16 @@
         <v>20</v>
       </c>
       <c r="DP7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ7">
         <v>3</v>
       </c>
       <c r="DR7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT7">
         <v>1</v>
@@ -5649,13 +5643,13 @@
         <v>2400</v>
       </c>
       <c r="DW7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="DX7" t="b">
         <v>1</v>
       </c>
       <c r="DY7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ7">
         <v>1</v>
@@ -5670,10 +5664,10 @@
         <v>9</v>
       </c>
       <c r="ED7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF7">
         <v>3</v>
@@ -5685,7 +5679,7 @@
         <v>20</v>
       </c>
       <c r="EI7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ7">
         <v>3</v>
@@ -5697,16 +5691,16 @@
         <v>20</v>
       </c>
       <c r="EM7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN7">
         <v>3</v>
       </c>
       <c r="EO7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ7">
         <v>0</v>
@@ -5715,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="EV7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW7">
         <v>1</v>
@@ -5730,10 +5724,10 @@
         <v>9</v>
       </c>
       <c r="FA7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC7">
         <v>3</v>
@@ -5745,7 +5739,7 @@
         <v>20</v>
       </c>
       <c r="FF7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG7">
         <v>3</v>
@@ -5757,13 +5751,13 @@
         <v>20</v>
       </c>
       <c r="FJ7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK7">
         <v>3</v>
       </c>
       <c r="FL7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM7" t="s">
         <v>280</v>
@@ -5784,7 +5778,7 @@
         <v>1</v>
       </c>
       <c r="FU7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="FV7">
         <v>75000</v>
@@ -5811,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="GM7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN7">
         <v>0.05</v>
@@ -5826,10 +5820,10 @@
         <v>8.5</v>
       </c>
       <c r="GR7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT7" t="s">
         <v>280</v>
@@ -5841,10 +5835,10 @@
         <v>1</v>
       </c>
       <c r="GW7">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="GX7">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="GY7">
         <v>0.95</v>
@@ -5871,63 +5865,69 @@
         <v>280</v>
       </c>
       <c r="HK7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL7" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM7">
         <v>86400</v>
       </c>
       <c r="HN7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO7">
         <v>86400</v>
       </c>
       <c r="HP7" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ7" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ7">
+        <v>1</v>
       </c>
       <c r="HR7" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS7" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS7">
+        <v>1</v>
       </c>
       <c r="HT7" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV7" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW7">
+        <v>265</v>
+      </c>
+      <c r="HW7" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX7" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY7">
         <v>86400</v>
       </c>
-      <c r="HX7">
+      <c r="HZ7">
         <v>86400</v>
       </c>
-      <c r="HY7">
+      <c r="IA7">
         <v>3600</v>
       </c>
     </row>
-    <row r="8" spans="1:233">
+    <row r="8" spans="1:235">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -5936,7 +5936,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -5948,13 +5948,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>4402000</v>
+        <v>5527000</v>
       </c>
       <c r="O8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -5969,10 +5969,10 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W8">
         <v>3</v>
@@ -5984,7 +5984,7 @@
         <v>20</v>
       </c>
       <c r="Z8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA8">
         <v>3</v>
@@ -5996,13 +5996,13 @@
         <v>20</v>
       </c>
       <c r="AD8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE8">
         <v>3</v>
       </c>
       <c r="AF8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG8">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>6</v>
       </c>
       <c r="AL8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM8">
         <v>1</v>
@@ -6029,10 +6029,10 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS8">
         <v>3</v>
@@ -6044,7 +6044,7 @@
         <v>20</v>
       </c>
       <c r="AV8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW8">
         <v>3</v>
@@ -6056,13 +6056,13 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA8">
         <v>3</v>
       </c>
       <c r="BB8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC8">
         <v>1</v>
@@ -6071,16 +6071,16 @@
         <v>1</v>
       </c>
       <c r="BE8">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="BG8">
         <v>55</v>
       </c>
       <c r="BH8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI8">
         <v>1</v>
@@ -6095,10 +6095,10 @@
         <v>9</v>
       </c>
       <c r="BM8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO8">
         <v>3</v>
@@ -6110,7 +6110,7 @@
         <v>20</v>
       </c>
       <c r="BR8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS8">
         <v>3</v>
@@ -6122,13 +6122,13 @@
         <v>20</v>
       </c>
       <c r="BV8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW8">
         <v>3</v>
       </c>
       <c r="BX8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY8">
         <v>1</v>
@@ -6137,16 +6137,16 @@
         <v>1</v>
       </c>
       <c r="CA8">
-        <v>1800000</v>
+        <v>2400000</v>
       </c>
       <c r="CB8" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="CC8">
         <v>55</v>
       </c>
       <c r="CD8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE8">
         <v>1</v>
@@ -6161,10 +6161,10 @@
         <v>9</v>
       </c>
       <c r="CI8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK8">
         <v>3</v>
@@ -6176,7 +6176,7 @@
         <v>20</v>
       </c>
       <c r="CN8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO8">
         <v>3</v>
@@ -6188,13 +6188,13 @@
         <v>20</v>
       </c>
       <c r="CR8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS8">
         <v>3</v>
       </c>
       <c r="CT8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU8">
         <v>1</v>
@@ -6203,22 +6203,22 @@
         <v>1</v>
       </c>
       <c r="CW8">
-        <v>6000</v>
+        <v>6900</v>
       </c>
       <c r="CX8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="CY8">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA8" t="b">
         <v>1</v>
       </c>
       <c r="DB8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC8">
         <v>1</v>
@@ -6233,10 +6233,10 @@
         <v>9</v>
       </c>
       <c r="DG8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI8">
         <v>3</v>
@@ -6248,7 +6248,7 @@
         <v>20</v>
       </c>
       <c r="DL8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM8">
         <v>3</v>
@@ -6260,16 +6260,16 @@
         <v>20</v>
       </c>
       <c r="DP8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ8">
         <v>3</v>
       </c>
       <c r="DR8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT8">
         <v>1</v>
@@ -6278,16 +6278,16 @@
         <v>1</v>
       </c>
       <c r="DV8">
-        <v>2200</v>
+        <v>3200</v>
       </c>
       <c r="DW8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DX8" t="b">
         <v>1</v>
       </c>
       <c r="DY8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ8">
         <v>1</v>
@@ -6302,10 +6302,10 @@
         <v>9</v>
       </c>
       <c r="ED8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF8">
         <v>3</v>
@@ -6317,7 +6317,7 @@
         <v>20</v>
       </c>
       <c r="EI8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ8">
         <v>3</v>
@@ -6329,16 +6329,16 @@
         <v>20</v>
       </c>
       <c r="EM8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN8">
         <v>3</v>
       </c>
       <c r="EO8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ8">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="EV8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW8">
         <v>1</v>
@@ -6362,10 +6362,10 @@
         <v>9</v>
       </c>
       <c r="FA8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC8">
         <v>3</v>
@@ -6377,7 +6377,7 @@
         <v>20</v>
       </c>
       <c r="FF8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG8">
         <v>3</v>
@@ -6389,13 +6389,13 @@
         <v>20</v>
       </c>
       <c r="FJ8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK8">
         <v>3</v>
       </c>
       <c r="FL8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM8" t="s">
         <v>280</v>
@@ -6416,19 +6416,19 @@
         <v>1</v>
       </c>
       <c r="FU8" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="FV8">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="FW8">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="FX8">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="FY8">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="FZ8">
         <v>0.9</v>
@@ -6443,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="GM8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN8">
         <v>0.05</v>
@@ -6458,10 +6458,10 @@
         <v>8.5</v>
       </c>
       <c r="GR8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT8" t="s">
         <v>280</v>
@@ -6473,10 +6473,10 @@
         <v>1</v>
       </c>
       <c r="GW8">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="GX8">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="GY8">
         <v>0.95</v>
@@ -6503,63 +6503,69 @@
         <v>280</v>
       </c>
       <c r="HK8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM8">
         <v>86400</v>
       </c>
       <c r="HN8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO8">
         <v>86400</v>
       </c>
       <c r="HP8" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ8" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ8">
+        <v>1</v>
       </c>
       <c r="HR8" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS8" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS8">
+        <v>1</v>
       </c>
       <c r="HT8" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV8" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW8">
+        <v>265</v>
+      </c>
+      <c r="HW8" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX8" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY8">
         <v>86400</v>
       </c>
-      <c r="HX8">
+      <c r="HZ8">
         <v>86400</v>
       </c>
-      <c r="HY8">
+      <c r="IA8">
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:233">
+    <row r="9" spans="1:235">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -6568,7 +6574,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -6580,13 +6586,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3564000</v>
+        <v>4536000</v>
       </c>
       <c r="O9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6601,10 +6607,10 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W9">
         <v>3</v>
@@ -6616,7 +6622,7 @@
         <v>20</v>
       </c>
       <c r="Z9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA9">
         <v>3</v>
@@ -6628,13 +6634,13 @@
         <v>20</v>
       </c>
       <c r="AD9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE9">
         <v>3</v>
       </c>
       <c r="AF9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG9">
         <v>0</v>
@@ -6646,7 +6652,7 @@
         <v>6</v>
       </c>
       <c r="AL9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM9">
         <v>1</v>
@@ -6661,10 +6667,10 @@
         <v>9</v>
       </c>
       <c r="AQ9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS9">
         <v>3</v>
@@ -6676,7 +6682,7 @@
         <v>20</v>
       </c>
       <c r="AV9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW9">
         <v>3</v>
@@ -6688,13 +6694,13 @@
         <v>20</v>
       </c>
       <c r="AZ9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA9">
         <v>3</v>
       </c>
       <c r="BB9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC9">
         <v>1</v>
@@ -6703,16 +6709,16 @@
         <v>1</v>
       </c>
       <c r="BE9">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="BG9">
         <v>55</v>
       </c>
       <c r="BH9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI9">
         <v>1</v>
@@ -6727,10 +6733,10 @@
         <v>9</v>
       </c>
       <c r="BM9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO9">
         <v>3</v>
@@ -6742,7 +6748,7 @@
         <v>20</v>
       </c>
       <c r="BR9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS9">
         <v>3</v>
@@ -6754,13 +6760,13 @@
         <v>20</v>
       </c>
       <c r="BV9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW9">
         <v>3</v>
       </c>
       <c r="BX9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY9">
         <v>1</v>
@@ -6769,16 +6775,16 @@
         <v>1</v>
       </c>
       <c r="CA9">
-        <v>2100000</v>
+        <v>3200000</v>
       </c>
       <c r="CB9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="CC9">
         <v>55</v>
       </c>
       <c r="CD9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE9">
         <v>1</v>
@@ -6793,10 +6799,10 @@
         <v>9</v>
       </c>
       <c r="CI9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK9">
         <v>3</v>
@@ -6808,7 +6814,7 @@
         <v>20</v>
       </c>
       <c r="CN9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO9">
         <v>3</v>
@@ -6820,13 +6826,13 @@
         <v>20</v>
       </c>
       <c r="CR9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS9">
         <v>3</v>
       </c>
       <c r="CT9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU9">
         <v>1</v>
@@ -6835,22 +6841,22 @@
         <v>1</v>
       </c>
       <c r="CW9">
-        <v>4700</v>
+        <v>7700</v>
       </c>
       <c r="CX9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="CY9">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="CZ9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DA9" t="b">
         <v>1</v>
       </c>
       <c r="DB9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC9">
         <v>1</v>
@@ -6865,10 +6871,10 @@
         <v>9</v>
       </c>
       <c r="DG9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI9">
         <v>3</v>
@@ -6880,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="DL9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM9">
         <v>3</v>
@@ -6892,16 +6898,16 @@
         <v>20</v>
       </c>
       <c r="DP9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ9">
         <v>3</v>
       </c>
       <c r="DR9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT9">
         <v>1</v>
@@ -6910,16 +6916,16 @@
         <v>1</v>
       </c>
       <c r="DV9">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="DW9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="DX9" t="b">
         <v>1</v>
       </c>
       <c r="DY9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ9">
         <v>1</v>
@@ -6934,10 +6940,10 @@
         <v>9</v>
       </c>
       <c r="ED9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF9">
         <v>3</v>
@@ -6949,7 +6955,7 @@
         <v>20</v>
       </c>
       <c r="EI9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ9">
         <v>3</v>
@@ -6961,16 +6967,16 @@
         <v>20</v>
       </c>
       <c r="EM9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN9">
         <v>3</v>
       </c>
       <c r="EO9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ9">
         <v>0</v>
@@ -6979,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="EV9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW9">
         <v>1</v>
@@ -6994,10 +7000,10 @@
         <v>9</v>
       </c>
       <c r="FA9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC9">
         <v>3</v>
@@ -7009,7 +7015,7 @@
         <v>20</v>
       </c>
       <c r="FF9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG9">
         <v>3</v>
@@ -7021,13 +7027,13 @@
         <v>20</v>
       </c>
       <c r="FJ9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK9">
         <v>3</v>
       </c>
       <c r="FL9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM9" t="s">
         <v>280</v>
@@ -7045,10 +7051,10 @@
         <v>1</v>
       </c>
       <c r="FT9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="FU9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FV9">
         <v>50000</v>
@@ -7074,8 +7080,35 @@
       <c r="GC9" t="b">
         <v>0</v>
       </c>
+      <c r="GD9" t="s">
+        <v>290</v>
+      </c>
+      <c r="GE9">
+        <v>75000</v>
+      </c>
+      <c r="GF9">
+        <v>7200</v>
+      </c>
+      <c r="GG9">
+        <v>11000</v>
+      </c>
+      <c r="GH9">
+        <v>100000</v>
+      </c>
+      <c r="GI9">
+        <v>0.9</v>
+      </c>
+      <c r="GJ9">
+        <v>0.8</v>
+      </c>
+      <c r="GK9" t="b">
+        <v>0</v>
+      </c>
+      <c r="GL9" t="b">
+        <v>0</v>
+      </c>
       <c r="GM9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN9">
         <v>0.05</v>
@@ -7090,10 +7123,10 @@
         <v>8.5</v>
       </c>
       <c r="GR9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT9" t="s">
         <v>280</v>
@@ -7105,10 +7138,10 @@
         <v>1</v>
       </c>
       <c r="GW9">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="GX9">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="GY9">
         <v>0.95</v>
@@ -7135,63 +7168,69 @@
         <v>280</v>
       </c>
       <c r="HK9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM9">
         <v>86400</v>
       </c>
       <c r="HN9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO9">
         <v>86400</v>
       </c>
       <c r="HP9" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ9" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ9">
+        <v>1</v>
       </c>
       <c r="HR9" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS9" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS9">
+        <v>1</v>
       </c>
       <c r="HT9" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV9" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW9">
+        <v>265</v>
+      </c>
+      <c r="HW9" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX9" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY9">
         <v>86400</v>
       </c>
-      <c r="HX9">
+      <c r="HZ9">
         <v>86400</v>
       </c>
-      <c r="HY9">
+      <c r="IA9">
         <v>3600</v>
       </c>
     </row>
-    <row r="10" spans="1:233">
+    <row r="10" spans="1:235">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -7200,7 +7239,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7215,10 +7254,10 @@
         <v>5527000</v>
       </c>
       <c r="O10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -7233,10 +7272,10 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W10">
         <v>3</v>
@@ -7248,7 +7287,7 @@
         <v>20</v>
       </c>
       <c r="Z10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA10">
         <v>3</v>
@@ -7260,13 +7299,13 @@
         <v>20</v>
       </c>
       <c r="AD10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE10">
         <v>3</v>
       </c>
       <c r="AF10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG10">
         <v>0</v>
@@ -7278,7 +7317,7 @@
         <v>6</v>
       </c>
       <c r="AL10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM10">
         <v>1</v>
@@ -7293,10 +7332,10 @@
         <v>9</v>
       </c>
       <c r="AQ10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS10">
         <v>3</v>
@@ -7308,7 +7347,7 @@
         <v>20</v>
       </c>
       <c r="AV10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW10">
         <v>3</v>
@@ -7320,13 +7359,13 @@
         <v>20</v>
       </c>
       <c r="AZ10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA10">
         <v>3</v>
       </c>
       <c r="BB10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC10">
         <v>1</v>
@@ -7335,16 +7374,16 @@
         <v>1</v>
       </c>
       <c r="BE10">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BF10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="BG10">
         <v>55</v>
       </c>
       <c r="BH10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI10">
         <v>1</v>
@@ -7359,10 +7398,10 @@
         <v>9</v>
       </c>
       <c r="BM10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO10">
         <v>3</v>
@@ -7374,7 +7413,7 @@
         <v>20</v>
       </c>
       <c r="BR10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS10">
         <v>3</v>
@@ -7386,13 +7425,13 @@
         <v>20</v>
       </c>
       <c r="BV10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW10">
         <v>3</v>
       </c>
       <c r="BX10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY10">
         <v>1</v>
@@ -7401,16 +7440,16 @@
         <v>1</v>
       </c>
       <c r="CA10">
-        <v>2100000</v>
+        <v>2800000</v>
       </c>
       <c r="CB10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="CC10">
         <v>55</v>
       </c>
       <c r="CD10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE10">
         <v>1</v>
@@ -7425,10 +7464,10 @@
         <v>9</v>
       </c>
       <c r="CI10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK10">
         <v>3</v>
@@ -7440,7 +7479,7 @@
         <v>20</v>
       </c>
       <c r="CN10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO10">
         <v>3</v>
@@ -7452,13 +7491,13 @@
         <v>20</v>
       </c>
       <c r="CR10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS10">
         <v>3</v>
       </c>
       <c r="CT10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU10">
         <v>1</v>
@@ -7467,10 +7506,10 @@
         <v>1</v>
       </c>
       <c r="CW10">
-        <v>9900</v>
+        <v>8800</v>
       </c>
       <c r="CX10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="CY10">
         <v>0</v>
@@ -7482,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="DB10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC10">
         <v>1</v>
@@ -7497,10 +7536,10 @@
         <v>9</v>
       </c>
       <c r="DG10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI10">
         <v>3</v>
@@ -7512,7 +7551,7 @@
         <v>20</v>
       </c>
       <c r="DL10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM10">
         <v>3</v>
@@ -7524,16 +7563,16 @@
         <v>20</v>
       </c>
       <c r="DP10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ10">
         <v>3</v>
       </c>
       <c r="DR10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT10">
         <v>1</v>
@@ -7542,16 +7581,16 @@
         <v>1</v>
       </c>
       <c r="DV10">
-        <v>3900</v>
+        <v>3100</v>
       </c>
       <c r="DW10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="DX10" t="b">
         <v>1</v>
       </c>
       <c r="DY10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ10">
         <v>1</v>
@@ -7566,10 +7605,10 @@
         <v>9</v>
       </c>
       <c r="ED10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF10">
         <v>3</v>
@@ -7581,7 +7620,7 @@
         <v>20</v>
       </c>
       <c r="EI10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ10">
         <v>3</v>
@@ -7593,16 +7632,16 @@
         <v>20</v>
       </c>
       <c r="EM10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN10">
         <v>3</v>
       </c>
       <c r="EO10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ10">
         <v>0</v>
@@ -7611,7 +7650,7 @@
         <v>0</v>
       </c>
       <c r="EV10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW10">
         <v>1</v>
@@ -7626,10 +7665,10 @@
         <v>9</v>
       </c>
       <c r="FA10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC10">
         <v>3</v>
@@ -7641,7 +7680,7 @@
         <v>20</v>
       </c>
       <c r="FF10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG10">
         <v>3</v>
@@ -7653,13 +7692,13 @@
         <v>20</v>
       </c>
       <c r="FJ10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK10">
         <v>3</v>
       </c>
       <c r="FL10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM10" t="s">
         <v>280</v>
@@ -7680,7 +7719,7 @@
         <v>1</v>
       </c>
       <c r="FU10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="FV10">
         <v>75000</v>
@@ -7707,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="GM10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN10">
         <v>0.05</v>
@@ -7722,10 +7761,10 @@
         <v>8.5</v>
       </c>
       <c r="GR10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT10" t="s">
         <v>280</v>
@@ -7767,57 +7806,63 @@
         <v>280</v>
       </c>
       <c r="HK10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM10">
         <v>86400</v>
       </c>
       <c r="HN10" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO10">
         <v>86400</v>
       </c>
       <c r="HP10" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ10" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ10">
+        <v>1</v>
       </c>
       <c r="HR10" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS10" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS10">
+        <v>1</v>
       </c>
       <c r="HT10" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV10" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW10">
+        <v>265</v>
+      </c>
+      <c r="HW10" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX10" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY10">
         <v>86400</v>
       </c>
-      <c r="HX10">
+      <c r="HZ10">
         <v>86400</v>
       </c>
-      <c r="HY10">
+      <c r="IA10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:233">
+    <row r="11" spans="1:235">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -7844,13 +7889,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>5527000</v>
+        <v>3648000</v>
       </c>
       <c r="O11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -7865,10 +7910,10 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="V11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="W11">
         <v>3</v>
@@ -7880,7 +7925,7 @@
         <v>20</v>
       </c>
       <c r="Z11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA11">
         <v>3</v>
@@ -7892,13 +7937,13 @@
         <v>20</v>
       </c>
       <c r="AD11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AE11">
         <v>3</v>
       </c>
       <c r="AF11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG11">
         <v>0</v>
@@ -7910,7 +7955,7 @@
         <v>6</v>
       </c>
       <c r="AL11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM11">
         <v>1</v>
@@ -7925,10 +7970,10 @@
         <v>9</v>
       </c>
       <c r="AQ11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AR11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AS11">
         <v>3</v>
@@ -7940,7 +7985,7 @@
         <v>20</v>
       </c>
       <c r="AV11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AW11">
         <v>3</v>
@@ -7952,13 +7997,13 @@
         <v>20</v>
       </c>
       <c r="AZ11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BA11">
         <v>3</v>
       </c>
       <c r="BB11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BC11">
         <v>1</v>
@@ -7970,13 +8015,13 @@
         <v>5500000</v>
       </c>
       <c r="BF11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BG11">
         <v>55</v>
       </c>
       <c r="BH11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BI11">
         <v>1</v>
@@ -7991,10 +8036,10 @@
         <v>9</v>
       </c>
       <c r="BM11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BN11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BO11">
         <v>3</v>
@@ -8006,7 +8051,7 @@
         <v>20</v>
       </c>
       <c r="BR11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BS11">
         <v>3</v>
@@ -8018,13 +8063,13 @@
         <v>20</v>
       </c>
       <c r="BV11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BW11">
         <v>3</v>
       </c>
       <c r="BX11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="BY11">
         <v>1</v>
@@ -8033,16 +8078,16 @@
         <v>1</v>
       </c>
       <c r="CA11">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="CB11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="CC11">
         <v>55</v>
       </c>
       <c r="CD11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="CE11">
         <v>1</v>
@@ -8057,10 +8102,10 @@
         <v>9</v>
       </c>
       <c r="CI11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="CJ11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CK11">
         <v>3</v>
@@ -8072,7 +8117,7 @@
         <v>20</v>
       </c>
       <c r="CN11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CO11">
         <v>3</v>
@@ -8084,13 +8129,13 @@
         <v>20</v>
       </c>
       <c r="CR11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="CS11">
         <v>3</v>
       </c>
       <c r="CT11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="CU11">
         <v>1</v>
@@ -8099,22 +8144,22 @@
         <v>1</v>
       </c>
       <c r="CW11">
-        <v>7100</v>
+        <v>4600</v>
       </c>
       <c r="CX11" t="s">
         <v>272</v>
       </c>
       <c r="CY11">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="CZ11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DA11" t="b">
         <v>1</v>
       </c>
       <c r="DB11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="DC11">
         <v>1</v>
@@ -8129,10 +8174,10 @@
         <v>9</v>
       </c>
       <c r="DG11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="DH11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DI11">
         <v>3</v>
@@ -8144,7 +8189,7 @@
         <v>20</v>
       </c>
       <c r="DL11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DM11">
         <v>3</v>
@@ -8156,16 +8201,16 @@
         <v>20</v>
       </c>
       <c r="DP11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="DQ11">
         <v>3</v>
       </c>
       <c r="DR11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="DS11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="DT11">
         <v>1</v>
@@ -8174,16 +8219,16 @@
         <v>1</v>
       </c>
       <c r="DV11">
-        <v>4400</v>
+        <v>2700</v>
       </c>
       <c r="DW11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="DX11" t="b">
         <v>1</v>
       </c>
       <c r="DY11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="DZ11">
         <v>1</v>
@@ -8198,10 +8243,10 @@
         <v>9</v>
       </c>
       <c r="ED11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="EE11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EF11">
         <v>3</v>
@@ -8213,7 +8258,7 @@
         <v>20</v>
       </c>
       <c r="EI11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EJ11">
         <v>3</v>
@@ -8225,16 +8270,16 @@
         <v>20</v>
       </c>
       <c r="EM11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="EN11">
         <v>3</v>
       </c>
       <c r="EO11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="EP11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="EQ11">
         <v>0</v>
@@ -8243,7 +8288,7 @@
         <v>0</v>
       </c>
       <c r="EV11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="EW11">
         <v>1</v>
@@ -8258,10 +8303,10 @@
         <v>9</v>
       </c>
       <c r="FA11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="FB11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FC11">
         <v>3</v>
@@ -8273,7 +8318,7 @@
         <v>20</v>
       </c>
       <c r="FF11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FG11">
         <v>3</v>
@@ -8285,13 +8330,13 @@
         <v>20</v>
       </c>
       <c r="FJ11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="FK11">
         <v>3</v>
       </c>
       <c r="FL11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="FM11" t="s">
         <v>280</v>
@@ -8312,19 +8357,19 @@
         <v>1</v>
       </c>
       <c r="FU11" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="FV11">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="FW11">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="FX11">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="FY11">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="FZ11">
         <v>0.9</v>
@@ -8339,7 +8384,7 @@
         <v>0</v>
       </c>
       <c r="GM11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GN11">
         <v>0.05</v>
@@ -8354,10 +8399,10 @@
         <v>8.5</v>
       </c>
       <c r="GR11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="GS11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GT11" t="s">
         <v>280</v>
@@ -8369,10 +8414,10 @@
         <v>1</v>
       </c>
       <c r="GW11">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="GX11">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="GY11">
         <v>0.95</v>
@@ -8399,48 +8444,54 @@
         <v>280</v>
       </c>
       <c r="HK11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HL11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="HM11">
         <v>86400</v>
       </c>
       <c r="HN11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="HO11">
         <v>86400</v>
       </c>
       <c r="HP11" t="s">
-        <v>263</v>
-      </c>
-      <c r="HQ11" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HQ11">
+        <v>1</v>
       </c>
       <c r="HR11" t="s">
-        <v>294</v>
-      </c>
-      <c r="HS11" t="s">
-        <v>263</v>
+        <v>265</v>
+      </c>
+      <c r="HS11">
+        <v>1</v>
       </c>
       <c r="HT11" t="s">
-        <v>263</v>
+        <v>296</v>
       </c>
       <c r="HU11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="HV11" t="s">
-        <v>294</v>
-      </c>
-      <c r="HW11">
+        <v>265</v>
+      </c>
+      <c r="HW11" t="s">
+        <v>265</v>
+      </c>
+      <c r="HX11" t="s">
+        <v>296</v>
+      </c>
+      <c r="HY11">
         <v>86400</v>
       </c>
-      <c r="HX11">
+      <c r="HZ11">
         <v>86400</v>
       </c>
-      <c r="HY11">
+      <c r="IA11">
         <v>3600</v>
       </c>
     </row>
@@ -8468,13 +8519,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -9131,34 +9182,34 @@
         <v>221</v>
       </c>
       <c r="HS1" s="1" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="HT1" s="1" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="HU1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="HV1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="HW1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="HX1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="HY1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="IB1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -9185,7 +9236,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9572,22 +9623,22 @@
         <v>193</v>
       </c>
       <c r="EE1" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="EF1" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="EG1" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="EH1" s="1" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="EI1" s="1" t="s">
         <v>198</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="EK1" s="1" t="s">
         <v>200</v>
@@ -9635,34 +9686,34 @@
         <v>221</v>
       </c>
       <c r="EZ1" s="1" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="FA1" s="1" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="FB1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="FC1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="FD1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="FG1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="FH1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -9689,7 +9740,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -10166,34 +10217,34 @@
         <v>221</v>
       </c>
       <c r="FI1" s="1" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="FJ1" s="1" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="FK1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="FL1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="FM1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="FP1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="FQ1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="FR1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -10478,34 +10529,34 @@
         <v>221</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="CU1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="CV1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -10562,58 +10613,58 @@
         <v>209</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>217</v>
@@ -10631,34 +10682,34 @@
         <v>221</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>222</v>
+        <v>300</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="331">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -741,55 +741,58 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>5H037HFdtfwXZUZ</t>
-  </si>
-  <si>
-    <t>r9XlEkjB03ngUIA</t>
-  </si>
-  <si>
-    <t>zqvGd5RqHVINoUX</t>
-  </si>
-  <si>
-    <t>wnjTcCEN6nPRCzQ</t>
-  </si>
-  <si>
-    <t>GbbvvEdaKgY1Fqa</t>
-  </si>
-  <si>
-    <t>Jvu0ynpoT3f78Kg</t>
-  </si>
-  <si>
-    <t>P9NgKpLx5RBto08</t>
-  </si>
-  <si>
-    <t>f72cz1ntdiFo2rn</t>
-  </si>
-  <si>
-    <t>2nLsNamutyl1ML2</t>
-  </si>
-  <si>
-    <t>2Vi4VyeJmIV3tKN</t>
+    <t>DYGMezeMcdBzkRE</t>
+  </si>
+  <si>
+    <t>3yZ7HjucQPUWBLV</t>
+  </si>
+  <si>
+    <t>CwxAe4i0Qo05kEy</t>
+  </si>
+  <si>
+    <t>bMNKj4RQXe3Bn5G</t>
+  </si>
+  <si>
+    <t>UfgFBNdFQIwN3aX</t>
+  </si>
+  <si>
+    <t>pzymfr2mXV8WUcn</t>
+  </si>
+  <si>
+    <t>QosLqiKD0U1v0co</t>
+  </si>
+  <si>
+    <t>A6Z44wNxl4MrGZO</t>
+  </si>
+  <si>
+    <t>W2oNQbQSIvLfC4j</t>
+  </si>
+  <si>
+    <t>OQxohNNX3xGnxLk</t>
+  </si>
+  <si>
+    <t>hh_3648_0.csv</t>
+  </si>
+  <si>
+    <t>hh_4402_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3125_0.csv</t>
+  </si>
+  <si>
+    <t>hh_2012_3.csv</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
   </si>
   <si>
     <t>hh_4536_0.csv</t>
   </si>
   <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
-  </si>
-  <si>
     <t>hh_3863_0.csv</t>
   </si>
   <si>
-    <t>hh_4402_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2455_0.csv</t>
-  </si>
-  <si>
-    <t>hh_2262_0.csv</t>
+    <t>hh_2687_0.csv</t>
   </si>
   <si>
     <t>perfect</t>
@@ -807,51 +810,51 @@
     <t>rfr</t>
   </si>
   <si>
-    <t>heat_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_4536_0.csv</t>
+    <t>heat_3648_0.csv</t>
+  </si>
+  <si>
+    <t>heat_gen_1_pu.csv</t>
+  </si>
+  <si>
+    <t>heat_3125_0.csv</t>
+  </si>
+  <si>
+    <t>heat_2012_3.csv</t>
   </si>
   <si>
     <t>heat_5527_0.csv</t>
   </si>
   <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
     <t>heat_gen_4_pu.csv</t>
   </si>
   <si>
-    <t>heat_4402_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2455_0.csv</t>
+    <t>heat_3863_0.csv</t>
   </si>
   <si>
     <t>heat_gen_0_pu.csv</t>
   </si>
   <si>
+    <t>heat_2687_0.csv</t>
+  </si>
+  <si>
     <t>naive</t>
   </si>
   <si>
-    <t>dhw_gen_3_pu.csv</t>
+    <t>dhw_gen_0_pu.csv</t>
+  </si>
+  <si>
+    <t>dhw_gen_5_pu.csv</t>
   </si>
   <si>
     <t>dhw_gen_6_pu.csv</t>
   </si>
   <si>
+    <t>dhw_gen_4_pu.csv</t>
+  </si>
+  <si>
     <t>dhw_gen_2_pu.csv</t>
   </si>
   <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -864,43 +867,43 @@
     <t>green_local</t>
   </si>
   <si>
+    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
+  </si>
+  <si>
+    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
+  </si>
+  <si>
+    <t>wind_Enercon_E-53-800_800000_53.json</t>
+  </si>
+  <si>
     <t>wind_Nordex_MM92_3300000_131.json</t>
   </si>
   <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-101-3500-E2_3500000_101.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
+    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
   </si>
   <si>
     <t>local</t>
   </si>
   <si>
+    <t>ev_fulltime_45.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_49.csv</t>
+  </si>
+  <si>
     <t>ev_fulltime_47.csv</t>
   </si>
   <si>
-    <t>ev_parttime_88.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_2.csv</t>
+    <t>ev_freetime_1.csv</t>
+  </si>
+  <si>
+    <t>ev_fulltime_48.csv</t>
   </si>
   <si>
     <t>ev_fulltime_46.csv</t>
   </si>
   <si>
-    <t>ev_freetime_3.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_48.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_42.csv</t>
+    <t>ev_parttime_89.csv</t>
   </si>
   <si>
     <t>min_soc</t>
@@ -2123,13 +2126,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>4536000</v>
+        <v>3648000</v>
       </c>
       <c r="O2" t="s">
         <v>250</v>
       </c>
       <c r="P2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2144,10 +2147,10 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W2">
         <v>3</v>
@@ -2159,7 +2162,7 @@
         <v>20</v>
       </c>
       <c r="Z2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA2">
         <v>3</v>
@@ -2171,13 +2174,13 @@
         <v>20</v>
       </c>
       <c r="AD2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE2">
         <v>3</v>
       </c>
       <c r="AF2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG2">
         <v>3</v>
@@ -2192,7 +2195,7 @@
         <v>6</v>
       </c>
       <c r="AM2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -2207,10 +2210,10 @@
         <v>9</v>
       </c>
       <c r="AR2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT2">
         <v>3</v>
@@ -2222,7 +2225,7 @@
         <v>20</v>
       </c>
       <c r="AW2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX2">
         <v>3</v>
@@ -2234,13 +2237,13 @@
         <v>20</v>
       </c>
       <c r="BA2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB2">
         <v>3</v>
       </c>
       <c r="BC2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD2">
         <v>3</v>
@@ -2255,13 +2258,13 @@
         <v>5500000</v>
       </c>
       <c r="BH2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="BI2">
         <v>55</v>
       </c>
       <c r="BJ2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK2">
         <v>1</v>
@@ -2276,10 +2279,10 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ2">
         <v>3</v>
@@ -2291,7 +2294,7 @@
         <v>20</v>
       </c>
       <c r="BT2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU2">
         <v>3</v>
@@ -2303,13 +2306,13 @@
         <v>20</v>
       </c>
       <c r="BX2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY2">
         <v>3</v>
       </c>
       <c r="BZ2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA2">
         <v>1</v>
@@ -2318,16 +2321,16 @@
         <v>1</v>
       </c>
       <c r="CC2">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="CD2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="CE2">
         <v>55</v>
       </c>
       <c r="CF2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG2">
         <v>1</v>
@@ -2342,10 +2345,10 @@
         <v>9</v>
       </c>
       <c r="CK2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM2">
         <v>3</v>
@@ -2357,7 +2360,7 @@
         <v>20</v>
       </c>
       <c r="CP2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ2">
         <v>3</v>
@@ -2369,13 +2372,13 @@
         <v>20</v>
       </c>
       <c r="CT2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU2">
         <v>3</v>
       </c>
       <c r="CV2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW2">
         <v>3</v>
@@ -2387,22 +2390,22 @@
         <v>1</v>
       </c>
       <c r="CZ2">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="DA2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB2">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="DC2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DD2" t="b">
         <v>1</v>
       </c>
       <c r="DE2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF2">
         <v>1</v>
@@ -2417,10 +2420,10 @@
         <v>9</v>
       </c>
       <c r="DJ2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL2">
         <v>3</v>
@@ -2432,7 +2435,7 @@
         <v>20</v>
       </c>
       <c r="DO2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP2">
         <v>3</v>
@@ -2444,37 +2447,37 @@
         <v>20</v>
       </c>
       <c r="DS2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT2">
         <v>3</v>
       </c>
       <c r="DU2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV2">
         <v>3</v>
       </c>
       <c r="DW2" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX2">
+        <v>1</v>
+      </c>
+      <c r="DY2">
+        <v>1</v>
+      </c>
+      <c r="DZ2">
+        <v>2600</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>282</v>
+      </c>
+      <c r="EB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC2" t="s">
         <v>280</v>
-      </c>
-      <c r="DX2">
-        <v>1</v>
-      </c>
-      <c r="DY2">
-        <v>1</v>
-      </c>
-      <c r="DZ2">
-        <v>2000</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>281</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>279</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -2489,10 +2492,10 @@
         <v>9</v>
       </c>
       <c r="EH2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ2">
         <v>3</v>
@@ -2504,7 +2507,7 @@
         <v>20</v>
       </c>
       <c r="EM2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN2">
         <v>3</v>
@@ -2516,19 +2519,19 @@
         <v>20</v>
       </c>
       <c r="EQ2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER2">
         <v>3</v>
       </c>
       <c r="ES2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET2">
         <v>3</v>
       </c>
       <c r="EU2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV2">
         <v>0</v>
@@ -2537,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="FA2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB2">
         <v>1</v>
@@ -2552,10 +2555,10 @@
         <v>9</v>
       </c>
       <c r="FF2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH2">
         <v>3</v>
@@ -2567,7 +2570,7 @@
         <v>20</v>
       </c>
       <c r="FK2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL2">
         <v>3</v>
@@ -2579,19 +2582,19 @@
         <v>20</v>
       </c>
       <c r="FO2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP2">
         <v>3</v>
       </c>
       <c r="FQ2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR2">
         <v>3</v>
       </c>
       <c r="FS2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT2">
         <v>0</v>
@@ -2600,16 +2603,16 @@
         <v>0</v>
       </c>
       <c r="FX2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY2">
         <v>1</v>
       </c>
       <c r="FZ2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="GA2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="GB2">
         <v>50000</v>
@@ -2635,8 +2638,35 @@
       <c r="GI2" t="b">
         <v>0</v>
       </c>
+      <c r="GJ2" t="s">
+        <v>291</v>
+      </c>
+      <c r="GK2">
+        <v>50000</v>
+      </c>
+      <c r="GL2">
+        <v>7200</v>
+      </c>
+      <c r="GM2">
+        <v>7200</v>
+      </c>
+      <c r="GN2">
+        <v>50000</v>
+      </c>
+      <c r="GO2">
+        <v>0.9</v>
+      </c>
+      <c r="GP2">
+        <v>0.8</v>
+      </c>
+      <c r="GQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="GR2" t="b">
+        <v>0</v>
+      </c>
       <c r="GS2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT2">
         <v>0.05</v>
@@ -2651,13 +2681,13 @@
         <v>8.5</v>
       </c>
       <c r="GX2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA2">
         <v>1</v>
@@ -2666,10 +2696,10 @@
         <v>1</v>
       </c>
       <c r="HC2">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="HD2">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="HE2">
         <v>0.95</v>
@@ -2684,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="HI2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ2">
         <v>0</v>
@@ -2693,49 +2723,49 @@
         <v>0</v>
       </c>
       <c r="HP2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS2">
         <v>86400</v>
       </c>
       <c r="HT2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU2">
         <v>86400</v>
       </c>
       <c r="HV2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW2">
         <v>1</v>
       </c>
       <c r="HX2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY2">
         <v>1</v>
       </c>
       <c r="HZ2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE2">
         <v>86400</v>
@@ -2779,13 +2809,13 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <v>4536000</v>
+        <v>4402000</v>
       </c>
       <c r="O3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2800,10 +2830,10 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -2815,7 +2845,7 @@
         <v>20</v>
       </c>
       <c r="Z3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA3">
         <v>3</v>
@@ -2827,13 +2857,13 @@
         <v>20</v>
       </c>
       <c r="AD3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE3">
         <v>3</v>
       </c>
       <c r="AF3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG3">
         <v>3</v>
@@ -2848,7 +2878,7 @@
         <v>6</v>
       </c>
       <c r="AM3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -2863,10 +2893,10 @@
         <v>9</v>
       </c>
       <c r="AR3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT3">
         <v>3</v>
@@ -2878,7 +2908,7 @@
         <v>20</v>
       </c>
       <c r="AW3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX3">
         <v>3</v>
@@ -2890,13 +2920,13 @@
         <v>20</v>
       </c>
       <c r="BA3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB3">
         <v>3</v>
       </c>
       <c r="BC3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD3">
         <v>3</v>
@@ -2911,13 +2941,13 @@
         <v>19500000</v>
       </c>
       <c r="BH3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="BI3">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BJ3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK3">
         <v>1</v>
@@ -2932,10 +2962,10 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ3">
         <v>3</v>
@@ -2947,7 +2977,7 @@
         <v>20</v>
       </c>
       <c r="BT3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU3">
         <v>3</v>
@@ -2959,13 +2989,13 @@
         <v>20</v>
       </c>
       <c r="BX3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY3">
         <v>3</v>
       </c>
       <c r="BZ3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA3">
         <v>1</v>
@@ -2977,13 +3007,13 @@
         <v>3200000</v>
       </c>
       <c r="CD3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="CE3">
         <v>55</v>
       </c>
       <c r="CF3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG3">
         <v>1</v>
@@ -2998,10 +3028,10 @@
         <v>9</v>
       </c>
       <c r="CK3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM3">
         <v>3</v>
@@ -3013,7 +3043,7 @@
         <v>20</v>
       </c>
       <c r="CP3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ3">
         <v>3</v>
@@ -3025,13 +3055,13 @@
         <v>20</v>
       </c>
       <c r="CT3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU3">
         <v>3</v>
       </c>
       <c r="CV3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW3">
         <v>3</v>
@@ -3043,22 +3073,22 @@
         <v>1</v>
       </c>
       <c r="CZ3">
-        <v>6200</v>
+        <v>5600</v>
       </c>
       <c r="DA3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB3">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="DC3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DD3" t="b">
         <v>1</v>
       </c>
       <c r="DE3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF3">
         <v>1</v>
@@ -3073,10 +3103,10 @@
         <v>9</v>
       </c>
       <c r="DJ3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL3">
         <v>3</v>
@@ -3088,7 +3118,7 @@
         <v>20</v>
       </c>
       <c r="DO3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP3">
         <v>3</v>
@@ -3100,37 +3130,37 @@
         <v>20</v>
       </c>
       <c r="DS3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT3">
         <v>3</v>
       </c>
       <c r="DU3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV3">
         <v>3</v>
       </c>
       <c r="DW3" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX3">
+        <v>1</v>
+      </c>
+      <c r="DY3">
+        <v>1</v>
+      </c>
+      <c r="DZ3">
+        <v>2900</v>
+      </c>
+      <c r="EA3" t="s">
+        <v>283</v>
+      </c>
+      <c r="EB3" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC3" t="s">
         <v>280</v>
-      </c>
-      <c r="DX3">
-        <v>1</v>
-      </c>
-      <c r="DY3">
-        <v>1</v>
-      </c>
-      <c r="DZ3">
-        <v>2800</v>
-      </c>
-      <c r="EA3" t="s">
-        <v>282</v>
-      </c>
-      <c r="EB3" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC3" t="s">
-        <v>279</v>
       </c>
       <c r="ED3">
         <v>1</v>
@@ -3145,10 +3175,10 @@
         <v>9</v>
       </c>
       <c r="EH3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ3">
         <v>3</v>
@@ -3160,7 +3190,7 @@
         <v>20</v>
       </c>
       <c r="EM3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN3">
         <v>3</v>
@@ -3172,19 +3202,19 @@
         <v>20</v>
       </c>
       <c r="EQ3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER3">
         <v>3</v>
       </c>
       <c r="ES3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET3">
         <v>3</v>
       </c>
       <c r="EU3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV3">
         <v>0</v>
@@ -3193,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="FA3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB3">
         <v>1</v>
@@ -3208,10 +3238,10 @@
         <v>9</v>
       </c>
       <c r="FF3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH3">
         <v>3</v>
@@ -3223,7 +3253,7 @@
         <v>20</v>
       </c>
       <c r="FK3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL3">
         <v>3</v>
@@ -3235,19 +3265,19 @@
         <v>20</v>
       </c>
       <c r="FO3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP3">
         <v>3</v>
       </c>
       <c r="FQ3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR3">
         <v>3</v>
       </c>
       <c r="FS3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT3">
         <v>0</v>
@@ -3256,28 +3286,28 @@
         <v>0</v>
       </c>
       <c r="FX3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY3">
         <v>1</v>
       </c>
       <c r="FZ3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="GA3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="GB3">
+        <v>75000</v>
+      </c>
+      <c r="GC3">
+        <v>7200</v>
+      </c>
+      <c r="GD3">
+        <v>11000</v>
+      </c>
+      <c r="GE3">
         <v>100000</v>
-      </c>
-      <c r="GC3">
-        <v>11000</v>
-      </c>
-      <c r="GD3">
-        <v>22000</v>
-      </c>
-      <c r="GE3">
-        <v>200000</v>
       </c>
       <c r="GF3">
         <v>0.9</v>
@@ -3291,8 +3321,35 @@
       <c r="GI3" t="b">
         <v>0</v>
       </c>
+      <c r="GJ3" t="s">
+        <v>292</v>
+      </c>
+      <c r="GK3">
+        <v>75000</v>
+      </c>
+      <c r="GL3">
+        <v>7200</v>
+      </c>
+      <c r="GM3">
+        <v>11000</v>
+      </c>
+      <c r="GN3">
+        <v>100000</v>
+      </c>
+      <c r="GO3">
+        <v>0.9</v>
+      </c>
+      <c r="GP3">
+        <v>0.8</v>
+      </c>
+      <c r="GQ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="GR3" t="b">
+        <v>0</v>
+      </c>
       <c r="GS3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT3">
         <v>0.05</v>
@@ -3307,13 +3364,13 @@
         <v>8.5</v>
       </c>
       <c r="GX3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA3">
         <v>1</v>
@@ -3322,10 +3379,10 @@
         <v>1</v>
       </c>
       <c r="HC3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="HD3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="HE3">
         <v>0.95</v>
@@ -3340,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="HI3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ3">
         <v>0</v>
@@ -3349,49 +3406,49 @@
         <v>0</v>
       </c>
       <c r="HP3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS3">
         <v>86400</v>
       </c>
       <c r="HT3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU3">
         <v>86400</v>
       </c>
       <c r="HV3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW3">
         <v>1</v>
       </c>
       <c r="HX3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY3">
         <v>1</v>
       </c>
       <c r="HZ3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE3">
         <v>86400</v>
@@ -3411,10 +3468,10 @@
         <v>242</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -3423,7 +3480,7 @@
         <v>2.6</v>
       </c>
       <c r="J4">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -3435,13 +3492,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>5527000</v>
+        <v>3125000</v>
       </c>
       <c r="O4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3456,10 +3513,10 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W4">
         <v>3</v>
@@ -3471,7 +3528,7 @@
         <v>20</v>
       </c>
       <c r="Z4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA4">
         <v>3</v>
@@ -3483,13 +3540,13 @@
         <v>20</v>
       </c>
       <c r="AD4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
       <c r="AF4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG4">
         <v>3</v>
@@ -3504,7 +3561,7 @@
         <v>6</v>
       </c>
       <c r="AM4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -3519,10 +3576,10 @@
         <v>9</v>
       </c>
       <c r="AR4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT4">
         <v>3</v>
@@ -3534,7 +3591,7 @@
         <v>20</v>
       </c>
       <c r="AW4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX4">
         <v>3</v>
@@ -3546,13 +3603,13 @@
         <v>20</v>
       </c>
       <c r="BA4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB4">
         <v>3</v>
       </c>
       <c r="BC4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD4">
         <v>3</v>
@@ -3564,16 +3621,16 @@
         <v>1</v>
       </c>
       <c r="BG4">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BH4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="BI4">
         <v>55</v>
       </c>
       <c r="BJ4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK4">
         <v>1</v>
@@ -3588,10 +3645,10 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ4">
         <v>3</v>
@@ -3603,7 +3660,7 @@
         <v>20</v>
       </c>
       <c r="BT4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU4">
         <v>3</v>
@@ -3615,13 +3672,13 @@
         <v>20</v>
       </c>
       <c r="BX4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY4">
         <v>3</v>
       </c>
       <c r="BZ4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA4">
         <v>1</v>
@@ -3633,13 +3690,13 @@
         <v>2400000</v>
       </c>
       <c r="CD4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="CE4">
         <v>55</v>
       </c>
       <c r="CF4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG4">
         <v>1</v>
@@ -3654,10 +3711,10 @@
         <v>9</v>
       </c>
       <c r="CK4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM4">
         <v>3</v>
@@ -3669,7 +3726,7 @@
         <v>20</v>
       </c>
       <c r="CP4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ4">
         <v>3</v>
@@ -3681,13 +3738,13 @@
         <v>20</v>
       </c>
       <c r="CT4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU4">
         <v>3</v>
       </c>
       <c r="CV4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW4">
         <v>3</v>
@@ -3699,22 +3756,22 @@
         <v>1</v>
       </c>
       <c r="CZ4">
-        <v>8600</v>
+        <v>5600</v>
       </c>
       <c r="DA4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB4">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="DC4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DD4" t="b">
         <v>1</v>
       </c>
       <c r="DE4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF4">
         <v>1</v>
@@ -3729,10 +3786,10 @@
         <v>9</v>
       </c>
       <c r="DJ4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL4">
         <v>3</v>
@@ -3744,7 +3801,7 @@
         <v>20</v>
       </c>
       <c r="DO4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP4">
         <v>3</v>
@@ -3756,19 +3813,19 @@
         <v>20</v>
       </c>
       <c r="DS4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT4">
         <v>3</v>
       </c>
       <c r="DU4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV4">
         <v>3</v>
       </c>
       <c r="DW4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="DX4">
         <v>1</v>
@@ -3777,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="DZ4">
-        <v>4100</v>
+        <v>2500</v>
       </c>
       <c r="EA4" t="s">
         <v>283</v>
@@ -3786,7 +3843,7 @@
         <v>1</v>
       </c>
       <c r="EC4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="ED4">
         <v>1</v>
@@ -3801,10 +3858,10 @@
         <v>9</v>
       </c>
       <c r="EH4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ4">
         <v>3</v>
@@ -3816,7 +3873,7 @@
         <v>20</v>
       </c>
       <c r="EM4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN4">
         <v>3</v>
@@ -3828,19 +3885,19 @@
         <v>20</v>
       </c>
       <c r="EQ4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER4">
         <v>3</v>
       </c>
       <c r="ES4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET4">
         <v>3</v>
       </c>
       <c r="EU4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV4">
         <v>0</v>
@@ -3849,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="FA4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB4">
         <v>1</v>
@@ -3864,10 +3921,10 @@
         <v>9</v>
       </c>
       <c r="FF4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH4">
         <v>3</v>
@@ -3879,7 +3936,7 @@
         <v>20</v>
       </c>
       <c r="FK4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL4">
         <v>3</v>
@@ -3891,19 +3948,19 @@
         <v>20</v>
       </c>
       <c r="FO4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP4">
         <v>3</v>
       </c>
       <c r="FQ4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR4">
         <v>3</v>
       </c>
       <c r="FS4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT4">
         <v>0</v>
@@ -3912,7 +3969,7 @@
         <v>0</v>
       </c>
       <c r="FX4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY4">
         <v>1</v>
@@ -3921,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="GA4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="GB4">
         <v>75000</v>
@@ -3948,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="GS4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT4">
         <v>0.05</v>
@@ -3963,13 +4020,13 @@
         <v>8.5</v>
       </c>
       <c r="GX4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA4">
         <v>1</v>
@@ -3978,10 +4035,10 @@
         <v>1</v>
       </c>
       <c r="HC4">
-        <v>5500</v>
+        <v>3100</v>
       </c>
       <c r="HD4">
-        <v>5500</v>
+        <v>3100</v>
       </c>
       <c r="HE4">
         <v>0.95</v>
@@ -3996,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="HI4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ4">
         <v>0</v>
@@ -4005,49 +4062,49 @@
         <v>0</v>
       </c>
       <c r="HP4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS4">
         <v>86400</v>
       </c>
       <c r="HT4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU4">
         <v>86400</v>
       </c>
       <c r="HV4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW4">
         <v>1</v>
       </c>
       <c r="HX4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY4">
         <v>1</v>
       </c>
       <c r="HZ4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE4">
         <v>86400</v>
@@ -4091,13 +4148,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>3648000</v>
+        <v>2012000</v>
       </c>
       <c r="O5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4112,10 +4169,10 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W5">
         <v>3</v>
@@ -4127,7 +4184,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA5">
         <v>3</v>
@@ -4139,13 +4196,13 @@
         <v>20</v>
       </c>
       <c r="AD5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE5">
         <v>3</v>
       </c>
       <c r="AF5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG5">
         <v>3</v>
@@ -4160,7 +4217,7 @@
         <v>6</v>
       </c>
       <c r="AM5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -4175,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="AR5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT5">
         <v>3</v>
@@ -4190,7 +4247,7 @@
         <v>20</v>
       </c>
       <c r="AW5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX5">
         <v>3</v>
@@ -4202,13 +4259,13 @@
         <v>20</v>
       </c>
       <c r="BA5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB5">
         <v>3</v>
       </c>
       <c r="BC5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD5">
         <v>3</v>
@@ -4223,13 +4280,13 @@
         <v>5500000</v>
       </c>
       <c r="BH5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="BI5">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BJ5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK5">
         <v>1</v>
@@ -4244,10 +4301,10 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ5">
         <v>3</v>
@@ -4259,7 +4316,7 @@
         <v>20</v>
       </c>
       <c r="BT5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU5">
         <v>3</v>
@@ -4271,13 +4328,13 @@
         <v>20</v>
       </c>
       <c r="BX5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY5">
         <v>3</v>
       </c>
       <c r="BZ5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA5">
         <v>1</v>
@@ -4286,16 +4343,16 @@
         <v>1</v>
       </c>
       <c r="CC5">
-        <v>1800000</v>
+        <v>2100000</v>
       </c>
       <c r="CD5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="CE5">
         <v>55</v>
       </c>
       <c r="CF5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG5">
         <v>1</v>
@@ -4310,10 +4367,10 @@
         <v>9</v>
       </c>
       <c r="CK5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM5">
         <v>3</v>
@@ -4325,7 +4382,7 @@
         <v>20</v>
       </c>
       <c r="CP5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ5">
         <v>3</v>
@@ -4337,13 +4394,13 @@
         <v>20</v>
       </c>
       <c r="CT5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU5">
         <v>3</v>
       </c>
       <c r="CV5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW5">
         <v>3</v>
@@ -4355,10 +4412,10 @@
         <v>1</v>
       </c>
       <c r="CZ5">
-        <v>6000</v>
+        <v>3100</v>
       </c>
       <c r="DA5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB5">
         <v>0</v>
@@ -4370,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="DE5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF5">
         <v>1</v>
@@ -4385,10 +4442,10 @@
         <v>9</v>
       </c>
       <c r="DJ5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL5">
         <v>3</v>
@@ -4400,7 +4457,7 @@
         <v>20</v>
       </c>
       <c r="DO5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP5">
         <v>3</v>
@@ -4412,19 +4469,19 @@
         <v>20</v>
       </c>
       <c r="DS5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT5">
         <v>3</v>
       </c>
       <c r="DU5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV5">
         <v>3</v>
       </c>
       <c r="DW5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="DX5">
         <v>1</v>
@@ -4433,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="DZ5">
-        <v>1900</v>
+        <v>1200</v>
       </c>
       <c r="EA5" t="s">
         <v>284</v>
@@ -4442,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="EC5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="ED5">
         <v>1</v>
@@ -4457,10 +4514,10 @@
         <v>9</v>
       </c>
       <c r="EH5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ5">
         <v>3</v>
@@ -4472,7 +4529,7 @@
         <v>20</v>
       </c>
       <c r="EM5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN5">
         <v>3</v>
@@ -4484,19 +4541,19 @@
         <v>20</v>
       </c>
       <c r="EQ5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER5">
         <v>3</v>
       </c>
       <c r="ES5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET5">
         <v>3</v>
       </c>
       <c r="EU5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV5">
         <v>0</v>
@@ -4505,7 +4562,7 @@
         <v>0</v>
       </c>
       <c r="FA5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB5">
         <v>1</v>
@@ -4520,10 +4577,10 @@
         <v>9</v>
       </c>
       <c r="FF5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH5">
         <v>3</v>
@@ -4535,7 +4592,7 @@
         <v>20</v>
       </c>
       <c r="FK5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL5">
         <v>3</v>
@@ -4547,19 +4604,19 @@
         <v>20</v>
       </c>
       <c r="FO5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP5">
         <v>3</v>
       </c>
       <c r="FQ5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR5">
         <v>3</v>
       </c>
       <c r="FS5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT5">
         <v>0</v>
@@ -4568,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="FX5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY5">
         <v>1</v>
@@ -4577,19 +4634,19 @@
         <v>1</v>
       </c>
       <c r="GA5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="GB5">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="GC5">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="GD5">
-        <v>22000</v>
+        <v>7200</v>
       </c>
       <c r="GE5">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="GF5">
         <v>0.9</v>
@@ -4604,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="GS5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT5">
         <v>0.05</v>
@@ -4619,13 +4676,13 @@
         <v>8.5</v>
       </c>
       <c r="GX5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA5">
         <v>1</v>
@@ -4634,10 +4691,10 @@
         <v>1</v>
       </c>
       <c r="HC5">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="HD5">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="HE5">
         <v>0.95</v>
@@ -4652,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="HI5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ5">
         <v>0</v>
@@ -4661,49 +4718,49 @@
         <v>0</v>
       </c>
       <c r="HP5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS5">
         <v>86400</v>
       </c>
       <c r="HT5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU5">
         <v>86400</v>
       </c>
       <c r="HV5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW5">
         <v>1</v>
       </c>
       <c r="HX5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY5">
         <v>1</v>
       </c>
       <c r="HZ5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE5">
         <v>86400</v>
@@ -4723,10 +4780,10 @@
         <v>244</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -4735,7 +4792,7 @@
         <v>2.6</v>
       </c>
       <c r="J6">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4747,13 +4804,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>3863000</v>
+        <v>5527000</v>
       </c>
       <c r="O6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4768,10 +4825,10 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W6">
         <v>3</v>
@@ -4783,7 +4840,7 @@
         <v>20</v>
       </c>
       <c r="Z6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -4795,13 +4852,13 @@
         <v>20</v>
       </c>
       <c r="AD6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE6">
         <v>3</v>
       </c>
       <c r="AF6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG6">
         <v>3</v>
@@ -4816,7 +4873,7 @@
         <v>6</v>
       </c>
       <c r="AM6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN6">
         <v>1</v>
@@ -4831,10 +4888,10 @@
         <v>9</v>
       </c>
       <c r="AR6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT6">
         <v>3</v>
@@ -4846,7 +4903,7 @@
         <v>20</v>
       </c>
       <c r="AW6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX6">
         <v>3</v>
@@ -4858,13 +4915,13 @@
         <v>20</v>
       </c>
       <c r="BA6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB6">
         <v>3</v>
       </c>
       <c r="BC6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD6">
         <v>3</v>
@@ -4876,16 +4933,16 @@
         <v>1</v>
       </c>
       <c r="BG6">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BH6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="BI6">
         <v>55</v>
       </c>
       <c r="BJ6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK6">
         <v>1</v>
@@ -4900,10 +4957,10 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ6">
         <v>3</v>
@@ -4915,7 +4972,7 @@
         <v>20</v>
       </c>
       <c r="BT6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU6">
         <v>3</v>
@@ -4927,13 +4984,13 @@
         <v>20</v>
       </c>
       <c r="BX6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY6">
         <v>3</v>
       </c>
       <c r="BZ6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA6">
         <v>1</v>
@@ -4942,16 +4999,16 @@
         <v>1</v>
       </c>
       <c r="CC6">
-        <v>2800000</v>
+        <v>2100000</v>
       </c>
       <c r="CD6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="CE6">
         <v>55</v>
       </c>
       <c r="CF6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG6">
         <v>1</v>
@@ -4966,10 +5023,10 @@
         <v>9</v>
       </c>
       <c r="CK6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM6">
         <v>3</v>
@@ -4981,7 +5038,7 @@
         <v>20</v>
       </c>
       <c r="CP6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ6">
         <v>3</v>
@@ -4993,13 +5050,13 @@
         <v>20</v>
       </c>
       <c r="CT6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU6">
         <v>3</v>
       </c>
       <c r="CV6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW6">
         <v>3</v>
@@ -5011,22 +5068,22 @@
         <v>1</v>
       </c>
       <c r="CZ6">
-        <v>5200</v>
+        <v>6700</v>
       </c>
       <c r="DA6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB6">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="DC6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DD6" t="b">
         <v>1</v>
       </c>
       <c r="DE6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF6">
         <v>1</v>
@@ -5041,10 +5098,10 @@
         <v>9</v>
       </c>
       <c r="DJ6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL6">
         <v>3</v>
@@ -5056,7 +5113,7 @@
         <v>20</v>
       </c>
       <c r="DO6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP6">
         <v>3</v>
@@ -5068,19 +5125,19 @@
         <v>20</v>
       </c>
       <c r="DS6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT6">
         <v>3</v>
       </c>
       <c r="DU6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV6">
         <v>3</v>
       </c>
       <c r="DW6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="DX6">
         <v>1</v>
@@ -5089,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="DZ6">
-        <v>2400</v>
+        <v>3900</v>
       </c>
       <c r="EA6" t="s">
         <v>284</v>
@@ -5098,7 +5155,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="ED6">
         <v>1</v>
@@ -5113,10 +5170,10 @@
         <v>9</v>
       </c>
       <c r="EH6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ6">
         <v>3</v>
@@ -5128,7 +5185,7 @@
         <v>20</v>
       </c>
       <c r="EM6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN6">
         <v>3</v>
@@ -5140,19 +5197,19 @@
         <v>20</v>
       </c>
       <c r="EQ6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER6">
         <v>3</v>
       </c>
       <c r="ES6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET6">
         <v>3</v>
       </c>
       <c r="EU6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV6">
         <v>0</v>
@@ -5161,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="FA6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB6">
         <v>1</v>
@@ -5176,10 +5233,10 @@
         <v>9</v>
       </c>
       <c r="FF6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH6">
         <v>3</v>
@@ -5191,7 +5248,7 @@
         <v>20</v>
       </c>
       <c r="FK6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL6">
         <v>3</v>
@@ -5203,19 +5260,19 @@
         <v>20</v>
       </c>
       <c r="FO6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP6">
         <v>3</v>
       </c>
       <c r="FQ6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR6">
         <v>3</v>
       </c>
       <c r="FS6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT6">
         <v>0</v>
@@ -5224,28 +5281,28 @@
         <v>0</v>
       </c>
       <c r="FX6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY6">
         <v>1</v>
       </c>
       <c r="FZ6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="GA6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="GB6">
-        <v>75000</v>
+        <v>50000</v>
       </c>
       <c r="GC6">
         <v>7200</v>
       </c>
       <c r="GD6">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="GE6">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="GF6">
         <v>0.9</v>
@@ -5259,35 +5316,8 @@
       <c r="GI6" t="b">
         <v>0</v>
       </c>
-      <c r="GJ6" t="s">
-        <v>289</v>
-      </c>
-      <c r="GK6">
-        <v>75000</v>
-      </c>
-      <c r="GL6">
-        <v>7200</v>
-      </c>
-      <c r="GM6">
-        <v>11000</v>
-      </c>
-      <c r="GN6">
-        <v>100000</v>
-      </c>
-      <c r="GO6">
-        <v>0.9</v>
-      </c>
-      <c r="GP6">
-        <v>0.8</v>
-      </c>
-      <c r="GQ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="GR6" t="b">
-        <v>0</v>
-      </c>
       <c r="GS6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT6">
         <v>0.05</v>
@@ -5302,13 +5332,13 @@
         <v>8.5</v>
       </c>
       <c r="GX6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA6">
         <v>1</v>
@@ -5317,10 +5347,10 @@
         <v>1</v>
       </c>
       <c r="HC6">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="HD6">
-        <v>3900</v>
+        <v>5500</v>
       </c>
       <c r="HE6">
         <v>0.95</v>
@@ -5335,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="HI6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ6">
         <v>0</v>
@@ -5344,49 +5374,49 @@
         <v>0</v>
       </c>
       <c r="HP6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS6">
         <v>86400</v>
       </c>
       <c r="HT6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU6">
         <v>86400</v>
       </c>
       <c r="HV6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW6">
         <v>1</v>
       </c>
       <c r="HX6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY6">
         <v>1</v>
       </c>
       <c r="HZ6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE6">
         <v>86400</v>
@@ -5406,10 +5436,10 @@
         <v>245</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H7">
         <v>2</v>
@@ -5418,7 +5448,7 @@
         <v>2.6</v>
       </c>
       <c r="J7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -5430,13 +5460,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>4402000</v>
+        <v>4536000</v>
       </c>
       <c r="O7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5451,10 +5481,10 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W7">
         <v>3</v>
@@ -5466,7 +5496,7 @@
         <v>20</v>
       </c>
       <c r="Z7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA7">
         <v>3</v>
@@ -5478,13 +5508,13 @@
         <v>20</v>
       </c>
       <c r="AD7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE7">
         <v>3</v>
       </c>
       <c r="AF7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG7">
         <v>3</v>
@@ -5499,7 +5529,7 @@
         <v>6</v>
       </c>
       <c r="AM7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -5514,10 +5544,10 @@
         <v>9</v>
       </c>
       <c r="AR7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT7">
         <v>3</v>
@@ -5529,7 +5559,7 @@
         <v>20</v>
       </c>
       <c r="AW7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX7">
         <v>3</v>
@@ -5541,13 +5571,13 @@
         <v>20</v>
       </c>
       <c r="BA7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB7">
         <v>3</v>
       </c>
       <c r="BC7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD7">
         <v>3</v>
@@ -5559,16 +5589,16 @@
         <v>1</v>
       </c>
       <c r="BG7">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BH7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="BI7">
         <v>55</v>
       </c>
       <c r="BJ7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK7">
         <v>1</v>
@@ -5583,10 +5613,10 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ7">
         <v>3</v>
@@ -5598,7 +5628,7 @@
         <v>20</v>
       </c>
       <c r="BT7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU7">
         <v>3</v>
@@ -5610,13 +5640,13 @@
         <v>20</v>
       </c>
       <c r="BX7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY7">
         <v>3</v>
       </c>
       <c r="BZ7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA7">
         <v>1</v>
@@ -5625,16 +5655,16 @@
         <v>1</v>
       </c>
       <c r="CC7">
-        <v>2100000</v>
+        <v>2400000</v>
       </c>
       <c r="CD7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="CE7">
         <v>55</v>
       </c>
       <c r="CF7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG7">
         <v>1</v>
@@ -5649,10 +5679,10 @@
         <v>9</v>
       </c>
       <c r="CK7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM7">
         <v>3</v>
@@ -5664,7 +5694,7 @@
         <v>20</v>
       </c>
       <c r="CP7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ7">
         <v>3</v>
@@ -5676,13 +5706,13 @@
         <v>20</v>
       </c>
       <c r="CT7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU7">
         <v>3</v>
       </c>
       <c r="CV7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW7">
         <v>3</v>
@@ -5694,10 +5724,10 @@
         <v>1</v>
       </c>
       <c r="CZ7">
-        <v>5400</v>
+        <v>8100</v>
       </c>
       <c r="DA7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB7">
         <v>0</v>
@@ -5709,7 +5739,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF7">
         <v>1</v>
@@ -5724,10 +5754,10 @@
         <v>9</v>
       </c>
       <c r="DJ7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL7">
         <v>3</v>
@@ -5739,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="DO7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP7">
         <v>3</v>
@@ -5751,37 +5781,37 @@
         <v>20</v>
       </c>
       <c r="DS7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT7">
         <v>3</v>
       </c>
       <c r="DU7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV7">
         <v>3</v>
       </c>
       <c r="DW7" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX7">
+        <v>1</v>
+      </c>
+      <c r="DY7">
+        <v>1</v>
+      </c>
+      <c r="DZ7">
+        <v>2000</v>
+      </c>
+      <c r="EA7" t="s">
+        <v>285</v>
+      </c>
+      <c r="EB7" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC7" t="s">
         <v>280</v>
-      </c>
-      <c r="DX7">
-        <v>1</v>
-      </c>
-      <c r="DY7">
-        <v>1</v>
-      </c>
-      <c r="DZ7">
-        <v>2400</v>
-      </c>
-      <c r="EA7" t="s">
-        <v>281</v>
-      </c>
-      <c r="EB7" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC7" t="s">
-        <v>279</v>
       </c>
       <c r="ED7">
         <v>1</v>
@@ -5796,10 +5826,10 @@
         <v>9</v>
       </c>
       <c r="EH7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ7">
         <v>3</v>
@@ -5811,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="EM7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN7">
         <v>3</v>
@@ -5823,19 +5853,19 @@
         <v>20</v>
       </c>
       <c r="EQ7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER7">
         <v>3</v>
       </c>
       <c r="ES7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET7">
         <v>3</v>
       </c>
       <c r="EU7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV7">
         <v>0</v>
@@ -5844,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="FA7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB7">
         <v>1</v>
@@ -5859,10 +5889,10 @@
         <v>9</v>
       </c>
       <c r="FF7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH7">
         <v>3</v>
@@ -5874,7 +5904,7 @@
         <v>20</v>
       </c>
       <c r="FK7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL7">
         <v>3</v>
@@ -5886,19 +5916,19 @@
         <v>20</v>
       </c>
       <c r="FO7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP7">
         <v>3</v>
       </c>
       <c r="FQ7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR7">
         <v>3</v>
       </c>
       <c r="FS7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT7">
         <v>0</v>
@@ -5907,28 +5937,28 @@
         <v>0</v>
       </c>
       <c r="FX7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY7">
         <v>1</v>
       </c>
       <c r="FZ7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="GA7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="GB7">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="GC7">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GD7">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="GE7">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="GF7">
         <v>0.9</v>
@@ -5942,35 +5972,8 @@
       <c r="GI7" t="b">
         <v>0</v>
       </c>
-      <c r="GJ7" t="s">
-        <v>293</v>
-      </c>
-      <c r="GK7">
-        <v>100000</v>
-      </c>
-      <c r="GL7">
-        <v>11000</v>
-      </c>
-      <c r="GM7">
-        <v>22000</v>
-      </c>
-      <c r="GN7">
-        <v>200000</v>
-      </c>
-      <c r="GO7">
-        <v>0.9</v>
-      </c>
-      <c r="GP7">
-        <v>0.8</v>
-      </c>
-      <c r="GQ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="GR7" t="b">
-        <v>0</v>
-      </c>
       <c r="GS7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT7">
         <v>0.05</v>
@@ -5985,13 +5988,13 @@
         <v>8.5</v>
       </c>
       <c r="GX7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA7">
         <v>1</v>
@@ -6000,10 +6003,10 @@
         <v>1</v>
       </c>
       <c r="HC7">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="HD7">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="HE7">
         <v>0.95</v>
@@ -6018,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="HI7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ7">
         <v>0</v>
@@ -6027,49 +6030,49 @@
         <v>0</v>
       </c>
       <c r="HP7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS7">
         <v>86400</v>
       </c>
       <c r="HT7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU7">
         <v>86400</v>
       </c>
       <c r="HV7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW7">
         <v>1</v>
       </c>
       <c r="HX7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY7">
         <v>1</v>
       </c>
       <c r="HZ7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE7">
         <v>86400</v>
@@ -6089,10 +6092,10 @@
         <v>246</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -6101,7 +6104,7 @@
         <v>2.6</v>
       </c>
       <c r="J8">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -6113,13 +6116,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>2455000</v>
+        <v>3863000</v>
       </c>
       <c r="O8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -6134,10 +6137,10 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W8">
         <v>3</v>
@@ -6149,7 +6152,7 @@
         <v>20</v>
       </c>
       <c r="Z8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA8">
         <v>3</v>
@@ -6161,13 +6164,13 @@
         <v>20</v>
       </c>
       <c r="AD8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE8">
         <v>3</v>
       </c>
       <c r="AF8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG8">
         <v>3</v>
@@ -6182,7 +6185,7 @@
         <v>6</v>
       </c>
       <c r="AM8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -6197,10 +6200,10 @@
         <v>9</v>
       </c>
       <c r="AR8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT8">
         <v>3</v>
@@ -6212,7 +6215,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX8">
         <v>3</v>
@@ -6224,13 +6227,13 @@
         <v>20</v>
       </c>
       <c r="BA8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB8">
         <v>3</v>
       </c>
       <c r="BC8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD8">
         <v>3</v>
@@ -6242,16 +6245,16 @@
         <v>1</v>
       </c>
       <c r="BG8">
-        <v>19500000</v>
+        <v>5500000</v>
       </c>
       <c r="BH8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="BI8">
         <v>35</v>
       </c>
       <c r="BJ8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK8">
         <v>1</v>
@@ -6266,10 +6269,10 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ8">
         <v>3</v>
@@ -6281,7 +6284,7 @@
         <v>20</v>
       </c>
       <c r="BT8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU8">
         <v>3</v>
@@ -6293,13 +6296,13 @@
         <v>20</v>
       </c>
       <c r="BX8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY8">
         <v>3</v>
       </c>
       <c r="BZ8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA8">
         <v>1</v>
@@ -6308,16 +6311,16 @@
         <v>1</v>
       </c>
       <c r="CC8">
-        <v>2800000</v>
+        <v>2100000</v>
       </c>
       <c r="CD8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="CE8">
         <v>55</v>
       </c>
       <c r="CF8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG8">
         <v>1</v>
@@ -6332,10 +6335,10 @@
         <v>9</v>
       </c>
       <c r="CK8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM8">
         <v>3</v>
@@ -6347,7 +6350,7 @@
         <v>20</v>
       </c>
       <c r="CP8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ8">
         <v>3</v>
@@ -6359,13 +6362,13 @@
         <v>20</v>
       </c>
       <c r="CT8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU8">
         <v>3</v>
       </c>
       <c r="CV8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW8">
         <v>3</v>
@@ -6377,10 +6380,10 @@
         <v>1</v>
       </c>
       <c r="CZ8">
-        <v>3400</v>
+        <v>5000</v>
       </c>
       <c r="DA8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB8">
         <v>0</v>
@@ -6392,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="DE8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF8">
         <v>1</v>
@@ -6407,10 +6410,10 @@
         <v>9</v>
       </c>
       <c r="DJ8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL8">
         <v>3</v>
@@ -6422,7 +6425,7 @@
         <v>20</v>
       </c>
       <c r="DO8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP8">
         <v>3</v>
@@ -6434,37 +6437,37 @@
         <v>20</v>
       </c>
       <c r="DS8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT8">
         <v>3</v>
       </c>
       <c r="DU8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV8">
         <v>3</v>
       </c>
       <c r="DW8" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX8">
+        <v>1</v>
+      </c>
+      <c r="DY8">
+        <v>1</v>
+      </c>
+      <c r="DZ8">
+        <v>1600</v>
+      </c>
+      <c r="EA8" t="s">
+        <v>286</v>
+      </c>
+      <c r="EB8" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC8" t="s">
         <v>280</v>
-      </c>
-      <c r="DX8">
-        <v>1</v>
-      </c>
-      <c r="DY8">
-        <v>1</v>
-      </c>
-      <c r="DZ8">
-        <v>1700</v>
-      </c>
-      <c r="EA8" t="s">
-        <v>284</v>
-      </c>
-      <c r="EB8" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC8" t="s">
-        <v>279</v>
       </c>
       <c r="ED8">
         <v>1</v>
@@ -6479,10 +6482,10 @@
         <v>9</v>
       </c>
       <c r="EH8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ8">
         <v>3</v>
@@ -6494,7 +6497,7 @@
         <v>20</v>
       </c>
       <c r="EM8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN8">
         <v>3</v>
@@ -6506,19 +6509,19 @@
         <v>20</v>
       </c>
       <c r="EQ8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER8">
         <v>3</v>
       </c>
       <c r="ES8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET8">
         <v>3</v>
       </c>
       <c r="EU8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV8">
         <v>0</v>
@@ -6527,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="FA8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB8">
         <v>1</v>
@@ -6542,10 +6545,10 @@
         <v>9</v>
       </c>
       <c r="FF8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH8">
         <v>3</v>
@@ -6557,7 +6560,7 @@
         <v>20</v>
       </c>
       <c r="FK8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL8">
         <v>3</v>
@@ -6569,19 +6572,19 @@
         <v>20</v>
       </c>
       <c r="FO8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP8">
         <v>3</v>
       </c>
       <c r="FQ8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR8">
         <v>3</v>
       </c>
       <c r="FS8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT8">
         <v>0</v>
@@ -6590,7 +6593,7 @@
         <v>0</v>
       </c>
       <c r="FX8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY8">
         <v>1</v>
@@ -6599,19 +6602,19 @@
         <v>1</v>
       </c>
       <c r="GA8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="GB8">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="GC8">
         <v>7200</v>
       </c>
       <c r="GD8">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GE8">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="GF8">
         <v>0.9</v>
@@ -6626,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="GS8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT8">
         <v>0.05</v>
@@ -6641,13 +6644,13 @@
         <v>8.5</v>
       </c>
       <c r="GX8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA8">
         <v>1</v>
@@ -6656,10 +6659,10 @@
         <v>1</v>
       </c>
       <c r="HC8">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="HD8">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="HE8">
         <v>0.95</v>
@@ -6674,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="HI8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ8">
         <v>0</v>
@@ -6683,49 +6686,49 @@
         <v>0</v>
       </c>
       <c r="HP8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS8">
         <v>86400</v>
       </c>
       <c r="HT8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU8">
         <v>86400</v>
       </c>
       <c r="HV8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW8">
         <v>1</v>
       </c>
       <c r="HX8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY8">
         <v>1</v>
       </c>
       <c r="HZ8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE8">
         <v>86400</v>
@@ -6745,10 +6748,10 @@
         <v>247</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -6757,7 +6760,7 @@
         <v>2.6</v>
       </c>
       <c r="J9">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -6769,13 +6772,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>5527000</v>
+        <v>3863000</v>
       </c>
       <c r="O9" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6790,10 +6793,10 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W9">
         <v>3</v>
@@ -6805,7 +6808,7 @@
         <v>20</v>
       </c>
       <c r="Z9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA9">
         <v>3</v>
@@ -6817,13 +6820,13 @@
         <v>20</v>
       </c>
       <c r="AD9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE9">
         <v>3</v>
       </c>
       <c r="AF9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG9">
         <v>3</v>
@@ -6838,7 +6841,7 @@
         <v>6</v>
       </c>
       <c r="AM9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN9">
         <v>1</v>
@@ -6853,10 +6856,10 @@
         <v>9</v>
       </c>
       <c r="AR9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT9">
         <v>3</v>
@@ -6868,7 +6871,7 @@
         <v>20</v>
       </c>
       <c r="AW9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX9">
         <v>3</v>
@@ -6880,13 +6883,13 @@
         <v>20</v>
       </c>
       <c r="BA9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB9">
         <v>3</v>
       </c>
       <c r="BC9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD9">
         <v>3</v>
@@ -6898,16 +6901,16 @@
         <v>1</v>
       </c>
       <c r="BG9">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BH9" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="BI9">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="BJ9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK9">
         <v>1</v>
@@ -6922,10 +6925,10 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ9">
         <v>3</v>
@@ -6937,7 +6940,7 @@
         <v>20</v>
       </c>
       <c r="BT9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU9">
         <v>3</v>
@@ -6949,13 +6952,13 @@
         <v>20</v>
       </c>
       <c r="BX9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY9">
         <v>3</v>
       </c>
       <c r="BZ9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA9">
         <v>1</v>
@@ -6964,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="CC9">
-        <v>2400000</v>
+        <v>3200000</v>
       </c>
       <c r="CD9" t="s">
         <v>275</v>
@@ -6973,7 +6976,7 @@
         <v>55</v>
       </c>
       <c r="CF9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG9">
         <v>1</v>
@@ -6988,10 +6991,10 @@
         <v>9</v>
       </c>
       <c r="CK9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM9">
         <v>3</v>
@@ -7003,7 +7006,7 @@
         <v>20</v>
       </c>
       <c r="CP9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ9">
         <v>3</v>
@@ -7015,13 +7018,13 @@
         <v>20</v>
       </c>
       <c r="CT9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU9">
         <v>3</v>
       </c>
       <c r="CV9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW9">
         <v>3</v>
@@ -7033,10 +7036,10 @@
         <v>1</v>
       </c>
       <c r="CZ9">
-        <v>9100</v>
+        <v>5500</v>
       </c>
       <c r="DA9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB9">
         <v>0</v>
@@ -7048,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="DE9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF9">
         <v>1</v>
@@ -7063,10 +7066,10 @@
         <v>9</v>
       </c>
       <c r="DJ9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL9">
         <v>3</v>
@@ -7078,7 +7081,7 @@
         <v>20</v>
       </c>
       <c r="DO9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP9">
         <v>3</v>
@@ -7090,37 +7093,37 @@
         <v>20</v>
       </c>
       <c r="DS9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT9">
         <v>3</v>
       </c>
       <c r="DU9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV9">
         <v>3</v>
       </c>
       <c r="DW9" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX9">
+        <v>1</v>
+      </c>
+      <c r="DY9">
+        <v>1</v>
+      </c>
+      <c r="DZ9">
+        <v>3000</v>
+      </c>
+      <c r="EA9" t="s">
+        <v>284</v>
+      </c>
+      <c r="EB9" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC9" t="s">
         <v>280</v>
-      </c>
-      <c r="DX9">
-        <v>1</v>
-      </c>
-      <c r="DY9">
-        <v>1</v>
-      </c>
-      <c r="DZ9">
-        <v>3800</v>
-      </c>
-      <c r="EA9" t="s">
-        <v>283</v>
-      </c>
-      <c r="EB9" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC9" t="s">
-        <v>279</v>
       </c>
       <c r="ED9">
         <v>1</v>
@@ -7135,10 +7138,10 @@
         <v>9</v>
       </c>
       <c r="EH9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ9">
         <v>3</v>
@@ -7150,7 +7153,7 @@
         <v>20</v>
       </c>
       <c r="EM9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN9">
         <v>3</v>
@@ -7162,19 +7165,19 @@
         <v>20</v>
       </c>
       <c r="EQ9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER9">
         <v>3</v>
       </c>
       <c r="ES9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET9">
         <v>3</v>
       </c>
       <c r="EU9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV9">
         <v>0</v>
@@ -7183,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="FA9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB9">
         <v>1</v>
@@ -7198,10 +7201,10 @@
         <v>9</v>
       </c>
       <c r="FF9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH9">
         <v>3</v>
@@ -7213,7 +7216,7 @@
         <v>20</v>
       </c>
       <c r="FK9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL9">
         <v>3</v>
@@ -7225,19 +7228,19 @@
         <v>20</v>
       </c>
       <c r="FO9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP9">
         <v>3</v>
       </c>
       <c r="FQ9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR9">
         <v>3</v>
       </c>
       <c r="FS9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT9">
         <v>0</v>
@@ -7246,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="FX9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY9">
         <v>1</v>
@@ -7255,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="GA9" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="GB9">
         <v>50000</v>
@@ -7282,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="GS9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT9">
         <v>0.05</v>
@@ -7297,13 +7300,13 @@
         <v>8.5</v>
       </c>
       <c r="GX9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA9">
         <v>1</v>
@@ -7312,10 +7315,10 @@
         <v>1</v>
       </c>
       <c r="HC9">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="HD9">
-        <v>5500</v>
+        <v>3900</v>
       </c>
       <c r="HE9">
         <v>0.95</v>
@@ -7330,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="HI9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ9">
         <v>0</v>
@@ -7339,49 +7342,49 @@
         <v>0</v>
       </c>
       <c r="HP9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS9">
         <v>86400</v>
       </c>
       <c r="HT9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU9">
         <v>86400</v>
       </c>
       <c r="HV9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW9">
         <v>1</v>
       </c>
       <c r="HX9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY9">
         <v>1</v>
       </c>
       <c r="HZ9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE9">
         <v>86400</v>
@@ -7401,10 +7404,10 @@
         <v>248</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -7413,7 +7416,7 @@
         <v>2.6</v>
       </c>
       <c r="J10">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7425,13 +7428,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>2262000</v>
+        <v>5527000</v>
       </c>
       <c r="O10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -7446,10 +7449,10 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W10">
         <v>3</v>
@@ -7461,7 +7464,7 @@
         <v>20</v>
       </c>
       <c r="Z10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA10">
         <v>3</v>
@@ -7473,13 +7476,13 @@
         <v>20</v>
       </c>
       <c r="AD10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE10">
         <v>3</v>
       </c>
       <c r="AF10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG10">
         <v>3</v>
@@ -7494,7 +7497,7 @@
         <v>6</v>
       </c>
       <c r="AM10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN10">
         <v>1</v>
@@ -7509,10 +7512,10 @@
         <v>9</v>
       </c>
       <c r="AR10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT10">
         <v>3</v>
@@ -7524,7 +7527,7 @@
         <v>20</v>
       </c>
       <c r="AW10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX10">
         <v>3</v>
@@ -7536,13 +7539,13 @@
         <v>20</v>
       </c>
       <c r="BA10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB10">
         <v>3</v>
       </c>
       <c r="BC10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD10">
         <v>3</v>
@@ -7554,16 +7557,16 @@
         <v>1</v>
       </c>
       <c r="BG10">
-        <v>5500000</v>
+        <v>19500000</v>
       </c>
       <c r="BH10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="BI10">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="BJ10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK10">
         <v>1</v>
@@ -7578,10 +7581,10 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ10">
         <v>3</v>
@@ -7593,7 +7596,7 @@
         <v>20</v>
       </c>
       <c r="BT10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU10">
         <v>3</v>
@@ -7605,13 +7608,13 @@
         <v>20</v>
       </c>
       <c r="BX10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY10">
         <v>3</v>
       </c>
       <c r="BZ10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA10">
         <v>1</v>
@@ -7620,16 +7623,16 @@
         <v>1</v>
       </c>
       <c r="CC10">
-        <v>2100000</v>
+        <v>2800000</v>
       </c>
       <c r="CD10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="CE10">
         <v>55</v>
       </c>
       <c r="CF10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG10">
         <v>1</v>
@@ -7644,10 +7647,10 @@
         <v>9</v>
       </c>
       <c r="CK10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM10">
         <v>3</v>
@@ -7659,7 +7662,7 @@
         <v>20</v>
       </c>
       <c r="CP10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ10">
         <v>3</v>
@@ -7671,13 +7674,13 @@
         <v>20</v>
       </c>
       <c r="CT10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU10">
         <v>3</v>
       </c>
       <c r="CV10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW10">
         <v>3</v>
@@ -7689,10 +7692,10 @@
         <v>1</v>
       </c>
       <c r="CZ10">
-        <v>3600</v>
+        <v>8600</v>
       </c>
       <c r="DA10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB10">
         <v>0</v>
@@ -7704,7 +7707,7 @@
         <v>1</v>
       </c>
       <c r="DE10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF10">
         <v>1</v>
@@ -7719,10 +7722,10 @@
         <v>9</v>
       </c>
       <c r="DJ10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL10">
         <v>3</v>
@@ -7734,7 +7737,7 @@
         <v>20</v>
       </c>
       <c r="DO10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP10">
         <v>3</v>
@@ -7746,37 +7749,37 @@
         <v>20</v>
       </c>
       <c r="DS10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT10">
         <v>3</v>
       </c>
       <c r="DU10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV10">
         <v>3</v>
       </c>
       <c r="DW10" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX10">
+        <v>1</v>
+      </c>
+      <c r="DY10">
+        <v>1</v>
+      </c>
+      <c r="DZ10">
+        <v>3000</v>
+      </c>
+      <c r="EA10" t="s">
+        <v>283</v>
+      </c>
+      <c r="EB10" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC10" t="s">
         <v>280</v>
-      </c>
-      <c r="DX10">
-        <v>1</v>
-      </c>
-      <c r="DY10">
-        <v>1</v>
-      </c>
-      <c r="DZ10">
-        <v>1800</v>
-      </c>
-      <c r="EA10" t="s">
-        <v>282</v>
-      </c>
-      <c r="EB10" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC10" t="s">
-        <v>279</v>
       </c>
       <c r="ED10">
         <v>1</v>
@@ -7791,10 +7794,10 @@
         <v>9</v>
       </c>
       <c r="EH10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ10">
         <v>3</v>
@@ -7806,7 +7809,7 @@
         <v>20</v>
       </c>
       <c r="EM10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN10">
         <v>3</v>
@@ -7818,19 +7821,19 @@
         <v>20</v>
       </c>
       <c r="EQ10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER10">
         <v>3</v>
       </c>
       <c r="ES10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET10">
         <v>3</v>
       </c>
       <c r="EU10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV10">
         <v>0</v>
@@ -7839,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="FA10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB10">
         <v>1</v>
@@ -7854,10 +7857,10 @@
         <v>9</v>
       </c>
       <c r="FF10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH10">
         <v>3</v>
@@ -7869,7 +7872,7 @@
         <v>20</v>
       </c>
       <c r="FK10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL10">
         <v>3</v>
@@ -7881,19 +7884,19 @@
         <v>20</v>
       </c>
       <c r="FO10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP10">
         <v>3</v>
       </c>
       <c r="FQ10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR10">
         <v>3</v>
       </c>
       <c r="FS10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT10">
         <v>0</v>
@@ -7902,28 +7905,28 @@
         <v>0</v>
       </c>
       <c r="FX10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY10">
         <v>1</v>
       </c>
       <c r="FZ10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="GA10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="GB10">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="GC10">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GD10">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="GE10">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="GF10">
         <v>0.9</v>
@@ -7937,35 +7940,8 @@
       <c r="GI10" t="b">
         <v>0</v>
       </c>
-      <c r="GJ10" t="s">
-        <v>292</v>
-      </c>
-      <c r="GK10">
-        <v>50000</v>
-      </c>
-      <c r="GL10">
-        <v>7200</v>
-      </c>
-      <c r="GM10">
-        <v>7200</v>
-      </c>
-      <c r="GN10">
-        <v>50000</v>
-      </c>
-      <c r="GO10">
-        <v>0.9</v>
-      </c>
-      <c r="GP10">
-        <v>0.8</v>
-      </c>
-      <c r="GQ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="GR10" t="b">
-        <v>0</v>
-      </c>
       <c r="GS10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT10">
         <v>0.05</v>
@@ -7980,13 +7956,13 @@
         <v>8.5</v>
       </c>
       <c r="GX10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA10">
         <v>1</v>
@@ -7995,10 +7971,10 @@
         <v>1</v>
       </c>
       <c r="HC10">
-        <v>2300</v>
+        <v>5500</v>
       </c>
       <c r="HD10">
-        <v>2300</v>
+        <v>5500</v>
       </c>
       <c r="HE10">
         <v>0.95</v>
@@ -8013,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="HI10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ10">
         <v>0</v>
@@ -8022,49 +7998,49 @@
         <v>0</v>
       </c>
       <c r="HP10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS10">
         <v>86400</v>
       </c>
       <c r="HT10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU10">
         <v>86400</v>
       </c>
       <c r="HV10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW10">
         <v>1</v>
       </c>
       <c r="HX10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY10">
         <v>1</v>
       </c>
       <c r="HZ10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE10">
         <v>86400</v>
@@ -8108,13 +8084,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>4402000</v>
+        <v>2687000</v>
       </c>
       <c r="O11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -8129,10 +8105,10 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="W11">
         <v>3</v>
@@ -8144,7 +8120,7 @@
         <v>20</v>
       </c>
       <c r="Z11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA11">
         <v>3</v>
@@ -8156,13 +8132,13 @@
         <v>20</v>
       </c>
       <c r="AD11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AE11">
         <v>3</v>
       </c>
       <c r="AF11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG11">
         <v>3</v>
@@ -8177,7 +8153,7 @@
         <v>6</v>
       </c>
       <c r="AM11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -8192,10 +8168,10 @@
         <v>9</v>
       </c>
       <c r="AR11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AT11">
         <v>3</v>
@@ -8207,7 +8183,7 @@
         <v>20</v>
       </c>
       <c r="AW11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AX11">
         <v>3</v>
@@ -8219,13 +8195,13 @@
         <v>20</v>
       </c>
       <c r="BA11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BB11">
         <v>3</v>
       </c>
       <c r="BC11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="BD11">
         <v>3</v>
@@ -8240,13 +8216,13 @@
         <v>19500000</v>
       </c>
       <c r="BH11" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="BI11">
         <v>55</v>
       </c>
       <c r="BJ11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BK11">
         <v>1</v>
@@ -8261,10 +8237,10 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="BP11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BQ11">
         <v>3</v>
@@ -8276,7 +8252,7 @@
         <v>20</v>
       </c>
       <c r="BT11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BU11">
         <v>3</v>
@@ -8288,13 +8264,13 @@
         <v>20</v>
       </c>
       <c r="BX11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BY11">
         <v>3</v>
       </c>
       <c r="BZ11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CA11">
         <v>1</v>
@@ -8306,13 +8282,13 @@
         <v>2400000</v>
       </c>
       <c r="CD11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="CE11">
         <v>55</v>
       </c>
       <c r="CF11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="CG11">
         <v>1</v>
@@ -8327,10 +8303,10 @@
         <v>9</v>
       </c>
       <c r="CK11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="CL11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CM11">
         <v>3</v>
@@ -8342,7 +8318,7 @@
         <v>20</v>
       </c>
       <c r="CP11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CQ11">
         <v>3</v>
@@ -8354,13 +8330,13 @@
         <v>20</v>
       </c>
       <c r="CT11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="CU11">
         <v>3</v>
       </c>
       <c r="CV11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="CW11">
         <v>3</v>
@@ -8372,10 +8348,10 @@
         <v>1</v>
       </c>
       <c r="CZ11">
-        <v>5400</v>
+        <v>3500</v>
       </c>
       <c r="DA11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="DB11">
         <v>-20</v>
@@ -8387,7 +8363,7 @@
         <v>1</v>
       </c>
       <c r="DE11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="DF11">
         <v>1</v>
@@ -8402,10 +8378,10 @@
         <v>9</v>
       </c>
       <c r="DJ11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="DK11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DL11">
         <v>3</v>
@@ -8417,7 +8393,7 @@
         <v>20</v>
       </c>
       <c r="DO11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DP11">
         <v>3</v>
@@ -8429,37 +8405,37 @@
         <v>20</v>
       </c>
       <c r="DS11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="DT11">
         <v>3</v>
       </c>
       <c r="DU11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="DV11">
         <v>3</v>
       </c>
       <c r="DW11" t="s">
+        <v>281</v>
+      </c>
+      <c r="DX11">
+        <v>1</v>
+      </c>
+      <c r="DY11">
+        <v>1</v>
+      </c>
+      <c r="DZ11">
+        <v>2100</v>
+      </c>
+      <c r="EA11" t="s">
+        <v>282</v>
+      </c>
+      <c r="EB11" t="b">
+        <v>1</v>
+      </c>
+      <c r="EC11" t="s">
         <v>280</v>
-      </c>
-      <c r="DX11">
-        <v>1</v>
-      </c>
-      <c r="DY11">
-        <v>1</v>
-      </c>
-      <c r="DZ11">
-        <v>2700</v>
-      </c>
-      <c r="EA11" t="s">
-        <v>284</v>
-      </c>
-      <c r="EB11" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC11" t="s">
-        <v>279</v>
       </c>
       <c r="ED11">
         <v>1</v>
@@ -8474,10 +8450,10 @@
         <v>9</v>
       </c>
       <c r="EH11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="EI11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EJ11">
         <v>3</v>
@@ -8489,7 +8465,7 @@
         <v>20</v>
       </c>
       <c r="EM11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="EN11">
         <v>3</v>
@@ -8501,19 +8477,19 @@
         <v>20</v>
       </c>
       <c r="EQ11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="ER11">
         <v>3</v>
       </c>
       <c r="ES11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="ET11">
         <v>3</v>
       </c>
       <c r="EU11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="EV11">
         <v>0</v>
@@ -8522,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="FA11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="FB11">
         <v>1</v>
@@ -8537,10 +8513,10 @@
         <v>9</v>
       </c>
       <c r="FF11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="FG11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FH11">
         <v>3</v>
@@ -8552,7 +8528,7 @@
         <v>20</v>
       </c>
       <c r="FK11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FL11">
         <v>3</v>
@@ -8564,19 +8540,19 @@
         <v>20</v>
       </c>
       <c r="FO11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="FP11">
         <v>3</v>
       </c>
       <c r="FQ11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="FR11">
         <v>3</v>
       </c>
       <c r="FS11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FT11">
         <v>0</v>
@@ -8585,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="FX11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="FY11">
         <v>1</v>
@@ -8621,7 +8597,7 @@
         <v>0</v>
       </c>
       <c r="GS11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="GT11">
         <v>0.05</v>
@@ -8636,13 +8612,13 @@
         <v>8.5</v>
       </c>
       <c r="GX11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="GY11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="GZ11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HA11">
         <v>1</v>
@@ -8651,10 +8627,10 @@
         <v>1</v>
       </c>
       <c r="HC11">
-        <v>4400</v>
+        <v>2700</v>
       </c>
       <c r="HD11">
-        <v>4400</v>
+        <v>2700</v>
       </c>
       <c r="HE11">
         <v>0.95</v>
@@ -8669,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="HI11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HJ11">
         <v>0</v>
@@ -8678,49 +8654,49 @@
         <v>0</v>
       </c>
       <c r="HP11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="HQ11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HR11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="HS11">
         <v>86400</v>
       </c>
       <c r="HT11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="HU11">
         <v>86400</v>
       </c>
       <c r="HV11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HW11">
         <v>1</v>
       </c>
       <c r="HX11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="HY11">
         <v>1</v>
       </c>
       <c r="HZ11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IA11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IB11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="IC11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="ID11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="IE11">
         <v>86400</v>
@@ -8756,13 +8732,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -8984,7 +8960,7 @@
         <v>76</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="CE1" s="1" t="s">
         <v>77</v>
@@ -9440,10 +9416,10 @@
         <v>227</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="IB1" s="1" t="s">
         <v>232</v>
@@ -9494,7 +9470,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9896,22 +9872,22 @@
         <v>199</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="EN1" s="1" t="s">
         <v>204</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="EP1" s="1" t="s">
         <v>206</v>
@@ -9959,10 +9935,10 @@
         <v>227</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="FG1" s="1" t="s">
         <v>232</v>
@@ -10013,7 +9989,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -10505,10 +10481,10 @@
         <v>227</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="FP1" s="1" t="s">
         <v>232</v>
@@ -10826,10 +10802,10 @@
         <v>227</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="CS1" s="1" t="s">
         <v>232</v>
@@ -10910,58 +10886,58 @@
         <v>215</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>223</v>
@@ -10979,10 +10955,10 @@
         <v>227</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>232</v>

--- a/02 - config/example_single_market/agents.xlsx
+++ b/02 - config/example_single_market/agents.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="309">
   <si>
     <t>general/agent_id</t>
   </si>
@@ -741,55 +741,52 @@
     <t>ems/fcasts/update</t>
   </si>
   <si>
-    <t>DYGMezeMcdBzkRE</t>
-  </si>
-  <si>
-    <t>3yZ7HjucQPUWBLV</t>
-  </si>
-  <si>
-    <t>CwxAe4i0Qo05kEy</t>
-  </si>
-  <si>
-    <t>bMNKj4RQXe3Bn5G</t>
-  </si>
-  <si>
-    <t>UfgFBNdFQIwN3aX</t>
-  </si>
-  <si>
-    <t>pzymfr2mXV8WUcn</t>
-  </si>
-  <si>
-    <t>QosLqiKD0U1v0co</t>
-  </si>
-  <si>
-    <t>A6Z44wNxl4MrGZO</t>
-  </si>
-  <si>
-    <t>W2oNQbQSIvLfC4j</t>
-  </si>
-  <si>
-    <t>OQxohNNX3xGnxLk</t>
-  </si>
-  <si>
-    <t>hh_3648_0.csv</t>
+    <t>6amLPGSnTedGjou</t>
+  </si>
+  <si>
+    <t>gQ7Sq3ucg78n4e2</t>
+  </si>
+  <si>
+    <t>0O9n4HIGxRrV58t</t>
+  </si>
+  <si>
+    <t>khzFYYWbb9gU6bQ</t>
+  </si>
+  <si>
+    <t>42KvQZD9ht2Hf7I</t>
+  </si>
+  <si>
+    <t>KO0lC3dN9zUuBwS</t>
+  </si>
+  <si>
+    <t>W16FZ8BxcyuuvrL</t>
+  </si>
+  <si>
+    <t>9l37kMNMXWcA0Nm</t>
+  </si>
+  <si>
+    <t>JHwCQsEwLJG3EbF</t>
+  </si>
+  <si>
+    <t>wi68hZKelP3cqgt</t>
+  </si>
+  <si>
+    <t>hh_5527_0.csv</t>
   </si>
   <si>
     <t>hh_4402_0.csv</t>
   </si>
   <si>
+    <t>hh_2959_0.csv</t>
+  </si>
+  <si>
+    <t>hh_3296_0.csv</t>
+  </si>
+  <si>
     <t>hh_3125_0.csv</t>
   </si>
   <si>
-    <t>hh_2012_3.csv</t>
-  </si>
-  <si>
-    <t>hh_5527_0.csv</t>
-  </si>
-  <si>
-    <t>hh_4536_0.csv</t>
-  </si>
-  <si>
-    <t>hh_3863_0.csv</t>
+    <t>hh_3564_0.csv</t>
   </si>
   <si>
     <t>hh_2687_0.csv</t>
@@ -810,51 +807,9 @@
     <t>rfr</t>
   </si>
   <si>
-    <t>heat_3648_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_1_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_3125_0.csv</t>
-  </si>
-  <si>
-    <t>heat_2012_3.csv</t>
-  </si>
-  <si>
-    <t>heat_5527_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_3863_0.csv</t>
-  </si>
-  <si>
-    <t>heat_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>heat_2687_0.csv</t>
-  </si>
-  <si>
     <t>naive</t>
   </si>
   <si>
-    <t>dhw_gen_0_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_5_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_6_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_4_pu.csv</t>
-  </si>
-  <si>
-    <t>dhw_gen_2_pu.csv</t>
-  </si>
-  <si>
     <t>average</t>
   </si>
   <si>
@@ -867,43 +822,22 @@
     <t>green_local</t>
   </si>
   <si>
-    <t>wind_Siemens_SWT-3.6-130_3600000_130.json</t>
-  </si>
-  <si>
-    <t>wind_Senvion-REpower_3.2M122_3200000_122.json</t>
-  </si>
-  <si>
-    <t>wind_Enercon_E-53-800_800000_53.json</t>
-  </si>
-  <si>
-    <t>wind_Nordex_MM92_3300000_131.json</t>
-  </si>
-  <si>
-    <t>wind_Vestas_V117-3.3-MW_3300000_117.json</t>
-  </si>
-  <si>
     <t>local</t>
   </si>
   <si>
-    <t>ev_fulltime_45.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_49.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_47.csv</t>
-  </si>
-  <si>
-    <t>ev_freetime_1.csv</t>
+    <t>ev_fulltime_43.csv</t>
+  </si>
+  <si>
+    <t>ev_freetime_3.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_88.csv</t>
+  </si>
+  <si>
+    <t>ev_parttime_89.csv</t>
   </si>
   <si>
     <t>ev_fulltime_48.csv</t>
-  </si>
-  <si>
-    <t>ev_fulltime_46.csv</t>
-  </si>
-  <si>
-    <t>ev_parttime_89.csv</t>
   </si>
   <si>
     <t>min_soc</t>
@@ -2102,10 +2036,10 @@
         <v>240</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -2114,7 +2048,7 @@
         <v>2.6</v>
       </c>
       <c r="J2">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -2126,13 +2060,13 @@
         <v>1</v>
       </c>
       <c r="N2">
-        <v>3648000</v>
+        <v>5527000</v>
       </c>
       <c r="O2" t="s">
         <v>250</v>
       </c>
       <c r="P2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q2">
         <v>1</v>
@@ -2147,40 +2081,40 @@
         <v>9</v>
       </c>
       <c r="U2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V2" t="s">
+        <v>259</v>
+      </c>
+      <c r="W2">
+        <v>3</v>
+      </c>
+      <c r="X2">
+        <v>20</v>
+      </c>
+      <c r="Y2">
+        <v>20</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>20</v>
+      </c>
+      <c r="AC2">
+        <v>20</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE2">
+        <v>3</v>
+      </c>
+      <c r="AF2" t="s">
         <v>260</v>
-      </c>
-      <c r="W2">
-        <v>3</v>
-      </c>
-      <c r="X2">
-        <v>20</v>
-      </c>
-      <c r="Y2">
-        <v>20</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA2">
-        <v>3</v>
-      </c>
-      <c r="AB2">
-        <v>20</v>
-      </c>
-      <c r="AC2">
-        <v>20</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE2">
-        <v>3</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>261</v>
       </c>
       <c r="AG2">
         <v>3</v>
@@ -2195,7 +2129,7 @@
         <v>6</v>
       </c>
       <c r="AM2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN2">
         <v>1</v>
@@ -2210,61 +2144,52 @@
         <v>9</v>
       </c>
       <c r="AR2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT2">
+        <v>3</v>
+      </c>
+      <c r="AU2">
+        <v>20</v>
+      </c>
+      <c r="AV2">
+        <v>20</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX2">
+        <v>3</v>
+      </c>
+      <c r="AY2">
+        <v>20</v>
+      </c>
+      <c r="AZ2">
+        <v>20</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB2">
+        <v>3</v>
+      </c>
+      <c r="BC2" t="s">
         <v>260</v>
       </c>
-      <c r="AT2">
-        <v>3</v>
-      </c>
-      <c r="AU2">
-        <v>20</v>
-      </c>
-      <c r="AV2">
-        <v>20</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX2">
-        <v>3</v>
-      </c>
-      <c r="AY2">
-        <v>20</v>
-      </c>
-      <c r="AZ2">
-        <v>20</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB2">
-        <v>3</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>261</v>
-      </c>
       <c r="BD2">
         <v>3</v>
       </c>
       <c r="BE2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>1</v>
-      </c>
-      <c r="BG2">
-        <v>5500000</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>263</v>
-      </c>
-      <c r="BI2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK2">
         <v>1</v>
@@ -2279,58 +2204,49 @@
         <v>9</v>
       </c>
       <c r="BO2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ2">
+        <v>3</v>
+      </c>
+      <c r="BR2">
+        <v>20</v>
+      </c>
+      <c r="BS2">
+        <v>20</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU2">
+        <v>3</v>
+      </c>
+      <c r="BV2">
+        <v>20</v>
+      </c>
+      <c r="BW2">
+        <v>20</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY2">
+        <v>3</v>
+      </c>
+      <c r="BZ2" t="s">
         <v>260</v>
       </c>
-      <c r="BQ2">
-        <v>3</v>
-      </c>
-      <c r="BR2">
-        <v>20</v>
-      </c>
-      <c r="BS2">
-        <v>20</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU2">
-        <v>3</v>
-      </c>
-      <c r="BV2">
-        <v>20</v>
-      </c>
-      <c r="BW2">
-        <v>20</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY2">
-        <v>3</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>261</v>
-      </c>
       <c r="CA2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB2">
-        <v>1</v>
-      </c>
-      <c r="CC2">
-        <v>1800000</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>273</v>
-      </c>
-      <c r="CE2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG2">
         <v>1</v>
@@ -2345,67 +2261,52 @@
         <v>9</v>
       </c>
       <c r="CK2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL2" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM2">
+        <v>3</v>
+      </c>
+      <c r="CN2">
+        <v>20</v>
+      </c>
+      <c r="CO2">
+        <v>20</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ2">
+        <v>3</v>
+      </c>
+      <c r="CR2">
+        <v>20</v>
+      </c>
+      <c r="CS2">
+        <v>20</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU2">
+        <v>3</v>
+      </c>
+      <c r="CV2" t="s">
         <v>260</v>
       </c>
-      <c r="CM2">
-        <v>3</v>
-      </c>
-      <c r="CN2">
-        <v>20</v>
-      </c>
-      <c r="CO2">
-        <v>20</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ2">
-        <v>3</v>
-      </c>
-      <c r="CR2">
-        <v>20</v>
-      </c>
-      <c r="CS2">
-        <v>20</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU2">
-        <v>3</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>261</v>
-      </c>
       <c r="CW2">
         <v>3</v>
       </c>
       <c r="CX2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY2">
-        <v>1</v>
-      </c>
-      <c r="CZ2">
-        <v>6100</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>279</v>
-      </c>
-      <c r="DB2">
-        <v>-20</v>
-      </c>
-      <c r="DC2">
-        <v>50</v>
-      </c>
-      <c r="DD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF2">
         <v>1</v>
@@ -2420,64 +2321,55 @@
         <v>9</v>
       </c>
       <c r="DJ2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL2">
+        <v>3</v>
+      </c>
+      <c r="DM2">
+        <v>20</v>
+      </c>
+      <c r="DN2">
+        <v>20</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP2">
+        <v>3</v>
+      </c>
+      <c r="DQ2">
+        <v>20</v>
+      </c>
+      <c r="DR2">
+        <v>20</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT2">
+        <v>3</v>
+      </c>
+      <c r="DU2" t="s">
         <v>260</v>
       </c>
-      <c r="DL2">
-        <v>3</v>
-      </c>
-      <c r="DM2">
-        <v>20</v>
-      </c>
-      <c r="DN2">
-        <v>20</v>
-      </c>
-      <c r="DO2" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP2">
-        <v>3</v>
-      </c>
-      <c r="DQ2">
-        <v>20</v>
-      </c>
-      <c r="DR2">
-        <v>20</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT2">
-        <v>3</v>
-      </c>
-      <c r="DU2" t="s">
-        <v>261</v>
-      </c>
       <c r="DV2">
         <v>3</v>
       </c>
       <c r="DW2" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY2">
-        <v>1</v>
-      </c>
-      <c r="DZ2">
-        <v>2600</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>282</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED2">
         <v>1</v>
@@ -2492,46 +2384,46 @@
         <v>9</v>
       </c>
       <c r="EH2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI2" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ2">
+        <v>3</v>
+      </c>
+      <c r="EK2">
+        <v>20</v>
+      </c>
+      <c r="EL2">
+        <v>20</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN2">
+        <v>3</v>
+      </c>
+      <c r="EO2">
+        <v>20</v>
+      </c>
+      <c r="EP2">
+        <v>20</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER2">
+        <v>3</v>
+      </c>
+      <c r="ES2" t="s">
         <v>260</v>
       </c>
-      <c r="EJ2">
-        <v>3</v>
-      </c>
-      <c r="EK2">
-        <v>20</v>
-      </c>
-      <c r="EL2">
-        <v>20</v>
-      </c>
-      <c r="EM2" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN2">
-        <v>3</v>
-      </c>
-      <c r="EO2">
-        <v>20</v>
-      </c>
-      <c r="EP2">
-        <v>20</v>
-      </c>
-      <c r="EQ2" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER2">
-        <v>3</v>
-      </c>
-      <c r="ES2" t="s">
-        <v>261</v>
-      </c>
       <c r="ET2">
         <v>3</v>
       </c>
       <c r="EU2" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV2">
         <v>0</v>
@@ -2540,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="FA2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB2">
         <v>1</v>
@@ -2555,46 +2447,46 @@
         <v>9</v>
       </c>
       <c r="FF2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG2" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH2">
+        <v>3</v>
+      </c>
+      <c r="FI2">
+        <v>20</v>
+      </c>
+      <c r="FJ2">
+        <v>20</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL2">
+        <v>3</v>
+      </c>
+      <c r="FM2">
+        <v>20</v>
+      </c>
+      <c r="FN2">
+        <v>20</v>
+      </c>
+      <c r="FO2" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP2">
+        <v>3</v>
+      </c>
+      <c r="FQ2" t="s">
         <v>260</v>
       </c>
-      <c r="FH2">
-        <v>3</v>
-      </c>
-      <c r="FI2">
-        <v>20</v>
-      </c>
-      <c r="FJ2">
-        <v>20</v>
-      </c>
-      <c r="FK2" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL2">
-        <v>3</v>
-      </c>
-      <c r="FM2">
-        <v>20</v>
-      </c>
-      <c r="FN2">
-        <v>20</v>
-      </c>
-      <c r="FO2" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP2">
-        <v>3</v>
-      </c>
-      <c r="FQ2" t="s">
-        <v>261</v>
-      </c>
       <c r="FR2">
         <v>3</v>
       </c>
       <c r="FS2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT2">
         <v>0</v>
@@ -2603,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="FX2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY2">
         <v>1</v>
@@ -2612,7 +2504,7 @@
         <v>2</v>
       </c>
       <c r="GA2" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="GB2">
         <v>50000</v>
@@ -2639,19 +2531,19 @@
         <v>0</v>
       </c>
       <c r="GJ2" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="GK2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="GL2">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GM2">
-        <v>7200</v>
+        <v>22000</v>
       </c>
       <c r="GN2">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="GO2">
         <v>0.9</v>
@@ -2666,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="GS2" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT2">
         <v>0.05</v>
@@ -2681,40 +2573,22 @@
         <v>8.5</v>
       </c>
       <c r="GX2" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY2" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HB2">
-        <v>1</v>
-      </c>
-      <c r="HC2">
-        <v>3600</v>
-      </c>
-      <c r="HD2">
-        <v>3600</v>
-      </c>
-      <c r="HE2">
-        <v>0.95</v>
-      </c>
-      <c r="HF2">
-        <v>0.1</v>
-      </c>
-      <c r="HG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH2" t="b">
         <v>0</v>
       </c>
       <c r="HI2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ2">
         <v>0</v>
@@ -2723,49 +2597,49 @@
         <v>0</v>
       </c>
       <c r="HP2" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ2" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR2" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS2">
         <v>86400</v>
       </c>
       <c r="HT2" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU2">
         <v>86400</v>
       </c>
       <c r="HV2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW2">
         <v>1</v>
       </c>
       <c r="HX2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY2">
         <v>1</v>
       </c>
       <c r="HZ2" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID2" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE2">
         <v>86400</v>
@@ -2785,10 +2659,10 @@
         <v>241</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2797,7 +2671,7 @@
         <v>2.6</v>
       </c>
       <c r="J3">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2815,7 +2689,7 @@
         <v>251</v>
       </c>
       <c r="P3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -2830,40 +2704,40 @@
         <v>9</v>
       </c>
       <c r="U3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V3" t="s">
+        <v>259</v>
+      </c>
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3">
+        <v>20</v>
+      </c>
+      <c r="Y3">
+        <v>20</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
+        <v>20</v>
+      </c>
+      <c r="AC3">
+        <v>20</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE3">
+        <v>3</v>
+      </c>
+      <c r="AF3" t="s">
         <v>260</v>
-      </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3">
-        <v>20</v>
-      </c>
-      <c r="Y3">
-        <v>20</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA3">
-        <v>3</v>
-      </c>
-      <c r="AB3">
-        <v>20</v>
-      </c>
-      <c r="AC3">
-        <v>20</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE3">
-        <v>3</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>261</v>
       </c>
       <c r="AG3">
         <v>3</v>
@@ -2878,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="AM3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN3">
         <v>1</v>
@@ -2893,61 +2767,52 @@
         <v>9</v>
       </c>
       <c r="AR3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT3">
+        <v>3</v>
+      </c>
+      <c r="AU3">
+        <v>20</v>
+      </c>
+      <c r="AV3">
+        <v>20</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX3">
+        <v>3</v>
+      </c>
+      <c r="AY3">
+        <v>20</v>
+      </c>
+      <c r="AZ3">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB3">
+        <v>3</v>
+      </c>
+      <c r="BC3" t="s">
         <v>260</v>
       </c>
-      <c r="AT3">
-        <v>3</v>
-      </c>
-      <c r="AU3">
-        <v>20</v>
-      </c>
-      <c r="AV3">
-        <v>20</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX3">
-        <v>3</v>
-      </c>
-      <c r="AY3">
-        <v>20</v>
-      </c>
-      <c r="AZ3">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB3">
-        <v>3</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>261</v>
-      </c>
       <c r="BD3">
         <v>3</v>
       </c>
       <c r="BE3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>1</v>
-      </c>
-      <c r="BG3">
-        <v>19500000</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>264</v>
-      </c>
-      <c r="BI3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK3">
         <v>1</v>
@@ -2962,58 +2827,49 @@
         <v>9</v>
       </c>
       <c r="BO3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP3" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ3">
+        <v>3</v>
+      </c>
+      <c r="BR3">
+        <v>20</v>
+      </c>
+      <c r="BS3">
+        <v>20</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU3">
+        <v>3</v>
+      </c>
+      <c r="BV3">
+        <v>20</v>
+      </c>
+      <c r="BW3">
+        <v>20</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY3">
+        <v>3</v>
+      </c>
+      <c r="BZ3" t="s">
         <v>260</v>
       </c>
-      <c r="BQ3">
-        <v>3</v>
-      </c>
-      <c r="BR3">
-        <v>20</v>
-      </c>
-      <c r="BS3">
-        <v>20</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU3">
-        <v>3</v>
-      </c>
-      <c r="BV3">
-        <v>20</v>
-      </c>
-      <c r="BW3">
-        <v>20</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY3">
-        <v>3</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>261</v>
-      </c>
       <c r="CA3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB3">
-        <v>1</v>
-      </c>
-      <c r="CC3">
-        <v>3200000</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>274</v>
-      </c>
-      <c r="CE3">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG3">
         <v>1</v>
@@ -3028,67 +2884,52 @@
         <v>9</v>
       </c>
       <c r="CK3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL3" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM3">
+        <v>3</v>
+      </c>
+      <c r="CN3">
+        <v>20</v>
+      </c>
+      <c r="CO3">
+        <v>20</v>
+      </c>
+      <c r="CP3" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ3">
+        <v>3</v>
+      </c>
+      <c r="CR3">
+        <v>20</v>
+      </c>
+      <c r="CS3">
+        <v>20</v>
+      </c>
+      <c r="CT3" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU3">
+        <v>3</v>
+      </c>
+      <c r="CV3" t="s">
         <v>260</v>
       </c>
-      <c r="CM3">
-        <v>3</v>
-      </c>
-      <c r="CN3">
-        <v>20</v>
-      </c>
-      <c r="CO3">
-        <v>20</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ3">
-        <v>3</v>
-      </c>
-      <c r="CR3">
-        <v>20</v>
-      </c>
-      <c r="CS3">
-        <v>20</v>
-      </c>
-      <c r="CT3" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU3">
-        <v>3</v>
-      </c>
-      <c r="CV3" t="s">
-        <v>261</v>
-      </c>
       <c r="CW3">
         <v>3</v>
       </c>
       <c r="CX3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY3">
-        <v>1</v>
-      </c>
-      <c r="CZ3">
-        <v>5600</v>
-      </c>
-      <c r="DA3" t="s">
-        <v>279</v>
-      </c>
-      <c r="DB3">
-        <v>0</v>
-      </c>
-      <c r="DC3">
-        <v>40</v>
-      </c>
-      <c r="DD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF3">
         <v>1</v>
@@ -3103,64 +2944,55 @@
         <v>9</v>
       </c>
       <c r="DJ3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK3" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL3">
+        <v>3</v>
+      </c>
+      <c r="DM3">
+        <v>20</v>
+      </c>
+      <c r="DN3">
+        <v>20</v>
+      </c>
+      <c r="DO3" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP3">
+        <v>3</v>
+      </c>
+      <c r="DQ3">
+        <v>20</v>
+      </c>
+      <c r="DR3">
+        <v>20</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT3">
+        <v>3</v>
+      </c>
+      <c r="DU3" t="s">
         <v>260</v>
       </c>
-      <c r="DL3">
-        <v>3</v>
-      </c>
-      <c r="DM3">
-        <v>20</v>
-      </c>
-      <c r="DN3">
-        <v>20</v>
-      </c>
-      <c r="DO3" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP3">
-        <v>3</v>
-      </c>
-      <c r="DQ3">
-        <v>20</v>
-      </c>
-      <c r="DR3">
-        <v>20</v>
-      </c>
-      <c r="DS3" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT3">
-        <v>3</v>
-      </c>
-      <c r="DU3" t="s">
-        <v>261</v>
-      </c>
       <c r="DV3">
         <v>3</v>
       </c>
       <c r="DW3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY3">
-        <v>1</v>
-      </c>
-      <c r="DZ3">
-        <v>2900</v>
-      </c>
-      <c r="EA3" t="s">
-        <v>283</v>
-      </c>
-      <c r="EB3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED3">
         <v>1</v>
@@ -3175,46 +3007,46 @@
         <v>9</v>
       </c>
       <c r="EH3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI3" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ3">
+        <v>3</v>
+      </c>
+      <c r="EK3">
+        <v>20</v>
+      </c>
+      <c r="EL3">
+        <v>20</v>
+      </c>
+      <c r="EM3" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN3">
+        <v>3</v>
+      </c>
+      <c r="EO3">
+        <v>20</v>
+      </c>
+      <c r="EP3">
+        <v>20</v>
+      </c>
+      <c r="EQ3" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER3">
+        <v>3</v>
+      </c>
+      <c r="ES3" t="s">
         <v>260</v>
       </c>
-      <c r="EJ3">
-        <v>3</v>
-      </c>
-      <c r="EK3">
-        <v>20</v>
-      </c>
-      <c r="EL3">
-        <v>20</v>
-      </c>
-      <c r="EM3" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN3">
-        <v>3</v>
-      </c>
-      <c r="EO3">
-        <v>20</v>
-      </c>
-      <c r="EP3">
-        <v>20</v>
-      </c>
-      <c r="EQ3" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER3">
-        <v>3</v>
-      </c>
-      <c r="ES3" t="s">
-        <v>261</v>
-      </c>
       <c r="ET3">
         <v>3</v>
       </c>
       <c r="EU3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV3">
         <v>0</v>
@@ -3223,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="FA3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB3">
         <v>1</v>
@@ -3238,46 +3070,46 @@
         <v>9</v>
       </c>
       <c r="FF3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG3" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH3">
+        <v>3</v>
+      </c>
+      <c r="FI3">
+        <v>20</v>
+      </c>
+      <c r="FJ3">
+        <v>20</v>
+      </c>
+      <c r="FK3" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL3">
+        <v>3</v>
+      </c>
+      <c r="FM3">
+        <v>20</v>
+      </c>
+      <c r="FN3">
+        <v>20</v>
+      </c>
+      <c r="FO3" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP3">
+        <v>3</v>
+      </c>
+      <c r="FQ3" t="s">
         <v>260</v>
       </c>
-      <c r="FH3">
-        <v>3</v>
-      </c>
-      <c r="FI3">
-        <v>20</v>
-      </c>
-      <c r="FJ3">
-        <v>20</v>
-      </c>
-      <c r="FK3" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL3">
-        <v>3</v>
-      </c>
-      <c r="FM3">
-        <v>20</v>
-      </c>
-      <c r="FN3">
-        <v>20</v>
-      </c>
-      <c r="FO3" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP3">
-        <v>3</v>
-      </c>
-      <c r="FQ3" t="s">
-        <v>261</v>
-      </c>
       <c r="FR3">
         <v>3</v>
       </c>
       <c r="FS3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT3">
         <v>0</v>
@@ -3286,16 +3118,16 @@
         <v>0</v>
       </c>
       <c r="FX3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY3">
         <v>1</v>
       </c>
       <c r="FZ3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="GA3" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="GB3">
         <v>75000</v>
@@ -3321,35 +3153,8 @@
       <c r="GI3" t="b">
         <v>0</v>
       </c>
-      <c r="GJ3" t="s">
-        <v>292</v>
-      </c>
-      <c r="GK3">
-        <v>75000</v>
-      </c>
-      <c r="GL3">
-        <v>7200</v>
-      </c>
-      <c r="GM3">
-        <v>11000</v>
-      </c>
-      <c r="GN3">
-        <v>100000</v>
-      </c>
-      <c r="GO3">
-        <v>0.9</v>
-      </c>
-      <c r="GP3">
-        <v>0.8</v>
-      </c>
-      <c r="GQ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="GR3" t="b">
-        <v>0</v>
-      </c>
       <c r="GS3" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT3">
         <v>0.05</v>
@@ -3364,40 +3169,22 @@
         <v>8.5</v>
       </c>
       <c r="GX3" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY3" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HB3">
-        <v>1</v>
-      </c>
-      <c r="HC3">
-        <v>4400</v>
-      </c>
-      <c r="HD3">
-        <v>4400</v>
-      </c>
-      <c r="HE3">
-        <v>0.95</v>
-      </c>
-      <c r="HF3">
-        <v>0.1</v>
-      </c>
-      <c r="HG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH3" t="b">
         <v>0</v>
       </c>
       <c r="HI3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ3">
         <v>0</v>
@@ -3406,49 +3193,49 @@
         <v>0</v>
       </c>
       <c r="HP3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ3" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR3" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS3">
         <v>86400</v>
       </c>
       <c r="HT3" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU3">
         <v>86400</v>
       </c>
       <c r="HV3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW3">
         <v>1</v>
       </c>
       <c r="HX3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY3">
         <v>1</v>
       </c>
       <c r="HZ3" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC3" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID3" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE3">
         <v>86400</v>
@@ -3492,13 +3279,13 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>3125000</v>
+        <v>5527000</v>
       </c>
       <c r="O4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="P4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -3513,40 +3300,40 @@
         <v>9</v>
       </c>
       <c r="U4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V4" t="s">
+        <v>259</v>
+      </c>
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4">
+        <v>20</v>
+      </c>
+      <c r="Y4">
+        <v>20</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <v>20</v>
+      </c>
+      <c r="AC4">
+        <v>20</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE4">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="s">
         <v>260</v>
-      </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-      <c r="X4">
-        <v>20</v>
-      </c>
-      <c r="Y4">
-        <v>20</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA4">
-        <v>3</v>
-      </c>
-      <c r="AB4">
-        <v>20</v>
-      </c>
-      <c r="AC4">
-        <v>20</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE4">
-        <v>3</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>261</v>
       </c>
       <c r="AG4">
         <v>3</v>
@@ -3561,7 +3348,7 @@
         <v>6</v>
       </c>
       <c r="AM4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN4">
         <v>1</v>
@@ -3576,61 +3363,52 @@
         <v>9</v>
       </c>
       <c r="AR4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS4" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT4">
+        <v>3</v>
+      </c>
+      <c r="AU4">
+        <v>20</v>
+      </c>
+      <c r="AV4">
+        <v>20</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX4">
+        <v>3</v>
+      </c>
+      <c r="AY4">
+        <v>20</v>
+      </c>
+      <c r="AZ4">
+        <v>20</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB4">
+        <v>3</v>
+      </c>
+      <c r="BC4" t="s">
         <v>260</v>
       </c>
-      <c r="AT4">
-        <v>3</v>
-      </c>
-      <c r="AU4">
-        <v>20</v>
-      </c>
-      <c r="AV4">
-        <v>20</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX4">
-        <v>3</v>
-      </c>
-      <c r="AY4">
-        <v>20</v>
-      </c>
-      <c r="AZ4">
-        <v>20</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB4">
-        <v>3</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>261</v>
-      </c>
       <c r="BD4">
         <v>3</v>
       </c>
       <c r="BE4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>1</v>
-      </c>
-      <c r="BG4">
-        <v>5500000</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>265</v>
-      </c>
-      <c r="BI4">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK4">
         <v>1</v>
@@ -3645,58 +3423,49 @@
         <v>9</v>
       </c>
       <c r="BO4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP4" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ4">
+        <v>3</v>
+      </c>
+      <c r="BR4">
+        <v>20</v>
+      </c>
+      <c r="BS4">
+        <v>20</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU4">
+        <v>3</v>
+      </c>
+      <c r="BV4">
+        <v>20</v>
+      </c>
+      <c r="BW4">
+        <v>20</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY4">
+        <v>3</v>
+      </c>
+      <c r="BZ4" t="s">
         <v>260</v>
       </c>
-      <c r="BQ4">
-        <v>3</v>
-      </c>
-      <c r="BR4">
-        <v>20</v>
-      </c>
-      <c r="BS4">
-        <v>20</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU4">
-        <v>3</v>
-      </c>
-      <c r="BV4">
-        <v>20</v>
-      </c>
-      <c r="BW4">
-        <v>20</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY4">
-        <v>3</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>261</v>
-      </c>
       <c r="CA4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB4">
-        <v>1</v>
-      </c>
-      <c r="CC4">
-        <v>2400000</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>274</v>
-      </c>
-      <c r="CE4">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG4">
         <v>1</v>
@@ -3711,41 +3480,41 @@
         <v>9</v>
       </c>
       <c r="CK4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL4" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM4">
+        <v>3</v>
+      </c>
+      <c r="CN4">
+        <v>20</v>
+      </c>
+      <c r="CO4">
+        <v>20</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ4">
+        <v>3</v>
+      </c>
+      <c r="CR4">
+        <v>20</v>
+      </c>
+      <c r="CS4">
+        <v>20</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU4">
+        <v>3</v>
+      </c>
+      <c r="CV4" t="s">
         <v>260</v>
       </c>
-      <c r="CM4">
-        <v>3</v>
-      </c>
-      <c r="CN4">
-        <v>20</v>
-      </c>
-      <c r="CO4">
-        <v>20</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ4">
-        <v>3</v>
-      </c>
-      <c r="CR4">
-        <v>20</v>
-      </c>
-      <c r="CS4">
-        <v>20</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU4">
-        <v>3</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>261</v>
-      </c>
       <c r="CW4">
         <v>3</v>
       </c>
@@ -3756,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="CZ4">
-        <v>5600</v>
+        <v>6700</v>
       </c>
       <c r="DA4" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB4">
         <v>-20</v>
@@ -3771,7 +3540,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF4">
         <v>1</v>
@@ -3786,64 +3555,55 @@
         <v>9</v>
       </c>
       <c r="DJ4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK4" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL4">
+        <v>3</v>
+      </c>
+      <c r="DM4">
+        <v>20</v>
+      </c>
+      <c r="DN4">
+        <v>20</v>
+      </c>
+      <c r="DO4" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP4">
+        <v>3</v>
+      </c>
+      <c r="DQ4">
+        <v>20</v>
+      </c>
+      <c r="DR4">
+        <v>20</v>
+      </c>
+      <c r="DS4" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT4">
+        <v>3</v>
+      </c>
+      <c r="DU4" t="s">
         <v>260</v>
       </c>
-      <c r="DL4">
-        <v>3</v>
-      </c>
-      <c r="DM4">
-        <v>20</v>
-      </c>
-      <c r="DN4">
-        <v>20</v>
-      </c>
-      <c r="DO4" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP4">
-        <v>3</v>
-      </c>
-      <c r="DQ4">
-        <v>20</v>
-      </c>
-      <c r="DR4">
-        <v>20</v>
-      </c>
-      <c r="DS4" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT4">
-        <v>3</v>
-      </c>
-      <c r="DU4" t="s">
-        <v>261</v>
-      </c>
       <c r="DV4">
         <v>3</v>
       </c>
       <c r="DW4" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY4">
-        <v>1</v>
-      </c>
-      <c r="DZ4">
-        <v>2500</v>
-      </c>
-      <c r="EA4" t="s">
-        <v>283</v>
-      </c>
-      <c r="EB4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED4">
         <v>1</v>
@@ -3858,46 +3618,46 @@
         <v>9</v>
       </c>
       <c r="EH4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI4" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ4">
+        <v>3</v>
+      </c>
+      <c r="EK4">
+        <v>20</v>
+      </c>
+      <c r="EL4">
+        <v>20</v>
+      </c>
+      <c r="EM4" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN4">
+        <v>3</v>
+      </c>
+      <c r="EO4">
+        <v>20</v>
+      </c>
+      <c r="EP4">
+        <v>20</v>
+      </c>
+      <c r="EQ4" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER4">
+        <v>3</v>
+      </c>
+      <c r="ES4" t="s">
         <v>260</v>
       </c>
-      <c r="EJ4">
-        <v>3</v>
-      </c>
-      <c r="EK4">
-        <v>20</v>
-      </c>
-      <c r="EL4">
-        <v>20</v>
-      </c>
-      <c r="EM4" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN4">
-        <v>3</v>
-      </c>
-      <c r="EO4">
-        <v>20</v>
-      </c>
-      <c r="EP4">
-        <v>20</v>
-      </c>
-      <c r="EQ4" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER4">
-        <v>3</v>
-      </c>
-      <c r="ES4" t="s">
-        <v>261</v>
-      </c>
       <c r="ET4">
         <v>3</v>
       </c>
       <c r="EU4" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV4">
         <v>0</v>
@@ -3906,7 +3666,7 @@
         <v>0</v>
       </c>
       <c r="FA4" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB4">
         <v>1</v>
@@ -3921,46 +3681,46 @@
         <v>9</v>
       </c>
       <c r="FF4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG4" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH4">
+        <v>3</v>
+      </c>
+      <c r="FI4">
+        <v>20</v>
+      </c>
+      <c r="FJ4">
+        <v>20</v>
+      </c>
+      <c r="FK4" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL4">
+        <v>3</v>
+      </c>
+      <c r="FM4">
+        <v>20</v>
+      </c>
+      <c r="FN4">
+        <v>20</v>
+      </c>
+      <c r="FO4" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP4">
+        <v>3</v>
+      </c>
+      <c r="FQ4" t="s">
         <v>260</v>
       </c>
-      <c r="FH4">
-        <v>3</v>
-      </c>
-      <c r="FI4">
-        <v>20</v>
-      </c>
-      <c r="FJ4">
-        <v>20</v>
-      </c>
-      <c r="FK4" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL4">
-        <v>3</v>
-      </c>
-      <c r="FM4">
-        <v>20</v>
-      </c>
-      <c r="FN4">
-        <v>20</v>
-      </c>
-      <c r="FO4" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP4">
-        <v>3</v>
-      </c>
-      <c r="FQ4" t="s">
-        <v>261</v>
-      </c>
       <c r="FR4">
         <v>3</v>
       </c>
       <c r="FS4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT4">
         <v>0</v>
@@ -3969,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="FX4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY4">
         <v>1</v>
@@ -3978,19 +3738,19 @@
         <v>1</v>
       </c>
       <c r="GA4" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="GB4">
-        <v>75000</v>
+        <v>100000</v>
       </c>
       <c r="GC4">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="GD4">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="GE4">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="GF4">
         <v>0.9</v>
@@ -4005,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="GS4" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT4">
         <v>0.05</v>
@@ -4020,13 +3780,13 @@
         <v>8.5</v>
       </c>
       <c r="GX4" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY4" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA4">
         <v>1</v>
@@ -4035,10 +3795,10 @@
         <v>1</v>
       </c>
       <c r="HC4">
-        <v>3100</v>
+        <v>5500</v>
       </c>
       <c r="HD4">
-        <v>3100</v>
+        <v>5500</v>
       </c>
       <c r="HE4">
         <v>0.95</v>
@@ -4053,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="HI4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ4">
         <v>0</v>
@@ -4062,49 +3822,49 @@
         <v>0</v>
       </c>
       <c r="HP4" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ4" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR4" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS4">
         <v>86400</v>
       </c>
       <c r="HT4" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU4">
         <v>86400</v>
       </c>
       <c r="HV4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW4">
         <v>1</v>
       </c>
       <c r="HX4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY4">
         <v>1</v>
       </c>
       <c r="HZ4" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC4" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID4" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE4">
         <v>86400</v>
@@ -4148,13 +3908,13 @@
         <v>1</v>
       </c>
       <c r="N5">
-        <v>2012000</v>
+        <v>4402000</v>
       </c>
       <c r="O5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -4169,40 +3929,40 @@
         <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V5" t="s">
+        <v>259</v>
+      </c>
+      <c r="W5">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>20</v>
+      </c>
+      <c r="Y5">
+        <v>20</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
+      <c r="AB5">
+        <v>20</v>
+      </c>
+      <c r="AC5">
+        <v>20</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE5">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="s">
         <v>260</v>
-      </c>
-      <c r="W5">
-        <v>3</v>
-      </c>
-      <c r="X5">
-        <v>20</v>
-      </c>
-      <c r="Y5">
-        <v>20</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>20</v>
-      </c>
-      <c r="AC5">
-        <v>20</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE5">
-        <v>3</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>261</v>
       </c>
       <c r="AG5">
         <v>3</v>
@@ -4217,7 +3977,7 @@
         <v>6</v>
       </c>
       <c r="AM5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -4232,61 +3992,52 @@
         <v>9</v>
       </c>
       <c r="AR5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS5" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT5">
+        <v>3</v>
+      </c>
+      <c r="AU5">
+        <v>20</v>
+      </c>
+      <c r="AV5">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX5">
+        <v>3</v>
+      </c>
+      <c r="AY5">
+        <v>20</v>
+      </c>
+      <c r="AZ5">
+        <v>20</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB5">
+        <v>3</v>
+      </c>
+      <c r="BC5" t="s">
         <v>260</v>
       </c>
-      <c r="AT5">
-        <v>3</v>
-      </c>
-      <c r="AU5">
-        <v>20</v>
-      </c>
-      <c r="AV5">
-        <v>20</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX5">
-        <v>3</v>
-      </c>
-      <c r="AY5">
-        <v>20</v>
-      </c>
-      <c r="AZ5">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB5">
-        <v>3</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>261</v>
-      </c>
       <c r="BD5">
         <v>3</v>
       </c>
       <c r="BE5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>1</v>
-      </c>
-      <c r="BG5">
-        <v>5500000</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>266</v>
-      </c>
-      <c r="BI5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK5">
         <v>1</v>
@@ -4301,58 +4052,49 @@
         <v>9</v>
       </c>
       <c r="BO5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP5" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ5">
+        <v>3</v>
+      </c>
+      <c r="BR5">
+        <v>20</v>
+      </c>
+      <c r="BS5">
+        <v>20</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU5">
+        <v>3</v>
+      </c>
+      <c r="BV5">
+        <v>20</v>
+      </c>
+      <c r="BW5">
+        <v>20</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY5">
+        <v>3</v>
+      </c>
+      <c r="BZ5" t="s">
         <v>260</v>
       </c>
-      <c r="BQ5">
-        <v>3</v>
-      </c>
-      <c r="BR5">
-        <v>20</v>
-      </c>
-      <c r="BS5">
-        <v>20</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU5">
-        <v>3</v>
-      </c>
-      <c r="BV5">
-        <v>20</v>
-      </c>
-      <c r="BW5">
-        <v>20</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY5">
-        <v>3</v>
-      </c>
-      <c r="BZ5" t="s">
-        <v>261</v>
-      </c>
       <c r="CA5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB5">
-        <v>1</v>
-      </c>
-      <c r="CC5">
-        <v>2100000</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>275</v>
-      </c>
-      <c r="CE5">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF5" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG5">
         <v>1</v>
@@ -4367,41 +4109,41 @@
         <v>9</v>
       </c>
       <c r="CK5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL5" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM5">
+        <v>3</v>
+      </c>
+      <c r="CN5">
+        <v>20</v>
+      </c>
+      <c r="CO5">
+        <v>20</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ5">
+        <v>3</v>
+      </c>
+      <c r="CR5">
+        <v>20</v>
+      </c>
+      <c r="CS5">
+        <v>20</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU5">
+        <v>3</v>
+      </c>
+      <c r="CV5" t="s">
         <v>260</v>
       </c>
-      <c r="CM5">
-        <v>3</v>
-      </c>
-      <c r="CN5">
-        <v>20</v>
-      </c>
-      <c r="CO5">
-        <v>20</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ5">
-        <v>3</v>
-      </c>
-      <c r="CR5">
-        <v>20</v>
-      </c>
-      <c r="CS5">
-        <v>20</v>
-      </c>
-      <c r="CT5" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU5">
-        <v>3</v>
-      </c>
-      <c r="CV5" t="s">
-        <v>261</v>
-      </c>
       <c r="CW5">
         <v>3</v>
       </c>
@@ -4412,10 +4154,10 @@
         <v>1</v>
       </c>
       <c r="CZ5">
-        <v>3100</v>
+        <v>5700</v>
       </c>
       <c r="DA5" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB5">
         <v>0</v>
@@ -4427,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="DE5" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF5">
         <v>1</v>
@@ -4442,64 +4184,55 @@
         <v>9</v>
       </c>
       <c r="DJ5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK5" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL5">
+        <v>3</v>
+      </c>
+      <c r="DM5">
+        <v>20</v>
+      </c>
+      <c r="DN5">
+        <v>20</v>
+      </c>
+      <c r="DO5" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP5">
+        <v>3</v>
+      </c>
+      <c r="DQ5">
+        <v>20</v>
+      </c>
+      <c r="DR5">
+        <v>20</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT5">
+        <v>3</v>
+      </c>
+      <c r="DU5" t="s">
         <v>260</v>
       </c>
-      <c r="DL5">
-        <v>3</v>
-      </c>
-      <c r="DM5">
-        <v>20</v>
-      </c>
-      <c r="DN5">
-        <v>20</v>
-      </c>
-      <c r="DO5" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP5">
-        <v>3</v>
-      </c>
-      <c r="DQ5">
-        <v>20</v>
-      </c>
-      <c r="DR5">
-        <v>20</v>
-      </c>
-      <c r="DS5" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT5">
-        <v>3</v>
-      </c>
-      <c r="DU5" t="s">
-        <v>261</v>
-      </c>
       <c r="DV5">
         <v>3</v>
       </c>
       <c r="DW5" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY5">
-        <v>1</v>
-      </c>
-      <c r="DZ5">
-        <v>1200</v>
-      </c>
-      <c r="EA5" t="s">
-        <v>284</v>
-      </c>
-      <c r="EB5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED5">
         <v>1</v>
@@ -4514,46 +4247,46 @@
         <v>9</v>
       </c>
       <c r="EH5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI5" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ5">
+        <v>3</v>
+      </c>
+      <c r="EK5">
+        <v>20</v>
+      </c>
+      <c r="EL5">
+        <v>20</v>
+      </c>
+      <c r="EM5" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN5">
+        <v>3</v>
+      </c>
+      <c r="EO5">
+        <v>20</v>
+      </c>
+      <c r="EP5">
+        <v>20</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER5">
+        <v>3</v>
+      </c>
+      <c r="ES5" t="s">
         <v>260</v>
       </c>
-      <c r="EJ5">
-        <v>3</v>
-      </c>
-      <c r="EK5">
-        <v>20</v>
-      </c>
-      <c r="EL5">
-        <v>20</v>
-      </c>
-      <c r="EM5" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN5">
-        <v>3</v>
-      </c>
-      <c r="EO5">
-        <v>20</v>
-      </c>
-      <c r="EP5">
-        <v>20</v>
-      </c>
-      <c r="EQ5" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER5">
-        <v>3</v>
-      </c>
-      <c r="ES5" t="s">
-        <v>261</v>
-      </c>
       <c r="ET5">
         <v>3</v>
       </c>
       <c r="EU5" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV5">
         <v>0</v>
@@ -4562,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="FA5" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB5">
         <v>1</v>
@@ -4577,46 +4310,46 @@
         <v>9</v>
       </c>
       <c r="FF5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG5" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH5">
+        <v>3</v>
+      </c>
+      <c r="FI5">
+        <v>20</v>
+      </c>
+      <c r="FJ5">
+        <v>20</v>
+      </c>
+      <c r="FK5" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL5">
+        <v>3</v>
+      </c>
+      <c r="FM5">
+        <v>20</v>
+      </c>
+      <c r="FN5">
+        <v>20</v>
+      </c>
+      <c r="FO5" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP5">
+        <v>3</v>
+      </c>
+      <c r="FQ5" t="s">
         <v>260</v>
       </c>
-      <c r="FH5">
-        <v>3</v>
-      </c>
-      <c r="FI5">
-        <v>20</v>
-      </c>
-      <c r="FJ5">
-        <v>20</v>
-      </c>
-      <c r="FK5" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL5">
-        <v>3</v>
-      </c>
-      <c r="FM5">
-        <v>20</v>
-      </c>
-      <c r="FN5">
-        <v>20</v>
-      </c>
-      <c r="FO5" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP5">
-        <v>3</v>
-      </c>
-      <c r="FQ5" t="s">
-        <v>261</v>
-      </c>
       <c r="FR5">
         <v>3</v>
       </c>
       <c r="FS5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT5">
         <v>0</v>
@@ -4625,43 +4358,16 @@
         <v>0</v>
       </c>
       <c r="FX5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FZ5">
-        <v>1</v>
-      </c>
-      <c r="GA5" t="s">
-        <v>290</v>
-      </c>
-      <c r="GB5">
-        <v>50000</v>
-      </c>
-      <c r="GC5">
-        <v>7200</v>
-      </c>
-      <c r="GD5">
-        <v>7200</v>
-      </c>
-      <c r="GE5">
-        <v>50000</v>
-      </c>
-      <c r="GF5">
-        <v>0.9</v>
-      </c>
-      <c r="GG5">
-        <v>0.8</v>
-      </c>
-      <c r="GH5" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI5" t="b">
         <v>0</v>
       </c>
       <c r="GS5" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT5">
         <v>0.05</v>
@@ -4676,40 +4382,22 @@
         <v>8.5</v>
       </c>
       <c r="GX5" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY5" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HB5">
-        <v>1</v>
-      </c>
-      <c r="HC5">
-        <v>2000</v>
-      </c>
-      <c r="HD5">
-        <v>2000</v>
-      </c>
-      <c r="HE5">
-        <v>0.95</v>
-      </c>
-      <c r="HF5">
-        <v>0.1</v>
-      </c>
-      <c r="HG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH5" t="b">
         <v>0</v>
       </c>
       <c r="HI5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ5">
         <v>0</v>
@@ -4718,49 +4406,49 @@
         <v>0</v>
       </c>
       <c r="HP5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ5" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR5" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS5">
         <v>86400</v>
       </c>
       <c r="HT5" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU5">
         <v>86400</v>
       </c>
       <c r="HV5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW5">
         <v>1</v>
       </c>
       <c r="HX5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY5">
         <v>1</v>
       </c>
       <c r="HZ5" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID5" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE5">
         <v>86400</v>
@@ -4804,13 +4492,13 @@
         <v>1</v>
       </c>
       <c r="N6">
-        <v>5527000</v>
+        <v>2959000</v>
       </c>
       <c r="O6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4825,40 +4513,40 @@
         <v>9</v>
       </c>
       <c r="U6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V6" t="s">
+        <v>259</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>20</v>
+      </c>
+      <c r="Y6">
+        <v>20</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>20</v>
+      </c>
+      <c r="AC6">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE6">
+        <v>3</v>
+      </c>
+      <c r="AF6" t="s">
         <v>260</v>
-      </c>
-      <c r="W6">
-        <v>3</v>
-      </c>
-      <c r="X6">
-        <v>20</v>
-      </c>
-      <c r="Y6">
-        <v>20</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA6">
-        <v>3</v>
-      </c>
-      <c r="AB6">
-        <v>20</v>
-      </c>
-      <c r="AC6">
-        <v>20</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE6">
-        <v>3</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>261</v>
       </c>
       <c r="AG6">
         <v>3</v>
@@ -4873,7 +4561,7 @@
         <v>6</v>
       </c>
       <c r="AM6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN6">
         <v>1</v>
@@ -4888,61 +4576,52 @@
         <v>9</v>
       </c>
       <c r="AR6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT6">
+        <v>3</v>
+      </c>
+      <c r="AU6">
+        <v>20</v>
+      </c>
+      <c r="AV6">
+        <v>20</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX6">
+        <v>3</v>
+      </c>
+      <c r="AY6">
+        <v>20</v>
+      </c>
+      <c r="AZ6">
+        <v>20</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB6">
+        <v>3</v>
+      </c>
+      <c r="BC6" t="s">
         <v>260</v>
       </c>
-      <c r="AT6">
-        <v>3</v>
-      </c>
-      <c r="AU6">
-        <v>20</v>
-      </c>
-      <c r="AV6">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX6">
-        <v>3</v>
-      </c>
-      <c r="AY6">
-        <v>20</v>
-      </c>
-      <c r="AZ6">
-        <v>20</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB6">
-        <v>3</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>261</v>
-      </c>
       <c r="BD6">
         <v>3</v>
       </c>
       <c r="BE6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF6">
-        <v>1</v>
-      </c>
-      <c r="BG6">
-        <v>5500000</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>267</v>
-      </c>
-      <c r="BI6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK6">
         <v>1</v>
@@ -4957,58 +4636,49 @@
         <v>9</v>
       </c>
       <c r="BO6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP6" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ6">
+        <v>3</v>
+      </c>
+      <c r="BR6">
+        <v>20</v>
+      </c>
+      <c r="BS6">
+        <v>20</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU6">
+        <v>3</v>
+      </c>
+      <c r="BV6">
+        <v>20</v>
+      </c>
+      <c r="BW6">
+        <v>20</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY6">
+        <v>3</v>
+      </c>
+      <c r="BZ6" t="s">
         <v>260</v>
       </c>
-      <c r="BQ6">
-        <v>3</v>
-      </c>
-      <c r="BR6">
-        <v>20</v>
-      </c>
-      <c r="BS6">
-        <v>20</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU6">
-        <v>3</v>
-      </c>
-      <c r="BV6">
-        <v>20</v>
-      </c>
-      <c r="BW6">
-        <v>20</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY6">
-        <v>3</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>261</v>
-      </c>
       <c r="CA6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB6">
-        <v>1</v>
-      </c>
-      <c r="CC6">
-        <v>2100000</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>276</v>
-      </c>
-      <c r="CE6">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF6" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG6">
         <v>1</v>
@@ -5023,41 +4693,41 @@
         <v>9</v>
       </c>
       <c r="CK6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL6" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM6">
+        <v>3</v>
+      </c>
+      <c r="CN6">
+        <v>20</v>
+      </c>
+      <c r="CO6">
+        <v>20</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ6">
+        <v>3</v>
+      </c>
+      <c r="CR6">
+        <v>20</v>
+      </c>
+      <c r="CS6">
+        <v>20</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU6">
+        <v>3</v>
+      </c>
+      <c r="CV6" t="s">
         <v>260</v>
       </c>
-      <c r="CM6">
-        <v>3</v>
-      </c>
-      <c r="CN6">
-        <v>20</v>
-      </c>
-      <c r="CO6">
-        <v>20</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ6">
-        <v>3</v>
-      </c>
-      <c r="CR6">
-        <v>20</v>
-      </c>
-      <c r="CS6">
-        <v>20</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU6">
-        <v>3</v>
-      </c>
-      <c r="CV6" t="s">
-        <v>261</v>
-      </c>
       <c r="CW6">
         <v>3</v>
       </c>
@@ -5068,10 +4738,10 @@
         <v>1</v>
       </c>
       <c r="CZ6">
-        <v>6700</v>
+        <v>4500</v>
       </c>
       <c r="DA6" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB6">
         <v>0</v>
@@ -5083,7 +4753,7 @@
         <v>1</v>
       </c>
       <c r="DE6" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF6">
         <v>1</v>
@@ -5098,64 +4768,55 @@
         <v>9</v>
       </c>
       <c r="DJ6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK6" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL6">
+        <v>3</v>
+      </c>
+      <c r="DM6">
+        <v>20</v>
+      </c>
+      <c r="DN6">
+        <v>20</v>
+      </c>
+      <c r="DO6" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP6">
+        <v>3</v>
+      </c>
+      <c r="DQ6">
+        <v>20</v>
+      </c>
+      <c r="DR6">
+        <v>20</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT6">
+        <v>3</v>
+      </c>
+      <c r="DU6" t="s">
         <v>260</v>
       </c>
-      <c r="DL6">
-        <v>3</v>
-      </c>
-      <c r="DM6">
-        <v>20</v>
-      </c>
-      <c r="DN6">
-        <v>20</v>
-      </c>
-      <c r="DO6" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP6">
-        <v>3</v>
-      </c>
-      <c r="DQ6">
-        <v>20</v>
-      </c>
-      <c r="DR6">
-        <v>20</v>
-      </c>
-      <c r="DS6" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT6">
-        <v>3</v>
-      </c>
-      <c r="DU6" t="s">
-        <v>261</v>
-      </c>
       <c r="DV6">
         <v>3</v>
       </c>
       <c r="DW6" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY6">
-        <v>1</v>
-      </c>
-      <c r="DZ6">
-        <v>3900</v>
-      </c>
-      <c r="EA6" t="s">
-        <v>284</v>
-      </c>
-      <c r="EB6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC6" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED6">
         <v>1</v>
@@ -5170,46 +4831,46 @@
         <v>9</v>
       </c>
       <c r="EH6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI6" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ6">
+        <v>3</v>
+      </c>
+      <c r="EK6">
+        <v>20</v>
+      </c>
+      <c r="EL6">
+        <v>20</v>
+      </c>
+      <c r="EM6" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN6">
+        <v>3</v>
+      </c>
+      <c r="EO6">
+        <v>20</v>
+      </c>
+      <c r="EP6">
+        <v>20</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER6">
+        <v>3</v>
+      </c>
+      <c r="ES6" t="s">
         <v>260</v>
       </c>
-      <c r="EJ6">
-        <v>3</v>
-      </c>
-      <c r="EK6">
-        <v>20</v>
-      </c>
-      <c r="EL6">
-        <v>20</v>
-      </c>
-      <c r="EM6" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN6">
-        <v>3</v>
-      </c>
-      <c r="EO6">
-        <v>20</v>
-      </c>
-      <c r="EP6">
-        <v>20</v>
-      </c>
-      <c r="EQ6" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER6">
-        <v>3</v>
-      </c>
-      <c r="ES6" t="s">
-        <v>261</v>
-      </c>
       <c r="ET6">
         <v>3</v>
       </c>
       <c r="EU6" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV6">
         <v>0</v>
@@ -5218,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="FA6" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB6">
         <v>1</v>
@@ -5233,46 +4894,46 @@
         <v>9</v>
       </c>
       <c r="FF6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG6" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH6">
+        <v>3</v>
+      </c>
+      <c r="FI6">
+        <v>20</v>
+      </c>
+      <c r="FJ6">
+        <v>20</v>
+      </c>
+      <c r="FK6" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL6">
+        <v>3</v>
+      </c>
+      <c r="FM6">
+        <v>20</v>
+      </c>
+      <c r="FN6">
+        <v>20</v>
+      </c>
+      <c r="FO6" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP6">
+        <v>3</v>
+      </c>
+      <c r="FQ6" t="s">
         <v>260</v>
       </c>
-      <c r="FH6">
-        <v>3</v>
-      </c>
-      <c r="FI6">
-        <v>20</v>
-      </c>
-      <c r="FJ6">
-        <v>20</v>
-      </c>
-      <c r="FK6" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL6">
-        <v>3</v>
-      </c>
-      <c r="FM6">
-        <v>20</v>
-      </c>
-      <c r="FN6">
-        <v>20</v>
-      </c>
-      <c r="FO6" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP6">
-        <v>3</v>
-      </c>
-      <c r="FQ6" t="s">
-        <v>261</v>
-      </c>
       <c r="FR6">
         <v>3</v>
       </c>
       <c r="FS6" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT6">
         <v>0</v>
@@ -5281,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="FX6" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY6">
         <v>1</v>
@@ -5290,7 +4951,7 @@
         <v>1</v>
       </c>
       <c r="GA6" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="GB6">
         <v>50000</v>
@@ -5317,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="GS6" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT6">
         <v>0.05</v>
@@ -5332,13 +4993,13 @@
         <v>8.5</v>
       </c>
       <c r="GX6" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY6" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ6" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA6">
         <v>1</v>
@@ -5347,10 +5008,10 @@
         <v>1</v>
       </c>
       <c r="HC6">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="HD6">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="HE6">
         <v>0.95</v>
@@ -5365,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="HI6" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ6">
         <v>0</v>
@@ -5374,49 +5035,49 @@
         <v>0</v>
       </c>
       <c r="HP6" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ6" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR6" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS6">
         <v>86400</v>
       </c>
       <c r="HT6" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU6">
         <v>86400</v>
       </c>
       <c r="HV6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW6">
         <v>1</v>
       </c>
       <c r="HX6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY6">
         <v>1</v>
       </c>
       <c r="HZ6" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID6" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE6">
         <v>86400</v>
@@ -5460,13 +5121,13 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>4536000</v>
+        <v>3296000</v>
       </c>
       <c r="O7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q7">
         <v>1</v>
@@ -5481,40 +5142,40 @@
         <v>9</v>
       </c>
       <c r="U7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V7" t="s">
+        <v>259</v>
+      </c>
+      <c r="W7">
+        <v>3</v>
+      </c>
+      <c r="X7">
+        <v>20</v>
+      </c>
+      <c r="Y7">
+        <v>20</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>20</v>
+      </c>
+      <c r="AC7">
+        <v>20</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE7">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="s">
         <v>260</v>
-      </c>
-      <c r="W7">
-        <v>3</v>
-      </c>
-      <c r="X7">
-        <v>20</v>
-      </c>
-      <c r="Y7">
-        <v>20</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7">
-        <v>20</v>
-      </c>
-      <c r="AC7">
-        <v>20</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE7">
-        <v>3</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>261</v>
       </c>
       <c r="AG7">
         <v>3</v>
@@ -5529,7 +5190,7 @@
         <v>6</v>
       </c>
       <c r="AM7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -5544,61 +5205,52 @@
         <v>9</v>
       </c>
       <c r="AR7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS7" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT7">
+        <v>3</v>
+      </c>
+      <c r="AU7">
+        <v>20</v>
+      </c>
+      <c r="AV7">
+        <v>20</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX7">
+        <v>3</v>
+      </c>
+      <c r="AY7">
+        <v>20</v>
+      </c>
+      <c r="AZ7">
+        <v>20</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB7">
+        <v>3</v>
+      </c>
+      <c r="BC7" t="s">
         <v>260</v>
       </c>
-      <c r="AT7">
-        <v>3</v>
-      </c>
-      <c r="AU7">
-        <v>20</v>
-      </c>
-      <c r="AV7">
-        <v>20</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX7">
-        <v>3</v>
-      </c>
-      <c r="AY7">
-        <v>20</v>
-      </c>
-      <c r="AZ7">
-        <v>20</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB7">
-        <v>3</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>261</v>
-      </c>
       <c r="BD7">
         <v>3</v>
       </c>
       <c r="BE7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>1</v>
-      </c>
-      <c r="BG7">
-        <v>19500000</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>268</v>
-      </c>
-      <c r="BI7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK7">
         <v>1</v>
@@ -5613,58 +5265,49 @@
         <v>9</v>
       </c>
       <c r="BO7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP7" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ7">
+        <v>3</v>
+      </c>
+      <c r="BR7">
+        <v>20</v>
+      </c>
+      <c r="BS7">
+        <v>20</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU7">
+        <v>3</v>
+      </c>
+      <c r="BV7">
+        <v>20</v>
+      </c>
+      <c r="BW7">
+        <v>20</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY7">
+        <v>3</v>
+      </c>
+      <c r="BZ7" t="s">
         <v>260</v>
       </c>
-      <c r="BQ7">
-        <v>3</v>
-      </c>
-      <c r="BR7">
-        <v>20</v>
-      </c>
-      <c r="BS7">
-        <v>20</v>
-      </c>
-      <c r="BT7" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU7">
-        <v>3</v>
-      </c>
-      <c r="BV7">
-        <v>20</v>
-      </c>
-      <c r="BW7">
-        <v>20</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY7">
-        <v>3</v>
-      </c>
-      <c r="BZ7" t="s">
-        <v>261</v>
-      </c>
       <c r="CA7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB7">
-        <v>1</v>
-      </c>
-      <c r="CC7">
-        <v>2400000</v>
-      </c>
-      <c r="CD7" t="s">
-        <v>273</v>
-      </c>
-      <c r="CE7">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG7">
         <v>1</v>
@@ -5679,41 +5322,41 @@
         <v>9</v>
       </c>
       <c r="CK7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL7" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM7">
+        <v>3</v>
+      </c>
+      <c r="CN7">
+        <v>20</v>
+      </c>
+      <c r="CO7">
+        <v>20</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ7">
+        <v>3</v>
+      </c>
+      <c r="CR7">
+        <v>20</v>
+      </c>
+      <c r="CS7">
+        <v>20</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU7">
+        <v>3</v>
+      </c>
+      <c r="CV7" t="s">
         <v>260</v>
       </c>
-      <c r="CM7">
-        <v>3</v>
-      </c>
-      <c r="CN7">
-        <v>20</v>
-      </c>
-      <c r="CO7">
-        <v>20</v>
-      </c>
-      <c r="CP7" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ7">
-        <v>3</v>
-      </c>
-      <c r="CR7">
-        <v>20</v>
-      </c>
-      <c r="CS7">
-        <v>20</v>
-      </c>
-      <c r="CT7" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU7">
-        <v>3</v>
-      </c>
-      <c r="CV7" t="s">
-        <v>261</v>
-      </c>
       <c r="CW7">
         <v>3</v>
       </c>
@@ -5724,10 +5367,10 @@
         <v>1</v>
       </c>
       <c r="CZ7">
-        <v>8100</v>
+        <v>5000</v>
       </c>
       <c r="DA7" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB7">
         <v>0</v>
@@ -5739,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="DE7" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF7">
         <v>1</v>
@@ -5754,64 +5397,55 @@
         <v>9</v>
       </c>
       <c r="DJ7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK7" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL7">
+        <v>3</v>
+      </c>
+      <c r="DM7">
+        <v>20</v>
+      </c>
+      <c r="DN7">
+        <v>20</v>
+      </c>
+      <c r="DO7" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP7">
+        <v>3</v>
+      </c>
+      <c r="DQ7">
+        <v>20</v>
+      </c>
+      <c r="DR7">
+        <v>20</v>
+      </c>
+      <c r="DS7" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT7">
+        <v>3</v>
+      </c>
+      <c r="DU7" t="s">
         <v>260</v>
       </c>
-      <c r="DL7">
-        <v>3</v>
-      </c>
-      <c r="DM7">
-        <v>20</v>
-      </c>
-      <c r="DN7">
-        <v>20</v>
-      </c>
-      <c r="DO7" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP7">
-        <v>3</v>
-      </c>
-      <c r="DQ7">
-        <v>20</v>
-      </c>
-      <c r="DR7">
-        <v>20</v>
-      </c>
-      <c r="DS7" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT7">
-        <v>3</v>
-      </c>
-      <c r="DU7" t="s">
-        <v>261</v>
-      </c>
       <c r="DV7">
         <v>3</v>
       </c>
       <c r="DW7" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY7">
-        <v>1</v>
-      </c>
-      <c r="DZ7">
-        <v>2000</v>
-      </c>
-      <c r="EA7" t="s">
-        <v>285</v>
-      </c>
-      <c r="EB7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC7" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED7">
         <v>1</v>
@@ -5826,46 +5460,46 @@
         <v>9</v>
       </c>
       <c r="EH7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI7" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ7">
+        <v>3</v>
+      </c>
+      <c r="EK7">
+        <v>20</v>
+      </c>
+      <c r="EL7">
+        <v>20</v>
+      </c>
+      <c r="EM7" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN7">
+        <v>3</v>
+      </c>
+      <c r="EO7">
+        <v>20</v>
+      </c>
+      <c r="EP7">
+        <v>20</v>
+      </c>
+      <c r="EQ7" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER7">
+        <v>3</v>
+      </c>
+      <c r="ES7" t="s">
         <v>260</v>
       </c>
-      <c r="EJ7">
-        <v>3</v>
-      </c>
-      <c r="EK7">
-        <v>20</v>
-      </c>
-      <c r="EL7">
-        <v>20</v>
-      </c>
-      <c r="EM7" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN7">
-        <v>3</v>
-      </c>
-      <c r="EO7">
-        <v>20</v>
-      </c>
-      <c r="EP7">
-        <v>20</v>
-      </c>
-      <c r="EQ7" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER7">
-        <v>3</v>
-      </c>
-      <c r="ES7" t="s">
-        <v>261</v>
-      </c>
       <c r="ET7">
         <v>3</v>
       </c>
       <c r="EU7" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV7">
         <v>0</v>
@@ -5874,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="FA7" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB7">
         <v>1</v>
@@ -5889,46 +5523,46 @@
         <v>9</v>
       </c>
       <c r="FF7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG7" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH7">
+        <v>3</v>
+      </c>
+      <c r="FI7">
+        <v>20</v>
+      </c>
+      <c r="FJ7">
+        <v>20</v>
+      </c>
+      <c r="FK7" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL7">
+        <v>3</v>
+      </c>
+      <c r="FM7">
+        <v>20</v>
+      </c>
+      <c r="FN7">
+        <v>20</v>
+      </c>
+      <c r="FO7" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP7">
+        <v>3</v>
+      </c>
+      <c r="FQ7" t="s">
         <v>260</v>
       </c>
-      <c r="FH7">
-        <v>3</v>
-      </c>
-      <c r="FI7">
-        <v>20</v>
-      </c>
-      <c r="FJ7">
-        <v>20</v>
-      </c>
-      <c r="FK7" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL7">
-        <v>3</v>
-      </c>
-      <c r="FM7">
-        <v>20</v>
-      </c>
-      <c r="FN7">
-        <v>20</v>
-      </c>
-      <c r="FO7" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP7">
-        <v>3</v>
-      </c>
-      <c r="FQ7" t="s">
-        <v>261</v>
-      </c>
       <c r="FR7">
         <v>3</v>
       </c>
       <c r="FS7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT7">
         <v>0</v>
@@ -5937,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="FX7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY7">
         <v>1</v>
@@ -5946,19 +5580,19 @@
         <v>1</v>
       </c>
       <c r="GA7" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="GB7">
+        <v>75000</v>
+      </c>
+      <c r="GC7">
+        <v>7200</v>
+      </c>
+      <c r="GD7">
+        <v>11000</v>
+      </c>
+      <c r="GE7">
         <v>100000</v>
-      </c>
-      <c r="GC7">
-        <v>11000</v>
-      </c>
-      <c r="GD7">
-        <v>22000</v>
-      </c>
-      <c r="GE7">
-        <v>200000</v>
       </c>
       <c r="GF7">
         <v>0.9</v>
@@ -5973,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="GS7" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT7">
         <v>0.05</v>
@@ -5988,13 +5622,13 @@
         <v>8.5</v>
       </c>
       <c r="GX7" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY7" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA7">
         <v>1</v>
@@ -6003,10 +5637,10 @@
         <v>1</v>
       </c>
       <c r="HC7">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="HD7">
-        <v>4500</v>
+        <v>3300</v>
       </c>
       <c r="HE7">
         <v>0.95</v>
@@ -6021,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="HI7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ7">
         <v>0</v>
@@ -6030,49 +5664,49 @@
         <v>0</v>
       </c>
       <c r="HP7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ7" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR7" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS7">
         <v>86400</v>
       </c>
       <c r="HT7" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU7">
         <v>86400</v>
       </c>
       <c r="HV7" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW7">
         <v>1</v>
       </c>
       <c r="HX7" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY7">
         <v>1</v>
       </c>
       <c r="HZ7" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA7" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB7" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC7" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID7" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE7">
         <v>86400</v>
@@ -6116,13 +5750,13 @@
         <v>1</v>
       </c>
       <c r="N8">
-        <v>3863000</v>
+        <v>3125000</v>
       </c>
       <c r="O8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -6137,40 +5771,40 @@
         <v>9</v>
       </c>
       <c r="U8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V8" t="s">
+        <v>259</v>
+      </c>
+      <c r="W8">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>20</v>
+      </c>
+      <c r="Y8">
+        <v>20</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
+      <c r="AB8">
+        <v>20</v>
+      </c>
+      <c r="AC8">
+        <v>20</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE8">
+        <v>3</v>
+      </c>
+      <c r="AF8" t="s">
         <v>260</v>
-      </c>
-      <c r="W8">
-        <v>3</v>
-      </c>
-      <c r="X8">
-        <v>20</v>
-      </c>
-      <c r="Y8">
-        <v>20</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA8">
-        <v>3</v>
-      </c>
-      <c r="AB8">
-        <v>20</v>
-      </c>
-      <c r="AC8">
-        <v>20</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE8">
-        <v>3</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>261</v>
       </c>
       <c r="AG8">
         <v>3</v>
@@ -6185,7 +5819,7 @@
         <v>6</v>
       </c>
       <c r="AM8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -6200,61 +5834,52 @@
         <v>9</v>
       </c>
       <c r="AR8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS8" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT8">
+        <v>3</v>
+      </c>
+      <c r="AU8">
+        <v>20</v>
+      </c>
+      <c r="AV8">
+        <v>20</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX8">
+        <v>3</v>
+      </c>
+      <c r="AY8">
+        <v>20</v>
+      </c>
+      <c r="AZ8">
+        <v>20</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB8">
+        <v>3</v>
+      </c>
+      <c r="BC8" t="s">
         <v>260</v>
       </c>
-      <c r="AT8">
-        <v>3</v>
-      </c>
-      <c r="AU8">
-        <v>20</v>
-      </c>
-      <c r="AV8">
-        <v>20</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX8">
-        <v>3</v>
-      </c>
-      <c r="AY8">
-        <v>20</v>
-      </c>
-      <c r="AZ8">
-        <v>20</v>
-      </c>
-      <c r="BA8" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB8">
-        <v>3</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>261</v>
-      </c>
       <c r="BD8">
         <v>3</v>
       </c>
       <c r="BE8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1</v>
-      </c>
-      <c r="BG8">
-        <v>5500000</v>
-      </c>
-      <c r="BH8" t="s">
-        <v>269</v>
-      </c>
-      <c r="BI8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK8">
         <v>1</v>
@@ -6269,58 +5894,49 @@
         <v>9</v>
       </c>
       <c r="BO8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP8" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ8">
+        <v>3</v>
+      </c>
+      <c r="BR8">
+        <v>20</v>
+      </c>
+      <c r="BS8">
+        <v>20</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU8">
+        <v>3</v>
+      </c>
+      <c r="BV8">
+        <v>20</v>
+      </c>
+      <c r="BW8">
+        <v>20</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY8">
+        <v>3</v>
+      </c>
+      <c r="BZ8" t="s">
         <v>260</v>
       </c>
-      <c r="BQ8">
-        <v>3</v>
-      </c>
-      <c r="BR8">
-        <v>20</v>
-      </c>
-      <c r="BS8">
-        <v>20</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU8">
-        <v>3</v>
-      </c>
-      <c r="BV8">
-        <v>20</v>
-      </c>
-      <c r="BW8">
-        <v>20</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY8">
-        <v>3</v>
-      </c>
-      <c r="BZ8" t="s">
-        <v>261</v>
-      </c>
       <c r="CA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB8">
-        <v>1</v>
-      </c>
-      <c r="CC8">
-        <v>2100000</v>
-      </c>
-      <c r="CD8" t="s">
-        <v>277</v>
-      </c>
-      <c r="CE8">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF8" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG8">
         <v>1</v>
@@ -6335,67 +5951,52 @@
         <v>9</v>
       </c>
       <c r="CK8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL8" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM8">
+        <v>3</v>
+      </c>
+      <c r="CN8">
+        <v>20</v>
+      </c>
+      <c r="CO8">
+        <v>20</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ8">
+        <v>3</v>
+      </c>
+      <c r="CR8">
+        <v>20</v>
+      </c>
+      <c r="CS8">
+        <v>20</v>
+      </c>
+      <c r="CT8" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU8">
+        <v>3</v>
+      </c>
+      <c r="CV8" t="s">
         <v>260</v>
       </c>
-      <c r="CM8">
-        <v>3</v>
-      </c>
-      <c r="CN8">
-        <v>20</v>
-      </c>
-      <c r="CO8">
-        <v>20</v>
-      </c>
-      <c r="CP8" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ8">
-        <v>3</v>
-      </c>
-      <c r="CR8">
-        <v>20</v>
-      </c>
-      <c r="CS8">
-        <v>20</v>
-      </c>
-      <c r="CT8" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU8">
-        <v>3</v>
-      </c>
-      <c r="CV8" t="s">
-        <v>261</v>
-      </c>
       <c r="CW8">
         <v>3</v>
       </c>
       <c r="CX8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY8">
-        <v>1</v>
-      </c>
-      <c r="CZ8">
-        <v>5000</v>
-      </c>
-      <c r="DA8" t="s">
-        <v>279</v>
-      </c>
-      <c r="DB8">
-        <v>0</v>
-      </c>
-      <c r="DC8">
-        <v>40</v>
-      </c>
-      <c r="DD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF8">
         <v>1</v>
@@ -6410,64 +6011,55 @@
         <v>9</v>
       </c>
       <c r="DJ8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK8" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL8">
+        <v>3</v>
+      </c>
+      <c r="DM8">
+        <v>20</v>
+      </c>
+      <c r="DN8">
+        <v>20</v>
+      </c>
+      <c r="DO8" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP8">
+        <v>3</v>
+      </c>
+      <c r="DQ8">
+        <v>20</v>
+      </c>
+      <c r="DR8">
+        <v>20</v>
+      </c>
+      <c r="DS8" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT8">
+        <v>3</v>
+      </c>
+      <c r="DU8" t="s">
         <v>260</v>
       </c>
-      <c r="DL8">
-        <v>3</v>
-      </c>
-      <c r="DM8">
-        <v>20</v>
-      </c>
-      <c r="DN8">
-        <v>20</v>
-      </c>
-      <c r="DO8" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP8">
-        <v>3</v>
-      </c>
-      <c r="DQ8">
-        <v>20</v>
-      </c>
-      <c r="DR8">
-        <v>20</v>
-      </c>
-      <c r="DS8" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT8">
-        <v>3</v>
-      </c>
-      <c r="DU8" t="s">
-        <v>261</v>
-      </c>
       <c r="DV8">
         <v>3</v>
       </c>
       <c r="DW8" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY8">
-        <v>1</v>
-      </c>
-      <c r="DZ8">
-        <v>1600</v>
-      </c>
-      <c r="EA8" t="s">
-        <v>286</v>
-      </c>
-      <c r="EB8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED8">
         <v>1</v>
@@ -6482,46 +6074,46 @@
         <v>9</v>
       </c>
       <c r="EH8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI8" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ8">
+        <v>3</v>
+      </c>
+      <c r="EK8">
+        <v>20</v>
+      </c>
+      <c r="EL8">
+        <v>20</v>
+      </c>
+      <c r="EM8" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN8">
+        <v>3</v>
+      </c>
+      <c r="EO8">
+        <v>20</v>
+      </c>
+      <c r="EP8">
+        <v>20</v>
+      </c>
+      <c r="EQ8" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER8">
+        <v>3</v>
+      </c>
+      <c r="ES8" t="s">
         <v>260</v>
       </c>
-      <c r="EJ8">
-        <v>3</v>
-      </c>
-      <c r="EK8">
-        <v>20</v>
-      </c>
-      <c r="EL8">
-        <v>20</v>
-      </c>
-      <c r="EM8" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN8">
-        <v>3</v>
-      </c>
-      <c r="EO8">
-        <v>20</v>
-      </c>
-      <c r="EP8">
-        <v>20</v>
-      </c>
-      <c r="EQ8" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER8">
-        <v>3</v>
-      </c>
-      <c r="ES8" t="s">
-        <v>261</v>
-      </c>
       <c r="ET8">
         <v>3</v>
       </c>
       <c r="EU8" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV8">
         <v>0</v>
@@ -6530,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="FA8" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB8">
         <v>1</v>
@@ -6545,46 +6137,46 @@
         <v>9</v>
       </c>
       <c r="FF8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG8" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH8">
+        <v>3</v>
+      </c>
+      <c r="FI8">
+        <v>20</v>
+      </c>
+      <c r="FJ8">
+        <v>20</v>
+      </c>
+      <c r="FK8" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL8">
+        <v>3</v>
+      </c>
+      <c r="FM8">
+        <v>20</v>
+      </c>
+      <c r="FN8">
+        <v>20</v>
+      </c>
+      <c r="FO8" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP8">
+        <v>3</v>
+      </c>
+      <c r="FQ8" t="s">
         <v>260</v>
       </c>
-      <c r="FH8">
-        <v>3</v>
-      </c>
-      <c r="FI8">
-        <v>20</v>
-      </c>
-      <c r="FJ8">
-        <v>20</v>
-      </c>
-      <c r="FK8" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL8">
-        <v>3</v>
-      </c>
-      <c r="FM8">
-        <v>20</v>
-      </c>
-      <c r="FN8">
-        <v>20</v>
-      </c>
-      <c r="FO8" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP8">
-        <v>3</v>
-      </c>
-      <c r="FQ8" t="s">
-        <v>261</v>
-      </c>
       <c r="FR8">
         <v>3</v>
       </c>
       <c r="FS8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT8">
         <v>0</v>
@@ -6593,43 +6185,16 @@
         <v>0</v>
       </c>
       <c r="FX8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FZ8">
-        <v>1</v>
-      </c>
-      <c r="GA8" t="s">
-        <v>293</v>
-      </c>
-      <c r="GB8">
-        <v>75000</v>
-      </c>
-      <c r="GC8">
-        <v>7200</v>
-      </c>
-      <c r="GD8">
-        <v>11000</v>
-      </c>
-      <c r="GE8">
-        <v>100000</v>
-      </c>
-      <c r="GF8">
-        <v>0.9</v>
-      </c>
-      <c r="GG8">
-        <v>0.8</v>
-      </c>
-      <c r="GH8" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI8" t="b">
         <v>0</v>
       </c>
       <c r="GS8" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT8">
         <v>0.05</v>
@@ -6644,40 +6209,22 @@
         <v>8.5</v>
       </c>
       <c r="GX8" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY8" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HB8">
-        <v>1</v>
-      </c>
-      <c r="HC8">
-        <v>3900</v>
-      </c>
-      <c r="HD8">
-        <v>3900</v>
-      </c>
-      <c r="HE8">
-        <v>0.95</v>
-      </c>
-      <c r="HF8">
-        <v>0.1</v>
-      </c>
-      <c r="HG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="HH8" t="b">
         <v>0</v>
       </c>
       <c r="HI8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ8">
         <v>0</v>
@@ -6686,49 +6233,49 @@
         <v>0</v>
       </c>
       <c r="HP8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ8" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR8" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS8">
         <v>86400</v>
       </c>
       <c r="HT8" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU8">
         <v>86400</v>
       </c>
       <c r="HV8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW8">
         <v>1</v>
       </c>
       <c r="HX8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY8">
         <v>1</v>
       </c>
       <c r="HZ8" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID8" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE8">
         <v>86400</v>
@@ -6772,13 +6319,13 @@
         <v>1</v>
       </c>
       <c r="N9">
-        <v>3863000</v>
+        <v>3564000</v>
       </c>
       <c r="O9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -6793,40 +6340,40 @@
         <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V9" t="s">
+        <v>259</v>
+      </c>
+      <c r="W9">
+        <v>3</v>
+      </c>
+      <c r="X9">
+        <v>20</v>
+      </c>
+      <c r="Y9">
+        <v>20</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AB9">
+        <v>20</v>
+      </c>
+      <c r="AC9">
+        <v>20</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE9">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="s">
         <v>260</v>
-      </c>
-      <c r="W9">
-        <v>3</v>
-      </c>
-      <c r="X9">
-        <v>20</v>
-      </c>
-      <c r="Y9">
-        <v>20</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA9">
-        <v>3</v>
-      </c>
-      <c r="AB9">
-        <v>20</v>
-      </c>
-      <c r="AC9">
-        <v>20</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE9">
-        <v>3</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>261</v>
       </c>
       <c r="AG9">
         <v>3</v>
@@ -6841,7 +6388,7 @@
         <v>6</v>
       </c>
       <c r="AM9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN9">
         <v>1</v>
@@ -6856,61 +6403,52 @@
         <v>9</v>
       </c>
       <c r="AR9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT9">
+        <v>3</v>
+      </c>
+      <c r="AU9">
+        <v>20</v>
+      </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX9">
+        <v>3</v>
+      </c>
+      <c r="AY9">
+        <v>20</v>
+      </c>
+      <c r="AZ9">
+        <v>20</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB9">
+        <v>3</v>
+      </c>
+      <c r="BC9" t="s">
         <v>260</v>
       </c>
-      <c r="AT9">
-        <v>3</v>
-      </c>
-      <c r="AU9">
-        <v>20</v>
-      </c>
-      <c r="AV9">
-        <v>20</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX9">
-        <v>3</v>
-      </c>
-      <c r="AY9">
-        <v>20</v>
-      </c>
-      <c r="AZ9">
-        <v>20</v>
-      </c>
-      <c r="BA9" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB9">
-        <v>3</v>
-      </c>
-      <c r="BC9" t="s">
-        <v>261</v>
-      </c>
       <c r="BD9">
         <v>3</v>
       </c>
       <c r="BE9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1</v>
-      </c>
-      <c r="BG9">
-        <v>19500000</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>270</v>
-      </c>
-      <c r="BI9">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK9">
         <v>1</v>
@@ -6925,58 +6463,49 @@
         <v>9</v>
       </c>
       <c r="BO9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ9">
+        <v>3</v>
+      </c>
+      <c r="BR9">
+        <v>20</v>
+      </c>
+      <c r="BS9">
+        <v>20</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU9">
+        <v>3</v>
+      </c>
+      <c r="BV9">
+        <v>20</v>
+      </c>
+      <c r="BW9">
+        <v>20</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY9">
+        <v>3</v>
+      </c>
+      <c r="BZ9" t="s">
         <v>260</v>
       </c>
-      <c r="BQ9">
-        <v>3</v>
-      </c>
-      <c r="BR9">
-        <v>20</v>
-      </c>
-      <c r="BS9">
-        <v>20</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU9">
-        <v>3</v>
-      </c>
-      <c r="BV9">
-        <v>20</v>
-      </c>
-      <c r="BW9">
-        <v>20</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY9">
-        <v>3</v>
-      </c>
-      <c r="BZ9" t="s">
-        <v>261</v>
-      </c>
       <c r="CA9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB9">
-        <v>1</v>
-      </c>
-      <c r="CC9">
-        <v>3200000</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>275</v>
-      </c>
-      <c r="CE9">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG9">
         <v>1</v>
@@ -6991,41 +6520,41 @@
         <v>9</v>
       </c>
       <c r="CK9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL9" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM9">
+        <v>3</v>
+      </c>
+      <c r="CN9">
+        <v>20</v>
+      </c>
+      <c r="CO9">
+        <v>20</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ9">
+        <v>3</v>
+      </c>
+      <c r="CR9">
+        <v>20</v>
+      </c>
+      <c r="CS9">
+        <v>20</v>
+      </c>
+      <c r="CT9" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU9">
+        <v>3</v>
+      </c>
+      <c r="CV9" t="s">
         <v>260</v>
       </c>
-      <c r="CM9">
-        <v>3</v>
-      </c>
-      <c r="CN9">
-        <v>20</v>
-      </c>
-      <c r="CO9">
-        <v>20</v>
-      </c>
-      <c r="CP9" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ9">
-        <v>3</v>
-      </c>
-      <c r="CR9">
-        <v>20</v>
-      </c>
-      <c r="CS9">
-        <v>20</v>
-      </c>
-      <c r="CT9" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU9">
-        <v>3</v>
-      </c>
-      <c r="CV9" t="s">
-        <v>261</v>
-      </c>
       <c r="CW9">
         <v>3</v>
       </c>
@@ -7036,10 +6565,10 @@
         <v>1</v>
       </c>
       <c r="CZ9">
-        <v>5500</v>
+        <v>6200</v>
       </c>
       <c r="DA9" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB9">
         <v>0</v>
@@ -7051,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="DE9" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF9">
         <v>1</v>
@@ -7066,64 +6595,55 @@
         <v>9</v>
       </c>
       <c r="DJ9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK9" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL9">
+        <v>3</v>
+      </c>
+      <c r="DM9">
+        <v>20</v>
+      </c>
+      <c r="DN9">
+        <v>20</v>
+      </c>
+      <c r="DO9" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP9">
+        <v>3</v>
+      </c>
+      <c r="DQ9">
+        <v>20</v>
+      </c>
+      <c r="DR9">
+        <v>20</v>
+      </c>
+      <c r="DS9" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT9">
+        <v>3</v>
+      </c>
+      <c r="DU9" t="s">
         <v>260</v>
       </c>
-      <c r="DL9">
-        <v>3</v>
-      </c>
-      <c r="DM9">
-        <v>20</v>
-      </c>
-      <c r="DN9">
-        <v>20</v>
-      </c>
-      <c r="DO9" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP9">
-        <v>3</v>
-      </c>
-      <c r="DQ9">
-        <v>20</v>
-      </c>
-      <c r="DR9">
-        <v>20</v>
-      </c>
-      <c r="DS9" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT9">
-        <v>3</v>
-      </c>
-      <c r="DU9" t="s">
-        <v>261</v>
-      </c>
       <c r="DV9">
         <v>3</v>
       </c>
       <c r="DW9" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY9">
-        <v>1</v>
-      </c>
-      <c r="DZ9">
-        <v>3000</v>
-      </c>
-      <c r="EA9" t="s">
-        <v>284</v>
-      </c>
-      <c r="EB9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED9">
         <v>1</v>
@@ -7138,46 +6658,46 @@
         <v>9</v>
       </c>
       <c r="EH9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI9" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ9">
+        <v>3</v>
+      </c>
+      <c r="EK9">
+        <v>20</v>
+      </c>
+      <c r="EL9">
+        <v>20</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN9">
+        <v>3</v>
+      </c>
+      <c r="EO9">
+        <v>20</v>
+      </c>
+      <c r="EP9">
+        <v>20</v>
+      </c>
+      <c r="EQ9" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER9">
+        <v>3</v>
+      </c>
+      <c r="ES9" t="s">
         <v>260</v>
       </c>
-      <c r="EJ9">
-        <v>3</v>
-      </c>
-      <c r="EK9">
-        <v>20</v>
-      </c>
-      <c r="EL9">
-        <v>20</v>
-      </c>
-      <c r="EM9" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN9">
-        <v>3</v>
-      </c>
-      <c r="EO9">
-        <v>20</v>
-      </c>
-      <c r="EP9">
-        <v>20</v>
-      </c>
-      <c r="EQ9" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER9">
-        <v>3</v>
-      </c>
-      <c r="ES9" t="s">
-        <v>261</v>
-      </c>
       <c r="ET9">
         <v>3</v>
       </c>
       <c r="EU9" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV9">
         <v>0</v>
@@ -7186,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="FA9" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB9">
         <v>1</v>
@@ -7201,46 +6721,46 @@
         <v>9</v>
       </c>
       <c r="FF9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG9" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH9">
+        <v>3</v>
+      </c>
+      <c r="FI9">
+        <v>20</v>
+      </c>
+      <c r="FJ9">
+        <v>20</v>
+      </c>
+      <c r="FK9" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL9">
+        <v>3</v>
+      </c>
+      <c r="FM9">
+        <v>20</v>
+      </c>
+      <c r="FN9">
+        <v>20</v>
+      </c>
+      <c r="FO9" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP9">
+        <v>3</v>
+      </c>
+      <c r="FQ9" t="s">
         <v>260</v>
       </c>
-      <c r="FH9">
-        <v>3</v>
-      </c>
-      <c r="FI9">
-        <v>20</v>
-      </c>
-      <c r="FJ9">
-        <v>20</v>
-      </c>
-      <c r="FK9" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL9">
-        <v>3</v>
-      </c>
-      <c r="FM9">
-        <v>20</v>
-      </c>
-      <c r="FN9">
-        <v>20</v>
-      </c>
-      <c r="FO9" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP9">
-        <v>3</v>
-      </c>
-      <c r="FQ9" t="s">
-        <v>261</v>
-      </c>
       <c r="FR9">
         <v>3</v>
       </c>
       <c r="FS9" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT9">
         <v>0</v>
@@ -7249,43 +6769,16 @@
         <v>0</v>
       </c>
       <c r="FX9" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FZ9">
-        <v>1</v>
-      </c>
-      <c r="GA9" t="s">
-        <v>294</v>
-      </c>
-      <c r="GB9">
-        <v>50000</v>
-      </c>
-      <c r="GC9">
-        <v>7200</v>
-      </c>
-      <c r="GD9">
-        <v>7200</v>
-      </c>
-      <c r="GE9">
-        <v>50000</v>
-      </c>
-      <c r="GF9">
-        <v>0.9</v>
-      </c>
-      <c r="GG9">
-        <v>0.8</v>
-      </c>
-      <c r="GH9" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI9" t="b">
         <v>0</v>
       </c>
       <c r="GS9" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT9">
         <v>0.05</v>
@@ -7300,13 +6793,13 @@
         <v>8.5</v>
       </c>
       <c r="GX9" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY9" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ9" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA9">
         <v>1</v>
@@ -7315,10 +6808,10 @@
         <v>1</v>
       </c>
       <c r="HC9">
-        <v>3900</v>
+        <v>3600</v>
       </c>
       <c r="HD9">
-        <v>3900</v>
+        <v>3600</v>
       </c>
       <c r="HE9">
         <v>0.95</v>
@@ -7333,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="HI9" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ9">
         <v>0</v>
@@ -7342,49 +6835,49 @@
         <v>0</v>
       </c>
       <c r="HP9" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ9" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR9" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS9">
         <v>86400</v>
       </c>
       <c r="HT9" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU9">
         <v>86400</v>
       </c>
       <c r="HV9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW9">
         <v>1</v>
       </c>
       <c r="HX9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY9">
         <v>1</v>
       </c>
       <c r="HZ9" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC9" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID9" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE9">
         <v>86400</v>
@@ -7428,13 +6921,13 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>5527000</v>
+        <v>2687000</v>
       </c>
       <c r="O10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -7449,40 +6942,40 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V10" t="s">
+        <v>259</v>
+      </c>
+      <c r="W10">
+        <v>3</v>
+      </c>
+      <c r="X10">
+        <v>20</v>
+      </c>
+      <c r="Y10">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>20</v>
+      </c>
+      <c r="AC10">
+        <v>20</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE10">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="s">
         <v>260</v>
-      </c>
-      <c r="W10">
-        <v>3</v>
-      </c>
-      <c r="X10">
-        <v>20</v>
-      </c>
-      <c r="Y10">
-        <v>20</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA10">
-        <v>3</v>
-      </c>
-      <c r="AB10">
-        <v>20</v>
-      </c>
-      <c r="AC10">
-        <v>20</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE10">
-        <v>3</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>261</v>
       </c>
       <c r="AG10">
         <v>3</v>
@@ -7497,7 +6990,7 @@
         <v>6</v>
       </c>
       <c r="AM10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN10">
         <v>1</v>
@@ -7512,61 +7005,52 @@
         <v>9</v>
       </c>
       <c r="AR10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT10">
+        <v>3</v>
+      </c>
+      <c r="AU10">
+        <v>20</v>
+      </c>
+      <c r="AV10">
+        <v>20</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX10">
+        <v>3</v>
+      </c>
+      <c r="AY10">
+        <v>20</v>
+      </c>
+      <c r="AZ10">
+        <v>20</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB10">
+        <v>3</v>
+      </c>
+      <c r="BC10" t="s">
         <v>260</v>
       </c>
-      <c r="AT10">
-        <v>3</v>
-      </c>
-      <c r="AU10">
-        <v>20</v>
-      </c>
-      <c r="AV10">
-        <v>20</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX10">
-        <v>3</v>
-      </c>
-      <c r="AY10">
-        <v>20</v>
-      </c>
-      <c r="AZ10">
-        <v>20</v>
-      </c>
-      <c r="BA10" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB10">
-        <v>3</v>
-      </c>
-      <c r="BC10" t="s">
-        <v>261</v>
-      </c>
       <c r="BD10">
         <v>3</v>
       </c>
       <c r="BE10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF10">
-        <v>1</v>
-      </c>
-      <c r="BG10">
-        <v>19500000</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>267</v>
-      </c>
-      <c r="BI10">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK10">
         <v>1</v>
@@ -7581,58 +7065,49 @@
         <v>9</v>
       </c>
       <c r="BO10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP10" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ10">
+        <v>3</v>
+      </c>
+      <c r="BR10">
+        <v>20</v>
+      </c>
+      <c r="BS10">
+        <v>20</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU10">
+        <v>3</v>
+      </c>
+      <c r="BV10">
+        <v>20</v>
+      </c>
+      <c r="BW10">
+        <v>20</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY10">
+        <v>3</v>
+      </c>
+      <c r="BZ10" t="s">
         <v>260</v>
       </c>
-      <c r="BQ10">
-        <v>3</v>
-      </c>
-      <c r="BR10">
-        <v>20</v>
-      </c>
-      <c r="BS10">
-        <v>20</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU10">
-        <v>3</v>
-      </c>
-      <c r="BV10">
-        <v>20</v>
-      </c>
-      <c r="BW10">
-        <v>20</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY10">
-        <v>3</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>261</v>
-      </c>
       <c r="CA10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB10">
-        <v>1</v>
-      </c>
-      <c r="CC10">
-        <v>2800000</v>
-      </c>
-      <c r="CD10" t="s">
-        <v>276</v>
-      </c>
-      <c r="CE10">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG10">
         <v>1</v>
@@ -7647,41 +7122,41 @@
         <v>9</v>
       </c>
       <c r="CK10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL10" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM10">
+        <v>3</v>
+      </c>
+      <c r="CN10">
+        <v>20</v>
+      </c>
+      <c r="CO10">
+        <v>20</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ10">
+        <v>3</v>
+      </c>
+      <c r="CR10">
+        <v>20</v>
+      </c>
+      <c r="CS10">
+        <v>20</v>
+      </c>
+      <c r="CT10" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU10">
+        <v>3</v>
+      </c>
+      <c r="CV10" t="s">
         <v>260</v>
       </c>
-      <c r="CM10">
-        <v>3</v>
-      </c>
-      <c r="CN10">
-        <v>20</v>
-      </c>
-      <c r="CO10">
-        <v>20</v>
-      </c>
-      <c r="CP10" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ10">
-        <v>3</v>
-      </c>
-      <c r="CR10">
-        <v>20</v>
-      </c>
-      <c r="CS10">
-        <v>20</v>
-      </c>
-      <c r="CT10" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU10">
-        <v>3</v>
-      </c>
-      <c r="CV10" t="s">
-        <v>261</v>
-      </c>
       <c r="CW10">
         <v>3</v>
       </c>
@@ -7692,22 +7167,22 @@
         <v>1</v>
       </c>
       <c r="CZ10">
-        <v>8600</v>
+        <v>4200</v>
       </c>
       <c r="DA10" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB10">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="DC10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="DD10" t="b">
         <v>1</v>
       </c>
       <c r="DE10" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF10">
         <v>1</v>
@@ -7722,64 +7197,55 @@
         <v>9</v>
       </c>
       <c r="DJ10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK10" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL10">
+        <v>3</v>
+      </c>
+      <c r="DM10">
+        <v>20</v>
+      </c>
+      <c r="DN10">
+        <v>20</v>
+      </c>
+      <c r="DO10" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP10">
+        <v>3</v>
+      </c>
+      <c r="DQ10">
+        <v>20</v>
+      </c>
+      <c r="DR10">
+        <v>20</v>
+      </c>
+      <c r="DS10" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT10">
+        <v>3</v>
+      </c>
+      <c r="DU10" t="s">
         <v>260</v>
       </c>
-      <c r="DL10">
-        <v>3</v>
-      </c>
-      <c r="DM10">
-        <v>20</v>
-      </c>
-      <c r="DN10">
-        <v>20</v>
-      </c>
-      <c r="DO10" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP10">
-        <v>3</v>
-      </c>
-      <c r="DQ10">
-        <v>20</v>
-      </c>
-      <c r="DR10">
-        <v>20</v>
-      </c>
-      <c r="DS10" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT10">
-        <v>3</v>
-      </c>
-      <c r="DU10" t="s">
-        <v>261</v>
-      </c>
       <c r="DV10">
         <v>3</v>
       </c>
       <c r="DW10" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY10">
-        <v>1</v>
-      </c>
-      <c r="DZ10">
-        <v>3000</v>
-      </c>
-      <c r="EA10" t="s">
-        <v>283</v>
-      </c>
-      <c r="EB10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC10" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED10">
         <v>1</v>
@@ -7794,46 +7260,46 @@
         <v>9</v>
       </c>
       <c r="EH10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI10" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ10">
+        <v>3</v>
+      </c>
+      <c r="EK10">
+        <v>20</v>
+      </c>
+      <c r="EL10">
+        <v>20</v>
+      </c>
+      <c r="EM10" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN10">
+        <v>3</v>
+      </c>
+      <c r="EO10">
+        <v>20</v>
+      </c>
+      <c r="EP10">
+        <v>20</v>
+      </c>
+      <c r="EQ10" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER10">
+        <v>3</v>
+      </c>
+      <c r="ES10" t="s">
         <v>260</v>
       </c>
-      <c r="EJ10">
-        <v>3</v>
-      </c>
-      <c r="EK10">
-        <v>20</v>
-      </c>
-      <c r="EL10">
-        <v>20</v>
-      </c>
-      <c r="EM10" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN10">
-        <v>3</v>
-      </c>
-      <c r="EO10">
-        <v>20</v>
-      </c>
-      <c r="EP10">
-        <v>20</v>
-      </c>
-      <c r="EQ10" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER10">
-        <v>3</v>
-      </c>
-      <c r="ES10" t="s">
-        <v>261</v>
-      </c>
       <c r="ET10">
         <v>3</v>
       </c>
       <c r="EU10" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV10">
         <v>0</v>
@@ -7842,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="FA10" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB10">
         <v>1</v>
@@ -7857,46 +7323,46 @@
         <v>9</v>
       </c>
       <c r="FF10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG10" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH10">
+        <v>3</v>
+      </c>
+      <c r="FI10">
+        <v>20</v>
+      </c>
+      <c r="FJ10">
+        <v>20</v>
+      </c>
+      <c r="FK10" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL10">
+        <v>3</v>
+      </c>
+      <c r="FM10">
+        <v>20</v>
+      </c>
+      <c r="FN10">
+        <v>20</v>
+      </c>
+      <c r="FO10" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP10">
+        <v>3</v>
+      </c>
+      <c r="FQ10" t="s">
         <v>260</v>
       </c>
-      <c r="FH10">
-        <v>3</v>
-      </c>
-      <c r="FI10">
-        <v>20</v>
-      </c>
-      <c r="FJ10">
-        <v>20</v>
-      </c>
-      <c r="FK10" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL10">
-        <v>3</v>
-      </c>
-      <c r="FM10">
-        <v>20</v>
-      </c>
-      <c r="FN10">
-        <v>20</v>
-      </c>
-      <c r="FO10" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP10">
-        <v>3</v>
-      </c>
-      <c r="FQ10" t="s">
-        <v>261</v>
-      </c>
       <c r="FR10">
         <v>3</v>
       </c>
       <c r="FS10" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT10">
         <v>0</v>
@@ -7905,43 +7371,16 @@
         <v>0</v>
       </c>
       <c r="FX10" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FZ10">
-        <v>1</v>
-      </c>
-      <c r="GA10" t="s">
-        <v>293</v>
-      </c>
-      <c r="GB10">
-        <v>100000</v>
-      </c>
-      <c r="GC10">
-        <v>11000</v>
-      </c>
-      <c r="GD10">
-        <v>22000</v>
-      </c>
-      <c r="GE10">
-        <v>200000</v>
-      </c>
-      <c r="GF10">
-        <v>0.9</v>
-      </c>
-      <c r="GG10">
-        <v>0.8</v>
-      </c>
-      <c r="GH10" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI10" t="b">
         <v>0</v>
       </c>
       <c r="GS10" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT10">
         <v>0.05</v>
@@ -7956,13 +7395,13 @@
         <v>8.5</v>
       </c>
       <c r="GX10" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY10" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ10" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA10">
         <v>1</v>
@@ -7971,10 +7410,10 @@
         <v>1</v>
       </c>
       <c r="HC10">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="HD10">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="HE10">
         <v>0.95</v>
@@ -7989,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="HI10" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ10">
         <v>0</v>
@@ -7998,49 +7437,49 @@
         <v>0</v>
       </c>
       <c r="HP10" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ10" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR10" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS10">
         <v>86400</v>
       </c>
       <c r="HT10" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU10">
         <v>86400</v>
       </c>
       <c r="HV10" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW10">
         <v>1</v>
       </c>
       <c r="HX10" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY10">
         <v>1</v>
       </c>
       <c r="HZ10" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA10" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB10" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC10" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID10" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE10">
         <v>86400</v>
@@ -8084,13 +7523,13 @@
         <v>1</v>
       </c>
       <c r="N11">
-        <v>2687000</v>
+        <v>3125000</v>
       </c>
       <c r="O11" t="s">
+        <v>254</v>
+      </c>
+      <c r="P11" t="s">
         <v>257</v>
-      </c>
-      <c r="P11" t="s">
-        <v>258</v>
       </c>
       <c r="Q11">
         <v>1</v>
@@ -8105,40 +7544,40 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V11" t="s">
+        <v>259</v>
+      </c>
+      <c r="W11">
+        <v>3</v>
+      </c>
+      <c r="X11">
+        <v>20</v>
+      </c>
+      <c r="Y11">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA11">
+        <v>3</v>
+      </c>
+      <c r="AB11">
+        <v>20</v>
+      </c>
+      <c r="AC11">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>259</v>
+      </c>
+      <c r="AE11">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="s">
         <v>260</v>
-      </c>
-      <c r="W11">
-        <v>3</v>
-      </c>
-      <c r="X11">
-        <v>20</v>
-      </c>
-      <c r="Y11">
-        <v>20</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>260</v>
-      </c>
-      <c r="AA11">
-        <v>3</v>
-      </c>
-      <c r="AB11">
-        <v>20</v>
-      </c>
-      <c r="AC11">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>260</v>
-      </c>
-      <c r="AE11">
-        <v>3</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>261</v>
       </c>
       <c r="AG11">
         <v>3</v>
@@ -8153,7 +7592,7 @@
         <v>6</v>
       </c>
       <c r="AM11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -8168,61 +7607,52 @@
         <v>9</v>
       </c>
       <c r="AR11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AS11" t="s">
+        <v>259</v>
+      </c>
+      <c r="AT11">
+        <v>3</v>
+      </c>
+      <c r="AU11">
+        <v>20</v>
+      </c>
+      <c r="AV11">
+        <v>20</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>259</v>
+      </c>
+      <c r="AX11">
+        <v>3</v>
+      </c>
+      <c r="AY11">
+        <v>20</v>
+      </c>
+      <c r="AZ11">
+        <v>20</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>259</v>
+      </c>
+      <c r="BB11">
+        <v>3</v>
+      </c>
+      <c r="BC11" t="s">
         <v>260</v>
       </c>
-      <c r="AT11">
-        <v>3</v>
-      </c>
-      <c r="AU11">
-        <v>20</v>
-      </c>
-      <c r="AV11">
-        <v>20</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX11">
-        <v>3</v>
-      </c>
-      <c r="AY11">
-        <v>20</v>
-      </c>
-      <c r="AZ11">
-        <v>20</v>
-      </c>
-      <c r="BA11" t="s">
-        <v>260</v>
-      </c>
-      <c r="BB11">
-        <v>3</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>261</v>
-      </c>
       <c r="BD11">
         <v>3</v>
       </c>
       <c r="BE11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>1</v>
-      </c>
-      <c r="BG11">
-        <v>19500000</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>271</v>
-      </c>
-      <c r="BI11">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="BK11">
         <v>1</v>
@@ -8237,58 +7667,49 @@
         <v>9</v>
       </c>
       <c r="BO11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="BP11" t="s">
+        <v>259</v>
+      </c>
+      <c r="BQ11">
+        <v>3</v>
+      </c>
+      <c r="BR11">
+        <v>20</v>
+      </c>
+      <c r="BS11">
+        <v>20</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>259</v>
+      </c>
+      <c r="BU11">
+        <v>3</v>
+      </c>
+      <c r="BV11">
+        <v>20</v>
+      </c>
+      <c r="BW11">
+        <v>20</v>
+      </c>
+      <c r="BX11" t="s">
+        <v>259</v>
+      </c>
+      <c r="BY11">
+        <v>3</v>
+      </c>
+      <c r="BZ11" t="s">
         <v>260</v>
       </c>
-      <c r="BQ11">
-        <v>3</v>
-      </c>
-      <c r="BR11">
-        <v>20</v>
-      </c>
-      <c r="BS11">
-        <v>20</v>
-      </c>
-      <c r="BT11" t="s">
-        <v>260</v>
-      </c>
-      <c r="BU11">
-        <v>3</v>
-      </c>
-      <c r="BV11">
-        <v>20</v>
-      </c>
-      <c r="BW11">
-        <v>20</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>260</v>
-      </c>
-      <c r="BY11">
-        <v>3</v>
-      </c>
-      <c r="BZ11" t="s">
-        <v>261</v>
-      </c>
       <c r="CA11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB11">
-        <v>1</v>
-      </c>
-      <c r="CC11">
-        <v>2400000</v>
-      </c>
-      <c r="CD11" t="s">
-        <v>273</v>
-      </c>
-      <c r="CE11">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="CF11" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="CG11">
         <v>1</v>
@@ -8303,41 +7724,41 @@
         <v>9</v>
       </c>
       <c r="CK11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="CL11" t="s">
+        <v>259</v>
+      </c>
+      <c r="CM11">
+        <v>3</v>
+      </c>
+      <c r="CN11">
+        <v>20</v>
+      </c>
+      <c r="CO11">
+        <v>20</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>259</v>
+      </c>
+      <c r="CQ11">
+        <v>3</v>
+      </c>
+      <c r="CR11">
+        <v>20</v>
+      </c>
+      <c r="CS11">
+        <v>20</v>
+      </c>
+      <c r="CT11" t="s">
+        <v>259</v>
+      </c>
+      <c r="CU11">
+        <v>3</v>
+      </c>
+      <c r="CV11" t="s">
         <v>260</v>
       </c>
-      <c r="CM11">
-        <v>3</v>
-      </c>
-      <c r="CN11">
-        <v>20</v>
-      </c>
-      <c r="CO11">
-        <v>20</v>
-      </c>
-      <c r="CP11" t="s">
-        <v>260</v>
-      </c>
-      <c r="CQ11">
-        <v>3</v>
-      </c>
-      <c r="CR11">
-        <v>20</v>
-      </c>
-      <c r="CS11">
-        <v>20</v>
-      </c>
-      <c r="CT11" t="s">
-        <v>260</v>
-      </c>
-      <c r="CU11">
-        <v>3</v>
-      </c>
-      <c r="CV11" t="s">
-        <v>261</v>
-      </c>
       <c r="CW11">
         <v>3</v>
       </c>
@@ -8348,22 +7769,22 @@
         <v>1</v>
       </c>
       <c r="CZ11">
-        <v>3500</v>
+        <v>4800</v>
       </c>
       <c r="DA11" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="DB11">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="DC11">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="DD11" t="b">
         <v>1</v>
       </c>
       <c r="DE11" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="DF11">
         <v>1</v>
@@ -8378,64 +7799,55 @@
         <v>9</v>
       </c>
       <c r="DJ11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="DK11" t="s">
+        <v>259</v>
+      </c>
+      <c r="DL11">
+        <v>3</v>
+      </c>
+      <c r="DM11">
+        <v>20</v>
+      </c>
+      <c r="DN11">
+        <v>20</v>
+      </c>
+      <c r="DO11" t="s">
+        <v>259</v>
+      </c>
+      <c r="DP11">
+        <v>3</v>
+      </c>
+      <c r="DQ11">
+        <v>20</v>
+      </c>
+      <c r="DR11">
+        <v>20</v>
+      </c>
+      <c r="DS11" t="s">
+        <v>259</v>
+      </c>
+      <c r="DT11">
+        <v>3</v>
+      </c>
+      <c r="DU11" t="s">
         <v>260</v>
       </c>
-      <c r="DL11">
-        <v>3</v>
-      </c>
-      <c r="DM11">
-        <v>20</v>
-      </c>
-      <c r="DN11">
-        <v>20</v>
-      </c>
-      <c r="DO11" t="s">
-        <v>260</v>
-      </c>
-      <c r="DP11">
-        <v>3</v>
-      </c>
-      <c r="DQ11">
-        <v>20</v>
-      </c>
-      <c r="DR11">
-        <v>20</v>
-      </c>
-      <c r="DS11" t="s">
-        <v>260</v>
-      </c>
-      <c r="DT11">
-        <v>3</v>
-      </c>
-      <c r="DU11" t="s">
-        <v>261</v>
-      </c>
       <c r="DV11">
         <v>3</v>
       </c>
       <c r="DW11" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="DX11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY11">
-        <v>1</v>
-      </c>
-      <c r="DZ11">
-        <v>2100</v>
-      </c>
-      <c r="EA11" t="s">
-        <v>282</v>
-      </c>
-      <c r="EB11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC11" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="ED11">
         <v>1</v>
@@ -8450,46 +7862,46 @@
         <v>9</v>
       </c>
       <c r="EH11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="EI11" t="s">
+        <v>259</v>
+      </c>
+      <c r="EJ11">
+        <v>3</v>
+      </c>
+      <c r="EK11">
+        <v>20</v>
+      </c>
+      <c r="EL11">
+        <v>20</v>
+      </c>
+      <c r="EM11" t="s">
+        <v>259</v>
+      </c>
+      <c r="EN11">
+        <v>3</v>
+      </c>
+      <c r="EO11">
+        <v>20</v>
+      </c>
+      <c r="EP11">
+        <v>20</v>
+      </c>
+      <c r="EQ11" t="s">
+        <v>259</v>
+      </c>
+      <c r="ER11">
+        <v>3</v>
+      </c>
+      <c r="ES11" t="s">
         <v>260</v>
       </c>
-      <c r="EJ11">
-        <v>3</v>
-      </c>
-      <c r="EK11">
-        <v>20</v>
-      </c>
-      <c r="EL11">
-        <v>20</v>
-      </c>
-      <c r="EM11" t="s">
-        <v>260</v>
-      </c>
-      <c r="EN11">
-        <v>3</v>
-      </c>
-      <c r="EO11">
-        <v>20</v>
-      </c>
-      <c r="EP11">
-        <v>20</v>
-      </c>
-      <c r="EQ11" t="s">
-        <v>260</v>
-      </c>
-      <c r="ER11">
-        <v>3</v>
-      </c>
-      <c r="ES11" t="s">
-        <v>261</v>
-      </c>
       <c r="ET11">
         <v>3</v>
       </c>
       <c r="EU11" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="EV11">
         <v>0</v>
@@ -8498,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="FA11" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="FB11">
         <v>1</v>
@@ -8513,46 +7925,46 @@
         <v>9</v>
       </c>
       <c r="FF11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="FG11" t="s">
+        <v>259</v>
+      </c>
+      <c r="FH11">
+        <v>3</v>
+      </c>
+      <c r="FI11">
+        <v>20</v>
+      </c>
+      <c r="FJ11">
+        <v>20</v>
+      </c>
+      <c r="FK11" t="s">
+        <v>259</v>
+      </c>
+      <c r="FL11">
+        <v>3</v>
+      </c>
+      <c r="FM11">
+        <v>20</v>
+      </c>
+      <c r="FN11">
+        <v>20</v>
+      </c>
+      <c r="FO11" t="s">
+        <v>259</v>
+      </c>
+      <c r="FP11">
+        <v>3</v>
+      </c>
+      <c r="FQ11" t="s">
         <v>260</v>
       </c>
-      <c r="FH11">
-        <v>3</v>
-      </c>
-      <c r="FI11">
-        <v>20</v>
-      </c>
-      <c r="FJ11">
-        <v>20</v>
-      </c>
-      <c r="FK11" t="s">
-        <v>260</v>
-      </c>
-      <c r="FL11">
-        <v>3</v>
-      </c>
-      <c r="FM11">
-        <v>20</v>
-      </c>
-      <c r="FN11">
-        <v>20</v>
-      </c>
-      <c r="FO11" t="s">
-        <v>260</v>
-      </c>
-      <c r="FP11">
-        <v>3</v>
-      </c>
-      <c r="FQ11" t="s">
-        <v>261</v>
-      </c>
       <c r="FR11">
         <v>3</v>
       </c>
       <c r="FS11" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FT11">
         <v>0</v>
@@ -8561,43 +7973,16 @@
         <v>0</v>
       </c>
       <c r="FX11" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="FY11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FZ11">
-        <v>1</v>
-      </c>
-      <c r="GA11" t="s">
-        <v>292</v>
-      </c>
-      <c r="GB11">
-        <v>75000</v>
-      </c>
-      <c r="GC11">
-        <v>7200</v>
-      </c>
-      <c r="GD11">
-        <v>11000</v>
-      </c>
-      <c r="GE11">
-        <v>100000</v>
-      </c>
-      <c r="GF11">
-        <v>0.9</v>
-      </c>
-      <c r="GG11">
-        <v>0.8</v>
-      </c>
-      <c r="GH11" t="b">
-        <v>0</v>
-      </c>
-      <c r="GI11" t="b">
         <v>0</v>
       </c>
       <c r="GS11" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="GT11">
         <v>0.05</v>
@@ -8612,13 +7997,13 @@
         <v>8.5</v>
       </c>
       <c r="GX11" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="GY11" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="GZ11" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HA11">
         <v>1</v>
@@ -8627,10 +8012,10 @@
         <v>1</v>
       </c>
       <c r="HC11">
-        <v>2700</v>
+        <v>3100</v>
       </c>
       <c r="HD11">
-        <v>2700</v>
+        <v>3100</v>
       </c>
       <c r="HE11">
         <v>0.95</v>
@@ -8645,7 +8030,7 @@
         <v>0</v>
       </c>
       <c r="HI11" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HJ11">
         <v>0</v>
@@ -8654,49 +8039,49 @@
         <v>0</v>
       </c>
       <c r="HP11" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="HQ11" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HR11" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="HS11">
         <v>86400</v>
       </c>
       <c r="HT11" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="HU11">
         <v>86400</v>
       </c>
       <c r="HV11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HW11">
         <v>1</v>
       </c>
       <c r="HX11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="HY11">
         <v>1</v>
       </c>
       <c r="HZ11" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IA11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IB11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="IC11" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="ID11" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="IE11">
         <v>86400</v>
@@ -8732,13 +8117,13 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -8960,7 +8345,7 @@
         <v>76</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="CE1" s="1" t="s">
         <v>77</v>
@@ -9416,10 +8801,10 @@
         <v>227</v>
       </c>
       <c r="HZ1" s="1" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="IA1" s="1" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="IB1" s="1" t="s">
         <v>232</v>
@@ -9470,7 +8855,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -9872,22 +9257,22 @@
         <v>199</v>
       </c>
       <c r="EJ1" s="1" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="EK1" s="1" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="EL1" s="1" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="EM1" s="1" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="EN1" s="1" t="s">
         <v>204</v>
       </c>
       <c r="EO1" s="1" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="EP1" s="1" t="s">
         <v>206</v>
@@ -9935,10 +9320,10 @@
         <v>227</v>
       </c>
       <c r="FE1" s="1" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="FF1" s="1" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="FG1" s="1" t="s">
         <v>232</v>
@@ -9989,7 +9374,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -10481,10 +9866,10 @@
         <v>227</v>
       </c>
       <c r="FN1" s="1" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="FO1" s="1" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="FP1" s="1" t="s">
         <v>232</v>
@@ -10802,10 +10187,10 @@
         <v>227</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="CS1" s="1" t="s">
         <v>232</v>
@@ -10886,58 +10271,58 @@
         <v>215</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>223</v>
@@ -10955,10 +10340,10 @@
         <v>227</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="AO1" s="1" t="s">
         <v>232</v>
